--- a/Dashboard_Data.xlsx
+++ b/Dashboard_Data.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30026"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29929"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Dell\Desktop\SDCC Data Set\files\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://alfanargroup-my.sharepoint.com/personal/ahmed_abdelzaher_alfanar_com/Documents/SDCC Dashboard/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A1474B3D-EE4D-4B3C-B193-C6E21A6F394D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="15" documentId="13_ncr:1_{A1474B3D-EE4D-4B3C-B193-C6E21A6F394D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{E6ABAC93-75B2-46FD-A923-67C4BD5B77BE}"/>
   <bookViews>
-    <workbookView xWindow="120" yWindow="0" windowWidth="22920" windowHeight="12360" tabRatio="500" firstSheet="8" activeTab="12" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="17520" tabRatio="500" firstSheet="3" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Header" sheetId="1" r:id="rId1"/>
@@ -979,12 +979,6 @@
     <xf numFmtId="0" fontId="2" fillId="12" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="9" fontId="3" fillId="5" borderId="1" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
@@ -1011,6 +1005,12 @@
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="7" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -1282,25 +1282,25 @@
     <tabColor rgb="FFE87722"/>
   </sheetPr>
   <dimension ref="A1:H6"/>
-  <sheetFormatPr defaultColWidth="8.6640625" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultColWidth="8.7109375" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="30" customWidth="1"/>
     <col min="2" max="2" width="40" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:8" ht="21.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A1" s="12" t="s">
+    <row r="1" spans="1:8" ht="21.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A1" s="22" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="12"/>
-      <c r="C1" s="12"/>
-      <c r="D1" s="12"/>
-      <c r="E1" s="12"/>
-      <c r="F1" s="12"/>
-      <c r="G1" s="12"/>
-      <c r="H1" s="12"/>
-    </row>
-    <row r="2" spans="1:8" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="B1" s="22"/>
+      <c r="C1" s="22"/>
+      <c r="D1" s="22"/>
+      <c r="E1" s="22"/>
+      <c r="F1" s="22"/>
+      <c r="G1" s="22"/>
+      <c r="H1" s="22"/>
+    </row>
+    <row r="2" spans="1:8" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A2" s="1" t="s">
         <v>1</v>
       </c>
@@ -1308,7 +1308,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="3" spans="1:8" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:8" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A3" s="2" t="s">
         <v>3</v>
       </c>
@@ -1316,7 +1316,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="4" spans="1:8" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:8" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A4" s="4" t="s">
         <v>5</v>
       </c>
@@ -1324,7 +1324,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="5" spans="1:8" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:8" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A5" s="2" t="s">
         <v>7</v>
       </c>
@@ -1332,7 +1332,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="6" spans="1:8" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:8" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A6" s="4" t="s">
         <v>9</v>
       </c>
@@ -1346,6 +1346,9 @@
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.511811023622047" footer="0.511811023622047"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300"/>
+  <headerFooter>
+    <oddFooter>&amp;C_x000D_&amp;1#&amp;"Aptos"&amp;10&amp;K0000FF CLASSIFICATION: Public</oddFooter>
+  </headerFooter>
 </worksheet>
 </file>
 
@@ -1355,7 +1358,7 @@
     <tabColor rgb="FFE87722"/>
   </sheetPr>
   <dimension ref="A1:H22"/>
-  <sheetFormatPr defaultColWidth="8.6640625" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultColWidth="8.7109375" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="12" customWidth="1"/>
     <col min="2" max="2" width="14" customWidth="1"/>
@@ -1367,19 +1370,19 @@
     <col min="8" max="8" width="30" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:8" ht="21.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A1" s="12" t="s">
+    <row r="1" spans="1:8" ht="21.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A1" s="22" t="s">
         <v>152</v>
       </c>
-      <c r="B1" s="12"/>
-      <c r="C1" s="12"/>
-      <c r="D1" s="12"/>
-      <c r="E1" s="12"/>
-      <c r="F1" s="12"/>
-      <c r="G1" s="12"/>
-      <c r="H1" s="12"/>
-    </row>
-    <row r="2" spans="1:8" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="B1" s="22"/>
+      <c r="C1" s="22"/>
+      <c r="D1" s="22"/>
+      <c r="E1" s="22"/>
+      <c r="F1" s="22"/>
+      <c r="G1" s="22"/>
+      <c r="H1" s="22"/>
+    </row>
+    <row r="2" spans="1:8" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A2" s="1" t="s">
         <v>153</v>
       </c>
@@ -1405,7 +1408,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="3" spans="1:8" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:8" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A3" s="6" t="s">
         <v>160</v>
       </c>
@@ -1427,7 +1430,7 @@
         <v>165</v>
       </c>
     </row>
-    <row r="4" spans="1:8" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:8" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A4" s="4" t="s">
         <v>166</v>
       </c>
@@ -1443,7 +1446,7 @@
       <c r="G4" s="4"/>
       <c r="H4" s="4"/>
     </row>
-    <row r="5" spans="1:8" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:8" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A5" s="2" t="s">
         <v>167</v>
       </c>
@@ -1459,7 +1462,7 @@
       <c r="G5" s="2"/>
       <c r="H5" s="2"/>
     </row>
-    <row r="6" spans="1:8" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:8" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A6" s="4" t="s">
         <v>168</v>
       </c>
@@ -1475,7 +1478,7 @@
       <c r="G6" s="4"/>
       <c r="H6" s="4"/>
     </row>
-    <row r="7" spans="1:8" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:8" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A7" s="6" t="s">
         <v>169</v>
       </c>
@@ -1495,7 +1498,7 @@
       <c r="G7" s="2"/>
       <c r="H7" s="2"/>
     </row>
-    <row r="8" spans="1:8" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:8" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A8" s="6" t="s">
         <v>171</v>
       </c>
@@ -1517,7 +1520,7 @@
         <v>174</v>
       </c>
     </row>
-    <row r="9" spans="1:8" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:8" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A9" s="2" t="s">
         <v>175</v>
       </c>
@@ -1533,7 +1536,7 @@
       <c r="G9" s="2"/>
       <c r="H9" s="2"/>
     </row>
-    <row r="10" spans="1:8" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:8" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A10" s="6" t="s">
         <v>176</v>
       </c>
@@ -1553,7 +1556,7 @@
       <c r="G10" s="4"/>
       <c r="H10" s="4"/>
     </row>
-    <row r="11" spans="1:8" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:8" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A11" s="2" t="s">
         <v>178</v>
       </c>
@@ -1569,7 +1572,7 @@
       <c r="G11" s="2"/>
       <c r="H11" s="2"/>
     </row>
-    <row r="12" spans="1:8" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:8" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A12" s="4" t="s">
         <v>179</v>
       </c>
@@ -1585,7 +1588,7 @@
       <c r="G12" s="4"/>
       <c r="H12" s="4"/>
     </row>
-    <row r="13" spans="1:8" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="13" spans="1:8" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A13" s="2" t="s">
         <v>180</v>
       </c>
@@ -1601,7 +1604,7 @@
       <c r="G13" s="2"/>
       <c r="H13" s="2"/>
     </row>
-    <row r="14" spans="1:8" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="14" spans="1:8" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A14" s="4" t="s">
         <v>181</v>
       </c>
@@ -1617,7 +1620,7 @@
       <c r="G14" s="4"/>
       <c r="H14" s="4"/>
     </row>
-    <row r="15" spans="1:8" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="15" spans="1:8" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A15" s="6" t="s">
         <v>182</v>
       </c>
@@ -1637,7 +1640,7 @@
       <c r="G15" s="2"/>
       <c r="H15" s="2"/>
     </row>
-    <row r="16" spans="1:8" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="16" spans="1:8" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A16" s="4" t="s">
         <v>184</v>
       </c>
@@ -1653,7 +1656,7 @@
       <c r="G16" s="4"/>
       <c r="H16" s="4"/>
     </row>
-    <row r="17" spans="1:8" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="17" spans="1:8" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A17" s="2" t="s">
         <v>185</v>
       </c>
@@ -1669,7 +1672,7 @@
       <c r="G17" s="2"/>
       <c r="H17" s="2"/>
     </row>
-    <row r="18" spans="1:8" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="18" spans="1:8" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A18" s="4" t="s">
         <v>186</v>
       </c>
@@ -1685,7 +1688,7 @@
       <c r="G18" s="4"/>
       <c r="H18" s="4"/>
     </row>
-    <row r="19" spans="1:8" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="19" spans="1:8" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A19" s="2" t="s">
         <v>187</v>
       </c>
@@ -1701,7 +1704,7 @@
       <c r="G19" s="2"/>
       <c r="H19" s="2"/>
     </row>
-    <row r="20" spans="1:8" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="20" spans="1:8" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A20" s="7" t="s">
         <v>188</v>
       </c>
@@ -1723,7 +1726,7 @@
         <v>189</v>
       </c>
     </row>
-    <row r="21" spans="1:8" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="21" spans="1:8" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A21" s="2" t="s">
         <v>190</v>
       </c>
@@ -1739,7 +1742,7 @@
       <c r="G21" s="2"/>
       <c r="H21" s="2"/>
     </row>
-    <row r="22" spans="1:8" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="22" spans="1:8" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A22" s="8" t="s">
         <v>191</v>
       </c>
@@ -1767,6 +1770,9 @@
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.511811023622047" footer="0.511811023622047"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300"/>
+  <headerFooter>
+    <oddFooter>&amp;C_x000D_&amp;1#&amp;"Aptos"&amp;10&amp;K0000FF CLASSIFICATION: Public</oddFooter>
+  </headerFooter>
 </worksheet>
 </file>
 
@@ -1776,7 +1782,7 @@
     <tabColor rgb="FFE87722"/>
   </sheetPr>
   <dimension ref="A1:H5"/>
-  <sheetFormatPr defaultColWidth="8.6640625" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultColWidth="8.7109375" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="4" customWidth="1"/>
     <col min="2" max="2" width="38" customWidth="1"/>
@@ -1786,19 +1792,19 @@
     <col min="6" max="6" width="10" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:8" ht="21.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A1" s="12" t="s">
+    <row r="1" spans="1:8" ht="21.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A1" s="22" t="s">
         <v>194</v>
       </c>
-      <c r="B1" s="12"/>
-      <c r="C1" s="12"/>
-      <c r="D1" s="12"/>
-      <c r="E1" s="12"/>
-      <c r="F1" s="12"/>
-      <c r="G1" s="12"/>
-      <c r="H1" s="12"/>
-    </row>
-    <row r="2" spans="1:8" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="B1" s="22"/>
+      <c r="C1" s="22"/>
+      <c r="D1" s="22"/>
+      <c r="E1" s="22"/>
+      <c r="F1" s="22"/>
+      <c r="G1" s="22"/>
+      <c r="H1" s="22"/>
+    </row>
+    <row r="2" spans="1:8" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A2" s="1" t="s">
         <v>195</v>
       </c>
@@ -1818,7 +1824,7 @@
         <v>200</v>
       </c>
     </row>
-    <row r="3" spans="1:8" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:8" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A3" s="2">
         <v>1</v>
       </c>
@@ -1838,7 +1844,7 @@
         <v>204</v>
       </c>
     </row>
-    <row r="4" spans="1:8" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:8" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A4" s="4">
         <v>2</v>
       </c>
@@ -1858,7 +1864,7 @@
         <v>204</v>
       </c>
     </row>
-    <row r="5" spans="1:8" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:8" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A5" s="2">
         <v>3</v>
       </c>
@@ -1884,6 +1890,9 @@
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.511811023622047" footer="0.511811023622047"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300"/>
+  <headerFooter>
+    <oddFooter>&amp;C_x000D_&amp;1#&amp;"Aptos"&amp;10&amp;K0000FF CLASSIFICATION: Public</oddFooter>
+  </headerFooter>
 </worksheet>
 </file>
 
@@ -1893,7 +1902,7 @@
     <tabColor rgb="FFE87722"/>
   </sheetPr>
   <dimension ref="A1:H10"/>
-  <sheetFormatPr defaultColWidth="8.6640625" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultColWidth="8.7109375" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="4" customWidth="1"/>
     <col min="2" max="2" width="26" customWidth="1"/>
@@ -1902,19 +1911,19 @@
     <col min="8" max="8" width="12" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:8" ht="21.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A1" s="12" t="s">
+    <row r="1" spans="1:8" ht="21.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A1" s="22" t="s">
         <v>211</v>
       </c>
-      <c r="B1" s="12"/>
-      <c r="C1" s="12"/>
-      <c r="D1" s="12"/>
-      <c r="E1" s="12"/>
-      <c r="F1" s="12"/>
-      <c r="G1" s="12"/>
-      <c r="H1" s="12"/>
-    </row>
-    <row r="2" spans="1:8" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="B1" s="22"/>
+      <c r="C1" s="22"/>
+      <c r="D1" s="22"/>
+      <c r="E1" s="22"/>
+      <c r="F1" s="22"/>
+      <c r="G1" s="22"/>
+      <c r="H1" s="22"/>
+    </row>
+    <row r="2" spans="1:8" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A2" s="1" t="s">
         <v>195</v>
       </c>
@@ -1940,7 +1949,7 @@
         <v>217</v>
       </c>
     </row>
-    <row r="3" spans="1:8" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:8" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A3" s="2">
         <v>1</v>
       </c>
@@ -1966,7 +1975,7 @@
         <v>221</v>
       </c>
     </row>
-    <row r="4" spans="1:8" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:8" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A4" s="4">
         <v>2</v>
       </c>
@@ -1992,7 +2001,7 @@
         <v>221</v>
       </c>
     </row>
-    <row r="5" spans="1:8" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:8" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A5" s="2">
         <v>3</v>
       </c>
@@ -2018,7 +2027,7 @@
         <v>221</v>
       </c>
     </row>
-    <row r="6" spans="1:8" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:8" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A6" s="4">
         <v>4</v>
       </c>
@@ -2044,7 +2053,7 @@
         <v>221</v>
       </c>
     </row>
-    <row r="7" spans="1:8" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:8" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A7" s="2">
         <v>5</v>
       </c>
@@ -2070,7 +2079,7 @@
         <v>221</v>
       </c>
     </row>
-    <row r="8" spans="1:8" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:8" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A8" s="4">
         <v>6</v>
       </c>
@@ -2096,7 +2105,7 @@
         <v>221</v>
       </c>
     </row>
-    <row r="9" spans="1:8" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:8" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A9" s="2">
         <v>7</v>
       </c>
@@ -2122,7 +2131,7 @@
         <v>221</v>
       </c>
     </row>
-    <row r="10" spans="1:8" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:8" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A10" s="4">
         <v>8</v>
       </c>
@@ -2154,6 +2163,9 @@
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.511811023622047" footer="0.511811023622047"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300"/>
+  <headerFooter>
+    <oddFooter>&amp;C_x000D_&amp;1#&amp;"Aptos"&amp;10&amp;K0000FF CLASSIFICATION: Public</oddFooter>
+  </headerFooter>
 </worksheet>
 </file>
 
@@ -2163,25 +2175,25 @@
     <tabColor rgb="FFE87722"/>
   </sheetPr>
   <dimension ref="A1:H6"/>
-  <sheetFormatPr defaultColWidth="8.6640625" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultColWidth="8.7109375" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="30" customWidth="1"/>
     <col min="2" max="2" width="50" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:8" ht="21.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A1" s="12" t="s">
+    <row r="1" spans="1:8" ht="21.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A1" s="22" t="s">
         <v>236</v>
       </c>
-      <c r="B1" s="12"/>
-      <c r="C1" s="12"/>
-      <c r="D1" s="12"/>
-      <c r="E1" s="12"/>
-      <c r="F1" s="12"/>
-      <c r="G1" s="12"/>
-      <c r="H1" s="12"/>
-    </row>
-    <row r="2" spans="1:8" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="B1" s="22"/>
+      <c r="C1" s="22"/>
+      <c r="D1" s="22"/>
+      <c r="E1" s="22"/>
+      <c r="F1" s="22"/>
+      <c r="G1" s="22"/>
+      <c r="H1" s="22"/>
+    </row>
+    <row r="2" spans="1:8" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A2" s="1" t="s">
         <v>1</v>
       </c>
@@ -2189,7 +2201,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="3" spans="1:8" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:8" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A3" s="2" t="s">
         <v>237</v>
       </c>
@@ -2197,7 +2209,7 @@
         <v>238</v>
       </c>
     </row>
-    <row r="4" spans="1:8" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:8" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A4" s="4" t="s">
         <v>239</v>
       </c>
@@ -2205,15 +2217,15 @@
         <v>240</v>
       </c>
     </row>
-    <row r="5" spans="1:8" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:8" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A5" s="2" t="s">
         <v>241</v>
       </c>
-      <c r="B5" s="23" t="s">
+      <c r="B5" s="21" t="s">
         <v>244</v>
       </c>
     </row>
-    <row r="6" spans="1:8" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:8" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A6" s="4" t="s">
         <v>242</v>
       </c>
@@ -2227,6 +2239,9 @@
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.511811023622047" footer="0.511811023622047"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300"/>
+  <headerFooter>
+    <oddFooter>&amp;C_x000D_&amp;1#&amp;"Aptos"&amp;10&amp;K0000FF CLASSIFICATION: Public</oddFooter>
+  </headerFooter>
 </worksheet>
 </file>
 
@@ -2236,26 +2251,26 @@
     <tabColor rgb="FFE87722"/>
   </sheetPr>
   <dimension ref="A1:H9"/>
-  <sheetFormatPr defaultColWidth="8.6640625" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultColWidth="8.7109375" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="32" customWidth="1"/>
     <col min="2" max="2" width="18" customWidth="1"/>
     <col min="3" max="3" width="40" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:8" ht="21.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A1" s="12" t="s">
+    <row r="1" spans="1:8" ht="21.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A1" s="22" t="s">
         <v>11</v>
       </c>
-      <c r="B1" s="12"/>
-      <c r="C1" s="12"/>
-      <c r="D1" s="12"/>
-      <c r="E1" s="12"/>
-      <c r="F1" s="12"/>
-      <c r="G1" s="12"/>
-      <c r="H1" s="12"/>
-    </row>
-    <row r="2" spans="1:8" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="B1" s="22"/>
+      <c r="C1" s="22"/>
+      <c r="D1" s="22"/>
+      <c r="E1" s="22"/>
+      <c r="F1" s="22"/>
+      <c r="G1" s="22"/>
+      <c r="H1" s="22"/>
+    </row>
+    <row r="2" spans="1:8" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A2" s="1" t="s">
         <v>1</v>
       </c>
@@ -2266,7 +2281,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="3" spans="1:8" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:8" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A3" s="2" t="s">
         <v>14</v>
       </c>
@@ -2275,7 +2290,7 @@
       </c>
       <c r="C3" s="2"/>
     </row>
-    <row r="4" spans="1:8" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:8" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A4" s="4" t="s">
         <v>16</v>
       </c>
@@ -2284,7 +2299,7 @@
       </c>
       <c r="C4" s="4"/>
     </row>
-    <row r="5" spans="1:8" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:8" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A5" s="2" t="s">
         <v>18</v>
       </c>
@@ -2293,7 +2308,7 @@
       </c>
       <c r="C5" s="2"/>
     </row>
-    <row r="6" spans="1:8" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:8" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A6" s="4" t="s">
         <v>20</v>
       </c>
@@ -2302,7 +2317,7 @@
       </c>
       <c r="C6" s="4"/>
     </row>
-    <row r="7" spans="1:8" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:8" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A7" s="2" t="s">
         <v>22</v>
       </c>
@@ -2311,7 +2326,7 @@
       </c>
       <c r="C7" s="2"/>
     </row>
-    <row r="8" spans="1:8" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:8" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A8" s="4" t="s">
         <v>24</v>
       </c>
@@ -2322,7 +2337,7 @@
         <v>26</v>
       </c>
     </row>
-    <row r="9" spans="1:8" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:8" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A9" s="2" t="s">
         <v>27</v>
       </c>
@@ -2339,6 +2354,9 @@
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.511811023622047" footer="0.511811023622047"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300"/>
+  <headerFooter>
+    <oddFooter>&amp;C_x000D_&amp;1#&amp;"Aptos"&amp;10&amp;K0000FF CLASSIFICATION: Public</oddFooter>
+  </headerFooter>
 </worksheet>
 </file>
 
@@ -2348,7 +2366,7 @@
     <tabColor rgb="FFE87722"/>
   </sheetPr>
   <dimension ref="A1:H9"/>
-  <sheetFormatPr defaultColWidth="8.6640625" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultColWidth="8.7109375" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="32" customWidth="1"/>
     <col min="2" max="2" width="22" customWidth="1"/>
@@ -2356,19 +2374,19 @@
     <col min="4" max="4" width="40" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:8" ht="21.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A1" s="12" t="s">
+    <row r="1" spans="1:8" ht="21.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A1" s="22" t="s">
         <v>30</v>
       </c>
-      <c r="B1" s="12"/>
-      <c r="C1" s="12"/>
-      <c r="D1" s="12"/>
-      <c r="E1" s="12"/>
-      <c r="F1" s="12"/>
-      <c r="G1" s="12"/>
-      <c r="H1" s="12"/>
-    </row>
-    <row r="2" spans="1:8" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="B1" s="22"/>
+      <c r="C1" s="22"/>
+      <c r="D1" s="22"/>
+      <c r="E1" s="22"/>
+      <c r="F1" s="22"/>
+      <c r="G1" s="22"/>
+      <c r="H1" s="22"/>
+    </row>
+    <row r="2" spans="1:8" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A2" s="1" t="s">
         <v>1</v>
       </c>
@@ -2382,7 +2400,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="3" spans="1:8" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:8" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A3" s="2" t="s">
         <v>33</v>
       </c>
@@ -2392,7 +2410,7 @@
       <c r="C3" s="2"/>
       <c r="D3" s="2"/>
     </row>
-    <row r="4" spans="1:8" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:8" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A4" s="4" t="s">
         <v>34</v>
       </c>
@@ -2402,7 +2420,7 @@
       <c r="C4" s="4"/>
       <c r="D4" s="4"/>
     </row>
-    <row r="5" spans="1:8" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:8" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A5" s="2" t="s">
         <v>35</v>
       </c>
@@ -2412,7 +2430,7 @@
       <c r="C5" s="2"/>
       <c r="D5" s="2"/>
     </row>
-    <row r="6" spans="1:8" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:8" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A6" s="4" t="s">
         <v>36</v>
       </c>
@@ -2422,7 +2440,7 @@
       <c r="C6" s="4"/>
       <c r="D6" s="4"/>
     </row>
-    <row r="7" spans="1:8" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:8" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A7" s="2" t="s">
         <v>37</v>
       </c>
@@ -2434,7 +2452,7 @@
         <v>38</v>
       </c>
     </row>
-    <row r="8" spans="1:8" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:8" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A8" s="4" t="s">
         <v>39</v>
       </c>
@@ -2444,7 +2462,7 @@
       <c r="C8" s="4"/>
       <c r="D8" s="4"/>
     </row>
-    <row r="9" spans="1:8" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:8" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A9" s="2" t="s">
         <v>40</v>
       </c>
@@ -2464,6 +2482,9 @@
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.511811023622047" footer="0.511811023622047"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300"/>
+  <headerFooter>
+    <oddFooter>&amp;C_x000D_&amp;1#&amp;"Aptos"&amp;10&amp;K0000FF CLASSIFICATION: Public</oddFooter>
+  </headerFooter>
 </worksheet>
 </file>
 
@@ -2473,7 +2494,7 @@
     <tabColor rgb="FFE87722"/>
   </sheetPr>
   <dimension ref="A1:H9"/>
-  <sheetFormatPr defaultColWidth="8.6640625" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultColWidth="8.7109375" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="32" customWidth="1"/>
     <col min="2" max="2" width="22" customWidth="1"/>
@@ -2481,19 +2502,19 @@
     <col min="4" max="4" width="40" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:8" ht="21.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A1" s="12" t="s">
+    <row r="1" spans="1:8" ht="21.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A1" s="22" t="s">
         <v>43</v>
       </c>
-      <c r="B1" s="12"/>
-      <c r="C1" s="12"/>
-      <c r="D1" s="12"/>
-      <c r="E1" s="12"/>
-      <c r="F1" s="12"/>
-      <c r="G1" s="12"/>
-      <c r="H1" s="12"/>
-    </row>
-    <row r="2" spans="1:8" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="B1" s="22"/>
+      <c r="C1" s="22"/>
+      <c r="D1" s="22"/>
+      <c r="E1" s="22"/>
+      <c r="F1" s="22"/>
+      <c r="G1" s="22"/>
+      <c r="H1" s="22"/>
+    </row>
+    <row r="2" spans="1:8" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A2" s="1" t="s">
         <v>1</v>
       </c>
@@ -2507,7 +2528,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="3" spans="1:8" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:8" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A3" s="2" t="s">
         <v>44</v>
       </c>
@@ -2519,7 +2540,7 @@
         <v>45</v>
       </c>
     </row>
-    <row r="4" spans="1:8" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:8" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A4" s="4" t="s">
         <v>46</v>
       </c>
@@ -2531,16 +2552,16 @@
         <v>48</v>
       </c>
     </row>
-    <row r="5" spans="1:8" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:8" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A5" s="2" t="s">
         <v>49</v>
       </c>
-      <c r="B5" s="14">
-        <v>0.75</v>
-      </c>
-      <c r="C5" s="15">
+      <c r="B5" s="12">
+        <v>0.8</v>
+      </c>
+      <c r="C5" s="13">
         <f>B5-B4</f>
-        <v>-0.25</v>
+        <v>-0.19999999999999996</v>
       </c>
       <c r="D5" s="2" t="s">
         <v>52</v>
@@ -2552,7 +2573,7 @@
         <v>51</v>
       </c>
     </row>
-    <row r="6" spans="1:8" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:8" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A6" s="4" t="s">
         <v>39</v>
       </c>
@@ -2564,7 +2585,7 @@
         <v>45</v>
       </c>
     </row>
-    <row r="7" spans="1:8" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:8" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A7" s="2" t="s">
         <v>40</v>
       </c>
@@ -2576,7 +2597,7 @@
         <v>45</v>
       </c>
     </row>
-    <row r="8" spans="1:8" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:8" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A8" s="4" t="s">
         <v>53</v>
       </c>
@@ -2588,7 +2609,7 @@
         <v>55</v>
       </c>
     </row>
-    <row r="9" spans="1:8" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:8" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A9" s="2" t="s">
         <v>56</v>
       </c>
@@ -2606,6 +2627,9 @@
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.511811023622047" footer="0.511811023622047"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300"/>
+  <headerFooter>
+    <oddFooter>&amp;C_x000D_&amp;1#&amp;"Aptos"&amp;10&amp;K0000FF CLASSIFICATION: Public</oddFooter>
+  </headerFooter>
 </worksheet>
 </file>
 
@@ -2615,7 +2639,7 @@
     <tabColor rgb="FFE87722"/>
   </sheetPr>
   <dimension ref="A1:H9"/>
-  <sheetFormatPr defaultColWidth="8.6640625" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultColWidth="8.7109375" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="32" customWidth="1"/>
     <col min="2" max="2" width="22" customWidth="1"/>
@@ -2624,19 +2648,19 @@
     <col min="5" max="5" width="35" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:8" ht="21.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A1" s="12" t="s">
+    <row r="1" spans="1:8" ht="21.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A1" s="22" t="s">
         <v>59</v>
       </c>
-      <c r="B1" s="12"/>
-      <c r="C1" s="12"/>
-      <c r="D1" s="12"/>
-      <c r="E1" s="12"/>
-      <c r="F1" s="12"/>
-      <c r="G1" s="12"/>
-      <c r="H1" s="12"/>
-    </row>
-    <row r="2" spans="1:8" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="B1" s="22"/>
+      <c r="C1" s="22"/>
+      <c r="D1" s="22"/>
+      <c r="E1" s="22"/>
+      <c r="F1" s="22"/>
+      <c r="G1" s="22"/>
+      <c r="H1" s="22"/>
+    </row>
+    <row r="2" spans="1:8" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A2" s="1" t="s">
         <v>1</v>
       </c>
@@ -2653,7 +2677,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="3" spans="1:8" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:8" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A3" s="2" t="s">
         <v>62</v>
       </c>
@@ -2668,7 +2692,7 @@
       </c>
       <c r="E3" s="2"/>
     </row>
-    <row r="4" spans="1:8" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:8" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A4" s="4" t="s">
         <v>65</v>
       </c>
@@ -2683,7 +2707,7 @@
       </c>
       <c r="E4" s="4"/>
     </row>
-    <row r="5" spans="1:8" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:8" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A5" s="2" t="s">
         <v>68</v>
       </c>
@@ -2698,7 +2722,7 @@
       </c>
       <c r="E5" s="2"/>
     </row>
-    <row r="6" spans="1:8" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:8" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A6" s="4" t="s">
         <v>69</v>
       </c>
@@ -2711,7 +2735,7 @@
       </c>
       <c r="E6" s="4"/>
     </row>
-    <row r="7" spans="1:8" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:8" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A7" s="2" t="s">
         <v>71</v>
       </c>
@@ -2726,7 +2750,7 @@
       </c>
       <c r="E7" s="2"/>
     </row>
-    <row r="8" spans="1:8" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:8" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A8" s="4" t="s">
         <v>73</v>
       </c>
@@ -2741,7 +2765,7 @@
         <v>75</v>
       </c>
     </row>
-    <row r="9" spans="1:8" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:8" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A9" s="2" t="s">
         <v>76</v>
       </c>
@@ -2762,6 +2786,9 @@
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.511811023622047" footer="0.511811023622047"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300"/>
+  <headerFooter>
+    <oddFooter>&amp;C_x000D_&amp;1#&amp;"Aptos"&amp;10&amp;K0000FF CLASSIFICATION: Public</oddFooter>
+  </headerFooter>
 </worksheet>
 </file>
 
@@ -2771,7 +2798,7 @@
     <tabColor rgb="FFE87722"/>
   </sheetPr>
   <dimension ref="A1:H6"/>
-  <sheetFormatPr defaultColWidth="8.6640625" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultColWidth="8.7109375" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="30" customWidth="1"/>
     <col min="2" max="2" width="20" customWidth="1"/>
@@ -2779,19 +2806,19 @@
     <col min="4" max="4" width="40" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:8" ht="21.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A1" s="12" t="s">
+    <row r="1" spans="1:8" ht="21.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A1" s="22" t="s">
         <v>79</v>
       </c>
-      <c r="B1" s="12"/>
-      <c r="C1" s="12"/>
-      <c r="D1" s="12"/>
-      <c r="E1" s="12"/>
-      <c r="F1" s="12"/>
-      <c r="G1" s="12"/>
-      <c r="H1" s="12"/>
-    </row>
-    <row r="2" spans="1:8" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="B1" s="22"/>
+      <c r="C1" s="22"/>
+      <c r="D1" s="22"/>
+      <c r="E1" s="22"/>
+      <c r="F1" s="22"/>
+      <c r="G1" s="22"/>
+      <c r="H1" s="22"/>
+    </row>
+    <row r="2" spans="1:8" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A2" s="1" t="s">
         <v>1</v>
       </c>
@@ -2805,7 +2832,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="3" spans="1:8" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:8" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A3" s="2" t="s">
         <v>82</v>
       </c>
@@ -2817,7 +2844,7 @@
         <v>83</v>
       </c>
     </row>
-    <row r="4" spans="1:8" ht="32.4" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:8" ht="32.450000000000003" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A4" s="4" t="s">
         <v>84</v>
       </c>
@@ -2829,7 +2856,7 @@
         <v>86</v>
       </c>
     </row>
-    <row r="5" spans="1:8" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:8" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A5" s="2" t="s">
         <v>87</v>
       </c>
@@ -2843,7 +2870,7 @@
         <v>89</v>
       </c>
     </row>
-    <row r="6" spans="1:8" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:8" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A6" s="4" t="s">
         <v>90</v>
       </c>
@@ -2863,6 +2890,9 @@
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.511811023622047" footer="0.511811023622047"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300"/>
+  <headerFooter>
+    <oddFooter>&amp;C_x000D_&amp;1#&amp;"Aptos"&amp;10&amp;K0000FF CLASSIFICATION: Public</oddFooter>
+  </headerFooter>
 </worksheet>
 </file>
 
@@ -2872,7 +2902,7 @@
     <tabColor rgb="FFE87722"/>
   </sheetPr>
   <dimension ref="A1:H21"/>
-  <sheetFormatPr defaultColWidth="8.6640625" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultColWidth="8.7109375" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="28" customWidth="1"/>
     <col min="2" max="2" width="16" customWidth="1"/>
@@ -2880,27 +2910,27 @@
     <col min="4" max="4" width="10" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:8" ht="21.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A1" s="12" t="s">
+    <row r="1" spans="1:8" ht="21.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A1" s="22" t="s">
         <v>92</v>
       </c>
-      <c r="B1" s="12"/>
-      <c r="C1" s="12"/>
-      <c r="D1" s="12"/>
-      <c r="E1" s="12"/>
-      <c r="F1" s="12"/>
-      <c r="G1" s="12"/>
-      <c r="H1" s="12"/>
-    </row>
-    <row r="2" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A2" s="13" t="s">
+      <c r="B1" s="22"/>
+      <c r="C1" s="22"/>
+      <c r="D1" s="22"/>
+      <c r="E1" s="22"/>
+      <c r="F1" s="22"/>
+      <c r="G1" s="22"/>
+      <c r="H1" s="22"/>
+    </row>
+    <row r="2" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A2" s="23" t="s">
         <v>93</v>
       </c>
-      <c r="B2" s="13"/>
-      <c r="C2" s="13"/>
-      <c r="D2" s="13"/>
-    </row>
-    <row r="3" spans="1:8" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="B2" s="23"/>
+      <c r="C2" s="23"/>
+      <c r="D2" s="23"/>
+    </row>
+    <row r="3" spans="1:8" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A3" s="1" t="s">
         <v>1</v>
       </c>
@@ -2912,7 +2942,7 @@
       </c>
       <c r="D3" s="1"/>
     </row>
-    <row r="4" spans="1:8" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:8" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A4" s="4" t="s">
         <v>94</v>
       </c>
@@ -2924,7 +2954,7 @@
       </c>
       <c r="D4" s="4"/>
     </row>
-    <row r="5" spans="1:8" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:8" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A5" s="2" t="s">
         <v>96</v>
       </c>
@@ -2936,7 +2966,7 @@
       </c>
       <c r="D5" s="2"/>
     </row>
-    <row r="6" spans="1:8" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:8" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A6" s="4" t="s">
         <v>98</v>
       </c>
@@ -2948,7 +2978,7 @@
       </c>
       <c r="D6" s="4"/>
     </row>
-    <row r="7" spans="1:8" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:8" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A7" s="2" t="s">
         <v>100</v>
       </c>
@@ -2960,16 +2990,16 @@
       </c>
       <c r="D7" s="2"/>
     </row>
-    <row r="8" spans="1:8" ht="6" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="9" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A9" s="13" t="s">
+    <row r="8" spans="1:8" ht="6" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="9" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A9" s="23" t="s">
         <v>103</v>
       </c>
-      <c r="B9" s="13"/>
-      <c r="C9" s="13"/>
-      <c r="D9" s="13"/>
-    </row>
-    <row r="10" spans="1:8" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="B9" s="23"/>
+      <c r="C9" s="23"/>
+      <c r="D9" s="23"/>
+    </row>
+    <row r="10" spans="1:8" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A10" s="1" t="s">
         <v>104</v>
       </c>
@@ -2981,7 +3011,7 @@
       </c>
       <c r="D10" s="1"/>
     </row>
-    <row r="11" spans="1:8" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:8" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A11" s="2" t="s">
         <v>106</v>
       </c>
@@ -2993,7 +3023,7 @@
       </c>
       <c r="D11" s="2"/>
     </row>
-    <row r="12" spans="1:8" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:8" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A12" s="4" t="s">
         <v>108</v>
       </c>
@@ -3005,16 +3035,16 @@
       </c>
       <c r="D12" s="4"/>
     </row>
-    <row r="13" spans="1:8" ht="6" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="14" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A14" s="13" t="s">
+    <row r="13" spans="1:8" ht="6" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="14" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A14" s="23" t="s">
         <v>109</v>
       </c>
-      <c r="B14" s="13"/>
-      <c r="C14" s="13"/>
-      <c r="D14" s="13"/>
-    </row>
-    <row r="15" spans="1:8" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="B14" s="23"/>
+      <c r="C14" s="23"/>
+      <c r="D14" s="23"/>
+    </row>
+    <row r="15" spans="1:8" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A15" s="1" t="s">
         <v>110</v>
       </c>
@@ -3026,7 +3056,7 @@
       </c>
       <c r="D15" s="1"/>
     </row>
-    <row r="16" spans="1:8" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="16" spans="1:8" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A16" s="4" t="s">
         <v>112</v>
       </c>
@@ -3039,7 +3069,7 @@
       </c>
       <c r="D16" s="4"/>
     </row>
-    <row r="17" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="17" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A17" s="2" t="s">
         <v>114</v>
       </c>
@@ -3052,7 +3082,7 @@
       </c>
       <c r="D17" s="2"/>
     </row>
-    <row r="18" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="18" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A18" s="4" t="s">
         <v>116</v>
       </c>
@@ -3065,7 +3095,7 @@
       </c>
       <c r="D18" s="4"/>
     </row>
-    <row r="19" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="19" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A19" s="2" t="s">
         <v>118</v>
       </c>
@@ -3078,7 +3108,7 @@
       </c>
       <c r="D19" s="2"/>
     </row>
-    <row r="20" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="20" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A20" s="4" t="s">
         <v>120</v>
       </c>
@@ -3091,7 +3121,7 @@
       </c>
       <c r="D20" s="4"/>
     </row>
-    <row r="21" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="21" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A21" s="2" t="s">
         <v>122</v>
       </c>
@@ -3113,6 +3143,9 @@
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.511811023622047" footer="0.511811023622047"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300"/>
+  <headerFooter>
+    <oddFooter>&amp;C_x000D_&amp;1#&amp;"Aptos"&amp;10&amp;K0000FF CLASSIFICATION: Public</oddFooter>
+  </headerFooter>
 </worksheet>
 </file>
 
@@ -3122,7 +3155,7 @@
     <tabColor rgb="FFE87722"/>
   </sheetPr>
   <dimension ref="A1:H8"/>
-  <sheetFormatPr defaultColWidth="8.6640625" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultColWidth="8.7109375" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="28" customWidth="1"/>
     <col min="2" max="4" width="10" customWidth="1"/>
@@ -3130,19 +3163,19 @@
     <col min="6" max="6" width="35" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:8" ht="21.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A1" s="12" t="s">
+    <row r="1" spans="1:8" ht="21.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A1" s="22" t="s">
         <v>124</v>
       </c>
-      <c r="B1" s="12"/>
-      <c r="C1" s="12"/>
-      <c r="D1" s="12"/>
-      <c r="E1" s="12"/>
-      <c r="F1" s="12"/>
-      <c r="G1" s="12"/>
-      <c r="H1" s="12"/>
-    </row>
-    <row r="2" spans="1:8" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="B1" s="22"/>
+      <c r="C1" s="22"/>
+      <c r="D1" s="22"/>
+      <c r="E1" s="22"/>
+      <c r="F1" s="22"/>
+      <c r="G1" s="22"/>
+      <c r="H1" s="22"/>
+    </row>
+    <row r="2" spans="1:8" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A2" s="1" t="s">
         <v>125</v>
       </c>
@@ -3162,7 +3195,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="3" spans="1:8" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:8" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A3" s="2" t="s">
         <v>130</v>
       </c>
@@ -3172,7 +3205,7 @@
       <c r="C3" s="2">
         <v>81</v>
       </c>
-      <c r="D3" s="21">
+      <c r="D3" s="19">
         <f>C3-B3</f>
         <v>-8.7999999999999972</v>
       </c>
@@ -3183,7 +3216,7 @@
         <v>132</v>
       </c>
     </row>
-    <row r="4" spans="1:8" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:8" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A4" s="4" t="s">
         <v>133</v>
       </c>
@@ -3193,7 +3226,7 @@
       <c r="C4" s="4">
         <v>99.1</v>
       </c>
-      <c r="D4" s="22">
+      <c r="D4" s="20">
         <f t="shared" ref="D4:D8" si="0">C4-B4</f>
         <v>-0.90000000000000568</v>
       </c>
@@ -3204,7 +3237,7 @@
         <v>135</v>
       </c>
     </row>
-    <row r="5" spans="1:8" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:8" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A5" s="2" t="s">
         <v>136</v>
       </c>
@@ -3214,7 +3247,7 @@
       <c r="C5" s="2">
         <v>94</v>
       </c>
-      <c r="D5" s="21">
+      <c r="D5" s="19">
         <f t="shared" si="0"/>
         <v>-5.9000000000000057</v>
       </c>
@@ -3225,7 +3258,7 @@
         <v>138</v>
       </c>
     </row>
-    <row r="6" spans="1:8" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:8" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A6" s="4" t="s">
         <v>139</v>
       </c>
@@ -3235,7 +3268,7 @@
       <c r="C6" s="4">
         <v>85.3</v>
       </c>
-      <c r="D6" s="22">
+      <c r="D6" s="20">
         <f t="shared" si="0"/>
         <v>-8.4000000000000057</v>
       </c>
@@ -3246,7 +3279,7 @@
         <v>132</v>
       </c>
     </row>
-    <row r="7" spans="1:8" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:8" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A7" s="2" t="s">
         <v>140</v>
       </c>
@@ -3256,7 +3289,7 @@
       <c r="C7" s="2">
         <v>89.6</v>
       </c>
-      <c r="D7" s="21">
+      <c r="D7" s="19">
         <f t="shared" si="0"/>
         <v>-7.5</v>
       </c>
@@ -3267,7 +3300,7 @@
         <v>138</v>
       </c>
     </row>
-    <row r="8" spans="1:8" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:8" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A8" s="4" t="s">
         <v>141</v>
       </c>
@@ -3277,7 +3310,7 @@
       <c r="C8" s="4">
         <v>14.2</v>
       </c>
-      <c r="D8" s="22">
+      <c r="D8" s="20">
         <f t="shared" si="0"/>
         <v>-34.799999999999997</v>
       </c>
@@ -3294,6 +3327,9 @@
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.511811023622047" footer="0.511811023622047"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300"/>
+  <headerFooter>
+    <oddFooter>&amp;C_x000D_&amp;1#&amp;"Aptos"&amp;10&amp;K0000FF CLASSIFICATION: Public</oddFooter>
+  </headerFooter>
 </worksheet>
 </file>
 
@@ -3303,7 +3339,7 @@
     <tabColor rgb="FFE87722"/>
   </sheetPr>
   <dimension ref="A1:H8"/>
-  <sheetFormatPr defaultColWidth="8.6640625" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultColWidth="8.7109375" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="18" customWidth="1"/>
     <col min="2" max="4" width="10" customWidth="1"/>
@@ -3311,19 +3347,19 @@
     <col min="6" max="6" width="40" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:8" ht="21.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A1" s="12" t="s">
+    <row r="1" spans="1:8" ht="21.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A1" s="22" t="s">
         <v>143</v>
       </c>
-      <c r="B1" s="12"/>
-      <c r="C1" s="12"/>
-      <c r="D1" s="12"/>
-      <c r="E1" s="12"/>
-      <c r="F1" s="12"/>
-      <c r="G1" s="12"/>
-      <c r="H1" s="12"/>
-    </row>
-    <row r="2" spans="1:8" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="B1" s="22"/>
+      <c r="C1" s="22"/>
+      <c r="D1" s="22"/>
+      <c r="E1" s="22"/>
+      <c r="F1" s="22"/>
+      <c r="G1" s="22"/>
+      <c r="H1" s="22"/>
+    </row>
+    <row r="2" spans="1:8" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A2" s="1" t="s">
         <v>144</v>
       </c>
@@ -3343,17 +3379,17 @@
         <v>13</v>
       </c>
     </row>
-    <row r="3" spans="1:8" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:8" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A3" s="2" t="s">
         <v>145</v>
       </c>
-      <c r="B3" s="16">
+      <c r="B3" s="14">
         <v>89.6</v>
       </c>
-      <c r="C3" s="16">
+      <c r="C3" s="14">
         <v>80.8</v>
       </c>
-      <c r="D3" s="19">
+      <c r="D3" s="17">
         <f>C3-B3</f>
         <v>-8.7999999999999972</v>
       </c>
@@ -3368,17 +3404,17 @@
         <v>80.8</v>
       </c>
     </row>
-    <row r="4" spans="1:8" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:8" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A4" s="4" t="s">
         <v>146</v>
       </c>
-      <c r="B4" s="17">
+      <c r="B4" s="15">
         <v>88.8</v>
       </c>
-      <c r="C4" s="17">
+      <c r="C4" s="15">
         <v>80.8</v>
       </c>
-      <c r="D4" s="20">
+      <c r="D4" s="18">
         <f t="shared" ref="D4:D7" si="0">C4-B4</f>
         <v>-8</v>
       </c>
@@ -3393,17 +3429,17 @@
         <v>80.8</v>
       </c>
     </row>
-    <row r="5" spans="1:8" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:8" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A5" s="2" t="s">
         <v>147</v>
       </c>
-      <c r="B5" s="16">
+      <c r="B5" s="14">
         <v>87</v>
       </c>
-      <c r="C5" s="16">
+      <c r="C5" s="14">
         <v>76.8</v>
       </c>
-      <c r="D5" s="19">
+      <c r="D5" s="17">
         <f t="shared" si="0"/>
         <v>-10.200000000000003</v>
       </c>
@@ -3420,17 +3456,17 @@
         <v>76.8</v>
       </c>
     </row>
-    <row r="6" spans="1:8" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:8" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A6" s="4" t="s">
         <v>149</v>
       </c>
-      <c r="B6" s="17">
+      <c r="B6" s="15">
         <v>95</v>
       </c>
-      <c r="C6" s="17">
+      <c r="C6" s="15">
         <v>83.6</v>
       </c>
-      <c r="D6" s="20">
+      <c r="D6" s="18">
         <f t="shared" si="0"/>
         <v>-11.400000000000006</v>
       </c>
@@ -3445,17 +3481,17 @@
         <v>83.6</v>
       </c>
     </row>
-    <row r="7" spans="1:8" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:8" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A7" s="2" t="s">
         <v>150</v>
       </c>
-      <c r="B7" s="16">
+      <c r="B7" s="14">
         <v>95.1</v>
       </c>
-      <c r="C7" s="16">
+      <c r="C7" s="14">
         <v>90</v>
       </c>
-      <c r="D7" s="19">
+      <c r="D7" s="17">
         <f t="shared" si="0"/>
         <v>-5.0999999999999943</v>
       </c>
@@ -3472,10 +3508,10 @@
         <v>90</v>
       </c>
     </row>
-    <row r="8" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A8" s="5"/>
-      <c r="B8" s="18"/>
-      <c r="C8" s="18"/>
+      <c r="B8" s="16"/>
+      <c r="C8" s="16"/>
       <c r="D8" s="5"/>
       <c r="E8" s="5"/>
       <c r="F8" s="5"/>
@@ -3486,5 +3522,8 @@
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.511811023622047" footer="0.511811023622047"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300"/>
+  <headerFooter>
+    <oddFooter>&amp;C_x000D_&amp;1#&amp;"Aptos"&amp;10&amp;K0000FF CLASSIFICATION: Public</oddFooter>
+  </headerFooter>
 </worksheet>
 </file>
--- a/Dashboard_Data.xlsx
+++ b/Dashboard_Data.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://alfanargroup-my.sharepoint.com/personal/ahmed_abdelzaher_alfanar_com/Documents/SDCC Dashboard/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="14_{682A7E4B-1055-4B0F-805D-134F59E89DE5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="1" documentId="14_{682A7E4B-1055-4B0F-805D-134F59E89DE5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{47C63B07-ADE5-433F-96FF-9EA0FCFC6C7D}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" tabRatio="500" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" tabRatio="500" activeTab="4" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Header" sheetId="1" r:id="rId1"/>
@@ -28,7 +28,6 @@
     <sheet name="Footer" sheetId="13" r:id="rId13"/>
   </sheets>
   <calcPr calcId="191029" iterateDelta="1E-4"/>
-  <fileRecoveryPr repairLoad="1"/>
   <extLst>
     <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
       <xcalcf:calcFeatures>
@@ -49,7 +48,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="381" uniqueCount="245">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="377" uniqueCount="242">
   <si>
     <t>HEADER — Dashboard Title &amp; PM</t>
   </si>
@@ -271,15 +270,6 @@
   </si>
   <si>
     <t>Text field — shown as-is</t>
-  </si>
-  <si>
-    <t>Cash Collected Gap</t>
-  </si>
-  <si>
-    <t>21 pts behind</t>
-  </si>
-  <si>
-    <t>Red</t>
   </si>
   <si>
     <t>CASH FLOW STATUS (SAR Millions)</t>
@@ -935,12 +925,6 @@
   </cellStyleXfs>
   <cellXfs count="18">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="2" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
@@ -982,6 +966,12 @@
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="9" fontId="3" fillId="4" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -1259,54 +1249,54 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:8" ht="21.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A1" s="2" t="s">
+      <c r="A1" s="16" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="2"/>
-      <c r="C1" s="2"/>
-      <c r="D1" s="2"/>
-      <c r="E1" s="2"/>
-      <c r="F1" s="2"/>
-      <c r="G1" s="2"/>
-      <c r="H1" s="2"/>
+      <c r="B1" s="16"/>
+      <c r="C1" s="16"/>
+      <c r="D1" s="16"/>
+      <c r="E1" s="16"/>
+      <c r="F1" s="16"/>
+      <c r="G1" s="16"/>
+      <c r="H1" s="16"/>
     </row>
     <row r="2" spans="1:8" ht="18" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A2" s="3" t="s">
+      <c r="A2" s="1" t="s">
         <v>1</v>
       </c>
-      <c r="B2" s="3" t="s">
+      <c r="B2" s="1" t="s">
         <v>2</v>
       </c>
     </row>
     <row r="3" spans="1:8" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A3" s="4" t="s">
+      <c r="A3" s="2" t="s">
         <v>3</v>
       </c>
-      <c r="B3" s="5" t="s">
+      <c r="B3" s="3" t="s">
         <v>4</v>
       </c>
     </row>
     <row r="4" spans="1:8" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A4" s="6" t="s">
+      <c r="A4" s="4" t="s">
         <v>5</v>
       </c>
-      <c r="B4" s="5" t="s">
+      <c r="B4" s="3" t="s">
         <v>6</v>
       </c>
     </row>
     <row r="5" spans="1:8" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A5" s="4" t="s">
+      <c r="A5" s="2" t="s">
         <v>7</v>
       </c>
-      <c r="B5" s="5" t="s">
+      <c r="B5" s="3" t="s">
         <v>8</v>
       </c>
     </row>
     <row r="6" spans="1:8" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A6" s="6" t="s">
+      <c r="A6" s="4" t="s">
         <v>9</v>
       </c>
-      <c r="B6" s="5" t="s">
+      <c r="B6" s="3" t="s">
         <v>10</v>
       </c>
     </row>
@@ -1341,397 +1331,397 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:8" ht="21.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A1" s="2" t="s">
+      <c r="A1" s="16" t="s">
+        <v>149</v>
+      </c>
+      <c r="B1" s="16"/>
+      <c r="C1" s="16"/>
+      <c r="D1" s="16"/>
+      <c r="E1" s="16"/>
+      <c r="F1" s="16"/>
+      <c r="G1" s="16"/>
+      <c r="H1" s="16"/>
+    </row>
+    <row r="2" spans="1:8" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A2" s="1" t="s">
+        <v>150</v>
+      </c>
+      <c r="B2" s="1" t="s">
+        <v>151</v>
+      </c>
+      <c r="C2" s="1" t="s">
         <v>152</v>
       </c>
-      <c r="B1" s="2"/>
-      <c r="C1" s="2"/>
-      <c r="D1" s="2"/>
-      <c r="E1" s="2"/>
-      <c r="F1" s="2"/>
-      <c r="G1" s="2"/>
-      <c r="H1" s="2"/>
-    </row>
-    <row r="2" spans="1:8" ht="18" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A2" s="3" t="s">
+      <c r="D2" s="1" t="s">
         <v>153</v>
       </c>
-      <c r="B2" s="3" t="s">
+      <c r="E2" s="1" t="s">
         <v>154</v>
       </c>
-      <c r="C2" s="3" t="s">
+      <c r="F2" s="1" t="s">
         <v>155</v>
       </c>
-      <c r="D2" s="3" t="s">
+      <c r="G2" s="1" t="s">
         <v>156</v>
       </c>
-      <c r="E2" s="3" t="s">
+      <c r="H2" s="1" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="3" spans="1:8" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A3" s="8" t="s">
         <v>157</v>
       </c>
-      <c r="F2" s="3" t="s">
+      <c r="B3" s="2" t="s">
         <v>158</v>
       </c>
-      <c r="G2" s="3" t="s">
+      <c r="C3" s="2" t="s">
         <v>159</v>
       </c>
-      <c r="H2" s="3" t="s">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="3" spans="1:8" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A3" s="10" t="s">
+      <c r="D3" s="2" t="s">
         <v>160</v>
       </c>
-      <c r="B3" s="4" t="s">
+      <c r="E3" s="2" t="s">
         <v>161</v>
       </c>
-      <c r="C3" s="4" t="s">
+      <c r="F3" s="2"/>
+      <c r="G3" s="2"/>
+      <c r="H3" s="2" t="s">
         <v>162</v>
       </c>
-      <c r="D3" s="4" t="s">
+    </row>
+    <row r="4" spans="1:8" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A4" s="4" t="s">
         <v>163</v>
       </c>
-      <c r="E3" s="4" t="s">
+      <c r="B4" s="4" t="s">
+        <v>161</v>
+      </c>
+      <c r="C4" s="4"/>
+      <c r="D4" s="4"/>
+      <c r="E4" s="4" t="s">
+        <v>161</v>
+      </c>
+      <c r="F4" s="4"/>
+      <c r="G4" s="4"/>
+      <c r="H4" s="4"/>
+    </row>
+    <row r="5" spans="1:8" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A5" s="2" t="s">
         <v>164</v>
       </c>
-      <c r="F3" s="4"/>
-      <c r="G3" s="4"/>
-      <c r="H3" s="4" t="s">
+      <c r="B5" s="2" t="s">
+        <v>161</v>
+      </c>
+      <c r="C5" s="2"/>
+      <c r="D5" s="2"/>
+      <c r="E5" s="2" t="s">
+        <v>161</v>
+      </c>
+      <c r="F5" s="2"/>
+      <c r="G5" s="2"/>
+      <c r="H5" s="2"/>
+    </row>
+    <row r="6" spans="1:8" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A6" s="4" t="s">
         <v>165</v>
       </c>
-    </row>
-    <row r="4" spans="1:8" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A4" s="6" t="s">
+      <c r="B6" s="4" t="s">
+        <v>161</v>
+      </c>
+      <c r="C6" s="4"/>
+      <c r="D6" s="4"/>
+      <c r="E6" s="4" t="s">
+        <v>161</v>
+      </c>
+      <c r="F6" s="4"/>
+      <c r="G6" s="4"/>
+      <c r="H6" s="4"/>
+    </row>
+    <row r="7" spans="1:8" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A7" s="8" t="s">
         <v>166</v>
       </c>
-      <c r="B4" s="6" t="s">
-        <v>164</v>
-      </c>
-      <c r="C4" s="6"/>
-      <c r="D4" s="6"/>
-      <c r="E4" s="6" t="s">
-        <v>164</v>
-      </c>
-      <c r="F4" s="6"/>
-      <c r="G4" s="6"/>
-      <c r="H4" s="6"/>
-    </row>
-    <row r="5" spans="1:8" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A5" s="4" t="s">
+      <c r="B7" s="2" t="s">
+        <v>158</v>
+      </c>
+      <c r="C7" s="2" t="s">
         <v>167</v>
       </c>
-      <c r="B5" s="4" t="s">
-        <v>164</v>
-      </c>
-      <c r="C5" s="4"/>
-      <c r="D5" s="4"/>
-      <c r="E5" s="4" t="s">
-        <v>164</v>
-      </c>
-      <c r="F5" s="4"/>
-      <c r="G5" s="4"/>
-      <c r="H5" s="4"/>
-    </row>
-    <row r="6" spans="1:8" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A6" s="6" t="s">
+      <c r="D7" s="2" t="s">
+        <v>160</v>
+      </c>
+      <c r="E7" s="2" t="s">
+        <v>161</v>
+      </c>
+      <c r="F7" s="2"/>
+      <c r="G7" s="2"/>
+      <c r="H7" s="2"/>
+    </row>
+    <row r="8" spans="1:8" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A8" s="8" t="s">
         <v>168</v>
       </c>
-      <c r="B6" s="6" t="s">
-        <v>164</v>
-      </c>
-      <c r="C6" s="6"/>
-      <c r="D6" s="6"/>
-      <c r="E6" s="6" t="s">
-        <v>164</v>
-      </c>
-      <c r="F6" s="6"/>
-      <c r="G6" s="6"/>
-      <c r="H6" s="6"/>
-    </row>
-    <row r="7" spans="1:8" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A7" s="10" t="s">
+      <c r="B8" s="4" t="s">
+        <v>158</v>
+      </c>
+      <c r="C8" s="4" t="s">
         <v>169</v>
       </c>
-      <c r="B7" s="4" t="s">
+      <c r="D8" s="4" t="s">
+        <v>170</v>
+      </c>
+      <c r="E8" s="4" t="s">
         <v>161</v>
       </c>
-      <c r="C7" s="4" t="s">
-        <v>170</v>
-      </c>
-      <c r="D7" s="4" t="s">
-        <v>163</v>
-      </c>
-      <c r="E7" s="4" t="s">
-        <v>164</v>
-      </c>
-      <c r="F7" s="4"/>
-      <c r="G7" s="4"/>
-      <c r="H7" s="4"/>
-    </row>
-    <row r="8" spans="1:8" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A8" s="10" t="s">
+      <c r="F8" s="4"/>
+      <c r="G8" s="4"/>
+      <c r="H8" s="4" t="s">
         <v>171</v>
       </c>
-      <c r="B8" s="6" t="s">
+    </row>
+    <row r="9" spans="1:8" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A9" s="2" t="s">
+        <v>172</v>
+      </c>
+      <c r="B9" s="2" t="s">
         <v>161</v>
       </c>
-      <c r="C8" s="6" t="s">
-        <v>172</v>
-      </c>
-      <c r="D8" s="6" t="s">
+      <c r="C9" s="2"/>
+      <c r="D9" s="2"/>
+      <c r="E9" s="2" t="s">
+        <v>161</v>
+      </c>
+      <c r="F9" s="2"/>
+      <c r="G9" s="2"/>
+      <c r="H9" s="2"/>
+    </row>
+    <row r="10" spans="1:8" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A10" s="8" t="s">
         <v>173</v>
       </c>
-      <c r="E8" s="6" t="s">
-        <v>164</v>
-      </c>
-      <c r="F8" s="6"/>
-      <c r="G8" s="6"/>
-      <c r="H8" s="6" t="s">
+      <c r="B10" s="4" t="s">
+        <v>158</v>
+      </c>
+      <c r="C10" s="4" t="s">
         <v>174</v>
       </c>
-    </row>
-    <row r="9" spans="1:8" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A9" s="4" t="s">
+      <c r="D10" s="4" t="s">
+        <v>160</v>
+      </c>
+      <c r="E10" s="4" t="s">
+        <v>161</v>
+      </c>
+      <c r="F10" s="4"/>
+      <c r="G10" s="4"/>
+      <c r="H10" s="4"/>
+    </row>
+    <row r="11" spans="1:8" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A11" s="2" t="s">
         <v>175</v>
       </c>
-      <c r="B9" s="4" t="s">
-        <v>164</v>
-      </c>
-      <c r="C9" s="4"/>
-      <c r="D9" s="4"/>
-      <c r="E9" s="4" t="s">
-        <v>164</v>
-      </c>
-      <c r="F9" s="4"/>
-      <c r="G9" s="4"/>
-      <c r="H9" s="4"/>
-    </row>
-    <row r="10" spans="1:8" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A10" s="10" t="s">
+      <c r="B11" s="2" t="s">
+        <v>161</v>
+      </c>
+      <c r="C11" s="2"/>
+      <c r="D11" s="2"/>
+      <c r="E11" s="2" t="s">
+        <v>161</v>
+      </c>
+      <c r="F11" s="2"/>
+      <c r="G11" s="2"/>
+      <c r="H11" s="2"/>
+    </row>
+    <row r="12" spans="1:8" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A12" s="4" t="s">
         <v>176</v>
       </c>
-      <c r="B10" s="6" t="s">
+      <c r="B12" s="4" t="s">
         <v>161</v>
       </c>
-      <c r="C10" s="6" t="s">
+      <c r="C12" s="4"/>
+      <c r="D12" s="4"/>
+      <c r="E12" s="4" t="s">
+        <v>161</v>
+      </c>
+      <c r="F12" s="4"/>
+      <c r="G12" s="4"/>
+      <c r="H12" s="4"/>
+    </row>
+    <row r="13" spans="1:8" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A13" s="2" t="s">
         <v>177</v>
       </c>
-      <c r="D10" s="6" t="s">
-        <v>163</v>
-      </c>
-      <c r="E10" s="6" t="s">
-        <v>164</v>
-      </c>
-      <c r="F10" s="6"/>
-      <c r="G10" s="6"/>
-      <c r="H10" s="6"/>
-    </row>
-    <row r="11" spans="1:8" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A11" s="4" t="s">
+      <c r="B13" s="2" t="s">
+        <v>161</v>
+      </c>
+      <c r="C13" s="2"/>
+      <c r="D13" s="2"/>
+      <c r="E13" s="2" t="s">
+        <v>161</v>
+      </c>
+      <c r="F13" s="2"/>
+      <c r="G13" s="2"/>
+      <c r="H13" s="2"/>
+    </row>
+    <row r="14" spans="1:8" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A14" s="4" t="s">
         <v>178</v>
       </c>
-      <c r="B11" s="4" t="s">
-        <v>164</v>
-      </c>
-      <c r="C11" s="4"/>
-      <c r="D11" s="4"/>
-      <c r="E11" s="4" t="s">
-        <v>164</v>
-      </c>
-      <c r="F11" s="4"/>
-      <c r="G11" s="4"/>
-      <c r="H11" s="4"/>
-    </row>
-    <row r="12" spans="1:8" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A12" s="6" t="s">
+      <c r="B14" s="4" t="s">
+        <v>161</v>
+      </c>
+      <c r="C14" s="4"/>
+      <c r="D14" s="4"/>
+      <c r="E14" s="4" t="s">
+        <v>161</v>
+      </c>
+      <c r="F14" s="4"/>
+      <c r="G14" s="4"/>
+      <c r="H14" s="4"/>
+    </row>
+    <row r="15" spans="1:8" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A15" s="8" t="s">
         <v>179</v>
       </c>
-      <c r="B12" s="6" t="s">
-        <v>164</v>
-      </c>
-      <c r="C12" s="6"/>
-      <c r="D12" s="6"/>
-      <c r="E12" s="6" t="s">
-        <v>164</v>
-      </c>
-      <c r="F12" s="6"/>
-      <c r="G12" s="6"/>
-      <c r="H12" s="6"/>
-    </row>
-    <row r="13" spans="1:8" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A13" s="4" t="s">
+      <c r="B15" s="2" t="s">
+        <v>158</v>
+      </c>
+      <c r="C15" s="2" t="s">
         <v>180</v>
       </c>
-      <c r="B13" s="4" t="s">
-        <v>164</v>
-      </c>
-      <c r="C13" s="4"/>
-      <c r="D13" s="4"/>
-      <c r="E13" s="4" t="s">
-        <v>164</v>
-      </c>
-      <c r="F13" s="4"/>
-      <c r="G13" s="4"/>
-      <c r="H13" s="4"/>
-    </row>
-    <row r="14" spans="1:8" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A14" s="6" t="s">
+      <c r="D15" s="2" t="s">
+        <v>160</v>
+      </c>
+      <c r="E15" s="2" t="s">
+        <v>161</v>
+      </c>
+      <c r="F15" s="2"/>
+      <c r="G15" s="2"/>
+      <c r="H15" s="2"/>
+    </row>
+    <row r="16" spans="1:8" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A16" s="4" t="s">
         <v>181</v>
       </c>
-      <c r="B14" s="6" t="s">
-        <v>164</v>
-      </c>
-      <c r="C14" s="6"/>
-      <c r="D14" s="6"/>
-      <c r="E14" s="6" t="s">
-        <v>164</v>
-      </c>
-      <c r="F14" s="6"/>
-      <c r="G14" s="6"/>
-      <c r="H14" s="6"/>
-    </row>
-    <row r="15" spans="1:8" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A15" s="10" t="s">
+      <c r="B16" s="4" t="s">
+        <v>161</v>
+      </c>
+      <c r="C16" s="4"/>
+      <c r="D16" s="4"/>
+      <c r="E16" s="4" t="s">
+        <v>161</v>
+      </c>
+      <c r="F16" s="4"/>
+      <c r="G16" s="4"/>
+      <c r="H16" s="4"/>
+    </row>
+    <row r="17" spans="1:8" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A17" s="2" t="s">
         <v>182</v>
       </c>
-      <c r="B15" s="4" t="s">
+      <c r="B17" s="2" t="s">
         <v>161</v>
       </c>
-      <c r="C15" s="4" t="s">
+      <c r="C17" s="2"/>
+      <c r="D17" s="2"/>
+      <c r="E17" s="2" t="s">
+        <v>161</v>
+      </c>
+      <c r="F17" s="2"/>
+      <c r="G17" s="2"/>
+      <c r="H17" s="2"/>
+    </row>
+    <row r="18" spans="1:8" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A18" s="4" t="s">
         <v>183</v>
       </c>
-      <c r="D15" s="4" t="s">
-        <v>163</v>
-      </c>
-      <c r="E15" s="4" t="s">
-        <v>164</v>
-      </c>
-      <c r="F15" s="4"/>
-      <c r="G15" s="4"/>
-      <c r="H15" s="4"/>
-    </row>
-    <row r="16" spans="1:8" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A16" s="6" t="s">
+      <c r="B18" s="4" t="s">
+        <v>161</v>
+      </c>
+      <c r="C18" s="4"/>
+      <c r="D18" s="4"/>
+      <c r="E18" s="4" t="s">
+        <v>161</v>
+      </c>
+      <c r="F18" s="4"/>
+      <c r="G18" s="4"/>
+      <c r="H18" s="4"/>
+    </row>
+    <row r="19" spans="1:8" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A19" s="2" t="s">
         <v>184</v>
       </c>
-      <c r="B16" s="6" t="s">
-        <v>164</v>
-      </c>
-      <c r="C16" s="6"/>
-      <c r="D16" s="6"/>
-      <c r="E16" s="6" t="s">
-        <v>164</v>
-      </c>
-      <c r="F16" s="6"/>
-      <c r="G16" s="6"/>
-      <c r="H16" s="6"/>
-    </row>
-    <row r="17" spans="1:8" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A17" s="4" t="s">
+      <c r="B19" s="2" t="s">
+        <v>161</v>
+      </c>
+      <c r="C19" s="2"/>
+      <c r="D19" s="2"/>
+      <c r="E19" s="2" t="s">
+        <v>161</v>
+      </c>
+      <c r="F19" s="2"/>
+      <c r="G19" s="2"/>
+      <c r="H19" s="2"/>
+    </row>
+    <row r="20" spans="1:8" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A20" s="9" t="s">
         <v>185</v>
       </c>
-      <c r="B17" s="4" t="s">
-        <v>164</v>
-      </c>
-      <c r="C17" s="4"/>
-      <c r="D17" s="4"/>
-      <c r="E17" s="4" t="s">
-        <v>164</v>
-      </c>
-      <c r="F17" s="4"/>
-      <c r="G17" s="4"/>
-      <c r="H17" s="4"/>
-    </row>
-    <row r="18" spans="1:8" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A18" s="6" t="s">
+      <c r="B20" s="9" t="s">
+        <v>161</v>
+      </c>
+      <c r="C20" s="9"/>
+      <c r="D20" s="9"/>
+      <c r="E20" s="9" t="s">
+        <v>158</v>
+      </c>
+      <c r="F20" s="9" t="s">
+        <v>24</v>
+      </c>
+      <c r="G20" s="9" t="s">
+        <v>25</v>
+      </c>
+      <c r="H20" s="9" t="s">
         <v>186</v>
       </c>
-      <c r="B18" s="6" t="s">
-        <v>164</v>
-      </c>
-      <c r="C18" s="6"/>
-      <c r="D18" s="6"/>
-      <c r="E18" s="6" t="s">
-        <v>164</v>
-      </c>
-      <c r="F18" s="6"/>
-      <c r="G18" s="6"/>
-      <c r="H18" s="6"/>
-    </row>
-    <row r="19" spans="1:8" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A19" s="4" t="s">
+    </row>
+    <row r="21" spans="1:8" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A21" s="2" t="s">
         <v>187</v>
       </c>
-      <c r="B19" s="4" t="s">
-        <v>164</v>
-      </c>
-      <c r="C19" s="4"/>
-      <c r="D19" s="4"/>
-      <c r="E19" s="4" t="s">
-        <v>164</v>
-      </c>
-      <c r="F19" s="4"/>
-      <c r="G19" s="4"/>
-      <c r="H19" s="4"/>
-    </row>
-    <row r="20" spans="1:8" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A20" s="11" t="s">
+      <c r="B21" s="2" t="s">
+        <v>161</v>
+      </c>
+      <c r="C21" s="2"/>
+      <c r="D21" s="2"/>
+      <c r="E21" s="2" t="s">
+        <v>161</v>
+      </c>
+      <c r="F21" s="2"/>
+      <c r="G21" s="2"/>
+      <c r="H21" s="2"/>
+    </row>
+    <row r="22" spans="1:8" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A22" s="10" t="s">
         <v>188</v>
       </c>
-      <c r="B20" s="11" t="s">
-        <v>164</v>
-      </c>
-      <c r="C20" s="11"/>
-      <c r="D20" s="11"/>
-      <c r="E20" s="11" t="s">
+      <c r="B22" s="10" t="s">
         <v>161</v>
       </c>
-      <c r="F20" s="11" t="s">
-        <v>24</v>
-      </c>
-      <c r="G20" s="11" t="s">
-        <v>25</v>
-      </c>
-      <c r="H20" s="11" t="s">
+      <c r="C22" s="10"/>
+      <c r="D22" s="10"/>
+      <c r="E22" s="10" t="s">
+        <v>158</v>
+      </c>
+      <c r="F22" s="10" t="s">
         <v>189</v>
       </c>
-    </row>
-    <row r="21" spans="1:8" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A21" s="4" t="s">
+      <c r="G22" s="10" t="s">
+        <v>28</v>
+      </c>
+      <c r="H22" s="10" t="s">
         <v>190</v>
-      </c>
-      <c r="B21" s="4" t="s">
-        <v>164</v>
-      </c>
-      <c r="C21" s="4"/>
-      <c r="D21" s="4"/>
-      <c r="E21" s="4" t="s">
-        <v>164</v>
-      </c>
-      <c r="F21" s="4"/>
-      <c r="G21" s="4"/>
-      <c r="H21" s="4"/>
-    </row>
-    <row r="22" spans="1:8" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A22" s="12" t="s">
-        <v>191</v>
-      </c>
-      <c r="B22" s="12" t="s">
-        <v>164</v>
-      </c>
-      <c r="C22" s="12"/>
-      <c r="D22" s="12"/>
-      <c r="E22" s="12" t="s">
-        <v>161</v>
-      </c>
-      <c r="F22" s="12" t="s">
-        <v>192</v>
-      </c>
-      <c r="G22" s="12" t="s">
-        <v>28</v>
-      </c>
-      <c r="H22" s="12" t="s">
-        <v>193</v>
       </c>
     </row>
   </sheetData>
@@ -1763,95 +1753,95 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:8" ht="21.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A1" s="2" t="s">
+      <c r="A1" s="16" t="s">
+        <v>191</v>
+      </c>
+      <c r="B1" s="16"/>
+      <c r="C1" s="16"/>
+      <c r="D1" s="16"/>
+      <c r="E1" s="16"/>
+      <c r="F1" s="16"/>
+      <c r="G1" s="16"/>
+      <c r="H1" s="16"/>
+    </row>
+    <row r="2" spans="1:8" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A2" s="1" t="s">
+        <v>192</v>
+      </c>
+      <c r="B2" s="1" t="s">
+        <v>193</v>
+      </c>
+      <c r="C2" s="1" t="s">
         <v>194</v>
       </c>
-      <c r="B1" s="2"/>
-      <c r="C1" s="2"/>
-      <c r="D1" s="2"/>
-      <c r="E1" s="2"/>
-      <c r="F1" s="2"/>
-      <c r="G1" s="2"/>
-      <c r="H1" s="2"/>
-    </row>
-    <row r="2" spans="1:8" ht="18" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A2" s="3" t="s">
+      <c r="D2" s="1" t="s">
         <v>195</v>
       </c>
-      <c r="B2" s="3" t="s">
+      <c r="E2" s="1" t="s">
         <v>196</v>
       </c>
-      <c r="C2" s="3" t="s">
+      <c r="F2" s="1" t="s">
         <v>197</v>
       </c>
-      <c r="D2" s="3" t="s">
+    </row>
+    <row r="3" spans="1:8" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A3" s="2">
+        <v>1</v>
+      </c>
+      <c r="B3" s="2" t="s">
         <v>198</v>
       </c>
-      <c r="E2" s="3" t="s">
+      <c r="C3" s="2" t="s">
+        <v>135</v>
+      </c>
+      <c r="D3" s="2" t="s">
         <v>199</v>
       </c>
-      <c r="F2" s="3" t="s">
+      <c r="E3" s="2" t="s">
         <v>200</v>
       </c>
-    </row>
-    <row r="3" spans="1:8" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A3" s="4">
-        <v>1</v>
-      </c>
-      <c r="B3" s="4" t="s">
+      <c r="F3" s="11" t="s">
         <v>201</v>
       </c>
-      <c r="C3" s="4" t="s">
-        <v>138</v>
-      </c>
-      <c r="D3" s="4" t="s">
+    </row>
+    <row r="4" spans="1:8" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A4" s="4">
+        <v>2</v>
+      </c>
+      <c r="B4" s="4" t="s">
         <v>202</v>
       </c>
-      <c r="E3" s="4" t="s">
+      <c r="C4" s="4" t="s">
+        <v>135</v>
+      </c>
+      <c r="D4" s="4" t="s">
         <v>203</v>
       </c>
-      <c r="F3" s="13" t="s">
+      <c r="E4" s="4" t="s">
         <v>204</v>
       </c>
-    </row>
-    <row r="4" spans="1:8" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A4" s="6">
-        <v>2</v>
-      </c>
-      <c r="B4" s="6" t="s">
+      <c r="F4" s="11" t="s">
+        <v>201</v>
+      </c>
+    </row>
+    <row r="5" spans="1:8" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A5" s="2">
+        <v>3</v>
+      </c>
+      <c r="B5" s="2" t="s">
         <v>205</v>
       </c>
-      <c r="C4" s="6" t="s">
-        <v>138</v>
-      </c>
-      <c r="D4" s="6" t="s">
+      <c r="C5" s="2" t="s">
+        <v>134</v>
+      </c>
+      <c r="D5" s="2" t="s">
+        <v>199</v>
+      </c>
+      <c r="E5" s="2" t="s">
         <v>206</v>
       </c>
-      <c r="E4" s="6" t="s">
+      <c r="F5" s="12" t="s">
         <v>207</v>
-      </c>
-      <c r="F4" s="13" t="s">
-        <v>204</v>
-      </c>
-    </row>
-    <row r="5" spans="1:8" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A5" s="4">
-        <v>3</v>
-      </c>
-      <c r="B5" s="4" t="s">
-        <v>208</v>
-      </c>
-      <c r="C5" s="4" t="s">
-        <v>137</v>
-      </c>
-      <c r="D5" s="4" t="s">
-        <v>202</v>
-      </c>
-      <c r="E5" s="4" t="s">
-        <v>209</v>
-      </c>
-      <c r="F5" s="14" t="s">
-        <v>210</v>
       </c>
     </row>
   </sheetData>
@@ -1882,249 +1872,249 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:8" ht="21.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A1" s="2" t="s">
+      <c r="A1" s="16" t="s">
+        <v>208</v>
+      </c>
+      <c r="B1" s="16"/>
+      <c r="C1" s="16"/>
+      <c r="D1" s="16"/>
+      <c r="E1" s="16"/>
+      <c r="F1" s="16"/>
+      <c r="G1" s="16"/>
+      <c r="H1" s="16"/>
+    </row>
+    <row r="2" spans="1:8" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A2" s="1" t="s">
+        <v>192</v>
+      </c>
+      <c r="B2" s="1" t="s">
+        <v>131</v>
+      </c>
+      <c r="C2" s="1" t="s">
+        <v>209</v>
+      </c>
+      <c r="D2" s="1" t="s">
+        <v>210</v>
+      </c>
+      <c r="E2" s="1" t="s">
         <v>211</v>
       </c>
-      <c r="B1" s="2"/>
-      <c r="C1" s="2"/>
-      <c r="D1" s="2"/>
-      <c r="E1" s="2"/>
-      <c r="F1" s="2"/>
-      <c r="G1" s="2"/>
-      <c r="H1" s="2"/>
-    </row>
-    <row r="2" spans="1:8" ht="18" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A2" s="3" t="s">
-        <v>195</v>
-      </c>
-      <c r="B2" s="3" t="s">
-        <v>134</v>
-      </c>
-      <c r="C2" s="3" t="s">
+      <c r="F2" s="1" t="s">
         <v>212</v>
       </c>
-      <c r="D2" s="3" t="s">
+      <c r="G2" s="1" t="s">
         <v>213</v>
       </c>
-      <c r="E2" s="3" t="s">
+      <c r="H2" s="1" t="s">
         <v>214</v>
       </c>
-      <c r="F2" s="3" t="s">
+    </row>
+    <row r="3" spans="1:8" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A3" s="2">
+        <v>1</v>
+      </c>
+      <c r="B3" s="2" t="s">
         <v>215</v>
       </c>
-      <c r="G2" s="3" t="s">
+      <c r="C3" s="2" t="s">
         <v>216</v>
       </c>
-      <c r="H2" s="3" t="s">
+      <c r="D3" s="2" t="s">
         <v>217</v>
       </c>
-    </row>
-    <row r="3" spans="1:8" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A3" s="4">
-        <v>1</v>
-      </c>
-      <c r="B3" s="4" t="s">
+      <c r="E3" s="2" t="s">
+        <v>47</v>
+      </c>
+      <c r="F3" s="2" t="s">
+        <v>47</v>
+      </c>
+      <c r="G3" s="2" t="s">
+        <v>47</v>
+      </c>
+      <c r="H3" s="13" t="s">
         <v>218</v>
       </c>
-      <c r="C3" s="4" t="s">
+    </row>
+    <row r="4" spans="1:8" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A4" s="4">
+        <v>2</v>
+      </c>
+      <c r="B4" s="4" t="s">
         <v>219</v>
       </c>
-      <c r="D3" s="4" t="s">
+      <c r="C4" s="4" t="s">
         <v>220</v>
       </c>
-      <c r="E3" s="4" t="s">
+      <c r="D4" s="4" t="s">
+        <v>217</v>
+      </c>
+      <c r="E4" s="4" t="s">
         <v>47</v>
       </c>
-      <c r="F3" s="4" t="s">
+      <c r="F4" s="4" t="s">
         <v>47</v>
       </c>
-      <c r="G3" s="4" t="s">
+      <c r="G4" s="4" t="s">
         <v>47</v>
       </c>
-      <c r="H3" s="15" t="s">
+      <c r="H4" s="13" t="s">
+        <v>218</v>
+      </c>
+    </row>
+    <row r="5" spans="1:8" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A5" s="2">
+        <v>3</v>
+      </c>
+      <c r="B5" s="2" t="s">
         <v>221</v>
       </c>
-    </row>
-    <row r="4" spans="1:8" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A4" s="6">
-        <v>2</v>
-      </c>
-      <c r="B4" s="6" t="s">
+      <c r="C5" s="2" t="s">
+        <v>203</v>
+      </c>
+      <c r="D5" s="2" t="s">
+        <v>217</v>
+      </c>
+      <c r="E5" s="2" t="s">
+        <v>47</v>
+      </c>
+      <c r="F5" s="2" t="s">
+        <v>47</v>
+      </c>
+      <c r="G5" s="2" t="s">
+        <v>47</v>
+      </c>
+      <c r="H5" s="13" t="s">
+        <v>218</v>
+      </c>
+    </row>
+    <row r="6" spans="1:8" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A6" s="4">
+        <v>4</v>
+      </c>
+      <c r="B6" s="4" t="s">
         <v>222</v>
       </c>
-      <c r="C4" s="6" t="s">
+      <c r="C6" s="4" t="s">
         <v>223</v>
       </c>
-      <c r="D4" s="6" t="s">
-        <v>220</v>
-      </c>
-      <c r="E4" s="6" t="s">
+      <c r="D6" s="4" t="s">
+        <v>217</v>
+      </c>
+      <c r="E6" s="4" t="s">
         <v>47</v>
       </c>
-      <c r="F4" s="6" t="s">
+      <c r="F6" s="4" t="s">
         <v>47</v>
       </c>
-      <c r="G4" s="6" t="s">
+      <c r="G6" s="4" t="s">
         <v>47</v>
       </c>
-      <c r="H4" s="15" t="s">
-        <v>221</v>
-      </c>
-    </row>
-    <row r="5" spans="1:8" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A5" s="4">
-        <v>3</v>
-      </c>
-      <c r="B5" s="4" t="s">
+      <c r="H6" s="13" t="s">
+        <v>218</v>
+      </c>
+    </row>
+    <row r="7" spans="1:8" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A7" s="2">
+        <v>5</v>
+      </c>
+      <c r="B7" s="2" t="s">
         <v>224</v>
       </c>
-      <c r="C5" s="4" t="s">
-        <v>206</v>
-      </c>
-      <c r="D5" s="4" t="s">
-        <v>220</v>
-      </c>
-      <c r="E5" s="4" t="s">
+      <c r="C7" s="2" t="s">
+        <v>225</v>
+      </c>
+      <c r="D7" s="2" t="s">
+        <v>217</v>
+      </c>
+      <c r="E7" s="2" t="s">
         <v>47</v>
       </c>
-      <c r="F5" s="4" t="s">
+      <c r="F7" s="2" t="s">
         <v>47</v>
       </c>
-      <c r="G5" s="4" t="s">
+      <c r="G7" s="2" t="s">
         <v>47</v>
       </c>
-      <c r="H5" s="15" t="s">
-        <v>221</v>
-      </c>
-    </row>
-    <row r="6" spans="1:8" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A6" s="6">
-        <v>4</v>
-      </c>
-      <c r="B6" s="6" t="s">
-        <v>225</v>
-      </c>
-      <c r="C6" s="6" t="s">
+      <c r="H7" s="13" t="s">
+        <v>218</v>
+      </c>
+    </row>
+    <row r="8" spans="1:8" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A8" s="4">
+        <v>6</v>
+      </c>
+      <c r="B8" s="4" t="s">
         <v>226</v>
       </c>
-      <c r="D6" s="6" t="s">
-        <v>220</v>
-      </c>
-      <c r="E6" s="6" t="s">
+      <c r="C8" s="4" t="s">
+        <v>227</v>
+      </c>
+      <c r="D8" s="4" t="s">
+        <v>217</v>
+      </c>
+      <c r="E8" s="4" t="s">
         <v>47</v>
       </c>
-      <c r="F6" s="6" t="s">
+      <c r="F8" s="4" t="s">
         <v>47</v>
       </c>
-      <c r="G6" s="6" t="s">
+      <c r="G8" s="4" t="s">
         <v>47</v>
       </c>
-      <c r="H6" s="15" t="s">
-        <v>221</v>
-      </c>
-    </row>
-    <row r="7" spans="1:8" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A7" s="4">
-        <v>5</v>
-      </c>
-      <c r="B7" s="4" t="s">
-        <v>227</v>
-      </c>
-      <c r="C7" s="4" t="s">
+      <c r="H8" s="13" t="s">
+        <v>218</v>
+      </c>
+    </row>
+    <row r="9" spans="1:8" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A9" s="2">
+        <v>7</v>
+      </c>
+      <c r="B9" s="2" t="s">
         <v>228</v>
       </c>
-      <c r="D7" s="4" t="s">
-        <v>220</v>
-      </c>
-      <c r="E7" s="4" t="s">
+      <c r="C9" s="2" t="s">
+        <v>229</v>
+      </c>
+      <c r="D9" s="2" t="s">
+        <v>217</v>
+      </c>
+      <c r="E9" s="2" t="s">
         <v>47</v>
       </c>
-      <c r="F7" s="4" t="s">
+      <c r="F9" s="2" t="s">
         <v>47</v>
       </c>
-      <c r="G7" s="4" t="s">
+      <c r="G9" s="2" t="s">
         <v>47</v>
       </c>
-      <c r="H7" s="15" t="s">
-        <v>221</v>
-      </c>
-    </row>
-    <row r="8" spans="1:8" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A8" s="6">
-        <v>6</v>
-      </c>
-      <c r="B8" s="6" t="s">
-        <v>229</v>
-      </c>
-      <c r="C8" s="6" t="s">
+      <c r="H9" s="13" t="s">
+        <v>218</v>
+      </c>
+    </row>
+    <row r="10" spans="1:8" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A10" s="4">
+        <v>8</v>
+      </c>
+      <c r="B10" s="4" t="s">
         <v>230</v>
       </c>
-      <c r="D8" s="6" t="s">
-        <v>220</v>
-      </c>
-      <c r="E8" s="6" t="s">
+      <c r="C10" s="4" t="s">
+        <v>203</v>
+      </c>
+      <c r="D10" s="4" t="s">
+        <v>217</v>
+      </c>
+      <c r="E10" s="4" t="s">
         <v>47</v>
       </c>
-      <c r="F8" s="6" t="s">
+      <c r="F10" s="4" t="s">
         <v>47</v>
       </c>
-      <c r="G8" s="6" t="s">
-        <v>47</v>
-      </c>
-      <c r="H8" s="15" t="s">
-        <v>221</v>
-      </c>
-    </row>
-    <row r="9" spans="1:8" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A9" s="4">
-        <v>7</v>
-      </c>
-      <c r="B9" s="4" t="s">
+      <c r="G10" s="4" t="s">
         <v>231</v>
       </c>
-      <c r="C9" s="4" t="s">
+      <c r="H10" s="11" t="s">
         <v>232</v>
-      </c>
-      <c r="D9" s="4" t="s">
-        <v>220</v>
-      </c>
-      <c r="E9" s="4" t="s">
-        <v>47</v>
-      </c>
-      <c r="F9" s="4" t="s">
-        <v>47</v>
-      </c>
-      <c r="G9" s="4" t="s">
-        <v>47</v>
-      </c>
-      <c r="H9" s="15" t="s">
-        <v>221</v>
-      </c>
-    </row>
-    <row r="10" spans="1:8" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A10" s="6">
-        <v>8</v>
-      </c>
-      <c r="B10" s="6" t="s">
-        <v>233</v>
-      </c>
-      <c r="C10" s="6" t="s">
-        <v>206</v>
-      </c>
-      <c r="D10" s="6" t="s">
-        <v>220</v>
-      </c>
-      <c r="E10" s="6" t="s">
-        <v>47</v>
-      </c>
-      <c r="F10" s="6" t="s">
-        <v>47</v>
-      </c>
-      <c r="G10" s="6" t="s">
-        <v>234</v>
-      </c>
-      <c r="H10" s="13" t="s">
-        <v>235</v>
       </c>
     </row>
   </sheetData>
@@ -2152,55 +2142,55 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:8" ht="21.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A1" s="2" t="s">
+      <c r="A1" s="16" t="s">
+        <v>233</v>
+      </c>
+      <c r="B1" s="16"/>
+      <c r="C1" s="16"/>
+      <c r="D1" s="16"/>
+      <c r="E1" s="16"/>
+      <c r="F1" s="16"/>
+      <c r="G1" s="16"/>
+      <c r="H1" s="16"/>
+    </row>
+    <row r="2" spans="1:8" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A2" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="B2" s="1" t="s">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="3" spans="1:8" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A3" s="2" t="s">
+        <v>234</v>
+      </c>
+      <c r="B3" s="3" t="s">
+        <v>235</v>
+      </c>
+    </row>
+    <row r="4" spans="1:8" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A4" s="4" t="s">
         <v>236</v>
       </c>
-      <c r="B1" s="2"/>
-      <c r="C1" s="2"/>
-      <c r="D1" s="2"/>
-      <c r="E1" s="2"/>
-      <c r="F1" s="2"/>
-      <c r="G1" s="2"/>
-      <c r="H1" s="2"/>
-    </row>
-    <row r="2" spans="1:8" ht="18" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A2" s="3" t="s">
-        <v>1</v>
-      </c>
-      <c r="B2" s="3" t="s">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="3" spans="1:8" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A3" s="4" t="s">
+      <c r="B4" s="3" t="s">
         <v>237</v>
       </c>
-      <c r="B3" s="5" t="s">
+    </row>
+    <row r="5" spans="1:8" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A5" s="2" t="s">
         <v>238</v>
       </c>
-    </row>
-    <row r="4" spans="1:8" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A4" s="6" t="s">
+      <c r="B5" s="3" t="s">
         <v>239</v>
       </c>
-      <c r="B4" s="5" t="s">
+    </row>
+    <row r="6" spans="1:8" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A6" s="4" t="s">
         <v>240</v>
       </c>
-    </row>
-    <row r="5" spans="1:8" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A5" s="4" t="s">
+      <c r="B6" s="3" t="s">
         <v>241</v>
-      </c>
-      <c r="B5" s="5" t="s">
-        <v>242</v>
-      </c>
-    </row>
-    <row r="6" spans="1:8" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A6" s="6" t="s">
-        <v>243</v>
-      </c>
-      <c r="B6" s="5" t="s">
-        <v>244</v>
       </c>
     </row>
   </sheetData>
@@ -2229,92 +2219,92 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:8" ht="21.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A1" s="2" t="s">
+      <c r="A1" s="16" t="s">
         <v>11</v>
       </c>
-      <c r="B1" s="2"/>
-      <c r="C1" s="2"/>
-      <c r="D1" s="2"/>
-      <c r="E1" s="2"/>
-      <c r="F1" s="2"/>
-      <c r="G1" s="2"/>
-      <c r="H1" s="2"/>
+      <c r="B1" s="16"/>
+      <c r="C1" s="16"/>
+      <c r="D1" s="16"/>
+      <c r="E1" s="16"/>
+      <c r="F1" s="16"/>
+      <c r="G1" s="16"/>
+      <c r="H1" s="16"/>
     </row>
     <row r="2" spans="1:8" ht="18" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A2" s="3" t="s">
+      <c r="A2" s="1" t="s">
         <v>1</v>
       </c>
-      <c r="B2" s="3" t="s">
+      <c r="B2" s="1" t="s">
         <v>12</v>
       </c>
-      <c r="C2" s="3" t="s">
+      <c r="C2" s="1" t="s">
         <v>13</v>
       </c>
     </row>
     <row r="3" spans="1:8" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A3" s="4" t="s">
+      <c r="A3" s="2" t="s">
         <v>14</v>
       </c>
-      <c r="B3" s="5" t="s">
+      <c r="B3" s="3" t="s">
         <v>15</v>
       </c>
-      <c r="C3" s="4"/>
+      <c r="C3" s="2"/>
     </row>
     <row r="4" spans="1:8" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A4" s="6" t="s">
+      <c r="A4" s="4" t="s">
         <v>16</v>
       </c>
-      <c r="B4" s="5" t="s">
+      <c r="B4" s="3" t="s">
         <v>17</v>
       </c>
-      <c r="C4" s="6"/>
+      <c r="C4" s="4"/>
     </row>
     <row r="5" spans="1:8" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A5" s="4" t="s">
+      <c r="A5" s="2" t="s">
         <v>18</v>
       </c>
-      <c r="B5" s="5" t="s">
+      <c r="B5" s="3" t="s">
         <v>19</v>
       </c>
-      <c r="C5" s="4"/>
+      <c r="C5" s="2"/>
     </row>
     <row r="6" spans="1:8" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A6" s="6" t="s">
+      <c r="A6" s="4" t="s">
         <v>20</v>
       </c>
-      <c r="B6" s="5" t="s">
+      <c r="B6" s="3" t="s">
         <v>21</v>
       </c>
-      <c r="C6" s="6"/>
+      <c r="C6" s="4"/>
     </row>
     <row r="7" spans="1:8" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A7" s="4" t="s">
+      <c r="A7" s="2" t="s">
         <v>22</v>
       </c>
-      <c r="B7" s="5" t="s">
+      <c r="B7" s="3" t="s">
         <v>23</v>
       </c>
-      <c r="C7" s="4"/>
+      <c r="C7" s="2"/>
     </row>
     <row r="8" spans="1:8" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A8" s="6" t="s">
+      <c r="A8" s="4" t="s">
         <v>24</v>
       </c>
-      <c r="B8" s="5" t="s">
+      <c r="B8" s="3" t="s">
         <v>25</v>
       </c>
-      <c r="C8" s="6" t="s">
+      <c r="C8" s="4" t="s">
         <v>26</v>
       </c>
     </row>
     <row r="9" spans="1:8" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A9" s="4" t="s">
+      <c r="A9" s="2" t="s">
         <v>27</v>
       </c>
-      <c r="B9" s="5" t="s">
+      <c r="B9" s="3" t="s">
         <v>28</v>
       </c>
-      <c r="C9" s="4" t="s">
+      <c r="C9" s="2" t="s">
         <v>29</v>
       </c>
     </row>
@@ -2345,104 +2335,104 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:8" ht="21.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A1" s="2" t="s">
+      <c r="A1" s="16" t="s">
         <v>30</v>
       </c>
-      <c r="B1" s="2"/>
-      <c r="C1" s="2"/>
-      <c r="D1" s="2"/>
-      <c r="E1" s="2"/>
-      <c r="F1" s="2"/>
-      <c r="G1" s="2"/>
-      <c r="H1" s="2"/>
+      <c r="B1" s="16"/>
+      <c r="C1" s="16"/>
+      <c r="D1" s="16"/>
+      <c r="E1" s="16"/>
+      <c r="F1" s="16"/>
+      <c r="G1" s="16"/>
+      <c r="H1" s="16"/>
     </row>
     <row r="2" spans="1:8" ht="18" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A2" s="3" t="s">
+      <c r="A2" s="1" t="s">
         <v>1</v>
       </c>
-      <c r="B2" s="3" t="s">
+      <c r="B2" s="1" t="s">
         <v>31</v>
       </c>
-      <c r="C2" s="3" t="s">
+      <c r="C2" s="1" t="s">
         <v>32</v>
       </c>
-      <c r="D2" s="3" t="s">
+      <c r="D2" s="1" t="s">
         <v>13</v>
       </c>
     </row>
     <row r="3" spans="1:8" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A3" s="4" t="s">
+      <c r="A3" s="2" t="s">
         <v>33</v>
       </c>
-      <c r="B3" s="5">
+      <c r="B3" s="3">
         <v>388016486</v>
       </c>
-      <c r="C3" s="4"/>
-      <c r="D3" s="4"/>
+      <c r="C3" s="2"/>
+      <c r="D3" s="2"/>
     </row>
     <row r="4" spans="1:8" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A4" s="6" t="s">
+      <c r="A4" s="4" t="s">
         <v>34</v>
       </c>
-      <c r="B4" s="5">
+      <c r="B4" s="3">
         <v>0</v>
       </c>
-      <c r="C4" s="6"/>
-      <c r="D4" s="6"/>
+      <c r="C4" s="4"/>
+      <c r="D4" s="4"/>
     </row>
     <row r="5" spans="1:8" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A5" s="4" t="s">
+      <c r="A5" s="2" t="s">
         <v>35</v>
       </c>
-      <c r="B5" s="5">
+      <c r="B5" s="3">
         <v>0</v>
       </c>
-      <c r="C5" s="4"/>
-      <c r="D5" s="4"/>
+      <c r="C5" s="2"/>
+      <c r="D5" s="2"/>
     </row>
     <row r="6" spans="1:8" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A6" s="6" t="s">
+      <c r="A6" s="4" t="s">
         <v>36</v>
       </c>
-      <c r="B6" s="5">
+      <c r="B6" s="3">
         <v>0</v>
       </c>
-      <c r="C6" s="6"/>
-      <c r="D6" s="6"/>
+      <c r="C6" s="4"/>
+      <c r="D6" s="4"/>
     </row>
     <row r="7" spans="1:8" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A7" s="4" t="s">
+      <c r="A7" s="2" t="s">
         <v>37</v>
       </c>
-      <c r="B7" s="5">
+      <c r="B7" s="3">
         <v>388016486</v>
       </c>
-      <c r="C7" s="4"/>
-      <c r="D7" s="4" t="s">
+      <c r="C7" s="2"/>
+      <c r="D7" s="2" t="s">
         <v>38</v>
       </c>
     </row>
     <row r="8" spans="1:8" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A8" s="6" t="s">
+      <c r="A8" s="4" t="s">
         <v>39</v>
       </c>
-      <c r="B8" s="5">
+      <c r="B8" s="3">
         <v>34426811</v>
       </c>
-      <c r="C8" s="6"/>
-      <c r="D8" s="6"/>
+      <c r="C8" s="4"/>
+      <c r="D8" s="4"/>
     </row>
     <row r="9" spans="1:8" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A9" s="4" t="s">
+      <c r="A9" s="2" t="s">
         <v>40</v>
       </c>
-      <c r="B9" s="5">
+      <c r="B9" s="3">
         <v>15596872</v>
       </c>
-      <c r="C9" s="4" t="s">
+      <c r="C9" s="2" t="s">
         <v>41</v>
       </c>
-      <c r="D9" s="4" t="s">
+      <c r="D9" s="2" t="s">
         <v>42</v>
       </c>
     </row>
@@ -2473,115 +2463,115 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:8" ht="21.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A1" s="2" t="s">
+      <c r="A1" s="16" t="s">
         <v>43</v>
       </c>
-      <c r="B1" s="2"/>
-      <c r="C1" s="2"/>
-      <c r="D1" s="2"/>
-      <c r="E1" s="2"/>
-      <c r="F1" s="2"/>
-      <c r="G1" s="2"/>
-      <c r="H1" s="2"/>
+      <c r="B1" s="16"/>
+      <c r="C1" s="16"/>
+      <c r="D1" s="16"/>
+      <c r="E1" s="16"/>
+      <c r="F1" s="16"/>
+      <c r="G1" s="16"/>
+      <c r="H1" s="16"/>
     </row>
     <row r="2" spans="1:8" ht="18" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A2" s="3" t="s">
+      <c r="A2" s="1" t="s">
         <v>1</v>
       </c>
-      <c r="B2" s="3" t="s">
+      <c r="B2" s="1" t="s">
         <v>2</v>
       </c>
-      <c r="C2" s="3" t="s">
+      <c r="C2" s="1" t="s">
         <v>32</v>
       </c>
-      <c r="D2" s="3" t="s">
+      <c r="D2" s="1" t="s">
         <v>13</v>
       </c>
     </row>
     <row r="3" spans="1:8" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A3" s="4" t="s">
+      <c r="A3" s="2" t="s">
         <v>44</v>
       </c>
-      <c r="B3" s="5">
+      <c r="B3" s="3">
         <v>355587125</v>
       </c>
-      <c r="C3" s="4"/>
-      <c r="D3" s="4" t="s">
+      <c r="C3" s="2"/>
+      <c r="D3" s="2" t="s">
         <v>45</v>
       </c>
     </row>
     <row r="4" spans="1:8" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A4" s="6" t="s">
+      <c r="A4" s="4" t="s">
         <v>46</v>
       </c>
-      <c r="B4" s="5" t="s">
+      <c r="B4" s="3" t="s">
         <v>47</v>
       </c>
-      <c r="C4" s="6"/>
-      <c r="D4" s="6" t="s">
+      <c r="C4" s="4"/>
+      <c r="D4" s="4" t="s">
         <v>48</v>
       </c>
     </row>
     <row r="5" spans="1:8" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A5" s="4" t="s">
+      <c r="A5" s="2" t="s">
         <v>49</v>
       </c>
-      <c r="B5" s="16">
+      <c r="B5" s="14">
         <v>0.45</v>
       </c>
-      <c r="C5" s="17">
+      <c r="C5" s="15">
         <f>B4-B5</f>
         <v>0.55000000000000004</v>
       </c>
-      <c r="D5" s="4" t="s">
+      <c r="D5" s="2" t="s">
         <v>50</v>
       </c>
     </row>
     <row r="6" spans="1:8" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A6" s="6" t="s">
+      <c r="A6" s="4" t="s">
         <v>39</v>
       </c>
-      <c r="B6" s="5">
+      <c r="B6" s="3">
         <v>34426811</v>
       </c>
-      <c r="C6" s="6"/>
-      <c r="D6" s="6" t="s">
+      <c r="C6" s="4"/>
+      <c r="D6" s="4" t="s">
         <v>45</v>
       </c>
     </row>
     <row r="7" spans="1:8" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A7" s="4" t="s">
+      <c r="A7" s="2" t="s">
         <v>40</v>
       </c>
-      <c r="B7" s="5">
+      <c r="B7" s="3">
         <v>15596872</v>
       </c>
-      <c r="C7" s="4"/>
-      <c r="D7" s="4" t="s">
+      <c r="C7" s="2"/>
+      <c r="D7" s="2" t="s">
         <v>45</v>
       </c>
     </row>
     <row r="8" spans="1:8" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A8" s="6" t="s">
+      <c r="A8" s="4" t="s">
         <v>51</v>
       </c>
-      <c r="B8" s="5" t="s">
+      <c r="B8" s="3" t="s">
         <v>52</v>
       </c>
-      <c r="C8" s="6"/>
-      <c r="D8" s="6" t="s">
+      <c r="C8" s="4"/>
+      <c r="D8" s="4" t="s">
         <v>53</v>
       </c>
     </row>
     <row r="9" spans="1:8" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A9" s="4" t="s">
+      <c r="A9" s="2" t="s">
         <v>54</v>
       </c>
-      <c r="B9" s="5" t="s">
+      <c r="B9" s="3" t="s">
         <v>55</v>
       </c>
-      <c r="C9" s="4"/>
-      <c r="D9" s="4" t="s">
+      <c r="C9" s="2"/>
+      <c r="D9" s="2" t="s">
         <v>56</v>
       </c>
     </row>
@@ -2602,7 +2592,7 @@
   <sheetPr>
     <tabColor rgb="FFE87722"/>
   </sheetPr>
-  <dimension ref="A1:H9"/>
+  <dimension ref="A1:H8"/>
   <sheetFormatPr defaultColWidth="8.7109375" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="32" customWidth="1"/>
@@ -2613,134 +2603,119 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:8" ht="21.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A1" s="2" t="s">
+      <c r="A1" s="16" t="s">
         <v>57</v>
       </c>
-      <c r="B1" s="2"/>
-      <c r="C1" s="2"/>
-      <c r="D1" s="2"/>
-      <c r="E1" s="2"/>
-      <c r="F1" s="2"/>
-      <c r="G1" s="2"/>
-      <c r="H1" s="2"/>
+      <c r="B1" s="16"/>
+      <c r="C1" s="16"/>
+      <c r="D1" s="16"/>
+      <c r="E1" s="16"/>
+      <c r="F1" s="16"/>
+      <c r="G1" s="16"/>
+      <c r="H1" s="16"/>
     </row>
     <row r="2" spans="1:8" ht="18" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A2" s="3" t="s">
+      <c r="A2" s="1" t="s">
         <v>1</v>
       </c>
-      <c r="B2" s="3" t="s">
+      <c r="B2" s="1" t="s">
         <v>31</v>
       </c>
-      <c r="C2" s="3" t="s">
+      <c r="C2" s="1" t="s">
         <v>58</v>
       </c>
-      <c r="D2" s="3" t="s">
+      <c r="D2" s="1" t="s">
         <v>59</v>
       </c>
-      <c r="E2" s="3" t="s">
+      <c r="E2" s="1" t="s">
         <v>13</v>
       </c>
     </row>
     <row r="3" spans="1:8" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A3" s="4" t="s">
+      <c r="A3" s="2" t="s">
         <v>60</v>
       </c>
-      <c r="B3" s="5">
+      <c r="B3" s="3">
         <v>204059236</v>
       </c>
-      <c r="C3" s="4" t="s">
+      <c r="C3" s="2" t="s">
         <v>61</v>
       </c>
-      <c r="D3" s="4" t="s">
+      <c r="D3" s="2" t="s">
         <v>62</v>
       </c>
-      <c r="E3" s="4"/>
+      <c r="E3" s="2"/>
     </row>
     <row r="4" spans="1:8" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A4" s="6" t="s">
+      <c r="A4" s="4" t="s">
         <v>63</v>
       </c>
-      <c r="B4" s="5">
+      <c r="B4" s="3">
         <v>152961744</v>
       </c>
-      <c r="C4" s="6" t="s">
+      <c r="C4" s="4" t="s">
         <v>64</v>
       </c>
-      <c r="D4" s="6" t="s">
+      <c r="D4" s="4" t="s">
         <v>65</v>
       </c>
-      <c r="E4" s="6"/>
+      <c r="E4" s="4"/>
     </row>
     <row r="5" spans="1:8" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A5" s="4" t="s">
+      <c r="A5" s="2" t="s">
         <v>66</v>
       </c>
-      <c r="B5" s="5">
+      <c r="B5" s="3">
         <v>152961744</v>
       </c>
-      <c r="C5" s="4" t="s">
+      <c r="C5" s="2" t="s">
         <v>64</v>
       </c>
-      <c r="D5" s="4" t="s">
+      <c r="D5" s="2" t="s">
         <v>65</v>
       </c>
-      <c r="E5" s="4"/>
+      <c r="E5" s="2"/>
     </row>
     <row r="6" spans="1:8" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A6" s="6" t="s">
+      <c r="A6" s="4" t="s">
         <v>67</v>
       </c>
-      <c r="B6" s="5">
+      <c r="B6" s="3">
         <v>0</v>
       </c>
-      <c r="C6" s="6"/>
-      <c r="D6" s="6" t="s">
+      <c r="C6" s="4"/>
+      <c r="D6" s="4" t="s">
         <v>68</v>
       </c>
-      <c r="E6" s="6"/>
+      <c r="E6" s="4"/>
     </row>
     <row r="7" spans="1:8" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A7" s="4" t="s">
+      <c r="A7" s="2" t="s">
         <v>69</v>
       </c>
-      <c r="B7" s="5">
+      <c r="B7" s="3">
         <v>68039022</v>
       </c>
-      <c r="C7" s="4" t="s">
+      <c r="C7" s="2" t="s">
         <v>70</v>
       </c>
-      <c r="D7" s="4" t="s">
+      <c r="D7" s="2" t="s">
         <v>65</v>
       </c>
-      <c r="E7" s="4"/>
+      <c r="E7" s="2"/>
     </row>
     <row r="8" spans="1:8" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A8" s="6" t="s">
+      <c r="A8" s="4" t="s">
         <v>71</v>
       </c>
-      <c r="B8" s="5" t="s">
+      <c r="B8" s="3" t="s">
         <v>72</v>
       </c>
-      <c r="C8" s="6"/>
-      <c r="D8" s="6" t="s">
+      <c r="C8" s="4"/>
+      <c r="D8" s="4" t="s">
         <v>68</v>
       </c>
-      <c r="E8" s="6" t="s">
-        <v>73</v>
-      </c>
-    </row>
-    <row r="9" spans="1:8" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A9" s="4" t="s">
-        <v>74</v>
-      </c>
-      <c r="B9" s="5" t="s">
-        <v>75</v>
-      </c>
-      <c r="C9" s="4"/>
-      <c r="D9" s="4" t="s">
-        <v>76</v>
-      </c>
-      <c r="E9" s="4" t="s">
+      <c r="E8" s="4" t="s">
         <v>73</v>
       </c>
     </row>
@@ -2771,81 +2746,81 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:8" ht="21.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A1" s="2" t="s">
+      <c r="A1" s="16" t="s">
+        <v>74</v>
+      </c>
+      <c r="B1" s="16"/>
+      <c r="C1" s="16"/>
+      <c r="D1" s="16"/>
+      <c r="E1" s="16"/>
+      <c r="F1" s="16"/>
+      <c r="G1" s="16"/>
+      <c r="H1" s="16"/>
+    </row>
+    <row r="2" spans="1:8" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A2" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="B2" s="1" t="s">
+        <v>75</v>
+      </c>
+      <c r="C2" s="1" t="s">
+        <v>76</v>
+      </c>
+      <c r="D2" s="1" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="3" spans="1:8" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A3" s="2" t="s">
         <v>77</v>
       </c>
-      <c r="B1" s="2"/>
-      <c r="C1" s="2"/>
-      <c r="D1" s="2"/>
-      <c r="E1" s="2"/>
-      <c r="F1" s="2"/>
-      <c r="G1" s="2"/>
-      <c r="H1" s="2"/>
-    </row>
-    <row r="2" spans="1:8" ht="18" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A2" s="3" t="s">
-        <v>1</v>
-      </c>
-      <c r="B2" s="3" t="s">
+      <c r="B3" s="3">
+        <v>-61.1</v>
+      </c>
+      <c r="C3" s="2"/>
+      <c r="D3" s="2" t="s">
         <v>78</v>
       </c>
-      <c r="C2" s="3" t="s">
+    </row>
+    <row r="4" spans="1:8" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A4" s="4" t="s">
         <v>79</v>
       </c>
-      <c r="D2" s="3" t="s">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="3" spans="1:8" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A3" s="4" t="s">
+      <c r="B4" s="3" t="s">
         <v>80</v>
       </c>
-      <c r="B3" s="5">
-        <v>-61.1</v>
-      </c>
-      <c r="C3" s="4"/>
-      <c r="D3" s="4" t="s">
+      <c r="C4" s="4"/>
+      <c r="D4" s="4" t="s">
         <v>81</v>
       </c>
     </row>
-    <row r="4" spans="1:8" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A4" s="6" t="s">
+    <row r="5" spans="1:8" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A5" s="2" t="s">
         <v>82</v>
       </c>
-      <c r="B4" s="5" t="s">
+      <c r="B5" s="3">
+        <v>68</v>
+      </c>
+      <c r="C5" s="2" t="s">
         <v>83</v>
       </c>
-      <c r="C4" s="6"/>
-      <c r="D4" s="6" t="s">
+      <c r="D5" s="2" t="s">
         <v>84</v>
       </c>
     </row>
-    <row r="5" spans="1:8" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A5" s="4" t="s">
+    <row r="6" spans="1:8" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A6" s="4" t="s">
         <v>85</v>
       </c>
-      <c r="B5" s="5">
-        <v>68</v>
-      </c>
-      <c r="C5" s="4" t="s">
+      <c r="B6" s="3">
+        <v>129.19999999999999</v>
+      </c>
+      <c r="C6" s="4" t="s">
+        <v>47</v>
+      </c>
+      <c r="D6" s="4" t="s">
         <v>86</v>
-      </c>
-      <c r="D5" s="4" t="s">
-        <v>87</v>
-      </c>
-    </row>
-    <row r="6" spans="1:8" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A6" s="6" t="s">
-        <v>88</v>
-      </c>
-      <c r="B6" s="5">
-        <v>129.19999999999999</v>
-      </c>
-      <c r="C6" s="6" t="s">
-        <v>47</v>
-      </c>
-      <c r="D6" s="6" t="s">
-        <v>89</v>
       </c>
     </row>
   </sheetData>
@@ -2875,228 +2850,228 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:8" ht="21.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A1" s="2" t="s">
+      <c r="A1" s="16" t="s">
+        <v>87</v>
+      </c>
+      <c r="B1" s="16"/>
+      <c r="C1" s="16"/>
+      <c r="D1" s="16"/>
+      <c r="E1" s="16"/>
+      <c r="F1" s="16"/>
+      <c r="G1" s="16"/>
+      <c r="H1" s="16"/>
+    </row>
+    <row r="2" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A2" s="17" t="s">
+        <v>88</v>
+      </c>
+      <c r="B2" s="17"/>
+      <c r="C2" s="17"/>
+      <c r="D2" s="17"/>
+    </row>
+    <row r="3" spans="1:8" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A3" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="B3" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="C3" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="D3" s="1"/>
+    </row>
+    <row r="4" spans="1:8" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A4" s="4" t="s">
+        <v>89</v>
+      </c>
+      <c r="B4" s="3">
+        <v>147</v>
+      </c>
+      <c r="C4" s="4" t="s">
         <v>90</v>
       </c>
-      <c r="B1" s="2"/>
-      <c r="C1" s="2"/>
-      <c r="D1" s="2"/>
-      <c r="E1" s="2"/>
-      <c r="F1" s="2"/>
-      <c r="G1" s="2"/>
-      <c r="H1" s="2"/>
-    </row>
-    <row r="2" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A2" s="1" t="s">
+      <c r="D4" s="4"/>
+    </row>
+    <row r="5" spans="1:8" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A5" s="2" t="s">
         <v>91</v>
       </c>
-      <c r="B2" s="1"/>
-      <c r="C2" s="1"/>
-      <c r="D2" s="1"/>
-    </row>
-    <row r="3" spans="1:8" ht="18" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A3" s="3" t="s">
-        <v>1</v>
-      </c>
-      <c r="B3" s="3" t="s">
-        <v>2</v>
-      </c>
-      <c r="C3" s="3" t="s">
-        <v>13</v>
-      </c>
-      <c r="D3" s="3"/>
-    </row>
-    <row r="4" spans="1:8" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A4" s="6" t="s">
+      <c r="B5" s="3">
+        <v>117</v>
+      </c>
+      <c r="C5" s="2" t="s">
         <v>92</v>
       </c>
-      <c r="B4" s="5">
-        <v>147</v>
-      </c>
-      <c r="C4" s="6" t="s">
+      <c r="D5" s="2"/>
+    </row>
+    <row r="6" spans="1:8" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A6" s="4" t="s">
         <v>93</v>
       </c>
-      <c r="D4" s="6"/>
-    </row>
-    <row r="5" spans="1:8" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A5" s="4" t="s">
+      <c r="B6" s="3">
+        <v>30</v>
+      </c>
+      <c r="C6" s="4" t="s">
         <v>94</v>
       </c>
-      <c r="B5" s="5">
-        <v>117</v>
-      </c>
-      <c r="C5" s="4" t="s">
+      <c r="D6" s="4"/>
+    </row>
+    <row r="7" spans="1:8" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A7" s="2" t="s">
         <v>95</v>
       </c>
-      <c r="D5" s="4"/>
-    </row>
-    <row r="6" spans="1:8" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A6" s="6" t="s">
+      <c r="B7" s="3" t="s">
         <v>96</v>
       </c>
-      <c r="B6" s="5">
-        <v>30</v>
-      </c>
-      <c r="C6" s="6" t="s">
+      <c r="C7" s="2" t="s">
         <v>97</v>
       </c>
-      <c r="D6" s="6"/>
-    </row>
-    <row r="7" spans="1:8" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A7" s="4" t="s">
-        <v>98</v>
-      </c>
-      <c r="B7" s="5" t="s">
-        <v>99</v>
-      </c>
-      <c r="C7" s="4" t="s">
-        <v>100</v>
-      </c>
-      <c r="D7" s="4"/>
+      <c r="D7" s="2"/>
     </row>
     <row r="8" spans="1:8" ht="6" customHeight="1" x14ac:dyDescent="0.25"/>
     <row r="9" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A9" s="1" t="s">
+      <c r="A9" s="17" t="s">
+        <v>98</v>
+      </c>
+      <c r="B9" s="17"/>
+      <c r="C9" s="17"/>
+      <c r="D9" s="17"/>
+    </row>
+    <row r="10" spans="1:8" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A10" s="1" t="s">
+        <v>99</v>
+      </c>
+      <c r="B10" s="1" t="s">
+        <v>100</v>
+      </c>
+      <c r="C10" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="D10" s="1"/>
+    </row>
+    <row r="11" spans="1:8" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A11" s="2" t="s">
         <v>101</v>
       </c>
-      <c r="B9" s="1"/>
-      <c r="C9" s="1"/>
-      <c r="D9" s="1"/>
-    </row>
-    <row r="10" spans="1:8" ht="18" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A10" s="3" t="s">
+      <c r="B11" s="3">
+        <v>42</v>
+      </c>
+      <c r="C11" s="2" t="s">
         <v>102</v>
       </c>
-      <c r="B10" s="3" t="s">
+      <c r="D11" s="2"/>
+    </row>
+    <row r="12" spans="1:8" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A12" s="4" t="s">
         <v>103</v>
       </c>
-      <c r="C10" s="3" t="s">
-        <v>13</v>
-      </c>
-      <c r="D10" s="3"/>
-    </row>
-    <row r="11" spans="1:8" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A11" s="4" t="s">
-        <v>104</v>
-      </c>
-      <c r="B11" s="5">
-        <v>42</v>
-      </c>
-      <c r="C11" s="4" t="s">
-        <v>105</v>
-      </c>
-      <c r="D11" s="4"/>
-    </row>
-    <row r="12" spans="1:8" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A12" s="6" t="s">
-        <v>106</v>
-      </c>
-      <c r="B12" s="5">
+      <c r="B12" s="3">
         <v>75</v>
       </c>
-      <c r="C12" s="6" t="s">
-        <v>105</v>
-      </c>
-      <c r="D12" s="6"/>
+      <c r="C12" s="4" t="s">
+        <v>102</v>
+      </c>
+      <c r="D12" s="4"/>
     </row>
     <row r="13" spans="1:8" ht="6" customHeight="1" x14ac:dyDescent="0.25"/>
     <row r="14" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A14" s="1" t="s">
+      <c r="A14" s="17" t="s">
+        <v>104</v>
+      </c>
+      <c r="B14" s="17"/>
+      <c r="C14" s="17"/>
+      <c r="D14" s="17"/>
+    </row>
+    <row r="15" spans="1:8" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A15" s="1" t="s">
+        <v>105</v>
+      </c>
+      <c r="B15" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="C15" s="1" t="s">
+        <v>106</v>
+      </c>
+      <c r="D15" s="1"/>
+    </row>
+    <row r="16" spans="1:8" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A16" s="4" t="s">
         <v>107</v>
       </c>
-      <c r="B14" s="1"/>
-      <c r="C14" s="1"/>
-      <c r="D14" s="1"/>
-    </row>
-    <row r="15" spans="1:8" ht="18" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A15" s="3" t="s">
-        <v>108</v>
-      </c>
-      <c r="B15" s="3" t="s">
-        <v>2</v>
-      </c>
-      <c r="C15" s="3" t="s">
-        <v>109</v>
-      </c>
-      <c r="D15" s="3"/>
-    </row>
-    <row r="16" spans="1:8" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A16" s="6" t="s">
-        <v>110</v>
-      </c>
-      <c r="B16" s="5">
+      <c r="B16" s="3">
         <f>B4/B5*100</f>
         <v>125.64102564102564</v>
       </c>
-      <c r="C16" s="6" t="s">
-        <v>111</v>
-      </c>
-      <c r="D16" s="6"/>
+      <c r="C16" s="4" t="s">
+        <v>108</v>
+      </c>
+      <c r="D16" s="4"/>
     </row>
     <row r="17" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A17" s="4" t="s">
-        <v>112</v>
-      </c>
-      <c r="B17" s="5">
+      <c r="A17" s="2" t="s">
+        <v>109</v>
+      </c>
+      <c r="B17" s="3">
         <f>B6/B5*100</f>
         <v>25.641025641025639</v>
       </c>
-      <c r="C17" s="4" t="s">
-        <v>113</v>
-      </c>
-      <c r="D17" s="4"/>
+      <c r="C17" s="2" t="s">
+        <v>110</v>
+      </c>
+      <c r="D17" s="2"/>
     </row>
     <row r="18" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A18" s="6" t="s">
-        <v>114</v>
-      </c>
-      <c r="B18" s="5">
+      <c r="A18" s="4" t="s">
+        <v>111</v>
+      </c>
+      <c r="B18" s="3">
         <f>B16</f>
         <v>125.64102564102564</v>
       </c>
-      <c r="C18" s="6" t="s">
-        <v>115</v>
-      </c>
-      <c r="D18" s="6"/>
+      <c r="C18" s="4" t="s">
+        <v>112</v>
+      </c>
+      <c r="D18" s="4"/>
     </row>
     <row r="19" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A19" s="4" t="s">
-        <v>116</v>
-      </c>
-      <c r="B19" s="5">
+      <c r="A19" s="2" t="s">
+        <v>113</v>
+      </c>
+      <c r="B19" s="3">
         <f>100-B16</f>
         <v>-25.641025641025635</v>
       </c>
-      <c r="C19" s="4" t="s">
-        <v>117</v>
-      </c>
-      <c r="D19" s="4"/>
+      <c r="C19" s="2" t="s">
+        <v>114</v>
+      </c>
+      <c r="D19" s="2"/>
     </row>
     <row r="20" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A20" s="6" t="s">
-        <v>118</v>
-      </c>
-      <c r="B20" s="5">
+      <c r="A20" s="4" t="s">
+        <v>115</v>
+      </c>
+      <c r="B20" s="3">
         <f>B17</f>
         <v>25.641025641025639</v>
       </c>
-      <c r="C20" s="6" t="s">
-        <v>119</v>
-      </c>
-      <c r="D20" s="6"/>
+      <c r="C20" s="4" t="s">
+        <v>116</v>
+      </c>
+      <c r="D20" s="4"/>
     </row>
     <row r="21" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A21" s="4" t="s">
-        <v>120</v>
-      </c>
-      <c r="B21" s="5">
+      <c r="A21" s="2" t="s">
+        <v>117</v>
+      </c>
+      <c r="B21" s="3">
         <f>100-B17</f>
         <v>74.358974358974365</v>
       </c>
-      <c r="C21" s="4" t="s">
-        <v>121</v>
-      </c>
-      <c r="D21" s="4"/>
+      <c r="C21" s="2" t="s">
+        <v>118</v>
+      </c>
+      <c r="D21" s="2"/>
     </row>
   </sheetData>
   <mergeCells count="4">
@@ -3128,161 +3103,161 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:8" ht="21.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A1" s="2" t="s">
+      <c r="A1" s="16" t="s">
+        <v>119</v>
+      </c>
+      <c r="B1" s="16"/>
+      <c r="C1" s="16"/>
+      <c r="D1" s="16"/>
+      <c r="E1" s="16"/>
+      <c r="F1" s="16"/>
+      <c r="G1" s="16"/>
+      <c r="H1" s="16"/>
+    </row>
+    <row r="2" spans="1:8" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A2" s="1" t="s">
+        <v>120</v>
+      </c>
+      <c r="B2" s="1" t="s">
+        <v>121</v>
+      </c>
+      <c r="C2" s="1" t="s">
         <v>122</v>
       </c>
-      <c r="B1" s="2"/>
-      <c r="C1" s="2"/>
-      <c r="D1" s="2"/>
-      <c r="E1" s="2"/>
-      <c r="F1" s="2"/>
-      <c r="G1" s="2"/>
-      <c r="H1" s="2"/>
-    </row>
-    <row r="2" spans="1:8" ht="18" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A2" s="3" t="s">
+      <c r="D2" s="1" t="s">
         <v>123</v>
       </c>
-      <c r="B2" s="3" t="s">
+      <c r="E2" s="1" t="s">
         <v>124</v>
       </c>
-      <c r="C2" s="3" t="s">
+      <c r="F2" s="1" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="3" spans="1:8" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A3" s="2" t="s">
         <v>125</v>
       </c>
-      <c r="D2" s="3" t="s">
-        <v>126</v>
-      </c>
-      <c r="E2" s="3" t="s">
-        <v>127</v>
-      </c>
-      <c r="F2" s="3" t="s">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="3" spans="1:8" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A3" s="4" t="s">
-        <v>128</v>
-      </c>
-      <c r="B3" s="4">
+      <c r="B3" s="2">
         <v>89.8</v>
       </c>
-      <c r="C3" s="4">
+      <c r="C3" s="2">
         <v>81</v>
       </c>
-      <c r="D3" s="7">
+      <c r="D3" s="5">
         <f t="shared" ref="D3:D8" si="0">-C3+B3</f>
         <v>8.7999999999999972</v>
       </c>
-      <c r="E3" s="4" t="s">
-        <v>129</v>
-      </c>
-      <c r="F3" s="4" t="s">
-        <v>130</v>
+      <c r="E3" s="2" t="s">
+        <v>126</v>
+      </c>
+      <c r="F3" s="2" t="s">
+        <v>127</v>
       </c>
     </row>
     <row r="4" spans="1:8" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A4" s="6" t="s">
-        <v>131</v>
-      </c>
-      <c r="B4" s="6">
+      <c r="A4" s="4" t="s">
+        <v>128</v>
+      </c>
+      <c r="B4" s="4">
         <v>100</v>
       </c>
-      <c r="C4" s="6">
+      <c r="C4" s="4">
         <v>99.1</v>
       </c>
-      <c r="D4" s="8">
+      <c r="D4" s="6">
         <f t="shared" si="0"/>
         <v>0.90000000000000568</v>
       </c>
-      <c r="E4" s="6" t="s">
-        <v>132</v>
-      </c>
-      <c r="F4" s="6" t="s">
-        <v>133</v>
+      <c r="E4" s="4" t="s">
+        <v>129</v>
+      </c>
+      <c r="F4" s="4" t="s">
+        <v>130</v>
       </c>
     </row>
     <row r="5" spans="1:8" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A5" s="4" t="s">
-        <v>134</v>
-      </c>
-      <c r="B5" s="4">
+      <c r="A5" s="2" t="s">
+        <v>131</v>
+      </c>
+      <c r="B5" s="2">
         <v>99.9</v>
       </c>
-      <c r="C5" s="4">
+      <c r="C5" s="2">
         <v>94</v>
       </c>
-      <c r="D5" s="7">
+      <c r="D5" s="5">
         <f t="shared" si="0"/>
         <v>5.9000000000000057</v>
       </c>
-      <c r="E5" s="4" t="s">
-        <v>135</v>
-      </c>
-      <c r="F5" s="4" t="s">
-        <v>136</v>
+      <c r="E5" s="2" t="s">
+        <v>132</v>
+      </c>
+      <c r="F5" s="2" t="s">
+        <v>133</v>
       </c>
     </row>
     <row r="6" spans="1:8" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A6" s="6" t="s">
-        <v>137</v>
-      </c>
-      <c r="B6" s="6">
+      <c r="A6" s="4" t="s">
+        <v>134</v>
+      </c>
+      <c r="B6" s="4">
         <v>93.7</v>
       </c>
-      <c r="C6" s="6">
+      <c r="C6" s="4">
         <v>85.3</v>
       </c>
-      <c r="D6" s="8">
+      <c r="D6" s="6">
         <f t="shared" si="0"/>
         <v>8.4000000000000057</v>
       </c>
-      <c r="E6" s="6" t="s">
-        <v>129</v>
-      </c>
-      <c r="F6" s="6" t="s">
-        <v>130</v>
+      <c r="E6" s="4" t="s">
+        <v>126</v>
+      </c>
+      <c r="F6" s="4" t="s">
+        <v>127</v>
       </c>
     </row>
     <row r="7" spans="1:8" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A7" s="4" t="s">
-        <v>138</v>
-      </c>
-      <c r="B7" s="4">
+      <c r="A7" s="2" t="s">
+        <v>135</v>
+      </c>
+      <c r="B7" s="2">
         <v>97.1</v>
       </c>
-      <c r="C7" s="4">
+      <c r="C7" s="2">
         <v>89.6</v>
       </c>
-      <c r="D7" s="7">
+      <c r="D7" s="5">
         <f t="shared" si="0"/>
         <v>7.5</v>
       </c>
-      <c r="E7" s="4" t="s">
-        <v>135</v>
-      </c>
-      <c r="F7" s="4" t="s">
+      <c r="E7" s="2" t="s">
+        <v>132</v>
+      </c>
+      <c r="F7" s="2" t="s">
+        <v>133</v>
+      </c>
+    </row>
+    <row r="8" spans="1:8" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A8" s="4" t="s">
         <v>136</v>
       </c>
-    </row>
-    <row r="8" spans="1:8" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A8" s="6" t="s">
-        <v>139</v>
-      </c>
-      <c r="B8" s="6">
+      <c r="B8" s="4">
         <v>49</v>
       </c>
-      <c r="C8" s="6">
+      <c r="C8" s="4">
         <v>14.2</v>
       </c>
-      <c r="D8" s="8">
+      <c r="D8" s="6">
         <f t="shared" si="0"/>
         <v>34.799999999999997</v>
       </c>
-      <c r="E8" s="6" t="s">
-        <v>129</v>
-      </c>
-      <c r="F8" s="6" t="s">
-        <v>140</v>
+      <c r="E8" s="4" t="s">
+        <v>126</v>
+      </c>
+      <c r="F8" s="4" t="s">
+        <v>137</v>
       </c>
     </row>
   </sheetData>
@@ -3312,147 +3287,147 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:8" ht="21.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A1" s="2" t="s">
-        <v>141</v>
-      </c>
-      <c r="B1" s="2"/>
-      <c r="C1" s="2"/>
-      <c r="D1" s="2"/>
-      <c r="E1" s="2"/>
-      <c r="F1" s="2"/>
-      <c r="G1" s="2"/>
-      <c r="H1" s="2"/>
+      <c r="A1" s="16" t="s">
+        <v>138</v>
+      </c>
+      <c r="B1" s="16"/>
+      <c r="C1" s="16"/>
+      <c r="D1" s="16"/>
+      <c r="E1" s="16"/>
+      <c r="F1" s="16"/>
+      <c r="G1" s="16"/>
+      <c r="H1" s="16"/>
     </row>
     <row r="2" spans="1:8" ht="18" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A2" s="3" t="s">
-        <v>142</v>
-      </c>
-      <c r="B2" s="3" t="s">
+      <c r="A2" s="1" t="s">
+        <v>139</v>
+      </c>
+      <c r="B2" s="1" t="s">
+        <v>121</v>
+      </c>
+      <c r="C2" s="1" t="s">
+        <v>122</v>
+      </c>
+      <c r="D2" s="1" t="s">
+        <v>123</v>
+      </c>
+      <c r="E2" s="1" t="s">
         <v>124</v>
       </c>
-      <c r="C2" s="3" t="s">
-        <v>125</v>
-      </c>
-      <c r="D2" s="3" t="s">
-        <v>126</v>
-      </c>
-      <c r="E2" s="3" t="s">
-        <v>127</v>
-      </c>
-      <c r="F2" s="3" t="s">
+      <c r="F2" s="1" t="s">
         <v>13</v>
       </c>
     </row>
     <row r="3" spans="1:8" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A3" s="4" t="s">
-        <v>143</v>
-      </c>
-      <c r="B3" s="4">
+      <c r="A3" s="2" t="s">
+        <v>140</v>
+      </c>
+      <c r="B3" s="2">
         <v>89.6</v>
       </c>
-      <c r="C3" s="4">
+      <c r="C3" s="2">
         <v>80.8</v>
       </c>
-      <c r="D3" s="7">
+      <c r="D3" s="5">
         <f>-C3+B3</f>
         <v>8.7999999999999972</v>
       </c>
-      <c r="E3" s="4" t="s">
-        <v>129</v>
-      </c>
-      <c r="F3" s="4"/>
+      <c r="E3" s="2" t="s">
+        <v>126</v>
+      </c>
+      <c r="F3" s="2"/>
     </row>
     <row r="4" spans="1:8" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A4" s="6" t="s">
-        <v>144</v>
-      </c>
-      <c r="B4" s="6">
+      <c r="A4" s="4" t="s">
+        <v>141</v>
+      </c>
+      <c r="B4" s="4">
         <v>88.8</v>
       </c>
-      <c r="C4" s="6">
+      <c r="C4" s="4">
         <v>80.8</v>
       </c>
-      <c r="D4" s="8">
+      <c r="D4" s="6">
         <f>-C4+B4</f>
         <v>8</v>
       </c>
-      <c r="E4" s="6" t="s">
-        <v>135</v>
-      </c>
-      <c r="F4" s="6"/>
+      <c r="E4" s="4" t="s">
+        <v>132</v>
+      </c>
+      <c r="F4" s="4"/>
     </row>
     <row r="5" spans="1:8" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A5" s="4" t="s">
-        <v>145</v>
-      </c>
-      <c r="B5" s="4">
+      <c r="A5" s="2" t="s">
+        <v>142</v>
+      </c>
+      <c r="B5" s="2">
         <v>87</v>
       </c>
-      <c r="C5" s="4">
+      <c r="C5" s="2">
         <v>76.8</v>
       </c>
-      <c r="D5" s="7">
+      <c r="D5" s="5">
         <f>-C5+B5</f>
         <v>10.200000000000003</v>
       </c>
-      <c r="E5" s="4" t="s">
-        <v>129</v>
-      </c>
-      <c r="F5" s="4" t="s">
-        <v>146</v>
+      <c r="E5" s="2" t="s">
+        <v>126</v>
+      </c>
+      <c r="F5" s="2" t="s">
+        <v>143</v>
       </c>
     </row>
     <row r="6" spans="1:8" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A6" s="6" t="s">
-        <v>147</v>
-      </c>
-      <c r="B6" s="6">
+      <c r="A6" s="4" t="s">
+        <v>144</v>
+      </c>
+      <c r="B6" s="4">
         <v>95</v>
       </c>
-      <c r="C6" s="6">
+      <c r="C6" s="4">
         <v>83.6</v>
       </c>
-      <c r="D6" s="8">
+      <c r="D6" s="6">
         <f>-C6+B6</f>
         <v>11.400000000000006</v>
       </c>
-      <c r="E6" s="6" t="s">
-        <v>129</v>
-      </c>
-      <c r="F6" s="6"/>
+      <c r="E6" s="4" t="s">
+        <v>126</v>
+      </c>
+      <c r="F6" s="4"/>
     </row>
     <row r="7" spans="1:8" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A7" s="4" t="s">
-        <v>148</v>
-      </c>
-      <c r="B7" s="4">
+      <c r="A7" s="2" t="s">
+        <v>145</v>
+      </c>
+      <c r="B7" s="2">
         <v>95.1</v>
       </c>
-      <c r="C7" s="4">
+      <c r="C7" s="2">
         <v>90</v>
       </c>
-      <c r="D7" s="7">
+      <c r="D7" s="5">
         <f>-C7+B7</f>
         <v>5.0999999999999943</v>
       </c>
-      <c r="E7" s="4" t="s">
-        <v>135</v>
-      </c>
-      <c r="F7" s="4" t="s">
-        <v>149</v>
+      <c r="E7" s="2" t="s">
+        <v>132</v>
+      </c>
+      <c r="F7" s="2" t="s">
+        <v>146</v>
       </c>
     </row>
     <row r="8" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A8" s="9" t="s">
-        <v>150</v>
-      </c>
-      <c r="B8" s="9" t="s">
-        <v>151</v>
-      </c>
-      <c r="C8" s="9"/>
-      <c r="D8" s="9"/>
-      <c r="E8" s="9"/>
-      <c r="F8" s="9"/>
+      <c r="A8" s="7" t="s">
+        <v>147</v>
+      </c>
+      <c r="B8" s="7" t="s">
+        <v>148</v>
+      </c>
+      <c r="C8" s="7"/>
+      <c r="D8" s="7"/>
+      <c r="E8" s="7"/>
+      <c r="F8" s="7"/>
     </row>
   </sheetData>
   <mergeCells count="1">

--- a/Dashboard_Data.xlsx
+++ b/Dashboard_Data.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://alfanargroup-my.sharepoint.com/personal/ahmed_abdelzaher_alfanar_com/Documents/SDCC Dashboard/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="1" documentId="14_{682A7E4B-1055-4B0F-805D-134F59E89DE5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{47C63B07-ADE5-433F-96FF-9EA0FCFC6C7D}"/>
+  <xr:revisionPtr revIDLastSave="165" documentId="14_{682A7E4B-1055-4B0F-805D-134F59E89DE5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{AC7FB250-0A9F-4C3F-8B20-C0F32970438A}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" tabRatio="500" activeTab="4" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" tabRatio="500" firstSheet="2" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Header" sheetId="1" r:id="rId1"/>
@@ -27,7 +27,7 @@
     <sheet name="Equipment_Status" sheetId="12" r:id="rId12"/>
     <sheet name="Footer" sheetId="13" r:id="rId13"/>
   </sheets>
-  <calcPr calcId="191029" iterateDelta="1E-4"/>
+  <calcPr calcId="191029"/>
   <extLst>
     <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
       <xcalcf:calcFeatures>
@@ -48,7 +48,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="377" uniqueCount="242">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="366" uniqueCount="237">
   <si>
     <t>HEADER — Dashboard Title &amp; PM</t>
   </si>
@@ -62,9 +62,6 @@
     <t>Dashboard Title</t>
   </si>
   <si>
-    <t>WESTERN REGION SDCC PROJECT DASHBOARD | PE-286</t>
-  </si>
-  <si>
     <t>Project Code</t>
   </si>
   <si>
@@ -74,9 +71,6 @@
     <t>Region</t>
   </si>
   <si>
-    <t>Western Region</t>
-  </si>
-  <si>
     <t>Project Manager</t>
   </si>
   <si>
@@ -134,9 +128,6 @@
     <t>Expected TCC</t>
   </si>
   <si>
-    <t>15-Oct-26</t>
-  </si>
-  <si>
     <t>Highlighted red in dashboard — delayed</t>
   </si>
   <si>
@@ -173,9 +164,6 @@
     <t>Rem. Contingency</t>
   </si>
   <si>
-    <t>45%</t>
-  </si>
-  <si>
     <t>Badge shown in amber/red in dashboard</t>
   </si>
   <si>
@@ -206,18 +194,12 @@
     <t>Contingency Used</t>
   </si>
   <si>
-    <t>~55%</t>
-  </si>
-  <si>
     <t>Amber in dashboard</t>
   </si>
   <si>
     <t>EOT Status</t>
   </si>
   <si>
-    <t>Not Submitted</t>
-  </si>
-  <si>
     <t>Red in dashboard</t>
   </si>
   <si>
@@ -233,18 +215,12 @@
     <t>Invoiceable Amount</t>
   </si>
   <si>
-    <t>53%</t>
-  </si>
-  <si>
     <t>Green</t>
   </si>
   <si>
     <t>Submitted Invoices</t>
   </si>
   <si>
-    <t>39%</t>
-  </si>
-  <si>
     <t>Amber</t>
   </si>
   <si>
@@ -260,15 +236,6 @@
     <t>Col. Amount Inc Adv</t>
   </si>
   <si>
-    <t>18%</t>
-  </si>
-  <si>
-    <t>Billing vs POC</t>
-  </si>
-  <si>
-    <t>39% / 40.9%</t>
-  </si>
-  <si>
     <t>Text field — shown as-is</t>
   </si>
   <si>
@@ -299,9 +266,6 @@
     <t>Cash In</t>
   </si>
   <si>
-    <t>52.6%</t>
-  </si>
-  <si>
     <t>Green bar; relative to Cash Out (max)</t>
   </si>
   <si>
@@ -338,9 +302,6 @@
     <t>Direct Share %</t>
   </si>
   <si>
-    <t>80%</t>
-  </si>
-  <si>
     <t>Shown as green text</t>
   </si>
   <si>
@@ -494,9 +455,6 @@
     <t>Footer Note (italic text shown below chart)</t>
   </si>
   <si>
-    <t>Jizan trails the plan most; Makkah leads on actual completion.</t>
-  </si>
-  <si>
     <t>PROJECTS TIMELINE — Monthly Milestones</t>
   </si>
   <si>
@@ -590,9 +548,6 @@
     <t>Nov-25</t>
   </si>
   <si>
-    <t>Stringing Start</t>
-  </si>
-  <si>
     <t>Dec-25</t>
   </si>
   <si>
@@ -644,36 +599,6 @@
     <t>Priority</t>
   </si>
   <si>
-    <t>Shortage of tower materials by SEC (02 No's)</t>
-  </si>
-  <si>
-    <t>SEC</t>
-  </si>
-  <si>
-    <t>Escalated to SEC-PDC; shortage list shared to push supplier. Continuous follow-up to expedite delivery.</t>
-  </si>
-  <si>
-    <t>HIGH</t>
-  </si>
-  <si>
-    <t>Delay in delivery of special towers by Alfanar</t>
-  </si>
-  <si>
-    <t>Energiya</t>
-  </si>
-  <si>
-    <t>12 of 14 towers received; remaining 2 (UDE-II) in progress. Continuous follow-up with supplier.</t>
-  </si>
-  <si>
-    <t>Delay in UGC works near TADCO S/S</t>
-  </si>
-  <si>
-    <t>SEC advised to start excavation from 26-Apr-26. Continuous follow-up to avoid further delay.</t>
-  </si>
-  <si>
-    <t>MEDIUM</t>
-  </si>
-  <si>
     <t>EQUIPMENT STATUS</t>
   </si>
   <si>
@@ -695,60 +620,12 @@
     <t>Status</t>
   </si>
   <si>
-    <t>Insulator</t>
-  </si>
-  <si>
-    <t>Zape</t>
-  </si>
-  <si>
     <t>Issued</t>
   </si>
   <si>
     <t>OK</t>
   </si>
   <si>
-    <t>Cable termination</t>
-  </si>
-  <si>
-    <t>PFISTER</t>
-  </si>
-  <si>
-    <t>Lattice Steel Gantry</t>
-  </si>
-  <si>
-    <t>Line hardware</t>
-  </si>
-  <si>
-    <t>Dalekovod</t>
-  </si>
-  <si>
-    <t>Dampers</t>
-  </si>
-  <si>
-    <t>PTE</t>
-  </si>
-  <si>
-    <t>Power Cables</t>
-  </si>
-  <si>
-    <t>Bahara</t>
-  </si>
-  <si>
-    <t>Surge Arrester</t>
-  </si>
-  <si>
-    <t>Tridelta</t>
-  </si>
-  <si>
-    <t>Lattice Steel Tower</t>
-  </si>
-  <si>
-    <t>98%</t>
-  </si>
-  <si>
-    <t>DELAYED</t>
-  </si>
-  <si>
     <t>FOOTER — Classification &amp; Branding</t>
   </si>
   <si>
@@ -761,26 +638,140 @@
     <t>Prepared Date</t>
   </si>
   <si>
-    <t>18 Apr 2026</t>
-  </si>
-  <si>
     <t>Department</t>
   </si>
   <si>
-    <t>alfanar OHTL Projects</t>
-  </si>
-  <si>
     <t>Brand Name</t>
   </si>
   <si>
     <t>alfanar</t>
+  </si>
+  <si>
+    <t>WESTERN &amp; SOUTHERN REGION SDCC PROJECT DASHBOARD | PE-286</t>
+  </si>
+  <si>
+    <t>Western &amp; SOUTHERN Region</t>
+  </si>
+  <si>
+    <t>Submitted</t>
+  </si>
+  <si>
+    <t>Billing vs Actual POC</t>
+  </si>
+  <si>
+    <t>Planned POC</t>
+  </si>
+  <si>
+    <t>MAD&amp; ABH Structur Completed</t>
+  </si>
+  <si>
+    <t>Jizan Structure Completed</t>
+  </si>
+  <si>
+    <t>CET Equip. Delivery</t>
+  </si>
+  <si>
+    <t>High</t>
+  </si>
+  <si>
+    <t>Supplier (Digital Era)</t>
+  </si>
+  <si>
+    <t>Procurement</t>
+  </si>
+  <si>
+    <t>SE</t>
+  </si>
+  <si>
+    <t>Engineering / Procurement</t>
+  </si>
+  <si>
+    <t>Delay Delivery of Low Current 3rd Fix Materials</t>
+  </si>
+  <si>
+    <t>PM to arrange a meeting with supplier top management to enhance the current delivery forecast dates to meet the TCC contractual date.</t>
+  </si>
+  <si>
+    <t>Delay Approval of Jockey Pumps (Fire Pumps Package)</t>
+  </si>
+  <si>
+    <t>SE to expedite the approval of Jockey Pumps to start manufacturing of materials and fulfill the supplied flow USA.</t>
+  </si>
+  <si>
+    <t>Delay Approval of LAN/WAN (M6 Routers) Which Fulfill Contract Requirements</t>
+  </si>
+  <si>
+    <t>Delay Delivery of DWDM (PO Issued to AES) – Waiting for Final Confirmation of Recent Traffic Plan</t>
+  </si>
+  <si>
+    <t>SE to expedite providing the confirmed recent traffic plan to start manufacturing materials of DWDM.</t>
+  </si>
+  <si>
+    <t>Approved design is to use (M14 routers), delivery duration 20–24 weeks.SE to approve Alfanar proposal to deliver (M6 routers) which have a delivery duration of 6–8 weeks.</t>
+  </si>
+  <si>
+    <t>48 VDC System</t>
+  </si>
+  <si>
+    <t>ADMS/DERMS Servers</t>
+  </si>
+  <si>
+    <t>CET</t>
+  </si>
+  <si>
+    <t>CRAC / PACU Units</t>
+  </si>
+  <si>
+    <t>Zamil</t>
+  </si>
+  <si>
+    <t>FM-200 Cylinders</t>
+  </si>
+  <si>
+    <t>DDC Panels</t>
+  </si>
+  <si>
+    <t>Marine</t>
+  </si>
+  <si>
+    <t>AC/DC Panels</t>
+  </si>
+  <si>
+    <t>AES</t>
+  </si>
+  <si>
+    <t>Delayed</t>
+  </si>
+  <si>
+    <t>Fire Pumps</t>
+  </si>
+  <si>
+    <t>80%*</t>
+  </si>
+  <si>
+    <t>Security System</t>
+  </si>
+  <si>
+    <t>ITC</t>
+  </si>
+  <si>
+    <t>N/A</t>
+  </si>
+  <si>
+    <t>Control Center</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="6" x14ac:knownFonts="1">
+  <numFmts count="4">
+    <numFmt numFmtId="43" formatCode="_(* #,##0.00_);_(* \(#,##0.00\);_(* &quot;-&quot;??_);_(@_)"/>
+    <numFmt numFmtId="165" formatCode="[$-409]d\-mmm\-yy;@"/>
+    <numFmt numFmtId="166" formatCode="0.0%"/>
+    <numFmt numFmtId="167" formatCode="0.0"/>
+  </numFmts>
+  <fonts count="7" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -793,36 +784,43 @@
       <sz val="12"/>
       <color rgb="FFFFFFFF"/>
       <name val="Arial"/>
-      <charset val="1"/>
+      <family val="2"/>
     </font>
     <font>
       <b/>
       <sz val="10"/>
       <color rgb="FFFFFFFF"/>
       <name val="Arial"/>
-      <charset val="1"/>
+      <family val="2"/>
     </font>
     <font>
       <sz val="10"/>
       <color rgb="FF1B2733"/>
       <name val="Arial"/>
-      <charset val="1"/>
+      <family val="2"/>
     </font>
     <font>
       <b/>
       <sz val="10"/>
       <color rgb="FFC0181D"/>
       <name val="Arial"/>
-      <charset val="1"/>
+      <family val="2"/>
     </font>
     <font>
       <sz val="9"/>
       <color rgb="FF6C7C8C"/>
       <name val="Arial"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="Calibri"/>
+      <family val="2"/>
       <charset val="1"/>
     </font>
   </fonts>
-  <fills count="13">
+  <fills count="12">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -885,12 +883,6 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFC85F10"/>
-        <bgColor rgb="FFE87722"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
         <fgColor rgb="FF1F8F3D"/>
         <bgColor rgb="FF008000"/>
       </patternFill>
@@ -920,10 +912,12 @@
       <diagonal/>
     </border>
   </borders>
-  <cellStyleXfs count="1">
+  <cellStyleXfs count="3">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
+    <xf numFmtId="43" fontId="6" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="9" fontId="6" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="18">
+  <cellXfs count="39">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -959,24 +953,83 @@
     <xf numFmtId="0" fontId="2" fillId="11" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="12" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="9" fontId="3" fillId="5" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="9" fontId="3" fillId="4" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="15" fontId="3" fillId="5" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="9" fontId="3" fillId="4" borderId="1" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="43" fontId="3" fillId="5" borderId="1" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="43" fontId="3" fillId="5" borderId="1" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="165" fontId="3" fillId="5" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="43" fontId="3" fillId="5" borderId="1" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="9" fontId="3" fillId="5" borderId="1" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="6" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="9" fontId="3" fillId="4" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="9" fontId="0" fillId="0" borderId="0" xfId="2" applyFont="1"/>
+    <xf numFmtId="9" fontId="3" fillId="5" borderId="1" xfId="2" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="9" fontId="3" fillId="5" borderId="1" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="10" fontId="3" fillId="5" borderId="1" xfId="2" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="166" fontId="3" fillId="4" borderId="1" xfId="2" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="167" fontId="3" fillId="4" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="167" fontId="3" fillId="6" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="17" fontId="3" fillId="8" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="17" fontId="3" fillId="4" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="15" fontId="3" fillId="9" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="15" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="9" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
   </cellXfs>
-  <cellStyles count="1">
+  <cellStyles count="3">
+    <cellStyle name="Comma" xfId="1" builtinId="3"/>
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
+    <cellStyle name="Percent" xfId="2" builtinId="5"/>
   </cellStyles>
   <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
@@ -1249,16 +1302,16 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:8" ht="21.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A1" s="16" t="s">
+      <c r="A1" s="13" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="16"/>
-      <c r="C1" s="16"/>
-      <c r="D1" s="16"/>
-      <c r="E1" s="16"/>
-      <c r="F1" s="16"/>
-      <c r="G1" s="16"/>
-      <c r="H1" s="16"/>
+      <c r="B1" s="13"/>
+      <c r="C1" s="13"/>
+      <c r="D1" s="13"/>
+      <c r="E1" s="13"/>
+      <c r="F1" s="13"/>
+      <c r="G1" s="13"/>
+      <c r="H1" s="13"/>
     </row>
     <row r="2" spans="1:8" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A2" s="1" t="s">
@@ -1268,36 +1321,36 @@
         <v>2</v>
       </c>
     </row>
-    <row r="3" spans="1:8" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:8" ht="25.5" x14ac:dyDescent="0.25">
       <c r="A3" s="2" t="s">
         <v>3</v>
       </c>
       <c r="B3" s="3" t="s">
+        <v>199</v>
+      </c>
+    </row>
+    <row r="4" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A4" s="4" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="4" spans="1:8" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A4" s="4" t="s">
+      <c r="B4" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="B4" s="3" t="s">
+    </row>
+    <row r="5" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A5" s="2" t="s">
         <v>6</v>
       </c>
-    </row>
-    <row r="5" spans="1:8" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A5" s="2" t="s">
+      <c r="B5" s="3" t="s">
+        <v>200</v>
+      </c>
+    </row>
+    <row r="6" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A6" s="4" t="s">
         <v>7</v>
       </c>
-      <c r="B5" s="3" t="s">
+      <c r="B6" s="3" t="s">
         <v>8</v>
-      </c>
-    </row>
-    <row r="6" spans="1:8" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A6" s="4" t="s">
-        <v>9</v>
-      </c>
-      <c r="B6" s="3" t="s">
-        <v>10</v>
       </c>
     </row>
   </sheetData>
@@ -1317,7 +1370,7 @@
   <sheetPr>
     <tabColor rgb="FFE87722"/>
   </sheetPr>
-  <dimension ref="A1:H22"/>
+  <dimension ref="A1:H30"/>
   <sheetFormatPr defaultColWidth="8.7109375" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="12" customWidth="1"/>
@@ -1331,76 +1384,76 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:8" ht="21.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A1" s="16" t="s">
-        <v>149</v>
-      </c>
-      <c r="B1" s="16"/>
-      <c r="C1" s="16"/>
-      <c r="D1" s="16"/>
-      <c r="E1" s="16"/>
-      <c r="F1" s="16"/>
-      <c r="G1" s="16"/>
-      <c r="H1" s="16"/>
+      <c r="A1" s="13" t="s">
+        <v>135</v>
+      </c>
+      <c r="B1" s="13"/>
+      <c r="C1" s="13"/>
+      <c r="D1" s="13"/>
+      <c r="E1" s="13"/>
+      <c r="F1" s="13"/>
+      <c r="G1" s="13"/>
+      <c r="H1" s="13"/>
     </row>
     <row r="2" spans="1:8" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A2" s="1" t="s">
-        <v>150</v>
+        <v>136</v>
       </c>
       <c r="B2" s="1" t="s">
-        <v>151</v>
+        <v>137</v>
       </c>
       <c r="C2" s="1" t="s">
-        <v>152</v>
+        <v>138</v>
       </c>
       <c r="D2" s="1" t="s">
-        <v>153</v>
+        <v>139</v>
       </c>
       <c r="E2" s="1" t="s">
-        <v>154</v>
+        <v>140</v>
       </c>
       <c r="F2" s="1" t="s">
-        <v>155</v>
+        <v>141</v>
       </c>
       <c r="G2" s="1" t="s">
-        <v>156</v>
+        <v>142</v>
       </c>
       <c r="H2" s="1" t="s">
-        <v>13</v>
+        <v>11</v>
       </c>
     </row>
     <row r="3" spans="1:8" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A3" s="8" t="s">
-        <v>157</v>
+        <v>143</v>
       </c>
       <c r="B3" s="2" t="s">
-        <v>158</v>
+        <v>144</v>
       </c>
       <c r="C3" s="2" t="s">
-        <v>159</v>
+        <v>145</v>
       </c>
       <c r="D3" s="2" t="s">
-        <v>160</v>
+        <v>146</v>
       </c>
       <c r="E3" s="2" t="s">
-        <v>161</v>
+        <v>147</v>
       </c>
       <c r="F3" s="2"/>
       <c r="G3" s="2"/>
       <c r="H3" s="2" t="s">
-        <v>162</v>
+        <v>148</v>
       </c>
     </row>
     <row r="4" spans="1:8" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A4" s="4" t="s">
-        <v>163</v>
+        <v>149</v>
       </c>
       <c r="B4" s="4" t="s">
-        <v>161</v>
+        <v>147</v>
       </c>
       <c r="C4" s="4"/>
       <c r="D4" s="4"/>
       <c r="E4" s="4" t="s">
-        <v>161</v>
+        <v>147</v>
       </c>
       <c r="F4" s="4"/>
       <c r="G4" s="4"/>
@@ -1408,15 +1461,15 @@
     </row>
     <row r="5" spans="1:8" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A5" s="2" t="s">
-        <v>164</v>
+        <v>150</v>
       </c>
       <c r="B5" s="2" t="s">
-        <v>161</v>
+        <v>147</v>
       </c>
       <c r="C5" s="2"/>
       <c r="D5" s="2"/>
       <c r="E5" s="2" t="s">
-        <v>161</v>
+        <v>147</v>
       </c>
       <c r="F5" s="2"/>
       <c r="G5" s="2"/>
@@ -1424,15 +1477,15 @@
     </row>
     <row r="6" spans="1:8" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A6" s="4" t="s">
-        <v>165</v>
+        <v>151</v>
       </c>
       <c r="B6" s="4" t="s">
-        <v>161</v>
+        <v>147</v>
       </c>
       <c r="C6" s="4"/>
       <c r="D6" s="4"/>
       <c r="E6" s="4" t="s">
-        <v>161</v>
+        <v>147</v>
       </c>
       <c r="F6" s="4"/>
       <c r="G6" s="4"/>
@@ -1440,19 +1493,19 @@
     </row>
     <row r="7" spans="1:8" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A7" s="8" t="s">
-        <v>166</v>
+        <v>152</v>
       </c>
       <c r="B7" s="2" t="s">
-        <v>158</v>
+        <v>144</v>
       </c>
       <c r="C7" s="2" t="s">
-        <v>167</v>
+        <v>153</v>
       </c>
       <c r="D7" s="2" t="s">
-        <v>160</v>
+        <v>146</v>
       </c>
       <c r="E7" s="2" t="s">
-        <v>161</v>
+        <v>147</v>
       </c>
       <c r="F7" s="2"/>
       <c r="G7" s="2"/>
@@ -1460,37 +1513,37 @@
     </row>
     <row r="8" spans="1:8" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A8" s="8" t="s">
-        <v>168</v>
+        <v>154</v>
       </c>
       <c r="B8" s="4" t="s">
-        <v>158</v>
+        <v>144</v>
       </c>
       <c r="C8" s="4" t="s">
-        <v>169</v>
+        <v>155</v>
       </c>
       <c r="D8" s="4" t="s">
-        <v>170</v>
+        <v>156</v>
       </c>
       <c r="E8" s="4" t="s">
-        <v>161</v>
+        <v>147</v>
       </c>
       <c r="F8" s="4"/>
       <c r="G8" s="4"/>
       <c r="H8" s="4" t="s">
-        <v>171</v>
+        <v>157</v>
       </c>
     </row>
     <row r="9" spans="1:8" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A9" s="2" t="s">
-        <v>172</v>
+        <v>158</v>
       </c>
       <c r="B9" s="2" t="s">
-        <v>161</v>
+        <v>147</v>
       </c>
       <c r="C9" s="2"/>
       <c r="D9" s="2"/>
       <c r="E9" s="2" t="s">
-        <v>161</v>
+        <v>147</v>
       </c>
       <c r="F9" s="2"/>
       <c r="G9" s="2"/>
@@ -1498,19 +1551,19 @@
     </row>
     <row r="10" spans="1:8" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A10" s="8" t="s">
-        <v>173</v>
+        <v>159</v>
       </c>
       <c r="B10" s="4" t="s">
-        <v>158</v>
+        <v>144</v>
       </c>
       <c r="C10" s="4" t="s">
-        <v>174</v>
+        <v>160</v>
       </c>
       <c r="D10" s="4" t="s">
-        <v>160</v>
+        <v>146</v>
       </c>
       <c r="E10" s="4" t="s">
-        <v>161</v>
+        <v>147</v>
       </c>
       <c r="F10" s="4"/>
       <c r="G10" s="4"/>
@@ -1518,15 +1571,15 @@
     </row>
     <row r="11" spans="1:8" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A11" s="2" t="s">
-        <v>175</v>
+        <v>161</v>
       </c>
       <c r="B11" s="2" t="s">
-        <v>161</v>
+        <v>147</v>
       </c>
       <c r="C11" s="2"/>
       <c r="D11" s="2"/>
       <c r="E11" s="2" t="s">
-        <v>161</v>
+        <v>147</v>
       </c>
       <c r="F11" s="2"/>
       <c r="G11" s="2"/>
@@ -1534,31 +1587,33 @@
     </row>
     <row r="12" spans="1:8" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A12" s="4" t="s">
-        <v>176</v>
+        <v>162</v>
       </c>
       <c r="B12" s="4" t="s">
-        <v>161</v>
+        <v>147</v>
       </c>
       <c r="C12" s="4"/>
       <c r="D12" s="4"/>
       <c r="E12" s="4" t="s">
-        <v>161</v>
+        <v>147</v>
       </c>
       <c r="F12" s="4"/>
       <c r="G12" s="4"/>
       <c r="H12" s="4"/>
     </row>
-    <row r="13" spans="1:8" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:8" ht="25.5" x14ac:dyDescent="0.25">
       <c r="A13" s="2" t="s">
-        <v>177</v>
+        <v>163</v>
       </c>
       <c r="B13" s="2" t="s">
-        <v>161</v>
-      </c>
-      <c r="C13" s="2"/>
+        <v>147</v>
+      </c>
+      <c r="C13" s="2" t="s">
+        <v>204</v>
+      </c>
       <c r="D13" s="2"/>
       <c r="E13" s="2" t="s">
-        <v>161</v>
+        <v>147</v>
       </c>
       <c r="F13" s="2"/>
       <c r="G13" s="2"/>
@@ -1566,15 +1621,17 @@
     </row>
     <row r="14" spans="1:8" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A14" s="4" t="s">
-        <v>178</v>
+        <v>164</v>
       </c>
       <c r="B14" s="4" t="s">
-        <v>161</v>
-      </c>
-      <c r="C14" s="4"/>
+        <v>147</v>
+      </c>
+      <c r="C14" s="4" t="s">
+        <v>205</v>
+      </c>
       <c r="D14" s="4"/>
       <c r="E14" s="4" t="s">
-        <v>161</v>
+        <v>147</v>
       </c>
       <c r="F14" s="4"/>
       <c r="G14" s="4"/>
@@ -1582,19 +1639,17 @@
     </row>
     <row r="15" spans="1:8" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A15" s="8" t="s">
-        <v>179</v>
+        <v>165</v>
       </c>
       <c r="B15" s="2" t="s">
-        <v>158</v>
-      </c>
-      <c r="C15" s="2" t="s">
-        <v>180</v>
-      </c>
+        <v>144</v>
+      </c>
+      <c r="C15" s="2"/>
       <c r="D15" s="2" t="s">
-        <v>160</v>
+        <v>146</v>
       </c>
       <c r="E15" s="2" t="s">
-        <v>161</v>
+        <v>147</v>
       </c>
       <c r="F15" s="2"/>
       <c r="G15" s="2"/>
@@ -1602,15 +1657,17 @@
     </row>
     <row r="16" spans="1:8" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A16" s="4" t="s">
-        <v>181</v>
+        <v>166</v>
       </c>
       <c r="B16" s="4" t="s">
-        <v>161</v>
-      </c>
-      <c r="C16" s="4"/>
+        <v>147</v>
+      </c>
+      <c r="C16" s="4" t="s">
+        <v>206</v>
+      </c>
       <c r="D16" s="4"/>
       <c r="E16" s="4" t="s">
-        <v>161</v>
+        <v>147</v>
       </c>
       <c r="F16" s="4"/>
       <c r="G16" s="4"/>
@@ -1618,15 +1675,15 @@
     </row>
     <row r="17" spans="1:8" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A17" s="2" t="s">
-        <v>182</v>
+        <v>167</v>
       </c>
       <c r="B17" s="2" t="s">
-        <v>161</v>
+        <v>147</v>
       </c>
       <c r="C17" s="2"/>
       <c r="D17" s="2"/>
       <c r="E17" s="2" t="s">
-        <v>161</v>
+        <v>147</v>
       </c>
       <c r="F17" s="2"/>
       <c r="G17" s="2"/>
@@ -1634,15 +1691,15 @@
     </row>
     <row r="18" spans="1:8" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A18" s="4" t="s">
-        <v>183</v>
+        <v>168</v>
       </c>
       <c r="B18" s="4" t="s">
-        <v>161</v>
+        <v>147</v>
       </c>
       <c r="C18" s="4"/>
       <c r="D18" s="4"/>
       <c r="E18" s="4" t="s">
-        <v>161</v>
+        <v>147</v>
       </c>
       <c r="F18" s="4"/>
       <c r="G18" s="4"/>
@@ -1650,78 +1707,191 @@
     </row>
     <row r="19" spans="1:8" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A19" s="2" t="s">
-        <v>184</v>
+        <v>169</v>
       </c>
       <c r="B19" s="2" t="s">
-        <v>161</v>
+        <v>147</v>
       </c>
       <c r="C19" s="2"/>
       <c r="D19" s="2"/>
       <c r="E19" s="2" t="s">
-        <v>161</v>
+        <v>147</v>
       </c>
       <c r="F19" s="2"/>
       <c r="G19" s="2"/>
       <c r="H19" s="2"/>
     </row>
     <row r="20" spans="1:8" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A20" s="9" t="s">
-        <v>185</v>
-      </c>
-      <c r="B20" s="9" t="s">
-        <v>161</v>
-      </c>
-      <c r="C20" s="9"/>
-      <c r="D20" s="9"/>
-      <c r="E20" s="9" t="s">
-        <v>158</v>
-      </c>
-      <c r="F20" s="9" t="s">
-        <v>24</v>
-      </c>
-      <c r="G20" s="9" t="s">
-        <v>25</v>
-      </c>
-      <c r="H20" s="9" t="s">
-        <v>186</v>
-      </c>
+      <c r="A20" s="2" t="s">
+        <v>170</v>
+      </c>
+      <c r="B20" s="2" t="s">
+        <v>147</v>
+      </c>
+      <c r="C20" s="2"/>
+      <c r="D20" s="2"/>
+      <c r="E20" s="2" t="s">
+        <v>147</v>
+      </c>
+      <c r="F20" s="2"/>
+      <c r="G20" s="2"/>
+      <c r="H20" s="2"/>
     </row>
     <row r="21" spans="1:8" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A21" s="2" t="s">
-        <v>187</v>
+        <v>172</v>
       </c>
       <c r="B21" s="2" t="s">
-        <v>161</v>
+        <v>147</v>
       </c>
       <c r="C21" s="2"/>
       <c r="D21" s="2"/>
       <c r="E21" s="2" t="s">
-        <v>161</v>
+        <v>147</v>
       </c>
       <c r="F21" s="2"/>
       <c r="G21" s="2"/>
       <c r="H21" s="2"/>
     </row>
     <row r="22" spans="1:8" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A22" s="10" t="s">
-        <v>188</v>
-      </c>
-      <c r="B22" s="10" t="s">
-        <v>161</v>
-      </c>
-      <c r="C22" s="10"/>
-      <c r="D22" s="10"/>
-      <c r="E22" s="10" t="s">
-        <v>158</v>
-      </c>
-      <c r="F22" s="10" t="s">
-        <v>189</v>
-      </c>
-      <c r="G22" s="10" t="s">
-        <v>28</v>
-      </c>
-      <c r="H22" s="10" t="s">
-        <v>190</v>
+      <c r="A22" s="2" t="s">
+        <v>173</v>
+      </c>
+      <c r="B22" s="2" t="s">
+        <v>147</v>
+      </c>
+      <c r="C22" s="2"/>
+      <c r="D22" s="2"/>
+      <c r="E22" s="2" t="s">
+        <v>144</v>
+      </c>
+      <c r="F22" s="2"/>
+      <c r="G22" s="2"/>
+      <c r="H22" s="2"/>
+    </row>
+    <row r="23" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A23" s="34">
+        <v>46204</v>
+      </c>
+      <c r="B23" s="9" t="s">
+        <v>147</v>
+      </c>
+      <c r="C23" s="9"/>
+      <c r="D23" s="9"/>
+      <c r="E23" s="9" t="s">
+        <v>144</v>
+      </c>
+      <c r="F23" s="9" t="s">
+        <v>22</v>
+      </c>
+      <c r="G23" s="9" t="s">
+        <v>23</v>
+      </c>
+      <c r="H23" s="9" t="s">
+        <v>171</v>
+      </c>
+    </row>
+    <row r="24" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A24" s="35">
+        <v>46235</v>
+      </c>
+      <c r="B24" s="2" t="s">
+        <v>147</v>
+      </c>
+      <c r="C24" s="2"/>
+      <c r="D24" s="2"/>
+      <c r="E24" s="2" t="s">
+        <v>147</v>
+      </c>
+      <c r="F24" s="2"/>
+      <c r="G24" s="2"/>
+      <c r="H24" s="2"/>
+    </row>
+    <row r="25" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A25" s="35">
+        <v>46266</v>
+      </c>
+      <c r="B25" s="2" t="s">
+        <v>147</v>
+      </c>
+      <c r="C25" s="2"/>
+      <c r="D25" s="2"/>
+      <c r="E25" s="2" t="s">
+        <v>147</v>
+      </c>
+      <c r="F25" s="2"/>
+      <c r="G25" s="2"/>
+      <c r="H25" s="2"/>
+    </row>
+    <row r="26" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A26" s="35">
+        <v>46296</v>
+      </c>
+      <c r="B26" s="2" t="s">
+        <v>147</v>
+      </c>
+      <c r="C26" s="2"/>
+      <c r="D26" s="2"/>
+      <c r="E26" s="2" t="s">
+        <v>147</v>
+      </c>
+      <c r="F26" s="2"/>
+      <c r="G26" s="2"/>
+      <c r="H26" s="2"/>
+    </row>
+    <row r="27" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A27" s="35">
+        <v>46327</v>
+      </c>
+      <c r="B27" s="2" t="s">
+        <v>147</v>
+      </c>
+      <c r="E27" s="2" t="s">
+        <v>147</v>
+      </c>
+    </row>
+    <row r="28" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A28" s="35">
+        <v>46357</v>
+      </c>
+      <c r="B28" s="2" t="s">
+        <v>147</v>
+      </c>
+      <c r="E28" s="2" t="s">
+        <v>147</v>
+      </c>
+    </row>
+    <row r="29" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A29" s="35">
+        <v>46388</v>
+      </c>
+      <c r="B29" s="2" t="s">
+        <v>147</v>
+      </c>
+      <c r="E29" s="2" t="s">
+        <v>147</v>
+      </c>
+    </row>
+    <row r="30" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A30" s="35">
+        <v>46419</v>
+      </c>
+      <c r="B30" s="10" t="s">
+        <v>147</v>
+      </c>
+      <c r="C30" s="10"/>
+      <c r="D30" s="10"/>
+      <c r="E30" s="10" t="s">
+        <v>144</v>
+      </c>
+      <c r="F30" s="10" t="s">
+        <v>174</v>
+      </c>
+      <c r="G30" s="36">
+        <v>46435</v>
+      </c>
+      <c r="H30" s="10" t="s">
+        <v>175</v>
       </c>
     </row>
   </sheetData>
@@ -1741,7 +1911,7 @@
   <sheetPr>
     <tabColor rgb="FFE87722"/>
   </sheetPr>
-  <dimension ref="A1:H5"/>
+  <dimension ref="A1:H6"/>
   <sheetFormatPr defaultColWidth="8.7109375" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="4" customWidth="1"/>
@@ -1753,94 +1923,114 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:8" ht="21.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A1" s="16" t="s">
-        <v>191</v>
-      </c>
-      <c r="B1" s="16"/>
-      <c r="C1" s="16"/>
-      <c r="D1" s="16"/>
-      <c r="E1" s="16"/>
-      <c r="F1" s="16"/>
-      <c r="G1" s="16"/>
-      <c r="H1" s="16"/>
+      <c r="A1" s="13" t="s">
+        <v>176</v>
+      </c>
+      <c r="B1" s="13"/>
+      <c r="C1" s="13"/>
+      <c r="D1" s="13"/>
+      <c r="E1" s="13"/>
+      <c r="F1" s="13"/>
+      <c r="G1" s="13"/>
+      <c r="H1" s="13"/>
     </row>
     <row r="2" spans="1:8" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A2" s="1" t="s">
-        <v>192</v>
+        <v>177</v>
       </c>
       <c r="B2" s="1" t="s">
-        <v>193</v>
+        <v>178</v>
       </c>
       <c r="C2" s="1" t="s">
-        <v>194</v>
+        <v>179</v>
       </c>
       <c r="D2" s="1" t="s">
-        <v>195</v>
+        <v>180</v>
       </c>
       <c r="E2" s="1" t="s">
-        <v>196</v>
+        <v>181</v>
       </c>
       <c r="F2" s="1" t="s">
-        <v>197</v>
-      </c>
-    </row>
-    <row r="3" spans="1:8" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+        <v>182</v>
+      </c>
+    </row>
+    <row r="3" spans="1:8" ht="38.25" x14ac:dyDescent="0.25">
       <c r="A3" s="2">
         <v>1</v>
       </c>
       <c r="B3" s="2" t="s">
-        <v>198</v>
+        <v>212</v>
       </c>
       <c r="C3" s="2" t="s">
-        <v>135</v>
+        <v>209</v>
       </c>
       <c r="D3" s="2" t="s">
-        <v>199</v>
+        <v>208</v>
       </c>
       <c r="E3" s="2" t="s">
-        <v>200</v>
+        <v>213</v>
       </c>
       <c r="F3" s="11" t="s">
-        <v>201</v>
-      </c>
-    </row>
-    <row r="4" spans="1:8" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+        <v>207</v>
+      </c>
+    </row>
+    <row r="4" spans="1:8" ht="25.5" x14ac:dyDescent="0.25">
       <c r="A4" s="4">
         <v>2</v>
       </c>
       <c r="B4" s="4" t="s">
-        <v>202</v>
+        <v>214</v>
       </c>
       <c r="C4" s="4" t="s">
-        <v>135</v>
+        <v>211</v>
       </c>
       <c r="D4" s="4" t="s">
-        <v>203</v>
+        <v>210</v>
       </c>
       <c r="E4" s="4" t="s">
-        <v>204</v>
+        <v>215</v>
       </c>
       <c r="F4" s="11" t="s">
-        <v>201</v>
-      </c>
-    </row>
-    <row r="5" spans="1:8" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+        <v>207</v>
+      </c>
+    </row>
+    <row r="5" spans="1:8" ht="38.25" x14ac:dyDescent="0.25">
       <c r="A5" s="2">
         <v>3</v>
       </c>
       <c r="B5" s="2" t="s">
-        <v>205</v>
+        <v>216</v>
       </c>
       <c r="C5" s="2" t="s">
-        <v>134</v>
+        <v>211</v>
       </c>
       <c r="D5" s="2" t="s">
-        <v>199</v>
+        <v>210</v>
       </c>
       <c r="E5" s="2" t="s">
-        <v>206</v>
-      </c>
-      <c r="F5" s="12" t="s">
+        <v>219</v>
+      </c>
+      <c r="F5" s="11" t="s">
+        <v>207</v>
+      </c>
+    </row>
+    <row r="6" spans="1:8" ht="38.25" x14ac:dyDescent="0.25">
+      <c r="A6" s="2">
+        <v>4</v>
+      </c>
+      <c r="B6" s="2" t="s">
+        <v>217</v>
+      </c>
+      <c r="C6" s="2" t="s">
+        <v>211</v>
+      </c>
+      <c r="D6" s="2" t="s">
+        <v>210</v>
+      </c>
+      <c r="E6" s="2" t="s">
+        <v>218</v>
+      </c>
+      <c r="F6" s="11" t="s">
         <v>207</v>
       </c>
     </row>
@@ -1861,7 +2051,7 @@
   <sheetPr>
     <tabColor rgb="FFE87722"/>
   </sheetPr>
-  <dimension ref="A1:H10"/>
+  <dimension ref="A1:U25"/>
   <sheetFormatPr defaultColWidth="8.7109375" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="4" customWidth="1"/>
@@ -1871,251 +2061,310 @@
     <col min="8" max="8" width="12" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:8" ht="21.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A1" s="16" t="s">
-        <v>208</v>
-      </c>
-      <c r="B1" s="16"/>
-      <c r="C1" s="16"/>
-      <c r="D1" s="16"/>
-      <c r="E1" s="16"/>
-      <c r="F1" s="16"/>
-      <c r="G1" s="16"/>
-      <c r="H1" s="16"/>
-    </row>
-    <row r="2" spans="1:8" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:21" ht="21.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A1" s="13" t="s">
+        <v>183</v>
+      </c>
+      <c r="B1" s="13"/>
+      <c r="C1" s="13"/>
+      <c r="D1" s="13"/>
+      <c r="E1" s="13"/>
+      <c r="F1" s="13"/>
+      <c r="G1" s="13"/>
+      <c r="H1" s="13"/>
+    </row>
+    <row r="2" spans="1:21" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A2" s="1" t="s">
-        <v>192</v>
+        <v>177</v>
       </c>
       <c r="B2" s="1" t="s">
-        <v>131</v>
+        <v>118</v>
       </c>
       <c r="C2" s="1" t="s">
-        <v>209</v>
+        <v>184</v>
       </c>
       <c r="D2" s="1" t="s">
-        <v>210</v>
+        <v>185</v>
       </c>
       <c r="E2" s="1" t="s">
-        <v>211</v>
+        <v>186</v>
       </c>
       <c r="F2" s="1" t="s">
-        <v>212</v>
+        <v>187</v>
       </c>
       <c r="G2" s="1" t="s">
-        <v>213</v>
+        <v>188</v>
       </c>
       <c r="H2" s="1" t="s">
-        <v>214</v>
-      </c>
-    </row>
-    <row r="3" spans="1:8" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+        <v>189</v>
+      </c>
+    </row>
+    <row r="3" spans="1:21" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A3" s="2">
         <v>1</v>
       </c>
       <c r="B3" s="2" t="s">
-        <v>215</v>
+        <v>221</v>
       </c>
       <c r="C3" s="2" t="s">
-        <v>216</v>
+        <v>222</v>
       </c>
       <c r="D3" s="2" t="s">
-        <v>217</v>
-      </c>
-      <c r="E3" s="2" t="s">
-        <v>47</v>
-      </c>
-      <c r="F3" s="2" t="s">
-        <v>47</v>
-      </c>
-      <c r="G3" s="2" t="s">
-        <v>47</v>
-      </c>
-      <c r="H3" s="13" t="s">
-        <v>218</v>
-      </c>
-    </row>
-    <row r="4" spans="1:8" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+        <v>190</v>
+      </c>
+      <c r="E3" s="2">
+        <v>1</v>
+      </c>
+      <c r="F3" s="2">
+        <v>1</v>
+      </c>
+      <c r="G3" s="2">
+        <v>1</v>
+      </c>
+      <c r="H3" s="12" t="s">
+        <v>191</v>
+      </c>
+    </row>
+    <row r="4" spans="1:21" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A4" s="4">
         <v>2</v>
       </c>
       <c r="B4" s="4" t="s">
-        <v>219</v>
+        <v>223</v>
       </c>
       <c r="C4" s="4" t="s">
-        <v>220</v>
+        <v>224</v>
       </c>
       <c r="D4" s="4" t="s">
-        <v>217</v>
-      </c>
-      <c r="E4" s="4" t="s">
-        <v>47</v>
-      </c>
-      <c r="F4" s="4" t="s">
-        <v>47</v>
-      </c>
-      <c r="G4" s="4" t="s">
-        <v>47</v>
-      </c>
-      <c r="H4" s="13" t="s">
-        <v>218</v>
-      </c>
-    </row>
-    <row r="5" spans="1:8" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+        <v>190</v>
+      </c>
+      <c r="E4" s="4">
+        <v>1</v>
+      </c>
+      <c r="F4" s="4">
+        <v>1</v>
+      </c>
+      <c r="G4" s="4">
+        <v>1</v>
+      </c>
+      <c r="H4" s="12" t="s">
+        <v>191</v>
+      </c>
+    </row>
+    <row r="5" spans="1:21" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A5" s="2">
         <v>3</v>
       </c>
       <c r="B5" s="2" t="s">
-        <v>221</v>
+        <v>225</v>
       </c>
       <c r="C5" s="2" t="s">
-        <v>203</v>
+        <v>224</v>
       </c>
       <c r="D5" s="2" t="s">
-        <v>217</v>
-      </c>
-      <c r="E5" s="2" t="s">
-        <v>47</v>
-      </c>
-      <c r="F5" s="2" t="s">
-        <v>47</v>
-      </c>
-      <c r="G5" s="2" t="s">
-        <v>47</v>
-      </c>
-      <c r="H5" s="13" t="s">
-        <v>218</v>
-      </c>
-    </row>
-    <row r="6" spans="1:8" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+        <v>190</v>
+      </c>
+      <c r="E5" s="2">
+        <v>1</v>
+      </c>
+      <c r="F5" s="2">
+        <v>1</v>
+      </c>
+      <c r="G5" s="2">
+        <v>1</v>
+      </c>
+      <c r="H5" s="12" t="s">
+        <v>191</v>
+      </c>
+    </row>
+    <row r="6" spans="1:21" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A6" s="4">
         <v>4</v>
       </c>
       <c r="B6" s="4" t="s">
-        <v>222</v>
+        <v>226</v>
       </c>
       <c r="C6" s="4" t="s">
-        <v>223</v>
+        <v>227</v>
       </c>
       <c r="D6" s="4" t="s">
-        <v>217</v>
-      </c>
-      <c r="E6" s="4" t="s">
-        <v>47</v>
-      </c>
-      <c r="F6" s="4" t="s">
-        <v>47</v>
-      </c>
-      <c r="G6" s="4" t="s">
-        <v>47</v>
-      </c>
-      <c r="H6" s="13" t="s">
-        <v>218</v>
-      </c>
-    </row>
-    <row r="7" spans="1:8" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+        <v>190</v>
+      </c>
+      <c r="E6" s="4">
+        <v>1</v>
+      </c>
+      <c r="F6" s="4">
+        <v>1</v>
+      </c>
+      <c r="G6" s="4">
+        <v>1</v>
+      </c>
+      <c r="H6" s="12" t="s">
+        <v>191</v>
+      </c>
+    </row>
+    <row r="7" spans="1:21" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A7" s="2">
         <v>5</v>
       </c>
       <c r="B7" s="2" t="s">
-        <v>224</v>
+        <v>228</v>
       </c>
       <c r="C7" s="2" t="s">
-        <v>225</v>
+        <v>229</v>
       </c>
       <c r="D7" s="2" t="s">
-        <v>217</v>
-      </c>
-      <c r="E7" s="2" t="s">
-        <v>47</v>
-      </c>
-      <c r="F7" s="2" t="s">
-        <v>47</v>
-      </c>
-      <c r="G7" s="2" t="s">
-        <v>47</v>
-      </c>
-      <c r="H7" s="13" t="s">
-        <v>218</v>
-      </c>
-    </row>
-    <row r="8" spans="1:8" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+        <v>190</v>
+      </c>
+      <c r="E7" s="2">
+        <v>1</v>
+      </c>
+      <c r="F7" s="2">
+        <v>0.9</v>
+      </c>
+      <c r="G7" s="2">
+        <v>0.9</v>
+      </c>
+      <c r="H7" s="11" t="s">
+        <v>230</v>
+      </c>
+    </row>
+    <row r="8" spans="1:21" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A8" s="4">
         <v>6</v>
       </c>
       <c r="B8" s="4" t="s">
-        <v>226</v>
+        <v>220</v>
       </c>
       <c r="C8" s="4" t="s">
-        <v>227</v>
+        <v>229</v>
       </c>
       <c r="D8" s="4" t="s">
-        <v>217</v>
-      </c>
-      <c r="E8" s="4" t="s">
-        <v>47</v>
-      </c>
-      <c r="F8" s="4" t="s">
-        <v>47</v>
-      </c>
-      <c r="G8" s="4" t="s">
-        <v>47</v>
-      </c>
-      <c r="H8" s="13" t="s">
-        <v>218</v>
-      </c>
-    </row>
-    <row r="9" spans="1:8" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+        <v>190</v>
+      </c>
+      <c r="E8" s="4">
+        <v>1</v>
+      </c>
+      <c r="F8" s="4">
+        <v>0</v>
+      </c>
+      <c r="G8" s="4">
+        <v>0</v>
+      </c>
+      <c r="H8" s="11" t="s">
+        <v>230</v>
+      </c>
+    </row>
+    <row r="9" spans="1:21" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A9" s="2">
         <v>7</v>
       </c>
       <c r="B9" s="2" t="s">
-        <v>228</v>
+        <v>231</v>
       </c>
       <c r="C9" s="2" t="s">
-        <v>229</v>
+        <v>224</v>
       </c>
       <c r="D9" s="2" t="s">
-        <v>217</v>
+        <v>190</v>
       </c>
       <c r="E9" s="2" t="s">
-        <v>47</v>
-      </c>
-      <c r="F9" s="2" t="s">
-        <v>47</v>
-      </c>
-      <c r="G9" s="2" t="s">
-        <v>47</v>
-      </c>
-      <c r="H9" s="13" t="s">
-        <v>218</v>
-      </c>
-    </row>
-    <row r="10" spans="1:8" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+        <v>232</v>
+      </c>
+      <c r="F9" s="2">
+        <v>0</v>
+      </c>
+      <c r="G9" s="2">
+        <v>0</v>
+      </c>
+      <c r="H9" s="11" t="s">
+        <v>230</v>
+      </c>
+    </row>
+    <row r="10" spans="1:21" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A10" s="4">
         <v>8</v>
       </c>
       <c r="B10" s="4" t="s">
+        <v>233</v>
+      </c>
+      <c r="C10" s="4" t="s">
+        <v>234</v>
+      </c>
+      <c r="D10" s="4" t="s">
+        <v>190</v>
+      </c>
+      <c r="E10" s="4">
+        <v>1</v>
+      </c>
+      <c r="F10" s="4" t="s">
+        <v>235</v>
+      </c>
+      <c r="G10" s="4">
+        <v>0.15</v>
+      </c>
+      <c r="H10" s="11" t="s">
         <v>230</v>
       </c>
-      <c r="C10" s="4" t="s">
-        <v>203</v>
-      </c>
-      <c r="D10" s="4" t="s">
-        <v>217</v>
-      </c>
-      <c r="E10" s="4" t="s">
-        <v>47</v>
-      </c>
-      <c r="F10" s="4" t="s">
-        <v>47</v>
-      </c>
-      <c r="G10" s="4" t="s">
-        <v>231</v>
-      </c>
-      <c r="H10" s="11" t="s">
-        <v>232</v>
-      </c>
+    </row>
+    <row r="11" spans="1:21" x14ac:dyDescent="0.25">
+      <c r="S11" s="38"/>
+      <c r="T11" s="38"/>
+      <c r="U11" s="38"/>
+    </row>
+    <row r="12" spans="1:21" x14ac:dyDescent="0.25">
+      <c r="S12" s="38"/>
+      <c r="T12" s="38"/>
+      <c r="U12" s="38"/>
+    </row>
+    <row r="13" spans="1:21" x14ac:dyDescent="0.25">
+      <c r="S13" s="38"/>
+      <c r="T13" s="38"/>
+      <c r="U13" s="38"/>
+    </row>
+    <row r="14" spans="1:21" x14ac:dyDescent="0.25">
+      <c r="S14" s="38"/>
+      <c r="T14" s="38"/>
+      <c r="U14" s="38"/>
+    </row>
+    <row r="15" spans="1:21" x14ac:dyDescent="0.25">
+      <c r="S15" s="38"/>
+      <c r="T15" s="38"/>
+      <c r="U15" s="38"/>
+    </row>
+    <row r="16" spans="1:21" x14ac:dyDescent="0.25">
+      <c r="S16" s="38"/>
+      <c r="T16" s="38"/>
+      <c r="U16" s="38"/>
+    </row>
+    <row r="17" spans="19:21" x14ac:dyDescent="0.25">
+      <c r="T17" s="38"/>
+      <c r="U17" s="38"/>
+    </row>
+    <row r="18" spans="19:21" x14ac:dyDescent="0.25">
+      <c r="S18" s="38"/>
+      <c r="U18" s="38"/>
+    </row>
+    <row r="19" spans="19:21" x14ac:dyDescent="0.25">
+      <c r="S19" s="37"/>
+    </row>
+    <row r="20" spans="19:21" x14ac:dyDescent="0.25">
+      <c r="S20" s="37"/>
+    </row>
+    <row r="21" spans="19:21" x14ac:dyDescent="0.25">
+      <c r="S21" s="37"/>
+    </row>
+    <row r="22" spans="19:21" x14ac:dyDescent="0.25">
+      <c r="S22" s="37"/>
+    </row>
+    <row r="23" spans="19:21" x14ac:dyDescent="0.25">
+      <c r="S23" s="37"/>
+    </row>
+    <row r="24" spans="19:21" x14ac:dyDescent="0.25">
+      <c r="S24" s="37"/>
+    </row>
+    <row r="25" spans="19:21" x14ac:dyDescent="0.25">
+      <c r="S25" s="37"/>
     </row>
   </sheetData>
   <mergeCells count="1">
@@ -2142,16 +2391,16 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:8" ht="21.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A1" s="16" t="s">
-        <v>233</v>
-      </c>
-      <c r="B1" s="16"/>
-      <c r="C1" s="16"/>
-      <c r="D1" s="16"/>
-      <c r="E1" s="16"/>
-      <c r="F1" s="16"/>
-      <c r="G1" s="16"/>
-      <c r="H1" s="16"/>
+      <c r="A1" s="13" t="s">
+        <v>192</v>
+      </c>
+      <c r="B1" s="13"/>
+      <c r="C1" s="13"/>
+      <c r="D1" s="13"/>
+      <c r="E1" s="13"/>
+      <c r="F1" s="13"/>
+      <c r="G1" s="13"/>
+      <c r="H1" s="13"/>
     </row>
     <row r="2" spans="1:8" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A2" s="1" t="s">
@@ -2163,34 +2412,34 @@
     </row>
     <row r="3" spans="1:8" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A3" s="2" t="s">
-        <v>234</v>
+        <v>193</v>
       </c>
       <c r="B3" s="3" t="s">
-        <v>235</v>
+        <v>194</v>
       </c>
     </row>
     <row r="4" spans="1:8" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A4" s="4" t="s">
-        <v>236</v>
-      </c>
-      <c r="B4" s="3" t="s">
-        <v>237</v>
+        <v>195</v>
+      </c>
+      <c r="B4" s="15">
+        <v>46176</v>
       </c>
     </row>
     <row r="5" spans="1:8" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A5" s="2" t="s">
-        <v>238</v>
+        <v>196</v>
       </c>
       <c r="B5" s="3" t="s">
-        <v>239</v>
+        <v>236</v>
       </c>
     </row>
     <row r="6" spans="1:8" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A6" s="4" t="s">
-        <v>240</v>
+        <v>197</v>
       </c>
       <c r="B6" s="3" t="s">
-        <v>241</v>
+        <v>198</v>
       </c>
     </row>
   </sheetData>
@@ -2219,93 +2468,93 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:8" ht="21.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A1" s="16" t="s">
-        <v>11</v>
-      </c>
-      <c r="B1" s="16"/>
-      <c r="C1" s="16"/>
-      <c r="D1" s="16"/>
-      <c r="E1" s="16"/>
-      <c r="F1" s="16"/>
-      <c r="G1" s="16"/>
-      <c r="H1" s="16"/>
+      <c r="A1" s="13" t="s">
+        <v>9</v>
+      </c>
+      <c r="B1" s="13"/>
+      <c r="C1" s="13"/>
+      <c r="D1" s="13"/>
+      <c r="E1" s="13"/>
+      <c r="F1" s="13"/>
+      <c r="G1" s="13"/>
+      <c r="H1" s="13"/>
     </row>
     <row r="2" spans="1:8" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A2" s="1" t="s">
         <v>1</v>
       </c>
       <c r="B2" s="1" t="s">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="C2" s="1" t="s">
-        <v>13</v>
+        <v>11</v>
       </c>
     </row>
     <row r="3" spans="1:8" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A3" s="2" t="s">
-        <v>14</v>
-      </c>
-      <c r="B3" s="3" t="s">
-        <v>15</v>
+        <v>12</v>
+      </c>
+      <c r="B3" s="19" t="s">
+        <v>13</v>
       </c>
       <c r="C3" s="2"/>
     </row>
     <row r="4" spans="1:8" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A4" s="4" t="s">
-        <v>16</v>
-      </c>
-      <c r="B4" s="3" t="s">
-        <v>17</v>
+        <v>14</v>
+      </c>
+      <c r="B4" s="19" t="s">
+        <v>15</v>
       </c>
       <c r="C4" s="4"/>
     </row>
     <row r="5" spans="1:8" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A5" s="2" t="s">
-        <v>18</v>
-      </c>
-      <c r="B5" s="3" t="s">
-        <v>19</v>
+        <v>16</v>
+      </c>
+      <c r="B5" s="19" t="s">
+        <v>17</v>
       </c>
       <c r="C5" s="2"/>
     </row>
     <row r="6" spans="1:8" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A6" s="4" t="s">
-        <v>20</v>
-      </c>
-      <c r="B6" s="3" t="s">
-        <v>21</v>
+        <v>18</v>
+      </c>
+      <c r="B6" s="19" t="s">
+        <v>19</v>
       </c>
       <c r="C6" s="4"/>
     </row>
     <row r="7" spans="1:8" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A7" s="2" t="s">
-        <v>22</v>
-      </c>
-      <c r="B7" s="3" t="s">
-        <v>23</v>
+        <v>20</v>
+      </c>
+      <c r="B7" s="19" t="s">
+        <v>21</v>
       </c>
       <c r="C7" s="2"/>
     </row>
     <row r="8" spans="1:8" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A8" s="4" t="s">
+        <v>22</v>
+      </c>
+      <c r="B8" s="19" t="s">
+        <v>23</v>
+      </c>
+      <c r="C8" s="4" t="s">
         <v>24</v>
-      </c>
-      <c r="B8" s="3" t="s">
-        <v>25</v>
-      </c>
-      <c r="C8" s="4" t="s">
-        <v>26</v>
       </c>
     </row>
     <row r="9" spans="1:8" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A9" s="2" t="s">
-        <v>27</v>
-      </c>
-      <c r="B9" s="3" t="s">
-        <v>28</v>
+        <v>25</v>
+      </c>
+      <c r="B9" s="19">
+        <v>46435</v>
       </c>
       <c r="C9" s="2" t="s">
-        <v>29</v>
+        <v>26</v>
       </c>
     </row>
   </sheetData>
@@ -2335,36 +2584,36 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:8" ht="21.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A1" s="16" t="s">
-        <v>30</v>
-      </c>
-      <c r="B1" s="16"/>
-      <c r="C1" s="16"/>
-      <c r="D1" s="16"/>
-      <c r="E1" s="16"/>
-      <c r="F1" s="16"/>
-      <c r="G1" s="16"/>
-      <c r="H1" s="16"/>
+      <c r="A1" s="13" t="s">
+        <v>27</v>
+      </c>
+      <c r="B1" s="13"/>
+      <c r="C1" s="13"/>
+      <c r="D1" s="13"/>
+      <c r="E1" s="13"/>
+      <c r="F1" s="13"/>
+      <c r="G1" s="13"/>
+      <c r="H1" s="13"/>
     </row>
     <row r="2" spans="1:8" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A2" s="1" t="s">
         <v>1</v>
       </c>
       <c r="B2" s="1" t="s">
-        <v>31</v>
+        <v>28</v>
       </c>
       <c r="C2" s="1" t="s">
-        <v>32</v>
+        <v>29</v>
       </c>
       <c r="D2" s="1" t="s">
-        <v>13</v>
+        <v>11</v>
       </c>
     </row>
     <row r="3" spans="1:8" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A3" s="2" t="s">
-        <v>33</v>
-      </c>
-      <c r="B3" s="3">
+        <v>30</v>
+      </c>
+      <c r="B3" s="18">
         <v>388016486</v>
       </c>
       <c r="C3" s="2"/>
@@ -2372,9 +2621,9 @@
     </row>
     <row r="4" spans="1:8" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A4" s="4" t="s">
-        <v>34</v>
-      </c>
-      <c r="B4" s="3">
+        <v>31</v>
+      </c>
+      <c r="B4" s="18">
         <v>0</v>
       </c>
       <c r="C4" s="4"/>
@@ -2382,9 +2631,9 @@
     </row>
     <row r="5" spans="1:8" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A5" s="2" t="s">
-        <v>35</v>
-      </c>
-      <c r="B5" s="3">
+        <v>32</v>
+      </c>
+      <c r="B5" s="18">
         <v>0</v>
       </c>
       <c r="C5" s="2"/>
@@ -2392,9 +2641,9 @@
     </row>
     <row r="6" spans="1:8" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A6" s="4" t="s">
-        <v>36</v>
-      </c>
-      <c r="B6" s="3">
+        <v>33</v>
+      </c>
+      <c r="B6" s="18">
         <v>0</v>
       </c>
       <c r="C6" s="4"/>
@@ -2402,21 +2651,21 @@
     </row>
     <row r="7" spans="1:8" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A7" s="2" t="s">
-        <v>37</v>
-      </c>
-      <c r="B7" s="3">
+        <v>34</v>
+      </c>
+      <c r="B7" s="18">
         <v>388016486</v>
       </c>
       <c r="C7" s="2"/>
       <c r="D7" s="2" t="s">
-        <v>38</v>
+        <v>35</v>
       </c>
     </row>
     <row r="8" spans="1:8" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A8" s="4" t="s">
-        <v>39</v>
-      </c>
-      <c r="B8" s="3">
+        <v>36</v>
+      </c>
+      <c r="B8" s="18">
         <v>34426811</v>
       </c>
       <c r="C8" s="4"/>
@@ -2424,16 +2673,17 @@
     </row>
     <row r="9" spans="1:8" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A9" s="2" t="s">
-        <v>40</v>
-      </c>
-      <c r="B9" s="3">
+        <v>37</v>
+      </c>
+      <c r="B9" s="18">
         <v>15596872</v>
       </c>
-      <c r="C9" s="2" t="s">
-        <v>41</v>
+      <c r="C9" s="16">
+        <f>B9/B8</f>
+        <v>0.45304434384003794</v>
       </c>
       <c r="D9" s="2" t="s">
-        <v>42</v>
+        <v>38</v>
       </c>
     </row>
   </sheetData>
@@ -2453,26 +2703,26 @@
   <sheetPr>
     <tabColor rgb="FFE87722"/>
   </sheetPr>
-  <dimension ref="A1:H9"/>
+  <dimension ref="A1:H10"/>
   <sheetFormatPr defaultColWidth="8.7109375" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="32" customWidth="1"/>
     <col min="2" max="2" width="22" customWidth="1"/>
-    <col min="3" max="3" width="14" customWidth="1"/>
+    <col min="3" max="3" width="14" style="26" customWidth="1"/>
     <col min="4" max="4" width="40" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:8" ht="21.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A1" s="16" t="s">
-        <v>43</v>
-      </c>
-      <c r="B1" s="16"/>
-      <c r="C1" s="16"/>
-      <c r="D1" s="16"/>
-      <c r="E1" s="16"/>
-      <c r="F1" s="16"/>
-      <c r="G1" s="16"/>
-      <c r="H1" s="16"/>
+      <c r="A1" s="13" t="s">
+        <v>39</v>
+      </c>
+      <c r="B1" s="13"/>
+      <c r="C1" s="13"/>
+      <c r="D1" s="13"/>
+      <c r="E1" s="13"/>
+      <c r="F1" s="13"/>
+      <c r="G1" s="13"/>
+      <c r="H1" s="13"/>
     </row>
     <row r="2" spans="1:8" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A2" s="1" t="s">
@@ -2482,97 +2732,108 @@
         <v>2</v>
       </c>
       <c r="C2" s="1" t="s">
-        <v>32</v>
+        <v>29</v>
       </c>
       <c r="D2" s="1" t="s">
-        <v>13</v>
+        <v>11</v>
       </c>
     </row>
     <row r="3" spans="1:8" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A3" s="2" t="s">
-        <v>44</v>
-      </c>
-      <c r="B3" s="3">
+        <v>40</v>
+      </c>
+      <c r="B3" s="21">
         <v>355587125</v>
       </c>
-      <c r="C3" s="2"/>
+      <c r="C3" s="23"/>
       <c r="D3" s="2" t="s">
-        <v>45</v>
+        <v>41</v>
       </c>
     </row>
     <row r="4" spans="1:8" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A4" s="4" t="s">
+        <v>42</v>
+      </c>
+      <c r="B4" s="22" t="s">
+        <v>43</v>
+      </c>
+      <c r="C4" s="24"/>
+      <c r="D4" s="4" t="s">
+        <v>44</v>
+      </c>
+    </row>
+    <row r="5" spans="1:8" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A5" s="4" t="s">
+        <v>203</v>
+      </c>
+      <c r="B5" s="22">
+        <v>0.68799999999999994</v>
+      </c>
+      <c r="C5" s="24"/>
+      <c r="D5" s="4"/>
+    </row>
+    <row r="6" spans="1:8" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A6" s="2" t="s">
+        <v>45</v>
+      </c>
+      <c r="B6" s="28">
+        <v>0.40899999999999997</v>
+      </c>
+      <c r="C6" s="25">
+        <f>B4-B6</f>
+        <v>0.59099999999999997</v>
+      </c>
+      <c r="D6" s="2" t="s">
         <v>46</v>
       </c>
-      <c r="B4" s="3" t="s">
+    </row>
+    <row r="7" spans="1:8" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A7" s="4" t="s">
+        <v>36</v>
+      </c>
+      <c r="B7" s="21">
+        <v>34426811</v>
+      </c>
+      <c r="C7" s="24"/>
+      <c r="D7" s="4" t="s">
+        <v>41</v>
+      </c>
+    </row>
+    <row r="8" spans="1:8" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A8" s="2" t="s">
+        <v>37</v>
+      </c>
+      <c r="B8" s="21">
+        <v>15596872</v>
+      </c>
+      <c r="C8" s="23"/>
+      <c r="D8" s="2" t="s">
+        <v>41</v>
+      </c>
+    </row>
+    <row r="9" spans="1:8" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A9" s="4" t="s">
         <v>47</v>
       </c>
-      <c r="C4" s="4"/>
-      <c r="D4" s="4" t="s">
+      <c r="B9" s="22">
+        <f>(B7-B8)/B7</f>
+        <v>0.54695565615996211</v>
+      </c>
+      <c r="C9" s="24"/>
+      <c r="D9" s="4" t="s">
         <v>48</v>
       </c>
     </row>
-    <row r="5" spans="1:8" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A5" s="2" t="s">
+    <row r="10" spans="1:8" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A10" s="2" t="s">
         <v>49</v>
       </c>
-      <c r="B5" s="14">
-        <v>0.45</v>
-      </c>
-      <c r="C5" s="15">
-        <f>B4-B5</f>
-        <v>0.55000000000000004</v>
-      </c>
-      <c r="D5" s="2" t="s">
+      <c r="B10" s="20" t="s">
+        <v>201</v>
+      </c>
+      <c r="C10" s="23"/>
+      <c r="D10" s="2" t="s">
         <v>50</v>
-      </c>
-    </row>
-    <row r="6" spans="1:8" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A6" s="4" t="s">
-        <v>39</v>
-      </c>
-      <c r="B6" s="3">
-        <v>34426811</v>
-      </c>
-      <c r="C6" s="4"/>
-      <c r="D6" s="4" t="s">
-        <v>45</v>
-      </c>
-    </row>
-    <row r="7" spans="1:8" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A7" s="2" t="s">
-        <v>40</v>
-      </c>
-      <c r="B7" s="3">
-        <v>15596872</v>
-      </c>
-      <c r="C7" s="2"/>
-      <c r="D7" s="2" t="s">
-        <v>45</v>
-      </c>
-    </row>
-    <row r="8" spans="1:8" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A8" s="4" t="s">
-        <v>51</v>
-      </c>
-      <c r="B8" s="3" t="s">
-        <v>52</v>
-      </c>
-      <c r="C8" s="4"/>
-      <c r="D8" s="4" t="s">
-        <v>53</v>
-      </c>
-    </row>
-    <row r="9" spans="1:8" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A9" s="2" t="s">
-        <v>54</v>
-      </c>
-      <c r="B9" s="3" t="s">
-        <v>55</v>
-      </c>
-      <c r="C9" s="2"/>
-      <c r="D9" s="2" t="s">
-        <v>56</v>
       </c>
     </row>
   </sheetData>
@@ -2603,120 +2864,126 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:8" ht="21.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A1" s="16" t="s">
-        <v>57</v>
-      </c>
-      <c r="B1" s="16"/>
-      <c r="C1" s="16"/>
-      <c r="D1" s="16"/>
-      <c r="E1" s="16"/>
-      <c r="F1" s="16"/>
-      <c r="G1" s="16"/>
-      <c r="H1" s="16"/>
+      <c r="A1" s="13" t="s">
+        <v>51</v>
+      </c>
+      <c r="B1" s="13"/>
+      <c r="C1" s="13"/>
+      <c r="D1" s="13"/>
+      <c r="E1" s="13"/>
+      <c r="F1" s="13"/>
+      <c r="G1" s="13"/>
+      <c r="H1" s="13"/>
     </row>
     <row r="2" spans="1:8" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A2" s="1" t="s">
         <v>1</v>
       </c>
       <c r="B2" s="1" t="s">
-        <v>31</v>
+        <v>28</v>
       </c>
       <c r="C2" s="1" t="s">
-        <v>58</v>
+        <v>52</v>
       </c>
       <c r="D2" s="1" t="s">
-        <v>59</v>
+        <v>53</v>
       </c>
       <c r="E2" s="1" t="s">
-        <v>13</v>
+        <v>11</v>
       </c>
     </row>
     <row r="3" spans="1:8" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A3" s="2" t="s">
-        <v>60</v>
-      </c>
-      <c r="B3" s="3">
+        <v>54</v>
+      </c>
+      <c r="B3" s="17">
         <v>204059236</v>
       </c>
-      <c r="C3" s="2" t="s">
-        <v>61</v>
+      <c r="C3" s="16">
+        <f>B3/Commercial_Info!$B$3</f>
+        <v>0.52590352050144595</v>
       </c>
       <c r="D3" s="2" t="s">
-        <v>62</v>
+        <v>55</v>
       </c>
       <c r="E3" s="2"/>
+      <c r="G3" s="27"/>
     </row>
     <row r="4" spans="1:8" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A4" s="4" t="s">
-        <v>63</v>
-      </c>
-      <c r="B4" s="3">
+        <v>56</v>
+      </c>
+      <c r="B4" s="17">
         <v>152961744</v>
       </c>
-      <c r="C4" s="4" t="s">
-        <v>64</v>
+      <c r="C4" s="16">
+        <f>B4/Commercial_Info!$B$3</f>
+        <v>0.39421454891481078</v>
       </c>
       <c r="D4" s="4" t="s">
-        <v>65</v>
+        <v>57</v>
       </c>
       <c r="E4" s="4"/>
     </row>
     <row r="5" spans="1:8" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A5" s="2" t="s">
-        <v>66</v>
-      </c>
-      <c r="B5" s="3">
+        <v>58</v>
+      </c>
+      <c r="B5" s="17">
         <v>152961744</v>
       </c>
-      <c r="C5" s="2" t="s">
-        <v>64</v>
+      <c r="C5" s="16">
+        <f>B5/Commercial_Info!$B$3</f>
+        <v>0.39421454891481078</v>
       </c>
       <c r="D5" s="2" t="s">
-        <v>65</v>
+        <v>57</v>
       </c>
       <c r="E5" s="2"/>
     </row>
     <row r="6" spans="1:8" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A6" s="4" t="s">
-        <v>67</v>
-      </c>
-      <c r="B6" s="3">
+        <v>59</v>
+      </c>
+      <c r="B6" s="17">
         <v>0</v>
       </c>
       <c r="C6" s="4"/>
       <c r="D6" s="4" t="s">
-        <v>68</v>
+        <v>60</v>
       </c>
       <c r="E6" s="4"/>
     </row>
     <row r="7" spans="1:8" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A7" s="2" t="s">
-        <v>69</v>
-      </c>
-      <c r="B7" s="3">
+        <v>61</v>
+      </c>
+      <c r="B7" s="17">
         <v>68039022</v>
       </c>
-      <c r="C7" s="2" t="s">
-        <v>70</v>
+      <c r="C7" s="16">
+        <f>B7/Commercial_Info!$B$3</f>
+        <v>0.17535085352017749</v>
       </c>
       <c r="D7" s="2" t="s">
-        <v>65</v>
+        <v>57</v>
       </c>
       <c r="E7" s="2"/>
     </row>
-    <row r="8" spans="1:8" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:8" ht="28.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A8" s="4" t="s">
-        <v>71</v>
-      </c>
-      <c r="B8" s="3" t="s">
-        <v>72</v>
+        <v>202</v>
+      </c>
+      <c r="B8" s="30" t="str">
+        <f>ROUNDUP(C4*100,0)&amp;"%"&amp;" / "&amp;ROUNDUP(Budgetary_Info!B6*100,0)&amp;"%"</f>
+        <v>40% / 41%</v>
       </c>
       <c r="C8" s="4"/>
       <c r="D8" s="4" t="s">
-        <v>68</v>
+        <v>60</v>
       </c>
       <c r="E8" s="4" t="s">
-        <v>73</v>
+        <v>62</v>
       </c>
     </row>
   </sheetData>
@@ -2746,81 +3013,82 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:8" ht="21.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A1" s="16" t="s">
-        <v>74</v>
-      </c>
-      <c r="B1" s="16"/>
-      <c r="C1" s="16"/>
-      <c r="D1" s="16"/>
-      <c r="E1" s="16"/>
-      <c r="F1" s="16"/>
-      <c r="G1" s="16"/>
-      <c r="H1" s="16"/>
+      <c r="A1" s="13" t="s">
+        <v>63</v>
+      </c>
+      <c r="B1" s="13"/>
+      <c r="C1" s="13"/>
+      <c r="D1" s="13"/>
+      <c r="E1" s="13"/>
+      <c r="F1" s="13"/>
+      <c r="G1" s="13"/>
+      <c r="H1" s="13"/>
     </row>
     <row r="2" spans="1:8" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A2" s="1" t="s">
         <v>1</v>
       </c>
       <c r="B2" s="1" t="s">
-        <v>75</v>
+        <v>64</v>
       </c>
       <c r="C2" s="1" t="s">
-        <v>76</v>
+        <v>65</v>
       </c>
       <c r="D2" s="1" t="s">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="3" spans="1:8" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="3" spans="1:8" ht="27" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A3" s="2" t="s">
-        <v>77</v>
+        <v>66</v>
       </c>
       <c r="B3" s="3">
         <v>-61.1</v>
       </c>
       <c r="C3" s="2"/>
       <c r="D3" s="2" t="s">
-        <v>78</v>
-      </c>
-    </row>
-    <row r="4" spans="1:8" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+        <v>67</v>
+      </c>
+    </row>
+    <row r="4" spans="1:8" ht="27" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A4" s="4" t="s">
-        <v>79</v>
+        <v>68</v>
       </c>
       <c r="B4" s="3" t="s">
-        <v>80</v>
+        <v>69</v>
       </c>
       <c r="C4" s="4"/>
       <c r="D4" s="4" t="s">
-        <v>81</v>
-      </c>
-    </row>
-    <row r="5" spans="1:8" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+        <v>70</v>
+      </c>
+    </row>
+    <row r="5" spans="1:8" ht="27" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A5" s="2" t="s">
-        <v>82</v>
+        <v>71</v>
       </c>
       <c r="B5" s="3">
         <v>68</v>
       </c>
-      <c r="C5" s="2" t="s">
-        <v>83</v>
+      <c r="C5" s="31">
+        <f>B5/B6</f>
+        <v>0.52631578947368429</v>
       </c>
       <c r="D5" s="2" t="s">
-        <v>84</v>
-      </c>
-    </row>
-    <row r="6" spans="1:8" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+        <v>72</v>
+      </c>
+    </row>
+    <row r="6" spans="1:8" ht="27" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A6" s="4" t="s">
-        <v>85</v>
+        <v>73</v>
       </c>
       <c r="B6" s="3">
         <v>129.19999999999999</v>
       </c>
       <c r="C6" s="4" t="s">
-        <v>47</v>
+        <v>43</v>
       </c>
       <c r="D6" s="4" t="s">
-        <v>86</v>
+        <v>74</v>
       </c>
     </row>
   </sheetData>
@@ -2850,24 +3118,24 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:8" ht="21.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A1" s="16" t="s">
-        <v>87</v>
-      </c>
-      <c r="B1" s="16"/>
-      <c r="C1" s="16"/>
-      <c r="D1" s="16"/>
-      <c r="E1" s="16"/>
-      <c r="F1" s="16"/>
-      <c r="G1" s="16"/>
-      <c r="H1" s="16"/>
+      <c r="A1" s="13" t="s">
+        <v>75</v>
+      </c>
+      <c r="B1" s="13"/>
+      <c r="C1" s="13"/>
+      <c r="D1" s="13"/>
+      <c r="E1" s="13"/>
+      <c r="F1" s="13"/>
+      <c r="G1" s="13"/>
+      <c r="H1" s="13"/>
     </row>
     <row r="2" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A2" s="17" t="s">
-        <v>88</v>
-      </c>
-      <c r="B2" s="17"/>
-      <c r="C2" s="17"/>
-      <c r="D2" s="17"/>
+      <c r="A2" s="14" t="s">
+        <v>76</v>
+      </c>
+      <c r="B2" s="14"/>
+      <c r="C2" s="14"/>
+      <c r="D2" s="14"/>
     </row>
     <row r="3" spans="1:8" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A3" s="1" t="s">
@@ -2877,199 +3145,201 @@
         <v>2</v>
       </c>
       <c r="C3" s="1" t="s">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="D3" s="1"/>
     </row>
     <row r="4" spans="1:8" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A4" s="4" t="s">
-        <v>89</v>
+        <v>77</v>
       </c>
       <c r="B4" s="3">
-        <v>147</v>
+        <f>B5+B6</f>
+        <v>751</v>
       </c>
       <c r="C4" s="4" t="s">
-        <v>90</v>
+        <v>78</v>
       </c>
       <c r="D4" s="4"/>
     </row>
     <row r="5" spans="1:8" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A5" s="2" t="s">
-        <v>91</v>
+        <v>79</v>
       </c>
       <c r="B5" s="3">
-        <v>117</v>
+        <v>654</v>
       </c>
       <c r="C5" s="2" t="s">
-        <v>92</v>
+        <v>80</v>
       </c>
       <c r="D5" s="2"/>
     </row>
     <row r="6" spans="1:8" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A6" s="4" t="s">
-        <v>93</v>
+        <v>81</v>
       </c>
       <c r="B6" s="3">
-        <v>30</v>
+        <v>97</v>
       </c>
       <c r="C6" s="4" t="s">
-        <v>94</v>
+        <v>82</v>
       </c>
       <c r="D6" s="4"/>
     </row>
     <row r="7" spans="1:8" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A7" s="2" t="s">
-        <v>95</v>
-      </c>
-      <c r="B7" s="3" t="s">
-        <v>96</v>
+        <v>83</v>
+      </c>
+      <c r="B7" s="29">
+        <f>B5/B4</f>
+        <v>0.87083888149134492</v>
       </c>
       <c r="C7" s="2" t="s">
-        <v>97</v>
+        <v>84</v>
       </c>
       <c r="D7" s="2"/>
     </row>
     <row r="8" spans="1:8" ht="6" customHeight="1" x14ac:dyDescent="0.25"/>
     <row r="9" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A9" s="17" t="s">
-        <v>98</v>
-      </c>
-      <c r="B9" s="17"/>
-      <c r="C9" s="17"/>
-      <c r="D9" s="17"/>
+      <c r="A9" s="14" t="s">
+        <v>85</v>
+      </c>
+      <c r="B9" s="14"/>
+      <c r="C9" s="14"/>
+      <c r="D9" s="14"/>
     </row>
     <row r="10" spans="1:8" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A10" s="1" t="s">
-        <v>99</v>
+        <v>86</v>
       </c>
       <c r="B10" s="1" t="s">
-        <v>100</v>
+        <v>87</v>
       </c>
       <c r="C10" s="1" t="s">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="D10" s="1"/>
     </row>
     <row r="11" spans="1:8" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A11" s="2" t="s">
-        <v>101</v>
+        <v>88</v>
       </c>
       <c r="B11" s="3">
-        <v>42</v>
+        <v>386</v>
       </c>
       <c r="C11" s="2" t="s">
-        <v>102</v>
+        <v>89</v>
       </c>
       <c r="D11" s="2"/>
     </row>
     <row r="12" spans="1:8" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A12" s="4" t="s">
-        <v>103</v>
+        <v>90</v>
       </c>
       <c r="B12" s="3">
-        <v>75</v>
+        <v>268</v>
       </c>
       <c r="C12" s="4" t="s">
-        <v>102</v>
+        <v>89</v>
       </c>
       <c r="D12" s="4"/>
     </row>
     <row r="13" spans="1:8" ht="6" customHeight="1" x14ac:dyDescent="0.25"/>
     <row r="14" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A14" s="17" t="s">
-        <v>104</v>
-      </c>
-      <c r="B14" s="17"/>
-      <c r="C14" s="17"/>
-      <c r="D14" s="17"/>
+      <c r="A14" s="14" t="s">
+        <v>91</v>
+      </c>
+      <c r="B14" s="14"/>
+      <c r="C14" s="14"/>
+      <c r="D14" s="14"/>
     </row>
     <row r="15" spans="1:8" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A15" s="1" t="s">
-        <v>105</v>
+        <v>92</v>
       </c>
       <c r="B15" s="1" t="s">
         <v>2</v>
       </c>
       <c r="C15" s="1" t="s">
-        <v>106</v>
+        <v>93</v>
       </c>
       <c r="D15" s="1"/>
     </row>
     <row r="16" spans="1:8" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A16" s="4" t="s">
-        <v>107</v>
+        <v>94</v>
       </c>
       <c r="B16" s="3">
         <f>B4/B5*100</f>
-        <v>125.64102564102564</v>
+        <v>114.83180428134557</v>
       </c>
       <c r="C16" s="4" t="s">
-        <v>108</v>
+        <v>95</v>
       </c>
       <c r="D16" s="4"/>
     </row>
     <row r="17" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A17" s="2" t="s">
-        <v>109</v>
+        <v>96</v>
       </c>
       <c r="B17" s="3">
         <f>B6/B5*100</f>
-        <v>25.641025641025639</v>
+        <v>14.831804281345565</v>
       </c>
       <c r="C17" s="2" t="s">
-        <v>110</v>
+        <v>97</v>
       </c>
       <c r="D17" s="2"/>
     </row>
     <row r="18" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A18" s="4" t="s">
-        <v>111</v>
+        <v>98</v>
       </c>
       <c r="B18" s="3">
         <f>B16</f>
-        <v>125.64102564102564</v>
+        <v>114.83180428134557</v>
       </c>
       <c r="C18" s="4" t="s">
-        <v>112</v>
+        <v>99</v>
       </c>
       <c r="D18" s="4"/>
     </row>
     <row r="19" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A19" s="2" t="s">
-        <v>113</v>
+        <v>100</v>
       </c>
       <c r="B19" s="3">
         <f>100-B16</f>
-        <v>-25.641025641025635</v>
+        <v>-14.831804281345569</v>
       </c>
       <c r="C19" s="2" t="s">
-        <v>114</v>
+        <v>101</v>
       </c>
       <c r="D19" s="2"/>
     </row>
     <row r="20" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A20" s="4" t="s">
-        <v>115</v>
+        <v>102</v>
       </c>
       <c r="B20" s="3">
         <f>B17</f>
-        <v>25.641025641025639</v>
+        <v>14.831804281345565</v>
       </c>
       <c r="C20" s="4" t="s">
-        <v>116</v>
+        <v>103</v>
       </c>
       <c r="D20" s="4"/>
     </row>
     <row r="21" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A21" s="2" t="s">
-        <v>117</v>
+        <v>104</v>
       </c>
       <c r="B21" s="3">
         <f>100-B17</f>
-        <v>74.358974358974365</v>
+        <v>85.168195718654431</v>
       </c>
       <c r="C21" s="2" t="s">
-        <v>118</v>
+        <v>105</v>
       </c>
       <c r="D21" s="2"/>
     </row>
@@ -3103,161 +3373,161 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:8" ht="21.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A1" s="16" t="s">
-        <v>119</v>
-      </c>
-      <c r="B1" s="16"/>
-      <c r="C1" s="16"/>
-      <c r="D1" s="16"/>
-      <c r="E1" s="16"/>
-      <c r="F1" s="16"/>
-      <c r="G1" s="16"/>
-      <c r="H1" s="16"/>
+      <c r="A1" s="13" t="s">
+        <v>106</v>
+      </c>
+      <c r="B1" s="13"/>
+      <c r="C1" s="13"/>
+      <c r="D1" s="13"/>
+      <c r="E1" s="13"/>
+      <c r="F1" s="13"/>
+      <c r="G1" s="13"/>
+      <c r="H1" s="13"/>
     </row>
     <row r="2" spans="1:8" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A2" s="1" t="s">
-        <v>120</v>
+        <v>107</v>
       </c>
       <c r="B2" s="1" t="s">
-        <v>121</v>
+        <v>108</v>
       </c>
       <c r="C2" s="1" t="s">
-        <v>122</v>
+        <v>109</v>
       </c>
       <c r="D2" s="1" t="s">
-        <v>123</v>
+        <v>110</v>
       </c>
       <c r="E2" s="1" t="s">
-        <v>124</v>
+        <v>111</v>
       </c>
       <c r="F2" s="1" t="s">
-        <v>13</v>
+        <v>11</v>
       </c>
     </row>
     <row r="3" spans="1:8" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A3" s="2" t="s">
-        <v>125</v>
-      </c>
-      <c r="B3" s="2">
-        <v>89.8</v>
-      </c>
-      <c r="C3" s="2">
-        <v>81</v>
+        <v>112</v>
+      </c>
+      <c r="B3" s="32">
+        <v>92.78</v>
+      </c>
+      <c r="C3" s="32">
+        <v>84.28</v>
       </c>
       <c r="D3" s="5">
         <f t="shared" ref="D3:D8" si="0">-C3+B3</f>
-        <v>8.7999999999999972</v>
+        <v>8.5</v>
       </c>
       <c r="E3" s="2" t="s">
-        <v>126</v>
+        <v>113</v>
       </c>
       <c r="F3" s="2" t="s">
-        <v>127</v>
+        <v>114</v>
       </c>
     </row>
     <row r="4" spans="1:8" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A4" s="4" t="s">
-        <v>128</v>
-      </c>
-      <c r="B4" s="4">
+        <v>115</v>
+      </c>
+      <c r="B4" s="33">
         <v>100</v>
       </c>
-      <c r="C4" s="4">
-        <v>99.1</v>
+      <c r="C4" s="33">
+        <v>99.25</v>
       </c>
       <c r="D4" s="6">
         <f t="shared" si="0"/>
-        <v>0.90000000000000568</v>
+        <v>0.75</v>
       </c>
       <c r="E4" s="4" t="s">
-        <v>129</v>
+        <v>116</v>
       </c>
       <c r="F4" s="4" t="s">
-        <v>130</v>
+        <v>117</v>
       </c>
     </row>
     <row r="5" spans="1:8" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A5" s="2" t="s">
-        <v>131</v>
-      </c>
-      <c r="B5" s="2">
-        <v>99.9</v>
-      </c>
-      <c r="C5" s="2">
-        <v>94</v>
+        <v>118</v>
+      </c>
+      <c r="B5" s="32">
+        <v>100</v>
+      </c>
+      <c r="C5" s="32">
+        <v>95.54</v>
       </c>
       <c r="D5" s="5">
         <f t="shared" si="0"/>
-        <v>5.9000000000000057</v>
+        <v>4.4599999999999937</v>
       </c>
       <c r="E5" s="2" t="s">
-        <v>132</v>
+        <v>119</v>
       </c>
       <c r="F5" s="2" t="s">
-        <v>133</v>
+        <v>120</v>
       </c>
     </row>
     <row r="6" spans="1:8" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A6" s="4" t="s">
-        <v>134</v>
-      </c>
-      <c r="B6" s="4">
-        <v>93.7</v>
-      </c>
-      <c r="C6" s="4">
-        <v>85.3</v>
+        <v>121</v>
+      </c>
+      <c r="B6" s="33">
+        <v>95.92</v>
+      </c>
+      <c r="C6" s="33">
+        <v>90.82</v>
       </c>
       <c r="D6" s="6">
         <f t="shared" si="0"/>
-        <v>8.4000000000000057</v>
+        <v>5.1000000000000085</v>
       </c>
       <c r="E6" s="4" t="s">
-        <v>126</v>
+        <v>113</v>
       </c>
       <c r="F6" s="4" t="s">
-        <v>127</v>
+        <v>114</v>
       </c>
     </row>
     <row r="7" spans="1:8" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A7" s="2" t="s">
-        <v>135</v>
-      </c>
-      <c r="B7" s="2">
-        <v>97.1</v>
-      </c>
-      <c r="C7" s="2">
-        <v>89.6</v>
+        <v>122</v>
+      </c>
+      <c r="B7" s="32">
+        <v>100</v>
+      </c>
+      <c r="C7" s="32">
+        <v>93.32</v>
       </c>
       <c r="D7" s="5">
         <f t="shared" si="0"/>
-        <v>7.5</v>
+        <v>6.6800000000000068</v>
       </c>
       <c r="E7" s="2" t="s">
-        <v>132</v>
+        <v>119</v>
       </c>
       <c r="F7" s="2" t="s">
-        <v>133</v>
+        <v>120</v>
       </c>
     </row>
     <row r="8" spans="1:8" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A8" s="4" t="s">
-        <v>136</v>
-      </c>
-      <c r="B8" s="4">
-        <v>49</v>
-      </c>
-      <c r="C8" s="4">
-        <v>14.2</v>
+        <v>123</v>
+      </c>
+      <c r="B8" s="33">
+        <v>68.05</v>
+      </c>
+      <c r="C8" s="33">
+        <v>22.08</v>
       </c>
       <c r="D8" s="6">
         <f t="shared" si="0"/>
-        <v>34.799999999999997</v>
+        <v>45.97</v>
       </c>
       <c r="E8" s="4" t="s">
-        <v>126</v>
+        <v>113</v>
       </c>
       <c r="F8" s="4" t="s">
-        <v>137</v>
+        <v>124</v>
       </c>
     </row>
   </sheetData>
@@ -3287,143 +3557,141 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:8" ht="21.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A1" s="16" t="s">
-        <v>138</v>
-      </c>
-      <c r="B1" s="16"/>
-      <c r="C1" s="16"/>
-      <c r="D1" s="16"/>
-      <c r="E1" s="16"/>
-      <c r="F1" s="16"/>
-      <c r="G1" s="16"/>
-      <c r="H1" s="16"/>
+      <c r="A1" s="13" t="s">
+        <v>125</v>
+      </c>
+      <c r="B1" s="13"/>
+      <c r="C1" s="13"/>
+      <c r="D1" s="13"/>
+      <c r="E1" s="13"/>
+      <c r="F1" s="13"/>
+      <c r="G1" s="13"/>
+      <c r="H1" s="13"/>
     </row>
     <row r="2" spans="1:8" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A2" s="1" t="s">
-        <v>139</v>
+        <v>126</v>
       </c>
       <c r="B2" s="1" t="s">
-        <v>121</v>
+        <v>108</v>
       </c>
       <c r="C2" s="1" t="s">
-        <v>122</v>
+        <v>109</v>
       </c>
       <c r="D2" s="1" t="s">
-        <v>123</v>
+        <v>110</v>
       </c>
       <c r="E2" s="1" t="s">
-        <v>124</v>
+        <v>111</v>
       </c>
       <c r="F2" s="1" t="s">
-        <v>13</v>
+        <v>11</v>
       </c>
     </row>
     <row r="3" spans="1:8" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A3" s="2" t="s">
-        <v>140</v>
+        <v>127</v>
       </c>
       <c r="B3" s="2">
-        <v>89.6</v>
+        <v>92.88</v>
       </c>
       <c r="C3" s="2">
-        <v>80.8</v>
+        <v>83.78</v>
       </c>
       <c r="D3" s="5">
         <f>-C3+B3</f>
-        <v>8.7999999999999972</v>
+        <v>9.0999999999999943</v>
       </c>
       <c r="E3" s="2" t="s">
-        <v>126</v>
+        <v>113</v>
       </c>
       <c r="F3" s="2"/>
     </row>
     <row r="4" spans="1:8" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A4" s="4" t="s">
-        <v>141</v>
+        <v>128</v>
       </c>
       <c r="B4" s="4">
-        <v>88.8</v>
+        <v>92.15</v>
       </c>
       <c r="C4" s="4">
-        <v>80.8</v>
+        <v>84.33</v>
       </c>
       <c r="D4" s="6">
         <f>-C4+B4</f>
-        <v>8</v>
+        <v>7.8200000000000074</v>
       </c>
       <c r="E4" s="4" t="s">
-        <v>132</v>
+        <v>119</v>
       </c>
       <c r="F4" s="4"/>
     </row>
     <row r="5" spans="1:8" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A5" s="2" t="s">
-        <v>142</v>
+        <v>129</v>
       </c>
       <c r="B5" s="2">
-        <v>87</v>
+        <v>90.96</v>
       </c>
       <c r="C5" s="2">
-        <v>76.8</v>
+        <v>81.37</v>
       </c>
       <c r="D5" s="5">
         <f>-C5+B5</f>
-        <v>10.200000000000003</v>
+        <v>9.5899999999999892</v>
       </c>
       <c r="E5" s="2" t="s">
-        <v>126</v>
+        <v>113</v>
       </c>
       <c r="F5" s="2" t="s">
-        <v>143</v>
+        <v>130</v>
       </c>
     </row>
     <row r="6" spans="1:8" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A6" s="4" t="s">
-        <v>144</v>
+        <v>131</v>
       </c>
       <c r="B6" s="4">
-        <v>95</v>
+        <v>95.89</v>
       </c>
       <c r="C6" s="4">
-        <v>83.6</v>
+        <v>86.1</v>
       </c>
       <c r="D6" s="6">
         <f>-C6+B6</f>
-        <v>11.400000000000006</v>
+        <v>9.7900000000000063</v>
       </c>
       <c r="E6" s="4" t="s">
-        <v>126</v>
+        <v>113</v>
       </c>
       <c r="F6" s="4"/>
     </row>
     <row r="7" spans="1:8" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A7" s="2" t="s">
-        <v>145</v>
+        <v>132</v>
       </c>
       <c r="B7" s="2">
-        <v>95.1</v>
+        <v>95.71</v>
       </c>
       <c r="C7" s="2">
-        <v>90</v>
+        <v>91.03</v>
       </c>
       <c r="D7" s="5">
         <f>-C7+B7</f>
-        <v>5.0999999999999943</v>
+        <v>4.6799999999999926</v>
       </c>
       <c r="E7" s="2" t="s">
-        <v>132</v>
+        <v>119</v>
       </c>
       <c r="F7" s="2" t="s">
-        <v>146</v>
+        <v>133</v>
       </c>
     </row>
     <row r="8" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A8" s="7" t="s">
-        <v>147</v>
-      </c>
-      <c r="B8" s="7" t="s">
-        <v>148</v>
-      </c>
+        <v>134</v>
+      </c>
+      <c r="B8" s="7"/>
       <c r="C8" s="7"/>
       <c r="D8" s="7"/>
       <c r="E8" s="7"/>

--- a/Dashboard_Data.xlsx
+++ b/Dashboard_Data.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://alfanargroup-my.sharepoint.com/personal/ahmed_abdelzaher_alfanar_com/Documents/SDCC Dashboard/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="165" documentId="14_{682A7E4B-1055-4B0F-805D-134F59E89DE5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{AC7FB250-0A9F-4C3F-8B20-C0F32970438A}"/>
+  <xr:revisionPtr revIDLastSave="180" documentId="14_{682A7E4B-1055-4B0F-805D-134F59E89DE5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{618910F2-EC23-4C0D-826B-EEEE754DF2AA}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" tabRatio="500" firstSheet="2" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" tabRatio="500" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Header" sheetId="1" r:id="rId1"/>
@@ -48,7 +48,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="366" uniqueCount="237">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="360" uniqueCount="232">
   <si>
     <t>HEADER — Dashboard Title &amp; PM</t>
   </si>
@@ -89,31 +89,16 @@
     <t>Contract Sign Date</t>
   </si>
   <si>
-    <t>24-Jul-24</t>
-  </si>
-  <si>
     <t>Madinah Handover</t>
   </si>
   <si>
-    <t>26-Aug-24</t>
-  </si>
-  <si>
     <t>Abha Handover</t>
   </si>
   <si>
-    <t>06-Oct-24</t>
-  </si>
-  <si>
     <t>Jizan Handover</t>
   </si>
   <si>
-    <t>02-Mar-25</t>
-  </si>
-  <si>
     <t>Jeddah / Makkah HO</t>
-  </si>
-  <si>
-    <t>22-Jun-25</t>
   </si>
   <si>
     <t>Contractual TCC</t>
@@ -767,11 +752,11 @@
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
   <numFmts count="4">
     <numFmt numFmtId="43" formatCode="_(* #,##0.00_);_(* \(#,##0.00\);_(* &quot;-&quot;??_);_(@_)"/>
-    <numFmt numFmtId="165" formatCode="[$-409]d\-mmm\-yy;@"/>
-    <numFmt numFmtId="166" formatCode="0.0%"/>
-    <numFmt numFmtId="167" formatCode="0.0"/>
+    <numFmt numFmtId="164" formatCode="[$-409]d\-mmm\-yy;@"/>
+    <numFmt numFmtId="165" formatCode="0.0%"/>
+    <numFmt numFmtId="166" formatCode="0.0"/>
   </numFmts>
-  <fonts count="7" x14ac:knownFonts="1">
+  <fonts count="8" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -815,6 +800,12 @@
     <font>
       <sz val="11"/>
       <color theme="1"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <charset val="1"/>
+    </font>
+    <font>
+      <sz val="8"/>
       <name val="Calibri"/>
       <family val="2"/>
       <charset val="1"/>
@@ -917,7 +908,7 @@
     <xf numFmtId="43" fontId="6" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="9" fontId="6" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="39">
+  <cellXfs count="38">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -953,12 +944,6 @@
     <xf numFmtId="0" fontId="2" fillId="11" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="15" fontId="3" fillId="5" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
@@ -971,7 +956,7 @@
     <xf numFmtId="43" fontId="3" fillId="5" borderId="1" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="165" fontId="3" fillId="5" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="164" fontId="3" fillId="5" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -996,22 +981,19 @@
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="9" fontId="0" fillId="0" borderId="0" xfId="2" applyFont="1"/>
-    <xf numFmtId="9" fontId="3" fillId="5" borderId="1" xfId="2" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="9" fontId="3" fillId="5" borderId="1" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="10" fontId="3" fillId="5" borderId="1" xfId="2" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="166" fontId="3" fillId="4" borderId="1" xfId="2" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="165" fontId="3" fillId="4" borderId="1" xfId="2" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="167" fontId="3" fillId="4" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="166" fontId="3" fillId="4" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="167" fontId="3" fillId="6" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="166" fontId="3" fillId="6" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="17" fontId="3" fillId="8" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -1025,6 +1007,12 @@
     </xf>
     <xf numFmtId="15" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="9" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
   </cellXfs>
   <cellStyles count="3">
     <cellStyle name="Comma" xfId="1" builtinId="3"/>
@@ -1302,16 +1290,16 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:8" ht="21.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A1" s="13" t="s">
+      <c r="A1" s="36" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="13"/>
-      <c r="C1" s="13"/>
-      <c r="D1" s="13"/>
-      <c r="E1" s="13"/>
-      <c r="F1" s="13"/>
-      <c r="G1" s="13"/>
-      <c r="H1" s="13"/>
+      <c r="B1" s="36"/>
+      <c r="C1" s="36"/>
+      <c r="D1" s="36"/>
+      <c r="E1" s="36"/>
+      <c r="F1" s="36"/>
+      <c r="G1" s="36"/>
+      <c r="H1" s="36"/>
     </row>
     <row r="2" spans="1:8" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A2" s="1" t="s">
@@ -1326,7 +1314,7 @@
         <v>3</v>
       </c>
       <c r="B3" s="3" t="s">
-        <v>199</v>
+        <v>194</v>
       </c>
     </row>
     <row r="4" spans="1:8" x14ac:dyDescent="0.25">
@@ -1342,7 +1330,7 @@
         <v>6</v>
       </c>
       <c r="B5" s="3" t="s">
-        <v>200</v>
+        <v>195</v>
       </c>
     </row>
     <row r="6" spans="1:8" x14ac:dyDescent="0.25">
@@ -1384,38 +1372,38 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:8" ht="21.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A1" s="13" t="s">
-        <v>135</v>
-      </c>
-      <c r="B1" s="13"/>
-      <c r="C1" s="13"/>
-      <c r="D1" s="13"/>
-      <c r="E1" s="13"/>
-      <c r="F1" s="13"/>
-      <c r="G1" s="13"/>
-      <c r="H1" s="13"/>
+      <c r="A1" s="36" t="s">
+        <v>130</v>
+      </c>
+      <c r="B1" s="36"/>
+      <c r="C1" s="36"/>
+      <c r="D1" s="36"/>
+      <c r="E1" s="36"/>
+      <c r="F1" s="36"/>
+      <c r="G1" s="36"/>
+      <c r="H1" s="36"/>
     </row>
     <row r="2" spans="1:8" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A2" s="1" t="s">
+        <v>131</v>
+      </c>
+      <c r="B2" s="1" t="s">
+        <v>132</v>
+      </c>
+      <c r="C2" s="1" t="s">
+        <v>133</v>
+      </c>
+      <c r="D2" s="1" t="s">
+        <v>134</v>
+      </c>
+      <c r="E2" s="1" t="s">
+        <v>135</v>
+      </c>
+      <c r="F2" s="1" t="s">
         <v>136</v>
       </c>
-      <c r="B2" s="1" t="s">
+      <c r="G2" s="1" t="s">
         <v>137</v>
-      </c>
-      <c r="C2" s="1" t="s">
-        <v>138</v>
-      </c>
-      <c r="D2" s="1" t="s">
-        <v>139</v>
-      </c>
-      <c r="E2" s="1" t="s">
-        <v>140</v>
-      </c>
-      <c r="F2" s="1" t="s">
-        <v>141</v>
-      </c>
-      <c r="G2" s="1" t="s">
-        <v>142</v>
       </c>
       <c r="H2" s="1" t="s">
         <v>11</v>
@@ -1423,37 +1411,37 @@
     </row>
     <row r="3" spans="1:8" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A3" s="8" t="s">
-        <v>143</v>
+        <v>138</v>
       </c>
       <c r="B3" s="2" t="s">
-        <v>144</v>
+        <v>139</v>
       </c>
       <c r="C3" s="2" t="s">
-        <v>145</v>
+        <v>140</v>
       </c>
       <c r="D3" s="2" t="s">
-        <v>146</v>
+        <v>141</v>
       </c>
       <c r="E3" s="2" t="s">
-        <v>147</v>
+        <v>142</v>
       </c>
       <c r="F3" s="2"/>
       <c r="G3" s="2"/>
       <c r="H3" s="2" t="s">
-        <v>148</v>
+        <v>143</v>
       </c>
     </row>
     <row r="4" spans="1:8" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A4" s="4" t="s">
-        <v>149</v>
+        <v>144</v>
       </c>
       <c r="B4" s="4" t="s">
-        <v>147</v>
+        <v>142</v>
       </c>
       <c r="C4" s="4"/>
       <c r="D4" s="4"/>
       <c r="E4" s="4" t="s">
-        <v>147</v>
+        <v>142</v>
       </c>
       <c r="F4" s="4"/>
       <c r="G4" s="4"/>
@@ -1461,15 +1449,15 @@
     </row>
     <row r="5" spans="1:8" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A5" s="2" t="s">
-        <v>150</v>
+        <v>145</v>
       </c>
       <c r="B5" s="2" t="s">
-        <v>147</v>
+        <v>142</v>
       </c>
       <c r="C5" s="2"/>
       <c r="D5" s="2"/>
       <c r="E5" s="2" t="s">
-        <v>147</v>
+        <v>142</v>
       </c>
       <c r="F5" s="2"/>
       <c r="G5" s="2"/>
@@ -1477,15 +1465,15 @@
     </row>
     <row r="6" spans="1:8" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A6" s="4" t="s">
-        <v>151</v>
+        <v>146</v>
       </c>
       <c r="B6" s="4" t="s">
-        <v>147</v>
+        <v>142</v>
       </c>
       <c r="C6" s="4"/>
       <c r="D6" s="4"/>
       <c r="E6" s="4" t="s">
-        <v>147</v>
+        <v>142</v>
       </c>
       <c r="F6" s="4"/>
       <c r="G6" s="4"/>
@@ -1493,19 +1481,19 @@
     </row>
     <row r="7" spans="1:8" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A7" s="8" t="s">
-        <v>152</v>
+        <v>147</v>
       </c>
       <c r="B7" s="2" t="s">
-        <v>144</v>
+        <v>139</v>
       </c>
       <c r="C7" s="2" t="s">
-        <v>153</v>
+        <v>148</v>
       </c>
       <c r="D7" s="2" t="s">
-        <v>146</v>
+        <v>141</v>
       </c>
       <c r="E7" s="2" t="s">
-        <v>147</v>
+        <v>142</v>
       </c>
       <c r="F7" s="2"/>
       <c r="G7" s="2"/>
@@ -1513,37 +1501,37 @@
     </row>
     <row r="8" spans="1:8" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A8" s="8" t="s">
-        <v>154</v>
+        <v>149</v>
       </c>
       <c r="B8" s="4" t="s">
-        <v>144</v>
+        <v>139</v>
       </c>
       <c r="C8" s="4" t="s">
-        <v>155</v>
+        <v>150</v>
       </c>
       <c r="D8" s="4" t="s">
-        <v>156</v>
+        <v>151</v>
       </c>
       <c r="E8" s="4" t="s">
-        <v>147</v>
+        <v>142</v>
       </c>
       <c r="F8" s="4"/>
       <c r="G8" s="4"/>
       <c r="H8" s="4" t="s">
-        <v>157</v>
+        <v>152</v>
       </c>
     </row>
     <row r="9" spans="1:8" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A9" s="2" t="s">
-        <v>158</v>
+        <v>153</v>
       </c>
       <c r="B9" s="2" t="s">
-        <v>147</v>
+        <v>142</v>
       </c>
       <c r="C9" s="2"/>
       <c r="D9" s="2"/>
       <c r="E9" s="2" t="s">
-        <v>147</v>
+        <v>142</v>
       </c>
       <c r="F9" s="2"/>
       <c r="G9" s="2"/>
@@ -1551,19 +1539,19 @@
     </row>
     <row r="10" spans="1:8" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A10" s="8" t="s">
-        <v>159</v>
+        <v>154</v>
       </c>
       <c r="B10" s="4" t="s">
-        <v>144</v>
+        <v>139</v>
       </c>
       <c r="C10" s="4" t="s">
-        <v>160</v>
+        <v>155</v>
       </c>
       <c r="D10" s="4" t="s">
-        <v>146</v>
+        <v>141</v>
       </c>
       <c r="E10" s="4" t="s">
-        <v>147</v>
+        <v>142</v>
       </c>
       <c r="F10" s="4"/>
       <c r="G10" s="4"/>
@@ -1571,15 +1559,15 @@
     </row>
     <row r="11" spans="1:8" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A11" s="2" t="s">
-        <v>161</v>
+        <v>156</v>
       </c>
       <c r="B11" s="2" t="s">
-        <v>147</v>
+        <v>142</v>
       </c>
       <c r="C11" s="2"/>
       <c r="D11" s="2"/>
       <c r="E11" s="2" t="s">
-        <v>147</v>
+        <v>142</v>
       </c>
       <c r="F11" s="2"/>
       <c r="G11" s="2"/>
@@ -1587,15 +1575,15 @@
     </row>
     <row r="12" spans="1:8" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A12" s="4" t="s">
-        <v>162</v>
+        <v>157</v>
       </c>
       <c r="B12" s="4" t="s">
-        <v>147</v>
+        <v>142</v>
       </c>
       <c r="C12" s="4"/>
       <c r="D12" s="4"/>
       <c r="E12" s="4" t="s">
-        <v>147</v>
+        <v>142</v>
       </c>
       <c r="F12" s="4"/>
       <c r="G12" s="4"/>
@@ -1603,17 +1591,17 @@
     </row>
     <row r="13" spans="1:8" ht="25.5" x14ac:dyDescent="0.25">
       <c r="A13" s="2" t="s">
-        <v>163</v>
+        <v>158</v>
       </c>
       <c r="B13" s="2" t="s">
-        <v>147</v>
+        <v>142</v>
       </c>
       <c r="C13" s="2" t="s">
-        <v>204</v>
+        <v>199</v>
       </c>
       <c r="D13" s="2"/>
       <c r="E13" s="2" t="s">
-        <v>147</v>
+        <v>142</v>
       </c>
       <c r="F13" s="2"/>
       <c r="G13" s="2"/>
@@ -1621,17 +1609,17 @@
     </row>
     <row r="14" spans="1:8" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A14" s="4" t="s">
-        <v>164</v>
+        <v>159</v>
       </c>
       <c r="B14" s="4" t="s">
-        <v>147</v>
+        <v>142</v>
       </c>
       <c r="C14" s="4" t="s">
-        <v>205</v>
+        <v>200</v>
       </c>
       <c r="D14" s="4"/>
       <c r="E14" s="4" t="s">
-        <v>147</v>
+        <v>142</v>
       </c>
       <c r="F14" s="4"/>
       <c r="G14" s="4"/>
@@ -1639,17 +1627,17 @@
     </row>
     <row r="15" spans="1:8" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A15" s="8" t="s">
-        <v>165</v>
+        <v>160</v>
       </c>
       <c r="B15" s="2" t="s">
-        <v>144</v>
+        <v>139</v>
       </c>
       <c r="C15" s="2"/>
       <c r="D15" s="2" t="s">
-        <v>146</v>
+        <v>141</v>
       </c>
       <c r="E15" s="2" t="s">
-        <v>147</v>
+        <v>142</v>
       </c>
       <c r="F15" s="2"/>
       <c r="G15" s="2"/>
@@ -1657,17 +1645,17 @@
     </row>
     <row r="16" spans="1:8" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A16" s="4" t="s">
-        <v>166</v>
+        <v>161</v>
       </c>
       <c r="B16" s="4" t="s">
-        <v>147</v>
+        <v>142</v>
       </c>
       <c r="C16" s="4" t="s">
-        <v>206</v>
+        <v>201</v>
       </c>
       <c r="D16" s="4"/>
       <c r="E16" s="4" t="s">
-        <v>147</v>
+        <v>142</v>
       </c>
       <c r="F16" s="4"/>
       <c r="G16" s="4"/>
@@ -1675,15 +1663,15 @@
     </row>
     <row r="17" spans="1:8" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A17" s="2" t="s">
-        <v>167</v>
+        <v>162</v>
       </c>
       <c r="B17" s="2" t="s">
-        <v>147</v>
+        <v>142</v>
       </c>
       <c r="C17" s="2"/>
       <c r="D17" s="2"/>
       <c r="E17" s="2" t="s">
-        <v>147</v>
+        <v>142</v>
       </c>
       <c r="F17" s="2"/>
       <c r="G17" s="2"/>
@@ -1691,15 +1679,15 @@
     </row>
     <row r="18" spans="1:8" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A18" s="4" t="s">
-        <v>168</v>
+        <v>163</v>
       </c>
       <c r="B18" s="4" t="s">
-        <v>147</v>
+        <v>142</v>
       </c>
       <c r="C18" s="4"/>
       <c r="D18" s="4"/>
       <c r="E18" s="4" t="s">
-        <v>147</v>
+        <v>142</v>
       </c>
       <c r="F18" s="4"/>
       <c r="G18" s="4"/>
@@ -1707,15 +1695,15 @@
     </row>
     <row r="19" spans="1:8" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A19" s="2" t="s">
-        <v>169</v>
+        <v>164</v>
       </c>
       <c r="B19" s="2" t="s">
-        <v>147</v>
+        <v>142</v>
       </c>
       <c r="C19" s="2"/>
       <c r="D19" s="2"/>
       <c r="E19" s="2" t="s">
-        <v>147</v>
+        <v>142</v>
       </c>
       <c r="F19" s="2"/>
       <c r="G19" s="2"/>
@@ -1723,15 +1711,15 @@
     </row>
     <row r="20" spans="1:8" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A20" s="2" t="s">
-        <v>170</v>
+        <v>165</v>
       </c>
       <c r="B20" s="2" t="s">
-        <v>147</v>
+        <v>142</v>
       </c>
       <c r="C20" s="2"/>
       <c r="D20" s="2"/>
       <c r="E20" s="2" t="s">
-        <v>147</v>
+        <v>142</v>
       </c>
       <c r="F20" s="2"/>
       <c r="G20" s="2"/>
@@ -1739,15 +1727,15 @@
     </row>
     <row r="21" spans="1:8" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A21" s="2" t="s">
-        <v>172</v>
+        <v>167</v>
       </c>
       <c r="B21" s="2" t="s">
-        <v>147</v>
+        <v>142</v>
       </c>
       <c r="C21" s="2"/>
       <c r="D21" s="2"/>
       <c r="E21" s="2" t="s">
-        <v>147</v>
+        <v>142</v>
       </c>
       <c r="F21" s="2"/>
       <c r="G21" s="2"/>
@@ -1755,143 +1743,143 @@
     </row>
     <row r="22" spans="1:8" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A22" s="2" t="s">
-        <v>173</v>
+        <v>168</v>
       </c>
       <c r="B22" s="2" t="s">
-        <v>147</v>
+        <v>142</v>
       </c>
       <c r="C22" s="2"/>
       <c r="D22" s="2"/>
       <c r="E22" s="2" t="s">
-        <v>144</v>
+        <v>139</v>
       </c>
       <c r="F22" s="2"/>
       <c r="G22" s="2"/>
       <c r="H22" s="2"/>
     </row>
     <row r="23" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A23" s="34">
+      <c r="A23" s="31">
         <v>46204</v>
       </c>
       <c r="B23" s="9" t="s">
-        <v>147</v>
+        <v>142</v>
       </c>
       <c r="C23" s="9"/>
       <c r="D23" s="9"/>
       <c r="E23" s="9" t="s">
-        <v>144</v>
+        <v>139</v>
       </c>
       <c r="F23" s="9" t="s">
-        <v>22</v>
+        <v>17</v>
       </c>
       <c r="G23" s="9" t="s">
-        <v>23</v>
+        <v>18</v>
       </c>
       <c r="H23" s="9" t="s">
-        <v>171</v>
+        <v>166</v>
       </c>
     </row>
     <row r="24" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A24" s="35">
+      <c r="A24" s="32">
         <v>46235</v>
       </c>
       <c r="B24" s="2" t="s">
-        <v>147</v>
+        <v>142</v>
       </c>
       <c r="C24" s="2"/>
       <c r="D24" s="2"/>
       <c r="E24" s="2" t="s">
-        <v>147</v>
+        <v>142</v>
       </c>
       <c r="F24" s="2"/>
       <c r="G24" s="2"/>
       <c r="H24" s="2"/>
     </row>
     <row r="25" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A25" s="35">
+      <c r="A25" s="32">
         <v>46266</v>
       </c>
       <c r="B25" s="2" t="s">
-        <v>147</v>
+        <v>142</v>
       </c>
       <c r="C25" s="2"/>
       <c r="D25" s="2"/>
       <c r="E25" s="2" t="s">
-        <v>147</v>
+        <v>142</v>
       </c>
       <c r="F25" s="2"/>
       <c r="G25" s="2"/>
       <c r="H25" s="2"/>
     </row>
     <row r="26" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A26" s="35">
+      <c r="A26" s="32">
         <v>46296</v>
       </c>
       <c r="B26" s="2" t="s">
-        <v>147</v>
+        <v>142</v>
       </c>
       <c r="C26" s="2"/>
       <c r="D26" s="2"/>
       <c r="E26" s="2" t="s">
-        <v>147</v>
+        <v>142</v>
       </c>
       <c r="F26" s="2"/>
       <c r="G26" s="2"/>
       <c r="H26" s="2"/>
     </row>
     <row r="27" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A27" s="35">
+      <c r="A27" s="32">
         <v>46327</v>
       </c>
       <c r="B27" s="2" t="s">
-        <v>147</v>
+        <v>142</v>
       </c>
       <c r="E27" s="2" t="s">
-        <v>147</v>
+        <v>142</v>
       </c>
     </row>
     <row r="28" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A28" s="35">
+      <c r="A28" s="32">
         <v>46357</v>
       </c>
       <c r="B28" s="2" t="s">
-        <v>147</v>
+        <v>142</v>
       </c>
       <c r="E28" s="2" t="s">
-        <v>147</v>
+        <v>142</v>
       </c>
     </row>
     <row r="29" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A29" s="35">
+      <c r="A29" s="32">
         <v>46388</v>
       </c>
       <c r="B29" s="2" t="s">
-        <v>147</v>
+        <v>142</v>
       </c>
       <c r="E29" s="2" t="s">
-        <v>147</v>
+        <v>142</v>
       </c>
     </row>
     <row r="30" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A30" s="35">
+      <c r="A30" s="32">
         <v>46419</v>
       </c>
       <c r="B30" s="10" t="s">
-        <v>147</v>
+        <v>142</v>
       </c>
       <c r="C30" s="10"/>
       <c r="D30" s="10"/>
       <c r="E30" s="10" t="s">
-        <v>144</v>
+        <v>139</v>
       </c>
       <c r="F30" s="10" t="s">
-        <v>174</v>
-      </c>
-      <c r="G30" s="36">
+        <v>169</v>
+      </c>
+      <c r="G30" s="33">
         <v>46435</v>
       </c>
       <c r="H30" s="10" t="s">
-        <v>175</v>
+        <v>170</v>
       </c>
     </row>
   </sheetData>
@@ -1923,35 +1911,35 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:8" ht="21.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A1" s="13" t="s">
-        <v>176</v>
-      </c>
-      <c r="B1" s="13"/>
-      <c r="C1" s="13"/>
-      <c r="D1" s="13"/>
-      <c r="E1" s="13"/>
-      <c r="F1" s="13"/>
-      <c r="G1" s="13"/>
-      <c r="H1" s="13"/>
+      <c r="A1" s="36" t="s">
+        <v>171</v>
+      </c>
+      <c r="B1" s="36"/>
+      <c r="C1" s="36"/>
+      <c r="D1" s="36"/>
+      <c r="E1" s="36"/>
+      <c r="F1" s="36"/>
+      <c r="G1" s="36"/>
+      <c r="H1" s="36"/>
     </row>
     <row r="2" spans="1:8" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A2" s="1" t="s">
+        <v>172</v>
+      </c>
+      <c r="B2" s="1" t="s">
+        <v>173</v>
+      </c>
+      <c r="C2" s="1" t="s">
+        <v>174</v>
+      </c>
+      <c r="D2" s="1" t="s">
+        <v>175</v>
+      </c>
+      <c r="E2" s="1" t="s">
+        <v>176</v>
+      </c>
+      <c r="F2" s="1" t="s">
         <v>177</v>
-      </c>
-      <c r="B2" s="1" t="s">
-        <v>178</v>
-      </c>
-      <c r="C2" s="1" t="s">
-        <v>179</v>
-      </c>
-      <c r="D2" s="1" t="s">
-        <v>180</v>
-      </c>
-      <c r="E2" s="1" t="s">
-        <v>181</v>
-      </c>
-      <c r="F2" s="1" t="s">
-        <v>182</v>
       </c>
     </row>
     <row r="3" spans="1:8" ht="38.25" x14ac:dyDescent="0.25">
@@ -1959,19 +1947,19 @@
         <v>1</v>
       </c>
       <c r="B3" s="2" t="s">
-        <v>212</v>
+        <v>207</v>
       </c>
       <c r="C3" s="2" t="s">
-        <v>209</v>
+        <v>204</v>
       </c>
       <c r="D3" s="2" t="s">
+        <v>203</v>
+      </c>
+      <c r="E3" s="2" t="s">
         <v>208</v>
       </c>
-      <c r="E3" s="2" t="s">
-        <v>213</v>
-      </c>
       <c r="F3" s="11" t="s">
-        <v>207</v>
+        <v>202</v>
       </c>
     </row>
     <row r="4" spans="1:8" ht="25.5" x14ac:dyDescent="0.25">
@@ -1979,19 +1967,19 @@
         <v>2</v>
       </c>
       <c r="B4" s="4" t="s">
-        <v>214</v>
+        <v>209</v>
       </c>
       <c r="C4" s="4" t="s">
-        <v>211</v>
+        <v>206</v>
       </c>
       <c r="D4" s="4" t="s">
+        <v>205</v>
+      </c>
+      <c r="E4" s="4" t="s">
         <v>210</v>
       </c>
-      <c r="E4" s="4" t="s">
-        <v>215</v>
-      </c>
       <c r="F4" s="11" t="s">
-        <v>207</v>
+        <v>202</v>
       </c>
     </row>
     <row r="5" spans="1:8" ht="38.25" x14ac:dyDescent="0.25">
@@ -1999,19 +1987,19 @@
         <v>3</v>
       </c>
       <c r="B5" s="2" t="s">
-        <v>216</v>
+        <v>211</v>
       </c>
       <c r="C5" s="2" t="s">
-        <v>211</v>
+        <v>206</v>
       </c>
       <c r="D5" s="2" t="s">
-        <v>210</v>
+        <v>205</v>
       </c>
       <c r="E5" s="2" t="s">
-        <v>219</v>
+        <v>214</v>
       </c>
       <c r="F5" s="11" t="s">
-        <v>207</v>
+        <v>202</v>
       </c>
     </row>
     <row r="6" spans="1:8" ht="38.25" x14ac:dyDescent="0.25">
@@ -2019,19 +2007,19 @@
         <v>4</v>
       </c>
       <c r="B6" s="2" t="s">
-        <v>217</v>
+        <v>212</v>
       </c>
       <c r="C6" s="2" t="s">
-        <v>211</v>
+        <v>206</v>
       </c>
       <c r="D6" s="2" t="s">
-        <v>210</v>
+        <v>205</v>
       </c>
       <c r="E6" s="2" t="s">
-        <v>218</v>
+        <v>213</v>
       </c>
       <c r="F6" s="11" t="s">
-        <v>207</v>
+        <v>202</v>
       </c>
     </row>
   </sheetData>
@@ -2062,41 +2050,41 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:21" ht="21.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A1" s="13" t="s">
-        <v>183</v>
-      </c>
-      <c r="B1" s="13"/>
-      <c r="C1" s="13"/>
-      <c r="D1" s="13"/>
-      <c r="E1" s="13"/>
-      <c r="F1" s="13"/>
-      <c r="G1" s="13"/>
-      <c r="H1" s="13"/>
+      <c r="A1" s="36" t="s">
+        <v>178</v>
+      </c>
+      <c r="B1" s="36"/>
+      <c r="C1" s="36"/>
+      <c r="D1" s="36"/>
+      <c r="E1" s="36"/>
+      <c r="F1" s="36"/>
+      <c r="G1" s="36"/>
+      <c r="H1" s="36"/>
     </row>
     <row r="2" spans="1:21" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A2" s="1" t="s">
-        <v>177</v>
+        <v>172</v>
       </c>
       <c r="B2" s="1" t="s">
-        <v>118</v>
+        <v>113</v>
       </c>
       <c r="C2" s="1" t="s">
+        <v>179</v>
+      </c>
+      <c r="D2" s="1" t="s">
+        <v>180</v>
+      </c>
+      <c r="E2" s="1" t="s">
+        <v>181</v>
+      </c>
+      <c r="F2" s="1" t="s">
+        <v>182</v>
+      </c>
+      <c r="G2" s="1" t="s">
+        <v>183</v>
+      </c>
+      <c r="H2" s="1" t="s">
         <v>184</v>
-      </c>
-      <c r="D2" s="1" t="s">
-        <v>185</v>
-      </c>
-      <c r="E2" s="1" t="s">
-        <v>186</v>
-      </c>
-      <c r="F2" s="1" t="s">
-        <v>187</v>
-      </c>
-      <c r="G2" s="1" t="s">
-        <v>188</v>
-      </c>
-      <c r="H2" s="1" t="s">
-        <v>189</v>
       </c>
     </row>
     <row r="3" spans="1:21" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
@@ -2104,13 +2092,13 @@
         <v>1</v>
       </c>
       <c r="B3" s="2" t="s">
-        <v>221</v>
+        <v>216</v>
       </c>
       <c r="C3" s="2" t="s">
-        <v>222</v>
+        <v>217</v>
       </c>
       <c r="D3" s="2" t="s">
-        <v>190</v>
+        <v>185</v>
       </c>
       <c r="E3" s="2">
         <v>1</v>
@@ -2122,7 +2110,7 @@
         <v>1</v>
       </c>
       <c r="H3" s="12" t="s">
-        <v>191</v>
+        <v>186</v>
       </c>
     </row>
     <row r="4" spans="1:21" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
@@ -2130,13 +2118,13 @@
         <v>2</v>
       </c>
       <c r="B4" s="4" t="s">
-        <v>223</v>
+        <v>218</v>
       </c>
       <c r="C4" s="4" t="s">
-        <v>224</v>
+        <v>219</v>
       </c>
       <c r="D4" s="4" t="s">
-        <v>190</v>
+        <v>185</v>
       </c>
       <c r="E4" s="4">
         <v>1</v>
@@ -2148,7 +2136,7 @@
         <v>1</v>
       </c>
       <c r="H4" s="12" t="s">
-        <v>191</v>
+        <v>186</v>
       </c>
     </row>
     <row r="5" spans="1:21" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
@@ -2156,13 +2144,13 @@
         <v>3</v>
       </c>
       <c r="B5" s="2" t="s">
-        <v>225</v>
+        <v>220</v>
       </c>
       <c r="C5" s="2" t="s">
-        <v>224</v>
+        <v>219</v>
       </c>
       <c r="D5" s="2" t="s">
-        <v>190</v>
+        <v>185</v>
       </c>
       <c r="E5" s="2">
         <v>1</v>
@@ -2174,7 +2162,7 @@
         <v>1</v>
       </c>
       <c r="H5" s="12" t="s">
-        <v>191</v>
+        <v>186</v>
       </c>
     </row>
     <row r="6" spans="1:21" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
@@ -2182,13 +2170,13 @@
         <v>4</v>
       </c>
       <c r="B6" s="4" t="s">
-        <v>226</v>
+        <v>221</v>
       </c>
       <c r="C6" s="4" t="s">
-        <v>227</v>
+        <v>222</v>
       </c>
       <c r="D6" s="4" t="s">
-        <v>190</v>
+        <v>185</v>
       </c>
       <c r="E6" s="4">
         <v>1</v>
@@ -2200,7 +2188,7 @@
         <v>1</v>
       </c>
       <c r="H6" s="12" t="s">
-        <v>191</v>
+        <v>186</v>
       </c>
     </row>
     <row r="7" spans="1:21" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
@@ -2208,13 +2196,13 @@
         <v>5</v>
       </c>
       <c r="B7" s="2" t="s">
-        <v>228</v>
+        <v>223</v>
       </c>
       <c r="C7" s="2" t="s">
-        <v>229</v>
+        <v>224</v>
       </c>
       <c r="D7" s="2" t="s">
-        <v>190</v>
+        <v>185</v>
       </c>
       <c r="E7" s="2">
         <v>1</v>
@@ -2226,7 +2214,7 @@
         <v>0.9</v>
       </c>
       <c r="H7" s="11" t="s">
-        <v>230</v>
+        <v>225</v>
       </c>
     </row>
     <row r="8" spans="1:21" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
@@ -2234,13 +2222,13 @@
         <v>6</v>
       </c>
       <c r="B8" s="4" t="s">
-        <v>220</v>
+        <v>215</v>
       </c>
       <c r="C8" s="4" t="s">
-        <v>229</v>
+        <v>224</v>
       </c>
       <c r="D8" s="4" t="s">
-        <v>190</v>
+        <v>185</v>
       </c>
       <c r="E8" s="4">
         <v>1</v>
@@ -2252,7 +2240,7 @@
         <v>0</v>
       </c>
       <c r="H8" s="11" t="s">
-        <v>230</v>
+        <v>225</v>
       </c>
     </row>
     <row r="9" spans="1:21" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
@@ -2260,16 +2248,16 @@
         <v>7</v>
       </c>
       <c r="B9" s="2" t="s">
-        <v>231</v>
+        <v>226</v>
       </c>
       <c r="C9" s="2" t="s">
-        <v>224</v>
+        <v>219</v>
       </c>
       <c r="D9" s="2" t="s">
-        <v>190</v>
+        <v>185</v>
       </c>
       <c r="E9" s="2" t="s">
-        <v>232</v>
+        <v>227</v>
       </c>
       <c r="F9" s="2">
         <v>0</v>
@@ -2278,7 +2266,7 @@
         <v>0</v>
       </c>
       <c r="H9" s="11" t="s">
-        <v>230</v>
+        <v>225</v>
       </c>
     </row>
     <row r="10" spans="1:21" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
@@ -2286,85 +2274,85 @@
         <v>8</v>
       </c>
       <c r="B10" s="4" t="s">
-        <v>233</v>
+        <v>228</v>
       </c>
       <c r="C10" s="4" t="s">
-        <v>234</v>
+        <v>229</v>
       </c>
       <c r="D10" s="4" t="s">
-        <v>190</v>
+        <v>185</v>
       </c>
       <c r="E10" s="4">
         <v>1</v>
       </c>
       <c r="F10" s="4" t="s">
-        <v>235</v>
+        <v>230</v>
       </c>
       <c r="G10" s="4">
         <v>0.15</v>
       </c>
       <c r="H10" s="11" t="s">
-        <v>230</v>
+        <v>225</v>
       </c>
     </row>
     <row r="11" spans="1:21" x14ac:dyDescent="0.25">
-      <c r="S11" s="38"/>
-      <c r="T11" s="38"/>
-      <c r="U11" s="38"/>
+      <c r="S11" s="35"/>
+      <c r="T11" s="35"/>
+      <c r="U11" s="35"/>
     </row>
     <row r="12" spans="1:21" x14ac:dyDescent="0.25">
-      <c r="S12" s="38"/>
-      <c r="T12" s="38"/>
-      <c r="U12" s="38"/>
+      <c r="S12" s="35"/>
+      <c r="T12" s="35"/>
+      <c r="U12" s="35"/>
     </row>
     <row r="13" spans="1:21" x14ac:dyDescent="0.25">
-      <c r="S13" s="38"/>
-      <c r="T13" s="38"/>
-      <c r="U13" s="38"/>
+      <c r="S13" s="35"/>
+      <c r="T13" s="35"/>
+      <c r="U13" s="35"/>
     </row>
     <row r="14" spans="1:21" x14ac:dyDescent="0.25">
-      <c r="S14" s="38"/>
-      <c r="T14" s="38"/>
-      <c r="U14" s="38"/>
+      <c r="S14" s="35"/>
+      <c r="T14" s="35"/>
+      <c r="U14" s="35"/>
     </row>
     <row r="15" spans="1:21" x14ac:dyDescent="0.25">
-      <c r="S15" s="38"/>
-      <c r="T15" s="38"/>
-      <c r="U15" s="38"/>
+      <c r="S15" s="35"/>
+      <c r="T15" s="35"/>
+      <c r="U15" s="35"/>
     </row>
     <row r="16" spans="1:21" x14ac:dyDescent="0.25">
-      <c r="S16" s="38"/>
-      <c r="T16" s="38"/>
-      <c r="U16" s="38"/>
+      <c r="S16" s="35"/>
+      <c r="T16" s="35"/>
+      <c r="U16" s="35"/>
     </row>
     <row r="17" spans="19:21" x14ac:dyDescent="0.25">
-      <c r="T17" s="38"/>
-      <c r="U17" s="38"/>
+      <c r="T17" s="35"/>
+      <c r="U17" s="35"/>
     </row>
     <row r="18" spans="19:21" x14ac:dyDescent="0.25">
-      <c r="S18" s="38"/>
-      <c r="U18" s="38"/>
+      <c r="S18" s="35"/>
+      <c r="U18" s="35"/>
     </row>
     <row r="19" spans="19:21" x14ac:dyDescent="0.25">
-      <c r="S19" s="37"/>
+      <c r="S19" s="34"/>
     </row>
     <row r="20" spans="19:21" x14ac:dyDescent="0.25">
-      <c r="S20" s="37"/>
+      <c r="S20" s="34"/>
     </row>
     <row r="21" spans="19:21" x14ac:dyDescent="0.25">
-      <c r="S21" s="37"/>
+      <c r="S21" s="34"/>
     </row>
     <row r="22" spans="19:21" x14ac:dyDescent="0.25">
-      <c r="S22" s="37"/>
+      <c r="S22" s="34"/>
     </row>
     <row r="23" spans="19:21" x14ac:dyDescent="0.25">
-      <c r="S23" s="37"/>
+      <c r="S23" s="34"/>
     </row>
     <row r="24" spans="19:21" x14ac:dyDescent="0.25">
-      <c r="S24" s="37"/>
+      <c r="S24" s="34"/>
     </row>
     <row r="25" spans="19:21" x14ac:dyDescent="0.25">
-      <c r="S25" s="37"/>
+      <c r="S25" s="34"/>
     </row>
   </sheetData>
   <mergeCells count="1">
@@ -2391,16 +2379,16 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:8" ht="21.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A1" s="13" t="s">
-        <v>192</v>
-      </c>
-      <c r="B1" s="13"/>
-      <c r="C1" s="13"/>
-      <c r="D1" s="13"/>
-      <c r="E1" s="13"/>
-      <c r="F1" s="13"/>
-      <c r="G1" s="13"/>
-      <c r="H1" s="13"/>
+      <c r="A1" s="36" t="s">
+        <v>187</v>
+      </c>
+      <c r="B1" s="36"/>
+      <c r="C1" s="36"/>
+      <c r="D1" s="36"/>
+      <c r="E1" s="36"/>
+      <c r="F1" s="36"/>
+      <c r="G1" s="36"/>
+      <c r="H1" s="36"/>
     </row>
     <row r="2" spans="1:8" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A2" s="1" t="s">
@@ -2412,34 +2400,34 @@
     </row>
     <row r="3" spans="1:8" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A3" s="2" t="s">
-        <v>193</v>
+        <v>188</v>
       </c>
       <c r="B3" s="3" t="s">
-        <v>194</v>
+        <v>189</v>
       </c>
     </row>
     <row r="4" spans="1:8" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A4" s="4" t="s">
-        <v>195</v>
-      </c>
-      <c r="B4" s="15">
+        <v>190</v>
+      </c>
+      <c r="B4" s="13">
         <v>46176</v>
       </c>
     </row>
     <row r="5" spans="1:8" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A5" s="2" t="s">
-        <v>196</v>
+        <v>191</v>
       </c>
       <c r="B5" s="3" t="s">
-        <v>236</v>
+        <v>231</v>
       </c>
     </row>
     <row r="6" spans="1:8" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A6" s="4" t="s">
-        <v>197</v>
+        <v>192</v>
       </c>
       <c r="B6" s="3" t="s">
-        <v>198</v>
+        <v>193</v>
       </c>
     </row>
   </sheetData>
@@ -2468,16 +2456,16 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:8" ht="21.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A1" s="13" t="s">
+      <c r="A1" s="36" t="s">
         <v>9</v>
       </c>
-      <c r="B1" s="13"/>
-      <c r="C1" s="13"/>
-      <c r="D1" s="13"/>
-      <c r="E1" s="13"/>
-      <c r="F1" s="13"/>
-      <c r="G1" s="13"/>
-      <c r="H1" s="13"/>
+      <c r="B1" s="36"/>
+      <c r="C1" s="36"/>
+      <c r="D1" s="36"/>
+      <c r="E1" s="36"/>
+      <c r="F1" s="36"/>
+      <c r="G1" s="36"/>
+      <c r="H1" s="36"/>
     </row>
     <row r="2" spans="1:8" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A2" s="1" t="s">
@@ -2494,73 +2482,74 @@
       <c r="A3" s="2" t="s">
         <v>12</v>
       </c>
-      <c r="B3" s="19" t="s">
-        <v>13</v>
+      <c r="B3" s="17">
+        <v>45497</v>
       </c>
       <c r="C3" s="2"/>
     </row>
     <row r="4" spans="1:8" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A4" s="4" t="s">
-        <v>14</v>
-      </c>
-      <c r="B4" s="19" t="s">
-        <v>15</v>
+        <v>13</v>
+      </c>
+      <c r="B4" s="17">
+        <v>45530</v>
       </c>
       <c r="C4" s="4"/>
     </row>
     <row r="5" spans="1:8" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A5" s="2" t="s">
-        <v>16</v>
-      </c>
-      <c r="B5" s="19" t="s">
-        <v>17</v>
+        <v>14</v>
+      </c>
+      <c r="B5" s="17">
+        <v>45571</v>
       </c>
       <c r="C5" s="2"/>
     </row>
     <row r="6" spans="1:8" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A6" s="4" t="s">
-        <v>18</v>
-      </c>
-      <c r="B6" s="19" t="s">
-        <v>19</v>
+        <v>15</v>
+      </c>
+      <c r="B6" s="17">
+        <v>45718</v>
       </c>
       <c r="C6" s="4"/>
     </row>
     <row r="7" spans="1:8" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A7" s="2" t="s">
-        <v>20</v>
-      </c>
-      <c r="B7" s="19" t="s">
-        <v>21</v>
+        <v>16</v>
+      </c>
+      <c r="B7" s="17">
+        <v>45830</v>
       </c>
       <c r="C7" s="2"/>
     </row>
     <row r="8" spans="1:8" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A8" s="4" t="s">
-        <v>22</v>
-      </c>
-      <c r="B8" s="19" t="s">
-        <v>23</v>
+        <v>17</v>
+      </c>
+      <c r="B8" s="17">
+        <v>46227</v>
       </c>
       <c r="C8" s="4" t="s">
-        <v>24</v>
+        <v>19</v>
       </c>
     </row>
     <row r="9" spans="1:8" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A9" s="2" t="s">
-        <v>25</v>
-      </c>
-      <c r="B9" s="19">
+        <v>20</v>
+      </c>
+      <c r="B9" s="17">
         <v>46435</v>
       </c>
       <c r="C9" s="2" t="s">
-        <v>26</v>
+        <v>21</v>
       </c>
     </row>
   </sheetData>
   <mergeCells count="1">
     <mergeCell ref="A1:H1"/>
   </mergeCells>
+  <phoneticPr fontId="7" type="noConversion"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.511811023622047" footer="0.511811023622047"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300"/>
   <headerFooter>
@@ -2584,26 +2573,26 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:8" ht="21.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A1" s="13" t="s">
-        <v>27</v>
-      </c>
-      <c r="B1" s="13"/>
-      <c r="C1" s="13"/>
-      <c r="D1" s="13"/>
-      <c r="E1" s="13"/>
-      <c r="F1" s="13"/>
-      <c r="G1" s="13"/>
-      <c r="H1" s="13"/>
+      <c r="A1" s="36" t="s">
+        <v>22</v>
+      </c>
+      <c r="B1" s="36"/>
+      <c r="C1" s="36"/>
+      <c r="D1" s="36"/>
+      <c r="E1" s="36"/>
+      <c r="F1" s="36"/>
+      <c r="G1" s="36"/>
+      <c r="H1" s="36"/>
     </row>
     <row r="2" spans="1:8" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A2" s="1" t="s">
         <v>1</v>
       </c>
       <c r="B2" s="1" t="s">
-        <v>28</v>
+        <v>23</v>
       </c>
       <c r="C2" s="1" t="s">
-        <v>29</v>
+        <v>24</v>
       </c>
       <c r="D2" s="1" t="s">
         <v>11</v>
@@ -2611,9 +2600,9 @@
     </row>
     <row r="3" spans="1:8" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A3" s="2" t="s">
-        <v>30</v>
-      </c>
-      <c r="B3" s="18">
+        <v>25</v>
+      </c>
+      <c r="B3" s="16">
         <v>388016486</v>
       </c>
       <c r="C3" s="2"/>
@@ -2621,9 +2610,9 @@
     </row>
     <row r="4" spans="1:8" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A4" s="4" t="s">
-        <v>31</v>
-      </c>
-      <c r="B4" s="18">
+        <v>26</v>
+      </c>
+      <c r="B4" s="16">
         <v>0</v>
       </c>
       <c r="C4" s="4"/>
@@ -2631,9 +2620,9 @@
     </row>
     <row r="5" spans="1:8" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A5" s="2" t="s">
-        <v>32</v>
-      </c>
-      <c r="B5" s="18">
+        <v>27</v>
+      </c>
+      <c r="B5" s="16">
         <v>0</v>
       </c>
       <c r="C5" s="2"/>
@@ -2641,9 +2630,9 @@
     </row>
     <row r="6" spans="1:8" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A6" s="4" t="s">
-        <v>33</v>
-      </c>
-      <c r="B6" s="18">
+        <v>28</v>
+      </c>
+      <c r="B6" s="16">
         <v>0</v>
       </c>
       <c r="C6" s="4"/>
@@ -2651,21 +2640,21 @@
     </row>
     <row r="7" spans="1:8" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A7" s="2" t="s">
-        <v>34</v>
-      </c>
-      <c r="B7" s="18">
+        <v>29</v>
+      </c>
+      <c r="B7" s="16">
         <v>388016486</v>
       </c>
       <c r="C7" s="2"/>
       <c r="D7" s="2" t="s">
-        <v>35</v>
+        <v>30</v>
       </c>
     </row>
     <row r="8" spans="1:8" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A8" s="4" t="s">
-        <v>36</v>
-      </c>
-      <c r="B8" s="18">
+        <v>31</v>
+      </c>
+      <c r="B8" s="16">
         <v>34426811</v>
       </c>
       <c r="C8" s="4"/>
@@ -2673,17 +2662,17 @@
     </row>
     <row r="9" spans="1:8" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A9" s="2" t="s">
-        <v>37</v>
-      </c>
-      <c r="B9" s="18">
+        <v>32</v>
+      </c>
+      <c r="B9" s="16">
         <v>15596872</v>
       </c>
-      <c r="C9" s="16">
+      <c r="C9" s="14">
         <f>B9/B8</f>
         <v>0.45304434384003794</v>
       </c>
       <c r="D9" s="2" t="s">
-        <v>38</v>
+        <v>33</v>
       </c>
     </row>
   </sheetData>
@@ -2708,21 +2697,21 @@
   <cols>
     <col min="1" max="1" width="32" customWidth="1"/>
     <col min="2" max="2" width="22" customWidth="1"/>
-    <col min="3" max="3" width="14" style="26" customWidth="1"/>
+    <col min="3" max="3" width="14" style="24" customWidth="1"/>
     <col min="4" max="4" width="40" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:8" ht="21.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A1" s="13" t="s">
-        <v>39</v>
-      </c>
-      <c r="B1" s="13"/>
-      <c r="C1" s="13"/>
-      <c r="D1" s="13"/>
-      <c r="E1" s="13"/>
-      <c r="F1" s="13"/>
-      <c r="G1" s="13"/>
-      <c r="H1" s="13"/>
+      <c r="A1" s="36" t="s">
+        <v>34</v>
+      </c>
+      <c r="B1" s="36"/>
+      <c r="C1" s="36"/>
+      <c r="D1" s="36"/>
+      <c r="E1" s="36"/>
+      <c r="F1" s="36"/>
+      <c r="G1" s="36"/>
+      <c r="H1" s="36"/>
     </row>
     <row r="2" spans="1:8" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A2" s="1" t="s">
@@ -2732,7 +2721,7 @@
         <v>2</v>
       </c>
       <c r="C2" s="1" t="s">
-        <v>29</v>
+        <v>24</v>
       </c>
       <c r="D2" s="1" t="s">
         <v>11</v>
@@ -2740,100 +2729,100 @@
     </row>
     <row r="3" spans="1:8" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A3" s="2" t="s">
-        <v>40</v>
-      </c>
-      <c r="B3" s="21">
+        <v>35</v>
+      </c>
+      <c r="B3" s="19">
         <v>355587125</v>
       </c>
-      <c r="C3" s="23"/>
+      <c r="C3" s="21"/>
       <c r="D3" s="2" t="s">
-        <v>41</v>
+        <v>36</v>
       </c>
     </row>
     <row r="4" spans="1:8" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A4" s="4" t="s">
-        <v>42</v>
-      </c>
-      <c r="B4" s="22" t="s">
-        <v>43</v>
-      </c>
-      <c r="C4" s="24"/>
+        <v>37</v>
+      </c>
+      <c r="B4" s="20" t="s">
+        <v>38</v>
+      </c>
+      <c r="C4" s="22"/>
       <c r="D4" s="4" t="s">
-        <v>44</v>
+        <v>39</v>
       </c>
     </row>
     <row r="5" spans="1:8" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A5" s="4" t="s">
-        <v>203</v>
-      </c>
-      <c r="B5" s="22">
+        <v>198</v>
+      </c>
+      <c r="B5" s="20">
         <v>0.68799999999999994</v>
       </c>
-      <c r="C5" s="24"/>
+      <c r="C5" s="22"/>
       <c r="D5" s="4"/>
     </row>
     <row r="6" spans="1:8" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A6" s="2" t="s">
-        <v>45</v>
-      </c>
-      <c r="B6" s="28">
+        <v>40</v>
+      </c>
+      <c r="B6" s="20">
         <v>0.40899999999999997</v>
       </c>
-      <c r="C6" s="25">
+      <c r="C6" s="23">
         <f>B4-B6</f>
         <v>0.59099999999999997</v>
       </c>
       <c r="D6" s="2" t="s">
-        <v>46</v>
+        <v>41</v>
       </c>
     </row>
     <row r="7" spans="1:8" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A7" s="4" t="s">
+        <v>31</v>
+      </c>
+      <c r="B7" s="19">
+        <v>34426811</v>
+      </c>
+      <c r="C7" s="22"/>
+      <c r="D7" s="4" t="s">
         <v>36</v>
-      </c>
-      <c r="B7" s="21">
-        <v>34426811</v>
-      </c>
-      <c r="C7" s="24"/>
-      <c r="D7" s="4" t="s">
-        <v>41</v>
       </c>
     </row>
     <row r="8" spans="1:8" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A8" s="2" t="s">
-        <v>37</v>
-      </c>
-      <c r="B8" s="21">
+        <v>32</v>
+      </c>
+      <c r="B8" s="19">
         <v>15596872</v>
       </c>
-      <c r="C8" s="23"/>
+      <c r="C8" s="21"/>
       <c r="D8" s="2" t="s">
-        <v>41</v>
+        <v>36</v>
       </c>
     </row>
     <row r="9" spans="1:8" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A9" s="4" t="s">
-        <v>47</v>
-      </c>
-      <c r="B9" s="22">
+        <v>42</v>
+      </c>
+      <c r="B9" s="20">
         <f>(B7-B8)/B7</f>
         <v>0.54695565615996211</v>
       </c>
-      <c r="C9" s="24"/>
+      <c r="C9" s="22"/>
       <c r="D9" s="4" t="s">
-        <v>48</v>
+        <v>43</v>
       </c>
     </row>
     <row r="10" spans="1:8" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A10" s="2" t="s">
-        <v>49</v>
-      </c>
-      <c r="B10" s="20" t="s">
-        <v>201</v>
-      </c>
-      <c r="C10" s="23"/>
+        <v>44</v>
+      </c>
+      <c r="B10" s="18" t="s">
+        <v>196</v>
+      </c>
+      <c r="C10" s="21"/>
       <c r="D10" s="2" t="s">
-        <v>50</v>
+        <v>45</v>
       </c>
     </row>
   </sheetData>
@@ -2864,29 +2853,29 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:8" ht="21.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A1" s="13" t="s">
-        <v>51</v>
-      </c>
-      <c r="B1" s="13"/>
-      <c r="C1" s="13"/>
-      <c r="D1" s="13"/>
-      <c r="E1" s="13"/>
-      <c r="F1" s="13"/>
-      <c r="G1" s="13"/>
-      <c r="H1" s="13"/>
+      <c r="A1" s="36" t="s">
+        <v>46</v>
+      </c>
+      <c r="B1" s="36"/>
+      <c r="C1" s="36"/>
+      <c r="D1" s="36"/>
+      <c r="E1" s="36"/>
+      <c r="F1" s="36"/>
+      <c r="G1" s="36"/>
+      <c r="H1" s="36"/>
     </row>
     <row r="2" spans="1:8" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A2" s="1" t="s">
         <v>1</v>
       </c>
       <c r="B2" s="1" t="s">
-        <v>28</v>
+        <v>23</v>
       </c>
       <c r="C2" s="1" t="s">
-        <v>52</v>
+        <v>47</v>
       </c>
       <c r="D2" s="1" t="s">
-        <v>53</v>
+        <v>48</v>
       </c>
       <c r="E2" s="1" t="s">
         <v>11</v>
@@ -2894,96 +2883,96 @@
     </row>
     <row r="3" spans="1:8" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A3" s="2" t="s">
-        <v>54</v>
-      </c>
-      <c r="B3" s="17">
+        <v>49</v>
+      </c>
+      <c r="B3" s="15">
         <v>204059236</v>
       </c>
-      <c r="C3" s="16">
+      <c r="C3" s="14">
         <f>B3/Commercial_Info!$B$3</f>
         <v>0.52590352050144595</v>
       </c>
       <c r="D3" s="2" t="s">
-        <v>55</v>
+        <v>50</v>
       </c>
       <c r="E3" s="2"/>
-      <c r="G3" s="27"/>
+      <c r="G3" s="25"/>
     </row>
     <row r="4" spans="1:8" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A4" s="4" t="s">
-        <v>56</v>
-      </c>
-      <c r="B4" s="17">
+        <v>51</v>
+      </c>
+      <c r="B4" s="15">
         <v>152961744</v>
       </c>
-      <c r="C4" s="16">
+      <c r="C4" s="14">
         <f>B4/Commercial_Info!$B$3</f>
         <v>0.39421454891481078</v>
       </c>
       <c r="D4" s="4" t="s">
-        <v>57</v>
+        <v>52</v>
       </c>
       <c r="E4" s="4"/>
     </row>
     <row r="5" spans="1:8" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A5" s="2" t="s">
-        <v>58</v>
-      </c>
-      <c r="B5" s="17">
+        <v>53</v>
+      </c>
+      <c r="B5" s="15">
         <v>152961744</v>
       </c>
-      <c r="C5" s="16">
+      <c r="C5" s="14">
         <f>B5/Commercial_Info!$B$3</f>
         <v>0.39421454891481078</v>
       </c>
       <c r="D5" s="2" t="s">
-        <v>57</v>
+        <v>52</v>
       </c>
       <c r="E5" s="2"/>
     </row>
     <row r="6" spans="1:8" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A6" s="4" t="s">
-        <v>59</v>
-      </c>
-      <c r="B6" s="17">
+        <v>54</v>
+      </c>
+      <c r="B6" s="15">
         <v>0</v>
       </c>
       <c r="C6" s="4"/>
       <c r="D6" s="4" t="s">
-        <v>60</v>
+        <v>55</v>
       </c>
       <c r="E6" s="4"/>
     </row>
     <row r="7" spans="1:8" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A7" s="2" t="s">
-        <v>61</v>
-      </c>
-      <c r="B7" s="17">
+        <v>56</v>
+      </c>
+      <c r="B7" s="15">
         <v>68039022</v>
       </c>
-      <c r="C7" s="16">
+      <c r="C7" s="14">
         <f>B7/Commercial_Info!$B$3</f>
         <v>0.17535085352017749</v>
       </c>
       <c r="D7" s="2" t="s">
-        <v>57</v>
+        <v>52</v>
       </c>
       <c r="E7" s="2"/>
     </row>
     <row r="8" spans="1:8" ht="28.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A8" s="4" t="s">
-        <v>202</v>
-      </c>
-      <c r="B8" s="30" t="str">
+        <v>197</v>
+      </c>
+      <c r="B8" s="27" t="str">
         <f>ROUNDUP(C4*100,0)&amp;"%"&amp;" / "&amp;ROUNDUP(Budgetary_Info!B6*100,0)&amp;"%"</f>
         <v>40% / 41%</v>
       </c>
       <c r="C8" s="4"/>
       <c r="D8" s="4" t="s">
-        <v>60</v>
+        <v>55</v>
       </c>
       <c r="E8" s="4" t="s">
-        <v>62</v>
+        <v>57</v>
       </c>
     </row>
   </sheetData>
@@ -3013,26 +3002,26 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:8" ht="21.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A1" s="13" t="s">
-        <v>63</v>
-      </c>
-      <c r="B1" s="13"/>
-      <c r="C1" s="13"/>
-      <c r="D1" s="13"/>
-      <c r="E1" s="13"/>
-      <c r="F1" s="13"/>
-      <c r="G1" s="13"/>
-      <c r="H1" s="13"/>
+      <c r="A1" s="36" t="s">
+        <v>58</v>
+      </c>
+      <c r="B1" s="36"/>
+      <c r="C1" s="36"/>
+      <c r="D1" s="36"/>
+      <c r="E1" s="36"/>
+      <c r="F1" s="36"/>
+      <c r="G1" s="36"/>
+      <c r="H1" s="36"/>
     </row>
     <row r="2" spans="1:8" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A2" s="1" t="s">
         <v>1</v>
       </c>
       <c r="B2" s="1" t="s">
-        <v>64</v>
+        <v>59</v>
       </c>
       <c r="C2" s="1" t="s">
-        <v>65</v>
+        <v>60</v>
       </c>
       <c r="D2" s="1" t="s">
         <v>11</v>
@@ -3040,55 +3029,55 @@
     </row>
     <row r="3" spans="1:8" ht="27" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A3" s="2" t="s">
-        <v>66</v>
+        <v>61</v>
       </c>
       <c r="B3" s="3">
         <v>-61.1</v>
       </c>
       <c r="C3" s="2"/>
       <c r="D3" s="2" t="s">
-        <v>67</v>
+        <v>62</v>
       </c>
     </row>
     <row r="4" spans="1:8" ht="27" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A4" s="4" t="s">
-        <v>68</v>
+        <v>63</v>
       </c>
       <c r="B4" s="3" t="s">
-        <v>69</v>
+        <v>64</v>
       </c>
       <c r="C4" s="4"/>
       <c r="D4" s="4" t="s">
-        <v>70</v>
+        <v>65</v>
       </c>
     </row>
     <row r="5" spans="1:8" ht="27" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A5" s="2" t="s">
-        <v>71</v>
+        <v>66</v>
       </c>
       <c r="B5" s="3">
         <v>68</v>
       </c>
-      <c r="C5" s="31">
+      <c r="C5" s="28">
         <f>B5/B6</f>
         <v>0.52631578947368429</v>
       </c>
       <c r="D5" s="2" t="s">
-        <v>72</v>
+        <v>67</v>
       </c>
     </row>
     <row r="6" spans="1:8" ht="27" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A6" s="4" t="s">
-        <v>73</v>
+        <v>68</v>
       </c>
       <c r="B6" s="3">
         <v>129.19999999999999</v>
       </c>
       <c r="C6" s="4" t="s">
-        <v>43</v>
+        <v>38</v>
       </c>
       <c r="D6" s="4" t="s">
-        <v>74</v>
+        <v>69</v>
       </c>
     </row>
   </sheetData>
@@ -3118,24 +3107,24 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:8" ht="21.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A1" s="13" t="s">
-        <v>75</v>
-      </c>
-      <c r="B1" s="13"/>
-      <c r="C1" s="13"/>
-      <c r="D1" s="13"/>
-      <c r="E1" s="13"/>
-      <c r="F1" s="13"/>
-      <c r="G1" s="13"/>
-      <c r="H1" s="13"/>
+      <c r="A1" s="36" t="s">
+        <v>70</v>
+      </c>
+      <c r="B1" s="36"/>
+      <c r="C1" s="36"/>
+      <c r="D1" s="36"/>
+      <c r="E1" s="36"/>
+      <c r="F1" s="36"/>
+      <c r="G1" s="36"/>
+      <c r="H1" s="36"/>
     </row>
     <row r="2" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A2" s="14" t="s">
-        <v>76</v>
-      </c>
-      <c r="B2" s="14"/>
-      <c r="C2" s="14"/>
-      <c r="D2" s="14"/>
+      <c r="A2" s="37" t="s">
+        <v>71</v>
+      </c>
+      <c r="B2" s="37"/>
+      <c r="C2" s="37"/>
+      <c r="D2" s="37"/>
     </row>
     <row r="3" spans="1:8" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A3" s="1" t="s">
@@ -3151,69 +3140,69 @@
     </row>
     <row r="4" spans="1:8" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A4" s="4" t="s">
-        <v>77</v>
+        <v>72</v>
       </c>
       <c r="B4" s="3">
         <f>B5+B6</f>
         <v>751</v>
       </c>
       <c r="C4" s="4" t="s">
-        <v>78</v>
+        <v>73</v>
       </c>
       <c r="D4" s="4"/>
     </row>
     <row r="5" spans="1:8" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A5" s="2" t="s">
-        <v>79</v>
+        <v>74</v>
       </c>
       <c r="B5" s="3">
         <v>654</v>
       </c>
       <c r="C5" s="2" t="s">
-        <v>80</v>
+        <v>75</v>
       </c>
       <c r="D5" s="2"/>
     </row>
     <row r="6" spans="1:8" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A6" s="4" t="s">
-        <v>81</v>
+        <v>76</v>
       </c>
       <c r="B6" s="3">
         <v>97</v>
       </c>
       <c r="C6" s="4" t="s">
-        <v>82</v>
+        <v>77</v>
       </c>
       <c r="D6" s="4"/>
     </row>
     <row r="7" spans="1:8" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A7" s="2" t="s">
-        <v>83</v>
-      </c>
-      <c r="B7" s="29">
+        <v>78</v>
+      </c>
+      <c r="B7" s="26">
         <f>B5/B4</f>
         <v>0.87083888149134492</v>
       </c>
       <c r="C7" s="2" t="s">
-        <v>84</v>
+        <v>79</v>
       </c>
       <c r="D7" s="2"/>
     </row>
     <row r="8" spans="1:8" ht="6" customHeight="1" x14ac:dyDescent="0.25"/>
     <row r="9" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A9" s="14" t="s">
-        <v>85</v>
-      </c>
-      <c r="B9" s="14"/>
-      <c r="C9" s="14"/>
-      <c r="D9" s="14"/>
+      <c r="A9" s="37" t="s">
+        <v>80</v>
+      </c>
+      <c r="B9" s="37"/>
+      <c r="C9" s="37"/>
+      <c r="D9" s="37"/>
     </row>
     <row r="10" spans="1:8" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A10" s="1" t="s">
-        <v>86</v>
+        <v>81</v>
       </c>
       <c r="B10" s="1" t="s">
-        <v>87</v>
+        <v>82</v>
       </c>
       <c r="C10" s="1" t="s">
         <v>11</v>
@@ -3222,124 +3211,124 @@
     </row>
     <row r="11" spans="1:8" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A11" s="2" t="s">
-        <v>88</v>
+        <v>83</v>
       </c>
       <c r="B11" s="3">
         <v>386</v>
       </c>
       <c r="C11" s="2" t="s">
-        <v>89</v>
+        <v>84</v>
       </c>
       <c r="D11" s="2"/>
     </row>
     <row r="12" spans="1:8" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A12" s="4" t="s">
-        <v>90</v>
+        <v>85</v>
       </c>
       <c r="B12" s="3">
         <v>268</v>
       </c>
       <c r="C12" s="4" t="s">
-        <v>89</v>
+        <v>84</v>
       </c>
       <c r="D12" s="4"/>
     </row>
     <row r="13" spans="1:8" ht="6" customHeight="1" x14ac:dyDescent="0.25"/>
     <row r="14" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A14" s="14" t="s">
-        <v>91</v>
-      </c>
-      <c r="B14" s="14"/>
-      <c r="C14" s="14"/>
-      <c r="D14" s="14"/>
+      <c r="A14" s="37" t="s">
+        <v>86</v>
+      </c>
+      <c r="B14" s="37"/>
+      <c r="C14" s="37"/>
+      <c r="D14" s="37"/>
     </row>
     <row r="15" spans="1:8" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A15" s="1" t="s">
-        <v>92</v>
+        <v>87</v>
       </c>
       <c r="B15" s="1" t="s">
         <v>2</v>
       </c>
       <c r="C15" s="1" t="s">
-        <v>93</v>
+        <v>88</v>
       </c>
       <c r="D15" s="1"/>
     </row>
     <row r="16" spans="1:8" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A16" s="4" t="s">
-        <v>94</v>
+        <v>89</v>
       </c>
       <c r="B16" s="3">
         <f>B4/B5*100</f>
         <v>114.83180428134557</v>
       </c>
       <c r="C16" s="4" t="s">
-        <v>95</v>
+        <v>90</v>
       </c>
       <c r="D16" s="4"/>
     </row>
     <row r="17" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A17" s="2" t="s">
-        <v>96</v>
+        <v>91</v>
       </c>
       <c r="B17" s="3">
         <f>B6/B5*100</f>
         <v>14.831804281345565</v>
       </c>
       <c r="C17" s="2" t="s">
-        <v>97</v>
+        <v>92</v>
       </c>
       <c r="D17" s="2"/>
     </row>
     <row r="18" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A18" s="4" t="s">
-        <v>98</v>
+        <v>93</v>
       </c>
       <c r="B18" s="3">
         <f>B16</f>
         <v>114.83180428134557</v>
       </c>
       <c r="C18" s="4" t="s">
-        <v>99</v>
+        <v>94</v>
       </c>
       <c r="D18" s="4"/>
     </row>
     <row r="19" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A19" s="2" t="s">
-        <v>100</v>
+        <v>95</v>
       </c>
       <c r="B19" s="3">
         <f>100-B16</f>
         <v>-14.831804281345569</v>
       </c>
       <c r="C19" s="2" t="s">
-        <v>101</v>
+        <v>96</v>
       </c>
       <c r="D19" s="2"/>
     </row>
     <row r="20" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A20" s="4" t="s">
-        <v>102</v>
+        <v>97</v>
       </c>
       <c r="B20" s="3">
         <f>B17</f>
         <v>14.831804281345565</v>
       </c>
       <c r="C20" s="4" t="s">
-        <v>103</v>
+        <v>98</v>
       </c>
       <c r="D20" s="4"/>
     </row>
     <row r="21" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A21" s="2" t="s">
-        <v>104</v>
+        <v>99</v>
       </c>
       <c r="B21" s="3">
         <f>100-B17</f>
         <v>85.168195718654431</v>
       </c>
       <c r="C21" s="2" t="s">
-        <v>105</v>
+        <v>100</v>
       </c>
       <c r="D21" s="2"/>
     </row>
@@ -3373,32 +3362,32 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:8" ht="21.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A1" s="13" t="s">
-        <v>106</v>
-      </c>
-      <c r="B1" s="13"/>
-      <c r="C1" s="13"/>
-      <c r="D1" s="13"/>
-      <c r="E1" s="13"/>
-      <c r="F1" s="13"/>
-      <c r="G1" s="13"/>
-      <c r="H1" s="13"/>
+      <c r="A1" s="36" t="s">
+        <v>101</v>
+      </c>
+      <c r="B1" s="36"/>
+      <c r="C1" s="36"/>
+      <c r="D1" s="36"/>
+      <c r="E1" s="36"/>
+      <c r="F1" s="36"/>
+      <c r="G1" s="36"/>
+      <c r="H1" s="36"/>
     </row>
     <row r="2" spans="1:8" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A2" s="1" t="s">
-        <v>107</v>
+        <v>102</v>
       </c>
       <c r="B2" s="1" t="s">
-        <v>108</v>
+        <v>103</v>
       </c>
       <c r="C2" s="1" t="s">
-        <v>109</v>
+        <v>104</v>
       </c>
       <c r="D2" s="1" t="s">
-        <v>110</v>
+        <v>105</v>
       </c>
       <c r="E2" s="1" t="s">
-        <v>111</v>
+        <v>106</v>
       </c>
       <c r="F2" s="1" t="s">
         <v>11</v>
@@ -3406,12 +3395,12 @@
     </row>
     <row r="3" spans="1:8" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A3" s="2" t="s">
-        <v>112</v>
-      </c>
-      <c r="B3" s="32">
+        <v>107</v>
+      </c>
+      <c r="B3" s="29">
         <v>92.78</v>
       </c>
-      <c r="C3" s="32">
+      <c r="C3" s="29">
         <v>84.28</v>
       </c>
       <c r="D3" s="5">
@@ -3419,20 +3408,20 @@
         <v>8.5</v>
       </c>
       <c r="E3" s="2" t="s">
-        <v>113</v>
+        <v>108</v>
       </c>
       <c r="F3" s="2" t="s">
-        <v>114</v>
+        <v>109</v>
       </c>
     </row>
     <row r="4" spans="1:8" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A4" s="4" t="s">
-        <v>115</v>
-      </c>
-      <c r="B4" s="33">
+        <v>110</v>
+      </c>
+      <c r="B4" s="30">
         <v>100</v>
       </c>
-      <c r="C4" s="33">
+      <c r="C4" s="30">
         <v>99.25</v>
       </c>
       <c r="D4" s="6">
@@ -3440,20 +3429,20 @@
         <v>0.75</v>
       </c>
       <c r="E4" s="4" t="s">
-        <v>116</v>
+        <v>111</v>
       </c>
       <c r="F4" s="4" t="s">
-        <v>117</v>
+        <v>112</v>
       </c>
     </row>
     <row r="5" spans="1:8" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A5" s="2" t="s">
-        <v>118</v>
-      </c>
-      <c r="B5" s="32">
+        <v>113</v>
+      </c>
+      <c r="B5" s="29">
         <v>100</v>
       </c>
-      <c r="C5" s="32">
+      <c r="C5" s="29">
         <v>95.54</v>
       </c>
       <c r="D5" s="5">
@@ -3461,20 +3450,20 @@
         <v>4.4599999999999937</v>
       </c>
       <c r="E5" s="2" t="s">
-        <v>119</v>
+        <v>114</v>
       </c>
       <c r="F5" s="2" t="s">
-        <v>120</v>
+        <v>115</v>
       </c>
     </row>
     <row r="6" spans="1:8" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A6" s="4" t="s">
-        <v>121</v>
-      </c>
-      <c r="B6" s="33">
+        <v>116</v>
+      </c>
+      <c r="B6" s="30">
         <v>95.92</v>
       </c>
-      <c r="C6" s="33">
+      <c r="C6" s="30">
         <v>90.82</v>
       </c>
       <c r="D6" s="6">
@@ -3482,20 +3471,20 @@
         <v>5.1000000000000085</v>
       </c>
       <c r="E6" s="4" t="s">
-        <v>113</v>
+        <v>108</v>
       </c>
       <c r="F6" s="4" t="s">
-        <v>114</v>
+        <v>109</v>
       </c>
     </row>
     <row r="7" spans="1:8" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A7" s="2" t="s">
-        <v>122</v>
-      </c>
-      <c r="B7" s="32">
+        <v>117</v>
+      </c>
+      <c r="B7" s="29">
         <v>100</v>
       </c>
-      <c r="C7" s="32">
+      <c r="C7" s="29">
         <v>93.32</v>
       </c>
       <c r="D7" s="5">
@@ -3503,20 +3492,20 @@
         <v>6.6800000000000068</v>
       </c>
       <c r="E7" s="2" t="s">
-        <v>119</v>
+        <v>114</v>
       </c>
       <c r="F7" s="2" t="s">
-        <v>120</v>
+        <v>115</v>
       </c>
     </row>
     <row r="8" spans="1:8" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A8" s="4" t="s">
-        <v>123</v>
-      </c>
-      <c r="B8" s="33">
+        <v>118</v>
+      </c>
+      <c r="B8" s="30">
         <v>68.05</v>
       </c>
-      <c r="C8" s="33">
+      <c r="C8" s="30">
         <v>22.08</v>
       </c>
       <c r="D8" s="6">
@@ -3524,10 +3513,10 @@
         <v>45.97</v>
       </c>
       <c r="E8" s="4" t="s">
-        <v>113</v>
+        <v>108</v>
       </c>
       <c r="F8" s="4" t="s">
-        <v>124</v>
+        <v>119</v>
       </c>
     </row>
   </sheetData>
@@ -3557,32 +3546,32 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:8" ht="21.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A1" s="13" t="s">
-        <v>125</v>
-      </c>
-      <c r="B1" s="13"/>
-      <c r="C1" s="13"/>
-      <c r="D1" s="13"/>
-      <c r="E1" s="13"/>
-      <c r="F1" s="13"/>
-      <c r="G1" s="13"/>
-      <c r="H1" s="13"/>
+      <c r="A1" s="36" t="s">
+        <v>120</v>
+      </c>
+      <c r="B1" s="36"/>
+      <c r="C1" s="36"/>
+      <c r="D1" s="36"/>
+      <c r="E1" s="36"/>
+      <c r="F1" s="36"/>
+      <c r="G1" s="36"/>
+      <c r="H1" s="36"/>
     </row>
     <row r="2" spans="1:8" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A2" s="1" t="s">
-        <v>126</v>
+        <v>121</v>
       </c>
       <c r="B2" s="1" t="s">
-        <v>108</v>
+        <v>103</v>
       </c>
       <c r="C2" s="1" t="s">
-        <v>109</v>
+        <v>104</v>
       </c>
       <c r="D2" s="1" t="s">
-        <v>110</v>
+        <v>105</v>
       </c>
       <c r="E2" s="1" t="s">
-        <v>111</v>
+        <v>106</v>
       </c>
       <c r="F2" s="1" t="s">
         <v>11</v>
@@ -3590,7 +3579,7 @@
     </row>
     <row r="3" spans="1:8" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A3" s="2" t="s">
-        <v>127</v>
+        <v>122</v>
       </c>
       <c r="B3" s="2">
         <v>92.88</v>
@@ -3603,13 +3592,13 @@
         <v>9.0999999999999943</v>
       </c>
       <c r="E3" s="2" t="s">
-        <v>113</v>
+        <v>108</v>
       </c>
       <c r="F3" s="2"/>
     </row>
     <row r="4" spans="1:8" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A4" s="4" t="s">
-        <v>128</v>
+        <v>123</v>
       </c>
       <c r="B4" s="4">
         <v>92.15</v>
@@ -3622,13 +3611,13 @@
         <v>7.8200000000000074</v>
       </c>
       <c r="E4" s="4" t="s">
-        <v>119</v>
+        <v>114</v>
       </c>
       <c r="F4" s="4"/>
     </row>
     <row r="5" spans="1:8" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A5" s="2" t="s">
-        <v>129</v>
+        <v>124</v>
       </c>
       <c r="B5" s="2">
         <v>90.96</v>
@@ -3641,15 +3630,15 @@
         <v>9.5899999999999892</v>
       </c>
       <c r="E5" s="2" t="s">
-        <v>113</v>
+        <v>108</v>
       </c>
       <c r="F5" s="2" t="s">
-        <v>130</v>
+        <v>125</v>
       </c>
     </row>
     <row r="6" spans="1:8" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A6" s="4" t="s">
-        <v>131</v>
+        <v>126</v>
       </c>
       <c r="B6" s="4">
         <v>95.89</v>
@@ -3662,13 +3651,13 @@
         <v>9.7900000000000063</v>
       </c>
       <c r="E6" s="4" t="s">
-        <v>113</v>
+        <v>108</v>
       </c>
       <c r="F6" s="4"/>
     </row>
     <row r="7" spans="1:8" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A7" s="2" t="s">
-        <v>132</v>
+        <v>127</v>
       </c>
       <c r="B7" s="2">
         <v>95.71</v>
@@ -3681,15 +3670,15 @@
         <v>4.6799999999999926</v>
       </c>
       <c r="E7" s="2" t="s">
-        <v>119</v>
+        <v>114</v>
       </c>
       <c r="F7" s="2" t="s">
-        <v>133</v>
+        <v>128</v>
       </c>
     </row>
     <row r="8" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A8" s="7" t="s">
-        <v>134</v>
+        <v>129</v>
       </c>
       <c r="B8" s="7"/>
       <c r="C8" s="7"/>

--- a/Dashboard_Data.xlsx
+++ b/Dashboard_Data.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://alfanargroup-my.sharepoint.com/personal/ahmed_abdelzaher_alfanar_com/Documents/SDCC Dashboard/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="180" documentId="14_{682A7E4B-1055-4B0F-805D-134F59E89DE5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{618910F2-EC23-4C0D-826B-EEEE754DF2AA}"/>
+  <xr:revisionPtr revIDLastSave="193" documentId="14_{682A7E4B-1055-4B0F-805D-134F59E89DE5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{F705040F-576A-44F7-8FEF-01C7EF0FC380}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" tabRatio="500" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" tabRatio="500" firstSheet="3" activeTab="9" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Header" sheetId="1" r:id="rId1"/>
@@ -48,7 +48,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="360" uniqueCount="232">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="340" uniqueCount="212">
   <si>
     <t>HEADER — Dashboard Title &amp; PM</t>
   </si>
@@ -464,9 +464,6 @@
     <t>TCC Box Date</t>
   </si>
   <si>
-    <t>Nov-24</t>
-  </si>
-  <si>
     <t>YES</t>
   </si>
   <si>
@@ -482,24 +479,9 @@
     <t>First month</t>
   </si>
   <si>
-    <t>Dec-24</t>
-  </si>
-  <si>
-    <t>Jan-25</t>
-  </si>
-  <si>
-    <t>Feb-25</t>
-  </si>
-  <si>
-    <t>Mar-25</t>
-  </si>
-  <si>
     <t>MADINAH P.C.</t>
   </si>
   <si>
-    <t>Apr-25</t>
-  </si>
-  <si>
     <t>ABHA P.C.</t>
   </si>
   <si>
@@ -509,52 +491,10 @@
     <t>Flag goes below bar</t>
   </si>
   <si>
-    <t>May-25</t>
-  </si>
-  <si>
-    <t>Jun-25</t>
-  </si>
-  <si>
     <t>JIZAN P.C.</t>
   </si>
   <si>
-    <t>Jul-25</t>
-  </si>
-  <si>
-    <t>Aug-25</t>
-  </si>
-  <si>
-    <t>Sep-25</t>
-  </si>
-  <si>
-    <t>Oct-25</t>
-  </si>
-  <si>
-    <t>Nov-25</t>
-  </si>
-  <si>
-    <t>Dec-25</t>
-  </si>
-  <si>
-    <t>Jan-26</t>
-  </si>
-  <si>
-    <t>Feb-26</t>
-  </si>
-  <si>
-    <t>Mar-26</t>
-  </si>
-  <si>
-    <t>Apr-26</t>
-  </si>
-  <si>
     <t>Orange cell</t>
-  </si>
-  <si>
-    <t>May-26</t>
-  </si>
-  <si>
-    <t>Jun-26</t>
   </si>
   <si>
     <t>Revised TCC</t>
@@ -811,7 +751,7 @@
       <charset val="1"/>
     </font>
   </fonts>
-  <fills count="12">
+  <fills count="11">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -846,12 +786,6 @@
       <patternFill patternType="solid">
         <fgColor rgb="FFEEF3F9"/>
         <bgColor rgb="FFFFFFFF"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFD6E4F0"/>
-        <bgColor rgb="FFEEF3F9"/>
       </patternFill>
     </fill>
     <fill>
@@ -908,7 +842,7 @@
     <xf numFmtId="43" fontId="6" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="9" fontId="6" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="38">
+  <cellXfs count="40">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -935,13 +869,10 @@
     <xf numFmtId="0" fontId="3" fillId="8" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="9" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    <xf numFmtId="0" fontId="2" fillId="9" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="10" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="11" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="15" fontId="3" fillId="5" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -996,13 +927,7 @@
     <xf numFmtId="166" fontId="3" fillId="6" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="17" fontId="3" fillId="8" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="17" fontId="3" fillId="4" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="15" fontId="3" fillId="9" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="15" fontId="3" fillId="8" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="15" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
@@ -1012,6 +937,21 @@
     </xf>
     <xf numFmtId="0" fontId="2" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="17" fontId="3" fillId="4" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="17" fontId="3" fillId="6" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="17" fontId="3" fillId="7" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="17" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="17" fontId="3" fillId="8" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="3">
@@ -1290,16 +1230,16 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:8" ht="21.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A1" s="36" t="s">
+      <c r="A1" s="33" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="36"/>
-      <c r="C1" s="36"/>
-      <c r="D1" s="36"/>
-      <c r="E1" s="36"/>
-      <c r="F1" s="36"/>
-      <c r="G1" s="36"/>
-      <c r="H1" s="36"/>
+      <c r="B1" s="33"/>
+      <c r="C1" s="33"/>
+      <c r="D1" s="33"/>
+      <c r="E1" s="33"/>
+      <c r="F1" s="33"/>
+      <c r="G1" s="33"/>
+      <c r="H1" s="33"/>
     </row>
     <row r="2" spans="1:8" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A2" s="1" t="s">
@@ -1314,7 +1254,7 @@
         <v>3</v>
       </c>
       <c r="B3" s="3" t="s">
-        <v>194</v>
+        <v>174</v>
       </c>
     </row>
     <row r="4" spans="1:8" x14ac:dyDescent="0.25">
@@ -1330,7 +1270,7 @@
         <v>6</v>
       </c>
       <c r="B5" s="3" t="s">
-        <v>195</v>
+        <v>175</v>
       </c>
     </row>
     <row r="6" spans="1:8" x14ac:dyDescent="0.25">
@@ -1372,16 +1312,16 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:8" ht="21.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A1" s="36" t="s">
+      <c r="A1" s="33" t="s">
         <v>130</v>
       </c>
-      <c r="B1" s="36"/>
-      <c r="C1" s="36"/>
-      <c r="D1" s="36"/>
-      <c r="E1" s="36"/>
-      <c r="F1" s="36"/>
-      <c r="G1" s="36"/>
-      <c r="H1" s="36"/>
+      <c r="B1" s="33"/>
+      <c r="C1" s="33"/>
+      <c r="D1" s="33"/>
+      <c r="E1" s="33"/>
+      <c r="F1" s="33"/>
+      <c r="G1" s="33"/>
+      <c r="H1" s="33"/>
     </row>
     <row r="2" spans="1:8" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A2" s="1" t="s">
@@ -1410,476 +1350,476 @@
       </c>
     </row>
     <row r="3" spans="1:8" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A3" s="8" t="s">
+      <c r="A3" s="35">
+        <v>46350</v>
+      </c>
+      <c r="B3" s="2" t="s">
         <v>138</v>
       </c>
-      <c r="B3" s="2" t="s">
+      <c r="C3" s="2" t="s">
         <v>139</v>
       </c>
-      <c r="C3" s="2" t="s">
+      <c r="D3" s="2" t="s">
         <v>140</v>
       </c>
-      <c r="D3" s="2" t="s">
-        <v>141</v>
-      </c>
       <c r="E3" s="2" t="s">
-        <v>142</v>
+        <v>141</v>
       </c>
       <c r="F3" s="2"/>
       <c r="G3" s="2"/>
       <c r="H3" s="2" t="s">
-        <v>143</v>
+        <v>142</v>
       </c>
     </row>
     <row r="4" spans="1:8" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A4" s="4" t="s">
-        <v>144</v>
+      <c r="A4" s="36">
+        <v>46380</v>
       </c>
       <c r="B4" s="4" t="s">
-        <v>142</v>
+        <v>141</v>
       </c>
       <c r="C4" s="4"/>
       <c r="D4" s="4"/>
       <c r="E4" s="4" t="s">
-        <v>142</v>
+        <v>141</v>
       </c>
       <c r="F4" s="4"/>
       <c r="G4" s="4"/>
       <c r="H4" s="4"/>
     </row>
     <row r="5" spans="1:8" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A5" s="2" t="s">
-        <v>145</v>
+      <c r="A5" s="35">
+        <v>46411</v>
       </c>
       <c r="B5" s="2" t="s">
-        <v>142</v>
+        <v>141</v>
       </c>
       <c r="C5" s="2"/>
       <c r="D5" s="2"/>
       <c r="E5" s="2" t="s">
-        <v>142</v>
+        <v>141</v>
       </c>
       <c r="F5" s="2"/>
       <c r="G5" s="2"/>
       <c r="H5" s="2"/>
     </row>
     <row r="6" spans="1:8" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A6" s="4" t="s">
-        <v>146</v>
+      <c r="A6" s="36">
+        <v>46442</v>
       </c>
       <c r="B6" s="4" t="s">
-        <v>142</v>
+        <v>141</v>
       </c>
       <c r="C6" s="4"/>
       <c r="D6" s="4"/>
       <c r="E6" s="4" t="s">
-        <v>142</v>
+        <v>141</v>
       </c>
       <c r="F6" s="4"/>
       <c r="G6" s="4"/>
       <c r="H6" s="4"/>
     </row>
     <row r="7" spans="1:8" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A7" s="8" t="s">
-        <v>147</v>
+      <c r="A7" s="35">
+        <v>46470</v>
       </c>
       <c r="B7" s="2" t="s">
-        <v>139</v>
+        <v>138</v>
       </c>
       <c r="C7" s="2" t="s">
-        <v>148</v>
+        <v>143</v>
       </c>
       <c r="D7" s="2" t="s">
-        <v>141</v>
+        <v>140</v>
       </c>
       <c r="E7" s="2" t="s">
-        <v>142</v>
+        <v>141</v>
       </c>
       <c r="F7" s="2"/>
       <c r="G7" s="2"/>
       <c r="H7" s="2"/>
     </row>
     <row r="8" spans="1:8" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A8" s="8" t="s">
-        <v>149</v>
+      <c r="A8" s="36">
+        <v>46501</v>
       </c>
       <c r="B8" s="4" t="s">
-        <v>139</v>
+        <v>138</v>
       </c>
       <c r="C8" s="4" t="s">
-        <v>150</v>
+        <v>144</v>
       </c>
       <c r="D8" s="4" t="s">
-        <v>151</v>
+        <v>145</v>
       </c>
       <c r="E8" s="4" t="s">
-        <v>142</v>
+        <v>141</v>
       </c>
       <c r="F8" s="4"/>
       <c r="G8" s="4"/>
       <c r="H8" s="4" t="s">
-        <v>152</v>
+        <v>146</v>
       </c>
     </row>
     <row r="9" spans="1:8" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A9" s="2" t="s">
-        <v>153</v>
+      <c r="A9" s="35">
+        <v>46531</v>
       </c>
       <c r="B9" s="2" t="s">
-        <v>142</v>
+        <v>141</v>
       </c>
       <c r="C9" s="2"/>
       <c r="D9" s="2"/>
       <c r="E9" s="2" t="s">
-        <v>142</v>
+        <v>141</v>
       </c>
       <c r="F9" s="2"/>
       <c r="G9" s="2"/>
       <c r="H9" s="2"/>
     </row>
     <row r="10" spans="1:8" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A10" s="8" t="s">
-        <v>154</v>
+      <c r="A10" s="36">
+        <v>46562</v>
       </c>
       <c r="B10" s="4" t="s">
-        <v>139</v>
+        <v>138</v>
       </c>
       <c r="C10" s="4" t="s">
-        <v>155</v>
+        <v>147</v>
       </c>
       <c r="D10" s="4" t="s">
-        <v>141</v>
+        <v>140</v>
       </c>
       <c r="E10" s="4" t="s">
-        <v>142</v>
+        <v>141</v>
       </c>
       <c r="F10" s="4"/>
       <c r="G10" s="4"/>
       <c r="H10" s="4"/>
     </row>
     <row r="11" spans="1:8" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A11" s="2" t="s">
-        <v>156</v>
+      <c r="A11" s="35">
+        <v>46592</v>
       </c>
       <c r="B11" s="2" t="s">
-        <v>142</v>
+        <v>141</v>
       </c>
       <c r="C11" s="2"/>
       <c r="D11" s="2"/>
       <c r="E11" s="2" t="s">
-        <v>142</v>
+        <v>141</v>
       </c>
       <c r="F11" s="2"/>
       <c r="G11" s="2"/>
       <c r="H11" s="2"/>
     </row>
     <row r="12" spans="1:8" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A12" s="4" t="s">
-        <v>157</v>
+      <c r="A12" s="36">
+        <v>46623</v>
       </c>
       <c r="B12" s="4" t="s">
-        <v>142</v>
+        <v>141</v>
       </c>
       <c r="C12" s="4"/>
       <c r="D12" s="4"/>
       <c r="E12" s="4" t="s">
-        <v>142</v>
+        <v>141</v>
       </c>
       <c r="F12" s="4"/>
       <c r="G12" s="4"/>
       <c r="H12" s="4"/>
     </row>
     <row r="13" spans="1:8" ht="25.5" x14ac:dyDescent="0.25">
-      <c r="A13" s="2" t="s">
-        <v>158</v>
+      <c r="A13" s="35">
+        <v>46654</v>
       </c>
       <c r="B13" s="2" t="s">
-        <v>142</v>
+        <v>141</v>
       </c>
       <c r="C13" s="2" t="s">
-        <v>199</v>
+        <v>179</v>
       </c>
       <c r="D13" s="2"/>
       <c r="E13" s="2" t="s">
-        <v>142</v>
+        <v>141</v>
       </c>
       <c r="F13" s="2"/>
       <c r="G13" s="2"/>
       <c r="H13" s="2"/>
     </row>
     <row r="14" spans="1:8" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A14" s="4" t="s">
-        <v>159</v>
+      <c r="A14" s="36">
+        <v>46684</v>
       </c>
       <c r="B14" s="4" t="s">
-        <v>142</v>
+        <v>141</v>
       </c>
       <c r="C14" s="4" t="s">
-        <v>200</v>
+        <v>180</v>
       </c>
       <c r="D14" s="4"/>
       <c r="E14" s="4" t="s">
-        <v>142</v>
+        <v>141</v>
       </c>
       <c r="F14" s="4"/>
       <c r="G14" s="4"/>
       <c r="H14" s="4"/>
     </row>
     <row r="15" spans="1:8" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A15" s="8" t="s">
-        <v>160</v>
+      <c r="A15" s="35">
+        <v>46715</v>
       </c>
       <c r="B15" s="2" t="s">
-        <v>139</v>
+        <v>138</v>
       </c>
       <c r="C15" s="2"/>
       <c r="D15" s="2" t="s">
-        <v>141</v>
+        <v>140</v>
       </c>
       <c r="E15" s="2" t="s">
-        <v>142</v>
+        <v>141</v>
       </c>
       <c r="F15" s="2"/>
       <c r="G15" s="2"/>
       <c r="H15" s="2"/>
     </row>
     <row r="16" spans="1:8" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A16" s="4" t="s">
-        <v>161</v>
+      <c r="A16" s="36">
+        <v>46745</v>
       </c>
       <c r="B16" s="4" t="s">
-        <v>142</v>
+        <v>141</v>
       </c>
       <c r="C16" s="4" t="s">
-        <v>201</v>
+        <v>181</v>
       </c>
       <c r="D16" s="4"/>
       <c r="E16" s="4" t="s">
-        <v>142</v>
+        <v>141</v>
       </c>
       <c r="F16" s="4"/>
       <c r="G16" s="4"/>
       <c r="H16" s="4"/>
     </row>
     <row r="17" spans="1:8" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A17" s="2" t="s">
-        <v>162</v>
+      <c r="A17" s="35">
+        <v>46776</v>
       </c>
       <c r="B17" s="2" t="s">
-        <v>142</v>
+        <v>141</v>
       </c>
       <c r="C17" s="2"/>
       <c r="D17" s="2"/>
       <c r="E17" s="2" t="s">
-        <v>142</v>
+        <v>141</v>
       </c>
       <c r="F17" s="2"/>
       <c r="G17" s="2"/>
       <c r="H17" s="2"/>
     </row>
     <row r="18" spans="1:8" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A18" s="4" t="s">
-        <v>163</v>
+      <c r="A18" s="36">
+        <v>46807</v>
       </c>
       <c r="B18" s="4" t="s">
-        <v>142</v>
+        <v>141</v>
       </c>
       <c r="C18" s="4"/>
       <c r="D18" s="4"/>
       <c r="E18" s="4" t="s">
-        <v>142</v>
+        <v>141</v>
       </c>
       <c r="F18" s="4"/>
       <c r="G18" s="4"/>
       <c r="H18" s="4"/>
     </row>
     <row r="19" spans="1:8" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A19" s="2" t="s">
-        <v>164</v>
+      <c r="A19" s="35">
+        <v>46836</v>
       </c>
       <c r="B19" s="2" t="s">
-        <v>142</v>
+        <v>141</v>
       </c>
       <c r="C19" s="2"/>
       <c r="D19" s="2"/>
       <c r="E19" s="2" t="s">
-        <v>142</v>
+        <v>141</v>
       </c>
       <c r="F19" s="2"/>
       <c r="G19" s="2"/>
       <c r="H19" s="2"/>
     </row>
     <row r="20" spans="1:8" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A20" s="2" t="s">
-        <v>165</v>
+      <c r="A20" s="35">
+        <v>46867</v>
       </c>
       <c r="B20" s="2" t="s">
-        <v>142</v>
+        <v>141</v>
       </c>
       <c r="C20" s="2"/>
       <c r="D20" s="2"/>
       <c r="E20" s="2" t="s">
-        <v>142</v>
+        <v>141</v>
       </c>
       <c r="F20" s="2"/>
       <c r="G20" s="2"/>
       <c r="H20" s="2"/>
     </row>
     <row r="21" spans="1:8" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A21" s="2" t="s">
-        <v>167</v>
+      <c r="A21" s="35">
+        <v>46897</v>
       </c>
       <c r="B21" s="2" t="s">
-        <v>142</v>
+        <v>141</v>
       </c>
       <c r="C21" s="2"/>
       <c r="D21" s="2"/>
       <c r="E21" s="2" t="s">
-        <v>142</v>
+        <v>141</v>
       </c>
       <c r="F21" s="2"/>
       <c r="G21" s="2"/>
       <c r="H21" s="2"/>
     </row>
     <row r="22" spans="1:8" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A22" s="2" t="s">
-        <v>168</v>
+      <c r="A22" s="35">
+        <v>46928</v>
       </c>
       <c r="B22" s="2" t="s">
-        <v>142</v>
+        <v>141</v>
       </c>
       <c r="C22" s="2"/>
       <c r="D22" s="2"/>
       <c r="E22" s="2" t="s">
-        <v>139</v>
+        <v>138</v>
       </c>
       <c r="F22" s="2"/>
       <c r="G22" s="2"/>
       <c r="H22" s="2"/>
     </row>
     <row r="23" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A23" s="31">
+      <c r="A23" s="37">
         <v>46204</v>
       </c>
-      <c r="B23" s="9" t="s">
-        <v>142</v>
-      </c>
-      <c r="C23" s="9"/>
-      <c r="D23" s="9"/>
-      <c r="E23" s="9" t="s">
-        <v>139</v>
-      </c>
-      <c r="F23" s="9" t="s">
+      <c r="B23" s="8" t="s">
+        <v>141</v>
+      </c>
+      <c r="C23" s="8"/>
+      <c r="D23" s="8"/>
+      <c r="E23" s="8" t="s">
+        <v>138</v>
+      </c>
+      <c r="F23" s="8" t="s">
         <v>17</v>
       </c>
-      <c r="G23" s="9" t="s">
+      <c r="G23" s="8" t="s">
         <v>18</v>
       </c>
-      <c r="H23" s="9" t="s">
-        <v>166</v>
+      <c r="H23" s="8" t="s">
+        <v>148</v>
       </c>
     </row>
     <row r="24" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A24" s="32">
+      <c r="A24" s="35">
         <v>46235</v>
       </c>
       <c r="B24" s="2" t="s">
-        <v>142</v>
+        <v>141</v>
       </c>
       <c r="C24" s="2"/>
       <c r="D24" s="2"/>
       <c r="E24" s="2" t="s">
-        <v>142</v>
+        <v>141</v>
       </c>
       <c r="F24" s="2"/>
       <c r="G24" s="2"/>
       <c r="H24" s="2"/>
     </row>
     <row r="25" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A25" s="32">
+      <c r="A25" s="35">
         <v>46266</v>
       </c>
       <c r="B25" s="2" t="s">
-        <v>142</v>
+        <v>141</v>
       </c>
       <c r="C25" s="2"/>
       <c r="D25" s="2"/>
       <c r="E25" s="2" t="s">
-        <v>142</v>
+        <v>141</v>
       </c>
       <c r="F25" s="2"/>
       <c r="G25" s="2"/>
       <c r="H25" s="2"/>
     </row>
     <row r="26" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A26" s="32">
+      <c r="A26" s="35">
         <v>46296</v>
       </c>
       <c r="B26" s="2" t="s">
-        <v>142</v>
+        <v>141</v>
       </c>
       <c r="C26" s="2"/>
       <c r="D26" s="2"/>
       <c r="E26" s="2" t="s">
-        <v>142</v>
+        <v>141</v>
       </c>
       <c r="F26" s="2"/>
       <c r="G26" s="2"/>
       <c r="H26" s="2"/>
     </row>
     <row r="27" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A27" s="32">
+      <c r="A27" s="38">
         <v>46327</v>
       </c>
       <c r="B27" s="2" t="s">
-        <v>142</v>
+        <v>141</v>
       </c>
       <c r="E27" s="2" t="s">
-        <v>142</v>
+        <v>141</v>
       </c>
     </row>
     <row r="28" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A28" s="32">
+      <c r="A28" s="38">
         <v>46357</v>
       </c>
       <c r="B28" s="2" t="s">
-        <v>142</v>
+        <v>141</v>
       </c>
       <c r="E28" s="2" t="s">
-        <v>142</v>
+        <v>141</v>
       </c>
     </row>
     <row r="29" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A29" s="32">
+      <c r="A29" s="38">
         <v>46388</v>
       </c>
       <c r="B29" s="2" t="s">
-        <v>142</v>
+        <v>141</v>
       </c>
       <c r="E29" s="2" t="s">
-        <v>142</v>
+        <v>141</v>
       </c>
     </row>
     <row r="30" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A30" s="32">
+      <c r="A30" s="39">
         <v>46419</v>
       </c>
-      <c r="B30" s="10" t="s">
-        <v>142</v>
-      </c>
-      <c r="C30" s="10"/>
-      <c r="D30" s="10"/>
-      <c r="E30" s="10" t="s">
-        <v>139</v>
-      </c>
-      <c r="F30" s="10" t="s">
-        <v>169</v>
-      </c>
-      <c r="G30" s="33">
+      <c r="B30" s="9" t="s">
+        <v>141</v>
+      </c>
+      <c r="C30" s="9"/>
+      <c r="D30" s="9"/>
+      <c r="E30" s="9" t="s">
+        <v>138</v>
+      </c>
+      <c r="F30" s="9" t="s">
+        <v>149</v>
+      </c>
+      <c r="G30" s="30">
         <v>46435</v>
       </c>
-      <c r="H30" s="10" t="s">
-        <v>170</v>
+      <c r="H30" s="9" t="s">
+        <v>150</v>
       </c>
     </row>
   </sheetData>
@@ -1911,35 +1851,35 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:8" ht="21.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A1" s="36" t="s">
-        <v>171</v>
-      </c>
-      <c r="B1" s="36"/>
-      <c r="C1" s="36"/>
-      <c r="D1" s="36"/>
-      <c r="E1" s="36"/>
-      <c r="F1" s="36"/>
-      <c r="G1" s="36"/>
-      <c r="H1" s="36"/>
+      <c r="A1" s="33" t="s">
+        <v>151</v>
+      </c>
+      <c r="B1" s="33"/>
+      <c r="C1" s="33"/>
+      <c r="D1" s="33"/>
+      <c r="E1" s="33"/>
+      <c r="F1" s="33"/>
+      <c r="G1" s="33"/>
+      <c r="H1" s="33"/>
     </row>
     <row r="2" spans="1:8" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A2" s="1" t="s">
-        <v>172</v>
+        <v>152</v>
       </c>
       <c r="B2" s="1" t="s">
-        <v>173</v>
+        <v>153</v>
       </c>
       <c r="C2" s="1" t="s">
-        <v>174</v>
+        <v>154</v>
       </c>
       <c r="D2" s="1" t="s">
-        <v>175</v>
+        <v>155</v>
       </c>
       <c r="E2" s="1" t="s">
-        <v>176</v>
+        <v>156</v>
       </c>
       <c r="F2" s="1" t="s">
-        <v>177</v>
+        <v>157</v>
       </c>
     </row>
     <row r="3" spans="1:8" ht="38.25" x14ac:dyDescent="0.25">
@@ -1947,19 +1887,19 @@
         <v>1</v>
       </c>
       <c r="B3" s="2" t="s">
-        <v>207</v>
+        <v>187</v>
       </c>
       <c r="C3" s="2" t="s">
-        <v>204</v>
+        <v>184</v>
       </c>
       <c r="D3" s="2" t="s">
-        <v>203</v>
+        <v>183</v>
       </c>
       <c r="E3" s="2" t="s">
-        <v>208</v>
-      </c>
-      <c r="F3" s="11" t="s">
-        <v>202</v>
+        <v>188</v>
+      </c>
+      <c r="F3" s="10" t="s">
+        <v>182</v>
       </c>
     </row>
     <row r="4" spans="1:8" ht="25.5" x14ac:dyDescent="0.25">
@@ -1967,19 +1907,19 @@
         <v>2</v>
       </c>
       <c r="B4" s="4" t="s">
-        <v>209</v>
+        <v>189</v>
       </c>
       <c r="C4" s="4" t="s">
-        <v>206</v>
+        <v>186</v>
       </c>
       <c r="D4" s="4" t="s">
-        <v>205</v>
+        <v>185</v>
       </c>
       <c r="E4" s="4" t="s">
-        <v>210</v>
-      </c>
-      <c r="F4" s="11" t="s">
-        <v>202</v>
+        <v>190</v>
+      </c>
+      <c r="F4" s="10" t="s">
+        <v>182</v>
       </c>
     </row>
     <row r="5" spans="1:8" ht="38.25" x14ac:dyDescent="0.25">
@@ -1987,19 +1927,19 @@
         <v>3</v>
       </c>
       <c r="B5" s="2" t="s">
-        <v>211</v>
+        <v>191</v>
       </c>
       <c r="C5" s="2" t="s">
-        <v>206</v>
+        <v>186</v>
       </c>
       <c r="D5" s="2" t="s">
-        <v>205</v>
+        <v>185</v>
       </c>
       <c r="E5" s="2" t="s">
-        <v>214</v>
-      </c>
-      <c r="F5" s="11" t="s">
-        <v>202</v>
+        <v>194</v>
+      </c>
+      <c r="F5" s="10" t="s">
+        <v>182</v>
       </c>
     </row>
     <row r="6" spans="1:8" ht="38.25" x14ac:dyDescent="0.25">
@@ -2007,19 +1947,19 @@
         <v>4</v>
       </c>
       <c r="B6" s="2" t="s">
-        <v>212</v>
+        <v>192</v>
       </c>
       <c r="C6" s="2" t="s">
-        <v>206</v>
+        <v>186</v>
       </c>
       <c r="D6" s="2" t="s">
-        <v>205</v>
+        <v>185</v>
       </c>
       <c r="E6" s="2" t="s">
-        <v>213</v>
-      </c>
-      <c r="F6" s="11" t="s">
-        <v>202</v>
+        <v>193</v>
+      </c>
+      <c r="F6" s="10" t="s">
+        <v>182</v>
       </c>
     </row>
   </sheetData>
@@ -2050,41 +1990,41 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:21" ht="21.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A1" s="36" t="s">
-        <v>178</v>
-      </c>
-      <c r="B1" s="36"/>
-      <c r="C1" s="36"/>
-      <c r="D1" s="36"/>
-      <c r="E1" s="36"/>
-      <c r="F1" s="36"/>
-      <c r="G1" s="36"/>
-      <c r="H1" s="36"/>
+      <c r="A1" s="33" t="s">
+        <v>158</v>
+      </c>
+      <c r="B1" s="33"/>
+      <c r="C1" s="33"/>
+      <c r="D1" s="33"/>
+      <c r="E1" s="33"/>
+      <c r="F1" s="33"/>
+      <c r="G1" s="33"/>
+      <c r="H1" s="33"/>
     </row>
     <row r="2" spans="1:21" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A2" s="1" t="s">
-        <v>172</v>
+        <v>152</v>
       </c>
       <c r="B2" s="1" t="s">
         <v>113</v>
       </c>
       <c r="C2" s="1" t="s">
-        <v>179</v>
+        <v>159</v>
       </c>
       <c r="D2" s="1" t="s">
-        <v>180</v>
+        <v>160</v>
       </c>
       <c r="E2" s="1" t="s">
-        <v>181</v>
+        <v>161</v>
       </c>
       <c r="F2" s="1" t="s">
-        <v>182</v>
+        <v>162</v>
       </c>
       <c r="G2" s="1" t="s">
-        <v>183</v>
+        <v>163</v>
       </c>
       <c r="H2" s="1" t="s">
-        <v>184</v>
+        <v>164</v>
       </c>
     </row>
     <row r="3" spans="1:21" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
@@ -2092,13 +2032,13 @@
         <v>1</v>
       </c>
       <c r="B3" s="2" t="s">
-        <v>216</v>
+        <v>196</v>
       </c>
       <c r="C3" s="2" t="s">
-        <v>217</v>
+        <v>197</v>
       </c>
       <c r="D3" s="2" t="s">
-        <v>185</v>
+        <v>165</v>
       </c>
       <c r="E3" s="2">
         <v>1</v>
@@ -2109,8 +2049,8 @@
       <c r="G3" s="2">
         <v>1</v>
       </c>
-      <c r="H3" s="12" t="s">
-        <v>186</v>
+      <c r="H3" s="11" t="s">
+        <v>166</v>
       </c>
     </row>
     <row r="4" spans="1:21" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
@@ -2118,13 +2058,13 @@
         <v>2</v>
       </c>
       <c r="B4" s="4" t="s">
-        <v>218</v>
+        <v>198</v>
       </c>
       <c r="C4" s="4" t="s">
-        <v>219</v>
+        <v>199</v>
       </c>
       <c r="D4" s="4" t="s">
-        <v>185</v>
+        <v>165</v>
       </c>
       <c r="E4" s="4">
         <v>1</v>
@@ -2135,8 +2075,8 @@
       <c r="G4" s="4">
         <v>1</v>
       </c>
-      <c r="H4" s="12" t="s">
-        <v>186</v>
+      <c r="H4" s="11" t="s">
+        <v>166</v>
       </c>
     </row>
     <row r="5" spans="1:21" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
@@ -2144,13 +2084,13 @@
         <v>3</v>
       </c>
       <c r="B5" s="2" t="s">
-        <v>220</v>
+        <v>200</v>
       </c>
       <c r="C5" s="2" t="s">
-        <v>219</v>
+        <v>199</v>
       </c>
       <c r="D5" s="2" t="s">
-        <v>185</v>
+        <v>165</v>
       </c>
       <c r="E5" s="2">
         <v>1</v>
@@ -2161,8 +2101,8 @@
       <c r="G5" s="2">
         <v>1</v>
       </c>
-      <c r="H5" s="12" t="s">
-        <v>186</v>
+      <c r="H5" s="11" t="s">
+        <v>166</v>
       </c>
     </row>
     <row r="6" spans="1:21" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
@@ -2170,13 +2110,13 @@
         <v>4</v>
       </c>
       <c r="B6" s="4" t="s">
-        <v>221</v>
+        <v>201</v>
       </c>
       <c r="C6" s="4" t="s">
-        <v>222</v>
+        <v>202</v>
       </c>
       <c r="D6" s="4" t="s">
-        <v>185</v>
+        <v>165</v>
       </c>
       <c r="E6" s="4">
         <v>1</v>
@@ -2187,8 +2127,8 @@
       <c r="G6" s="4">
         <v>1</v>
       </c>
-      <c r="H6" s="12" t="s">
-        <v>186</v>
+      <c r="H6" s="11" t="s">
+        <v>166</v>
       </c>
     </row>
     <row r="7" spans="1:21" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
@@ -2196,13 +2136,13 @@
         <v>5</v>
       </c>
       <c r="B7" s="2" t="s">
-        <v>223</v>
+        <v>203</v>
       </c>
       <c r="C7" s="2" t="s">
-        <v>224</v>
+        <v>204</v>
       </c>
       <c r="D7" s="2" t="s">
-        <v>185</v>
+        <v>165</v>
       </c>
       <c r="E7" s="2">
         <v>1</v>
@@ -2213,8 +2153,8 @@
       <c r="G7" s="2">
         <v>0.9</v>
       </c>
-      <c r="H7" s="11" t="s">
-        <v>225</v>
+      <c r="H7" s="10" t="s">
+        <v>205</v>
       </c>
     </row>
     <row r="8" spans="1:21" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
@@ -2222,13 +2162,13 @@
         <v>6</v>
       </c>
       <c r="B8" s="4" t="s">
-        <v>215</v>
+        <v>195</v>
       </c>
       <c r="C8" s="4" t="s">
-        <v>224</v>
+        <v>204</v>
       </c>
       <c r="D8" s="4" t="s">
-        <v>185</v>
+        <v>165</v>
       </c>
       <c r="E8" s="4">
         <v>1</v>
@@ -2239,8 +2179,8 @@
       <c r="G8" s="4">
         <v>0</v>
       </c>
-      <c r="H8" s="11" t="s">
-        <v>225</v>
+      <c r="H8" s="10" t="s">
+        <v>205</v>
       </c>
     </row>
     <row r="9" spans="1:21" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
@@ -2248,16 +2188,16 @@
         <v>7</v>
       </c>
       <c r="B9" s="2" t="s">
-        <v>226</v>
+        <v>206</v>
       </c>
       <c r="C9" s="2" t="s">
-        <v>219</v>
+        <v>199</v>
       </c>
       <c r="D9" s="2" t="s">
-        <v>185</v>
+        <v>165</v>
       </c>
       <c r="E9" s="2" t="s">
-        <v>227</v>
+        <v>207</v>
       </c>
       <c r="F9" s="2">
         <v>0</v>
@@ -2265,8 +2205,8 @@
       <c r="G9" s="2">
         <v>0</v>
       </c>
-      <c r="H9" s="11" t="s">
-        <v>225</v>
+      <c r="H9" s="10" t="s">
+        <v>205</v>
       </c>
     </row>
     <row r="10" spans="1:21" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
@@ -2274,85 +2214,85 @@
         <v>8</v>
       </c>
       <c r="B10" s="4" t="s">
-        <v>228</v>
+        <v>208</v>
       </c>
       <c r="C10" s="4" t="s">
-        <v>229</v>
+        <v>209</v>
       </c>
       <c r="D10" s="4" t="s">
-        <v>185</v>
+        <v>165</v>
       </c>
       <c r="E10" s="4">
         <v>1</v>
       </c>
       <c r="F10" s="4" t="s">
-        <v>230</v>
+        <v>210</v>
       </c>
       <c r="G10" s="4">
         <v>0.15</v>
       </c>
-      <c r="H10" s="11" t="s">
-        <v>225</v>
+      <c r="H10" s="10" t="s">
+        <v>205</v>
       </c>
     </row>
     <row r="11" spans="1:21" x14ac:dyDescent="0.25">
-      <c r="S11" s="35"/>
-      <c r="T11" s="35"/>
-      <c r="U11" s="35"/>
+      <c r="S11" s="32"/>
+      <c r="T11" s="32"/>
+      <c r="U11" s="32"/>
     </row>
     <row r="12" spans="1:21" x14ac:dyDescent="0.25">
-      <c r="S12" s="35"/>
-      <c r="T12" s="35"/>
-      <c r="U12" s="35"/>
+      <c r="S12" s="32"/>
+      <c r="T12" s="32"/>
+      <c r="U12" s="32"/>
     </row>
     <row r="13" spans="1:21" x14ac:dyDescent="0.25">
-      <c r="S13" s="35"/>
-      <c r="T13" s="35"/>
-      <c r="U13" s="35"/>
+      <c r="S13" s="32"/>
+      <c r="T13" s="32"/>
+      <c r="U13" s="32"/>
     </row>
     <row r="14" spans="1:21" x14ac:dyDescent="0.25">
-      <c r="S14" s="35"/>
-      <c r="T14" s="35"/>
-      <c r="U14" s="35"/>
+      <c r="S14" s="32"/>
+      <c r="T14" s="32"/>
+      <c r="U14" s="32"/>
     </row>
     <row r="15" spans="1:21" x14ac:dyDescent="0.25">
-      <c r="S15" s="35"/>
-      <c r="T15" s="35"/>
-      <c r="U15" s="35"/>
+      <c r="S15" s="32"/>
+      <c r="T15" s="32"/>
+      <c r="U15" s="32"/>
     </row>
     <row r="16" spans="1:21" x14ac:dyDescent="0.25">
-      <c r="S16" s="35"/>
-      <c r="T16" s="35"/>
-      <c r="U16" s="35"/>
+      <c r="S16" s="32"/>
+      <c r="T16" s="32"/>
+      <c r="U16" s="32"/>
     </row>
     <row r="17" spans="19:21" x14ac:dyDescent="0.25">
-      <c r="T17" s="35"/>
-      <c r="U17" s="35"/>
+      <c r="T17" s="32"/>
+      <c r="U17" s="32"/>
     </row>
     <row r="18" spans="19:21" x14ac:dyDescent="0.25">
-      <c r="S18" s="35"/>
-      <c r="U18" s="35"/>
+      <c r="S18" s="32"/>
+      <c r="U18" s="32"/>
     </row>
     <row r="19" spans="19:21" x14ac:dyDescent="0.25">
-      <c r="S19" s="34"/>
+      <c r="S19" s="31"/>
     </row>
     <row r="20" spans="19:21" x14ac:dyDescent="0.25">
-      <c r="S20" s="34"/>
+      <c r="S20" s="31"/>
     </row>
     <row r="21" spans="19:21" x14ac:dyDescent="0.25">
-      <c r="S21" s="34"/>
+      <c r="S21" s="31"/>
     </row>
     <row r="22" spans="19:21" x14ac:dyDescent="0.25">
-      <c r="S22" s="34"/>
+      <c r="S22" s="31"/>
     </row>
     <row r="23" spans="19:21" x14ac:dyDescent="0.25">
-      <c r="S23" s="34"/>
+      <c r="S23" s="31"/>
     </row>
     <row r="24" spans="19:21" x14ac:dyDescent="0.25">
-      <c r="S24" s="34"/>
+      <c r="S24" s="31"/>
     </row>
     <row r="25" spans="19:21" x14ac:dyDescent="0.25">
-      <c r="S25" s="34"/>
+      <c r="S25" s="31"/>
     </row>
   </sheetData>
   <mergeCells count="1">
@@ -2379,16 +2319,16 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:8" ht="21.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A1" s="36" t="s">
-        <v>187</v>
-      </c>
-      <c r="B1" s="36"/>
-      <c r="C1" s="36"/>
-      <c r="D1" s="36"/>
-      <c r="E1" s="36"/>
-      <c r="F1" s="36"/>
-      <c r="G1" s="36"/>
-      <c r="H1" s="36"/>
+      <c r="A1" s="33" t="s">
+        <v>167</v>
+      </c>
+      <c r="B1" s="33"/>
+      <c r="C1" s="33"/>
+      <c r="D1" s="33"/>
+      <c r="E1" s="33"/>
+      <c r="F1" s="33"/>
+      <c r="G1" s="33"/>
+      <c r="H1" s="33"/>
     </row>
     <row r="2" spans="1:8" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A2" s="1" t="s">
@@ -2400,34 +2340,34 @@
     </row>
     <row r="3" spans="1:8" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A3" s="2" t="s">
-        <v>188</v>
+        <v>168</v>
       </c>
       <c r="B3" s="3" t="s">
-        <v>189</v>
+        <v>169</v>
       </c>
     </row>
     <row r="4" spans="1:8" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A4" s="4" t="s">
-        <v>190</v>
-      </c>
-      <c r="B4" s="13">
+        <v>170</v>
+      </c>
+      <c r="B4" s="12">
         <v>46176</v>
       </c>
     </row>
     <row r="5" spans="1:8" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A5" s="2" t="s">
-        <v>191</v>
+        <v>171</v>
       </c>
       <c r="B5" s="3" t="s">
-        <v>231</v>
+        <v>211</v>
       </c>
     </row>
     <row r="6" spans="1:8" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A6" s="4" t="s">
-        <v>192</v>
+        <v>172</v>
       </c>
       <c r="B6" s="3" t="s">
-        <v>193</v>
+        <v>173</v>
       </c>
     </row>
   </sheetData>
@@ -2456,16 +2396,16 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:8" ht="21.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A1" s="36" t="s">
+      <c r="A1" s="33" t="s">
         <v>9</v>
       </c>
-      <c r="B1" s="36"/>
-      <c r="C1" s="36"/>
-      <c r="D1" s="36"/>
-      <c r="E1" s="36"/>
-      <c r="F1" s="36"/>
-      <c r="G1" s="36"/>
-      <c r="H1" s="36"/>
+      <c r="B1" s="33"/>
+      <c r="C1" s="33"/>
+      <c r="D1" s="33"/>
+      <c r="E1" s="33"/>
+      <c r="F1" s="33"/>
+      <c r="G1" s="33"/>
+      <c r="H1" s="33"/>
     </row>
     <row r="2" spans="1:8" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A2" s="1" t="s">
@@ -2482,7 +2422,7 @@
       <c r="A3" s="2" t="s">
         <v>12</v>
       </c>
-      <c r="B3" s="17">
+      <c r="B3" s="16">
         <v>45497</v>
       </c>
       <c r="C3" s="2"/>
@@ -2491,7 +2431,7 @@
       <c r="A4" s="4" t="s">
         <v>13</v>
       </c>
-      <c r="B4" s="17">
+      <c r="B4" s="16">
         <v>45530</v>
       </c>
       <c r="C4" s="4"/>
@@ -2500,7 +2440,7 @@
       <c r="A5" s="2" t="s">
         <v>14</v>
       </c>
-      <c r="B5" s="17">
+      <c r="B5" s="16">
         <v>45571</v>
       </c>
       <c r="C5" s="2"/>
@@ -2509,7 +2449,7 @@
       <c r="A6" s="4" t="s">
         <v>15</v>
       </c>
-      <c r="B6" s="17">
+      <c r="B6" s="16">
         <v>45718</v>
       </c>
       <c r="C6" s="4"/>
@@ -2518,7 +2458,7 @@
       <c r="A7" s="2" t="s">
         <v>16</v>
       </c>
-      <c r="B7" s="17">
+      <c r="B7" s="16">
         <v>45830</v>
       </c>
       <c r="C7" s="2"/>
@@ -2527,7 +2467,7 @@
       <c r="A8" s="4" t="s">
         <v>17</v>
       </c>
-      <c r="B8" s="17">
+      <c r="B8" s="16">
         <v>46227</v>
       </c>
       <c r="C8" s="4" t="s">
@@ -2538,7 +2478,7 @@
       <c r="A9" s="2" t="s">
         <v>20</v>
       </c>
-      <c r="B9" s="17">
+      <c r="B9" s="16">
         <v>46435</v>
       </c>
       <c r="C9" s="2" t="s">
@@ -2573,16 +2513,16 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:8" ht="21.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A1" s="36" t="s">
+      <c r="A1" s="33" t="s">
         <v>22</v>
       </c>
-      <c r="B1" s="36"/>
-      <c r="C1" s="36"/>
-      <c r="D1" s="36"/>
-      <c r="E1" s="36"/>
-      <c r="F1" s="36"/>
-      <c r="G1" s="36"/>
-      <c r="H1" s="36"/>
+      <c r="B1" s="33"/>
+      <c r="C1" s="33"/>
+      <c r="D1" s="33"/>
+      <c r="E1" s="33"/>
+      <c r="F1" s="33"/>
+      <c r="G1" s="33"/>
+      <c r="H1" s="33"/>
     </row>
     <row r="2" spans="1:8" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A2" s="1" t="s">
@@ -2602,7 +2542,7 @@
       <c r="A3" s="2" t="s">
         <v>25</v>
       </c>
-      <c r="B3" s="16">
+      <c r="B3" s="15">
         <v>388016486</v>
       </c>
       <c r="C3" s="2"/>
@@ -2612,7 +2552,7 @@
       <c r="A4" s="4" t="s">
         <v>26</v>
       </c>
-      <c r="B4" s="16">
+      <c r="B4" s="15">
         <v>0</v>
       </c>
       <c r="C4" s="4"/>
@@ -2622,7 +2562,7 @@
       <c r="A5" s="2" t="s">
         <v>27</v>
       </c>
-      <c r="B5" s="16">
+      <c r="B5" s="15">
         <v>0</v>
       </c>
       <c r="C5" s="2"/>
@@ -2632,7 +2572,7 @@
       <c r="A6" s="4" t="s">
         <v>28</v>
       </c>
-      <c r="B6" s="16">
+      <c r="B6" s="15">
         <v>0</v>
       </c>
       <c r="C6" s="4"/>
@@ -2642,7 +2582,7 @@
       <c r="A7" s="2" t="s">
         <v>29</v>
       </c>
-      <c r="B7" s="16">
+      <c r="B7" s="15">
         <v>388016486</v>
       </c>
       <c r="C7" s="2"/>
@@ -2654,7 +2594,7 @@
       <c r="A8" s="4" t="s">
         <v>31</v>
       </c>
-      <c r="B8" s="16">
+      <c r="B8" s="15">
         <v>34426811</v>
       </c>
       <c r="C8" s="4"/>
@@ -2664,10 +2604,10 @@
       <c r="A9" s="2" t="s">
         <v>32</v>
       </c>
-      <c r="B9" s="16">
+      <c r="B9" s="15">
         <v>15596872</v>
       </c>
-      <c r="C9" s="14">
+      <c r="C9" s="13">
         <f>B9/B8</f>
         <v>0.45304434384003794</v>
       </c>
@@ -2697,21 +2637,21 @@
   <cols>
     <col min="1" max="1" width="32" customWidth="1"/>
     <col min="2" max="2" width="22" customWidth="1"/>
-    <col min="3" max="3" width="14" style="24" customWidth="1"/>
+    <col min="3" max="3" width="14" style="23" customWidth="1"/>
     <col min="4" max="4" width="40" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:8" ht="21.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A1" s="36" t="s">
+      <c r="A1" s="33" t="s">
         <v>34</v>
       </c>
-      <c r="B1" s="36"/>
-      <c r="C1" s="36"/>
-      <c r="D1" s="36"/>
-      <c r="E1" s="36"/>
-      <c r="F1" s="36"/>
-      <c r="G1" s="36"/>
-      <c r="H1" s="36"/>
+      <c r="B1" s="33"/>
+      <c r="C1" s="33"/>
+      <c r="D1" s="33"/>
+      <c r="E1" s="33"/>
+      <c r="F1" s="33"/>
+      <c r="G1" s="33"/>
+      <c r="H1" s="33"/>
     </row>
     <row r="2" spans="1:8" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A2" s="1" t="s">
@@ -2731,10 +2671,10 @@
       <c r="A3" s="2" t="s">
         <v>35</v>
       </c>
-      <c r="B3" s="19">
+      <c r="B3" s="18">
         <v>355587125</v>
       </c>
-      <c r="C3" s="21"/>
+      <c r="C3" s="20"/>
       <c r="D3" s="2" t="s">
         <v>36</v>
       </c>
@@ -2743,32 +2683,32 @@
       <c r="A4" s="4" t="s">
         <v>37</v>
       </c>
-      <c r="B4" s="20" t="s">
+      <c r="B4" s="19" t="s">
         <v>38</v>
       </c>
-      <c r="C4" s="22"/>
+      <c r="C4" s="21"/>
       <c r="D4" s="4" t="s">
         <v>39</v>
       </c>
     </row>
     <row r="5" spans="1:8" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A5" s="4" t="s">
-        <v>198</v>
-      </c>
-      <c r="B5" s="20">
+        <v>178</v>
+      </c>
+      <c r="B5" s="19">
         <v>0.68799999999999994</v>
       </c>
-      <c r="C5" s="22"/>
+      <c r="C5" s="21"/>
       <c r="D5" s="4"/>
     </row>
     <row r="6" spans="1:8" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A6" s="2" t="s">
         <v>40</v>
       </c>
-      <c r="B6" s="20">
+      <c r="B6" s="19">
         <v>0.40899999999999997</v>
       </c>
-      <c r="C6" s="23">
+      <c r="C6" s="22">
         <f>B4-B6</f>
         <v>0.59099999999999997</v>
       </c>
@@ -2780,10 +2720,10 @@
       <c r="A7" s="4" t="s">
         <v>31</v>
       </c>
-      <c r="B7" s="19">
+      <c r="B7" s="18">
         <v>34426811</v>
       </c>
-      <c r="C7" s="22"/>
+      <c r="C7" s="21"/>
       <c r="D7" s="4" t="s">
         <v>36</v>
       </c>
@@ -2792,10 +2732,10 @@
       <c r="A8" s="2" t="s">
         <v>32</v>
       </c>
-      <c r="B8" s="19">
+      <c r="B8" s="18">
         <v>15596872</v>
       </c>
-      <c r="C8" s="21"/>
+      <c r="C8" s="20"/>
       <c r="D8" s="2" t="s">
         <v>36</v>
       </c>
@@ -2804,11 +2744,11 @@
       <c r="A9" s="4" t="s">
         <v>42</v>
       </c>
-      <c r="B9" s="20">
+      <c r="B9" s="19">
         <f>(B7-B8)/B7</f>
         <v>0.54695565615996211</v>
       </c>
-      <c r="C9" s="22"/>
+      <c r="C9" s="21"/>
       <c r="D9" s="4" t="s">
         <v>43</v>
       </c>
@@ -2817,10 +2757,10 @@
       <c r="A10" s="2" t="s">
         <v>44</v>
       </c>
-      <c r="B10" s="18" t="s">
-        <v>196</v>
-      </c>
-      <c r="C10" s="21"/>
+      <c r="B10" s="17" t="s">
+        <v>176</v>
+      </c>
+      <c r="C10" s="20"/>
       <c r="D10" s="2" t="s">
         <v>45</v>
       </c>
@@ -2853,16 +2793,16 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:8" ht="21.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A1" s="36" t="s">
+      <c r="A1" s="33" t="s">
         <v>46</v>
       </c>
-      <c r="B1" s="36"/>
-      <c r="C1" s="36"/>
-      <c r="D1" s="36"/>
-      <c r="E1" s="36"/>
-      <c r="F1" s="36"/>
-      <c r="G1" s="36"/>
-      <c r="H1" s="36"/>
+      <c r="B1" s="33"/>
+      <c r="C1" s="33"/>
+      <c r="D1" s="33"/>
+      <c r="E1" s="33"/>
+      <c r="F1" s="33"/>
+      <c r="G1" s="33"/>
+      <c r="H1" s="33"/>
     </row>
     <row r="2" spans="1:8" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A2" s="1" t="s">
@@ -2885,10 +2825,10 @@
       <c r="A3" s="2" t="s">
         <v>49</v>
       </c>
-      <c r="B3" s="15">
+      <c r="B3" s="14">
         <v>204059236</v>
       </c>
-      <c r="C3" s="14">
+      <c r="C3" s="13">
         <f>B3/Commercial_Info!$B$3</f>
         <v>0.52590352050144595</v>
       </c>
@@ -2896,16 +2836,16 @@
         <v>50</v>
       </c>
       <c r="E3" s="2"/>
-      <c r="G3" s="25"/>
+      <c r="G3" s="24"/>
     </row>
     <row r="4" spans="1:8" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A4" s="4" t="s">
         <v>51</v>
       </c>
-      <c r="B4" s="15">
+      <c r="B4" s="14">
         <v>152961744</v>
       </c>
-      <c r="C4" s="14">
+      <c r="C4" s="13">
         <f>B4/Commercial_Info!$B$3</f>
         <v>0.39421454891481078</v>
       </c>
@@ -2918,10 +2858,10 @@
       <c r="A5" s="2" t="s">
         <v>53</v>
       </c>
-      <c r="B5" s="15">
+      <c r="B5" s="14">
         <v>152961744</v>
       </c>
-      <c r="C5" s="14">
+      <c r="C5" s="13">
         <f>B5/Commercial_Info!$B$3</f>
         <v>0.39421454891481078</v>
       </c>
@@ -2934,7 +2874,7 @@
       <c r="A6" s="4" t="s">
         <v>54</v>
       </c>
-      <c r="B6" s="15">
+      <c r="B6" s="14">
         <v>0</v>
       </c>
       <c r="C6" s="4"/>
@@ -2947,10 +2887,10 @@
       <c r="A7" s="2" t="s">
         <v>56</v>
       </c>
-      <c r="B7" s="15">
+      <c r="B7" s="14">
         <v>68039022</v>
       </c>
-      <c r="C7" s="14">
+      <c r="C7" s="13">
         <f>B7/Commercial_Info!$B$3</f>
         <v>0.17535085352017749</v>
       </c>
@@ -2961,9 +2901,9 @@
     </row>
     <row r="8" spans="1:8" ht="28.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A8" s="4" t="s">
-        <v>197</v>
-      </c>
-      <c r="B8" s="27" t="str">
+        <v>177</v>
+      </c>
+      <c r="B8" s="26" t="str">
         <f>ROUNDUP(C4*100,0)&amp;"%"&amp;" / "&amp;ROUNDUP(Budgetary_Info!B6*100,0)&amp;"%"</f>
         <v>40% / 41%</v>
       </c>
@@ -3002,16 +2942,16 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:8" ht="21.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A1" s="36" t="s">
+      <c r="A1" s="33" t="s">
         <v>58</v>
       </c>
-      <c r="B1" s="36"/>
-      <c r="C1" s="36"/>
-      <c r="D1" s="36"/>
-      <c r="E1" s="36"/>
-      <c r="F1" s="36"/>
-      <c r="G1" s="36"/>
-      <c r="H1" s="36"/>
+      <c r="B1" s="33"/>
+      <c r="C1" s="33"/>
+      <c r="D1" s="33"/>
+      <c r="E1" s="33"/>
+      <c r="F1" s="33"/>
+      <c r="G1" s="33"/>
+      <c r="H1" s="33"/>
     </row>
     <row r="2" spans="1:8" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A2" s="1" t="s">
@@ -3058,7 +2998,7 @@
       <c r="B5" s="3">
         <v>68</v>
       </c>
-      <c r="C5" s="28">
+      <c r="C5" s="27">
         <f>B5/B6</f>
         <v>0.52631578947368429</v>
       </c>
@@ -3107,24 +3047,24 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:8" ht="21.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A1" s="36" t="s">
+      <c r="A1" s="33" t="s">
         <v>70</v>
       </c>
-      <c r="B1" s="36"/>
-      <c r="C1" s="36"/>
-      <c r="D1" s="36"/>
-      <c r="E1" s="36"/>
-      <c r="F1" s="36"/>
-      <c r="G1" s="36"/>
-      <c r="H1" s="36"/>
+      <c r="B1" s="33"/>
+      <c r="C1" s="33"/>
+      <c r="D1" s="33"/>
+      <c r="E1" s="33"/>
+      <c r="F1" s="33"/>
+      <c r="G1" s="33"/>
+      <c r="H1" s="33"/>
     </row>
     <row r="2" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A2" s="37" t="s">
+      <c r="A2" s="34" t="s">
         <v>71</v>
       </c>
-      <c r="B2" s="37"/>
-      <c r="C2" s="37"/>
-      <c r="D2" s="37"/>
+      <c r="B2" s="34"/>
+      <c r="C2" s="34"/>
+      <c r="D2" s="34"/>
     </row>
     <row r="3" spans="1:8" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A3" s="1" t="s">
@@ -3179,7 +3119,7 @@
       <c r="A7" s="2" t="s">
         <v>78</v>
       </c>
-      <c r="B7" s="26">
+      <c r="B7" s="25">
         <f>B5/B4</f>
         <v>0.87083888149134492</v>
       </c>
@@ -3190,12 +3130,12 @@
     </row>
     <row r="8" spans="1:8" ht="6" customHeight="1" x14ac:dyDescent="0.25"/>
     <row r="9" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A9" s="37" t="s">
+      <c r="A9" s="34" t="s">
         <v>80</v>
       </c>
-      <c r="B9" s="37"/>
-      <c r="C9" s="37"/>
-      <c r="D9" s="37"/>
+      <c r="B9" s="34"/>
+      <c r="C9" s="34"/>
+      <c r="D9" s="34"/>
     </row>
     <row r="10" spans="1:8" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A10" s="1" t="s">
@@ -3235,12 +3175,12 @@
     </row>
     <row r="13" spans="1:8" ht="6" customHeight="1" x14ac:dyDescent="0.25"/>
     <row r="14" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A14" s="37" t="s">
+      <c r="A14" s="34" t="s">
         <v>86</v>
       </c>
-      <c r="B14" s="37"/>
-      <c r="C14" s="37"/>
-      <c r="D14" s="37"/>
+      <c r="B14" s="34"/>
+      <c r="C14" s="34"/>
+      <c r="D14" s="34"/>
     </row>
     <row r="15" spans="1:8" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A15" s="1" t="s">
@@ -3362,16 +3302,16 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:8" ht="21.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A1" s="36" t="s">
+      <c r="A1" s="33" t="s">
         <v>101</v>
       </c>
-      <c r="B1" s="36"/>
-      <c r="C1" s="36"/>
-      <c r="D1" s="36"/>
-      <c r="E1" s="36"/>
-      <c r="F1" s="36"/>
-      <c r="G1" s="36"/>
-      <c r="H1" s="36"/>
+      <c r="B1" s="33"/>
+      <c r="C1" s="33"/>
+      <c r="D1" s="33"/>
+      <c r="E1" s="33"/>
+      <c r="F1" s="33"/>
+      <c r="G1" s="33"/>
+      <c r="H1" s="33"/>
     </row>
     <row r="2" spans="1:8" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A2" s="1" t="s">
@@ -3397,10 +3337,10 @@
       <c r="A3" s="2" t="s">
         <v>107</v>
       </c>
-      <c r="B3" s="29">
+      <c r="B3" s="28">
         <v>92.78</v>
       </c>
-      <c r="C3" s="29">
+      <c r="C3" s="28">
         <v>84.28</v>
       </c>
       <c r="D3" s="5">
@@ -3418,10 +3358,10 @@
       <c r="A4" s="4" t="s">
         <v>110</v>
       </c>
-      <c r="B4" s="30">
+      <c r="B4" s="29">
         <v>100</v>
       </c>
-      <c r="C4" s="30">
+      <c r="C4" s="29">
         <v>99.25</v>
       </c>
       <c r="D4" s="6">
@@ -3439,10 +3379,10 @@
       <c r="A5" s="2" t="s">
         <v>113</v>
       </c>
-      <c r="B5" s="29">
+      <c r="B5" s="28">
         <v>100</v>
       </c>
-      <c r="C5" s="29">
+      <c r="C5" s="28">
         <v>95.54</v>
       </c>
       <c r="D5" s="5">
@@ -3460,10 +3400,10 @@
       <c r="A6" s="4" t="s">
         <v>116</v>
       </c>
-      <c r="B6" s="30">
+      <c r="B6" s="29">
         <v>95.92</v>
       </c>
-      <c r="C6" s="30">
+      <c r="C6" s="29">
         <v>90.82</v>
       </c>
       <c r="D6" s="6">
@@ -3481,10 +3421,10 @@
       <c r="A7" s="2" t="s">
         <v>117</v>
       </c>
-      <c r="B7" s="29">
+      <c r="B7" s="28">
         <v>100</v>
       </c>
-      <c r="C7" s="29">
+      <c r="C7" s="28">
         <v>93.32</v>
       </c>
       <c r="D7" s="5">
@@ -3502,10 +3442,10 @@
       <c r="A8" s="4" t="s">
         <v>118</v>
       </c>
-      <c r="B8" s="30">
+      <c r="B8" s="29">
         <v>68.05</v>
       </c>
-      <c r="C8" s="30">
+      <c r="C8" s="29">
         <v>22.08</v>
       </c>
       <c r="D8" s="6">
@@ -3546,16 +3486,16 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:8" ht="21.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A1" s="36" t="s">
+      <c r="A1" s="33" t="s">
         <v>120</v>
       </c>
-      <c r="B1" s="36"/>
-      <c r="C1" s="36"/>
-      <c r="D1" s="36"/>
-      <c r="E1" s="36"/>
-      <c r="F1" s="36"/>
-      <c r="G1" s="36"/>
-      <c r="H1" s="36"/>
+      <c r="B1" s="33"/>
+      <c r="C1" s="33"/>
+      <c r="D1" s="33"/>
+      <c r="E1" s="33"/>
+      <c r="F1" s="33"/>
+      <c r="G1" s="33"/>
+      <c r="H1" s="33"/>
     </row>
     <row r="2" spans="1:8" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A2" s="1" t="s">

--- a/Dashboard_Data.xlsx
+++ b/Dashboard_Data.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://alfanargroup-my.sharepoint.com/personal/ahmed_abdelzaher_alfanar_com/Documents/SDCC Dashboard/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="193" documentId="14_{682A7E4B-1055-4B0F-805D-134F59E89DE5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{F705040F-576A-44F7-8FEF-01C7EF0FC380}"/>
+  <xr:revisionPtr revIDLastSave="196" documentId="14_{682A7E4B-1055-4B0F-805D-134F59E89DE5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{0F59A4CF-FCA6-4A64-ACA2-36A76E1298F0}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" tabRatio="500" firstSheet="3" activeTab="9" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -842,7 +842,7 @@
     <xf numFmtId="43" fontId="6" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="9" fontId="6" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="40">
+  <cellXfs count="37">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -932,26 +932,17 @@
     </xf>
     <xf numFmtId="15" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="9" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="17" fontId="3" fillId="4" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="17" fontId="3" fillId="6" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="17" fontId="3" fillId="7" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="17" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="17" fontId="3" fillId="8" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="3">
@@ -1230,16 +1221,16 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:8" ht="21.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A1" s="33" t="s">
+      <c r="A1" s="35" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="33"/>
-      <c r="C1" s="33"/>
-      <c r="D1" s="33"/>
-      <c r="E1" s="33"/>
-      <c r="F1" s="33"/>
-      <c r="G1" s="33"/>
-      <c r="H1" s="33"/>
+      <c r="B1" s="35"/>
+      <c r="C1" s="35"/>
+      <c r="D1" s="35"/>
+      <c r="E1" s="35"/>
+      <c r="F1" s="35"/>
+      <c r="G1" s="35"/>
+      <c r="H1" s="35"/>
     </row>
     <row r="2" spans="1:8" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A2" s="1" t="s">
@@ -1312,16 +1303,16 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:8" ht="21.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A1" s="33" t="s">
+      <c r="A1" s="35" t="s">
         <v>130</v>
       </c>
-      <c r="B1" s="33"/>
-      <c r="C1" s="33"/>
-      <c r="D1" s="33"/>
-      <c r="E1" s="33"/>
-      <c r="F1" s="33"/>
-      <c r="G1" s="33"/>
-      <c r="H1" s="33"/>
+      <c r="B1" s="35"/>
+      <c r="C1" s="35"/>
+      <c r="D1" s="35"/>
+      <c r="E1" s="35"/>
+      <c r="F1" s="35"/>
+      <c r="G1" s="35"/>
+      <c r="H1" s="35"/>
     </row>
     <row r="2" spans="1:8" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A2" s="1" t="s">
@@ -1350,8 +1341,8 @@
       </c>
     </row>
     <row r="3" spans="1:8" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A3" s="35">
-        <v>46350</v>
+      <c r="A3" s="33">
+        <v>45620</v>
       </c>
       <c r="B3" s="2" t="s">
         <v>138</v>
@@ -1372,8 +1363,8 @@
       </c>
     </row>
     <row r="4" spans="1:8" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A4" s="36">
-        <v>46380</v>
+      <c r="A4" s="34">
+        <v>45650</v>
       </c>
       <c r="B4" s="4" t="s">
         <v>141</v>
@@ -1388,8 +1379,8 @@
       <c r="H4" s="4"/>
     </row>
     <row r="5" spans="1:8" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A5" s="35">
-        <v>46411</v>
+      <c r="A5" s="33">
+        <v>45681</v>
       </c>
       <c r="B5" s="2" t="s">
         <v>141</v>
@@ -1404,8 +1395,8 @@
       <c r="H5" s="2"/>
     </row>
     <row r="6" spans="1:8" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A6" s="36">
-        <v>46442</v>
+      <c r="A6" s="34">
+        <v>45712</v>
       </c>
       <c r="B6" s="4" t="s">
         <v>141</v>
@@ -1420,8 +1411,8 @@
       <c r="H6" s="4"/>
     </row>
     <row r="7" spans="1:8" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A7" s="35">
-        <v>46470</v>
+      <c r="A7" s="33">
+        <v>45740</v>
       </c>
       <c r="B7" s="2" t="s">
         <v>138</v>
@@ -1440,8 +1431,8 @@
       <c r="H7" s="2"/>
     </row>
     <row r="8" spans="1:8" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A8" s="36">
-        <v>46501</v>
+      <c r="A8" s="34">
+        <v>45771</v>
       </c>
       <c r="B8" s="4" t="s">
         <v>138</v>
@@ -1462,8 +1453,8 @@
       </c>
     </row>
     <row r="9" spans="1:8" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A9" s="35">
-        <v>46531</v>
+      <c r="A9" s="33">
+        <v>45801</v>
       </c>
       <c r="B9" s="2" t="s">
         <v>141</v>
@@ -1478,8 +1469,8 @@
       <c r="H9" s="2"/>
     </row>
     <row r="10" spans="1:8" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A10" s="36">
-        <v>46562</v>
+      <c r="A10" s="34">
+        <v>45832</v>
       </c>
       <c r="B10" s="4" t="s">
         <v>138</v>
@@ -1498,8 +1489,8 @@
       <c r="H10" s="4"/>
     </row>
     <row r="11" spans="1:8" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A11" s="35">
-        <v>46592</v>
+      <c r="A11" s="33">
+        <v>45862</v>
       </c>
       <c r="B11" s="2" t="s">
         <v>141</v>
@@ -1514,8 +1505,8 @@
       <c r="H11" s="2"/>
     </row>
     <row r="12" spans="1:8" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A12" s="36">
-        <v>46623</v>
+      <c r="A12" s="34">
+        <v>45893</v>
       </c>
       <c r="B12" s="4" t="s">
         <v>141</v>
@@ -1530,8 +1521,8 @@
       <c r="H12" s="4"/>
     </row>
     <row r="13" spans="1:8" ht="25.5" x14ac:dyDescent="0.25">
-      <c r="A13" s="35">
-        <v>46654</v>
+      <c r="A13" s="33">
+        <v>45924</v>
       </c>
       <c r="B13" s="2" t="s">
         <v>141</v>
@@ -1548,8 +1539,8 @@
       <c r="H13" s="2"/>
     </row>
     <row r="14" spans="1:8" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A14" s="36">
-        <v>46684</v>
+      <c r="A14" s="34">
+        <v>45954</v>
       </c>
       <c r="B14" s="4" t="s">
         <v>141</v>
@@ -1566,8 +1557,8 @@
       <c r="H14" s="4"/>
     </row>
     <row r="15" spans="1:8" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A15" s="35">
-        <v>46715</v>
+      <c r="A15" s="33">
+        <v>45985</v>
       </c>
       <c r="B15" s="2" t="s">
         <v>138</v>
@@ -1584,8 +1575,8 @@
       <c r="H15" s="2"/>
     </row>
     <row r="16" spans="1:8" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A16" s="36">
-        <v>46745</v>
+      <c r="A16" s="34">
+        <v>46015</v>
       </c>
       <c r="B16" s="4" t="s">
         <v>141</v>
@@ -1602,8 +1593,8 @@
       <c r="H16" s="4"/>
     </row>
     <row r="17" spans="1:8" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A17" s="35">
-        <v>46776</v>
+      <c r="A17" s="33">
+        <v>46046</v>
       </c>
       <c r="B17" s="2" t="s">
         <v>141</v>
@@ -1618,8 +1609,8 @@
       <c r="H17" s="2"/>
     </row>
     <row r="18" spans="1:8" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A18" s="36">
-        <v>46807</v>
+      <c r="A18" s="34">
+        <v>46077</v>
       </c>
       <c r="B18" s="4" t="s">
         <v>141</v>
@@ -1634,8 +1625,8 @@
       <c r="H18" s="4"/>
     </row>
     <row r="19" spans="1:8" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A19" s="35">
-        <v>46836</v>
+      <c r="A19" s="33">
+        <v>46105</v>
       </c>
       <c r="B19" s="2" t="s">
         <v>141</v>
@@ -1650,8 +1641,8 @@
       <c r="H19" s="2"/>
     </row>
     <row r="20" spans="1:8" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A20" s="35">
-        <v>46867</v>
+      <c r="A20" s="34">
+        <v>46136</v>
       </c>
       <c r="B20" s="2" t="s">
         <v>141</v>
@@ -1666,8 +1657,8 @@
       <c r="H20" s="2"/>
     </row>
     <row r="21" spans="1:8" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A21" s="35">
-        <v>46897</v>
+      <c r="A21" s="33">
+        <v>46166</v>
       </c>
       <c r="B21" s="2" t="s">
         <v>141</v>
@@ -1682,8 +1673,8 @@
       <c r="H21" s="2"/>
     </row>
     <row r="22" spans="1:8" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A22" s="35">
-        <v>46928</v>
+      <c r="A22" s="34">
+        <v>46197</v>
       </c>
       <c r="B22" s="2" t="s">
         <v>141</v>
@@ -1698,8 +1689,8 @@
       <c r="H22" s="2"/>
     </row>
     <row r="23" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A23" s="37">
-        <v>46204</v>
+      <c r="A23" s="33">
+        <v>46227</v>
       </c>
       <c r="B23" s="8" t="s">
         <v>141</v>
@@ -1720,8 +1711,8 @@
       </c>
     </row>
     <row r="24" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A24" s="35">
-        <v>46235</v>
+      <c r="A24" s="34">
+        <v>46258</v>
       </c>
       <c r="B24" s="2" t="s">
         <v>141</v>
@@ -1736,8 +1727,8 @@
       <c r="H24" s="2"/>
     </row>
     <row r="25" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A25" s="35">
-        <v>46266</v>
+      <c r="A25" s="33">
+        <v>46289</v>
       </c>
       <c r="B25" s="2" t="s">
         <v>141</v>
@@ -1752,8 +1743,8 @@
       <c r="H25" s="2"/>
     </row>
     <row r="26" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A26" s="35">
-        <v>46296</v>
+      <c r="A26" s="34">
+        <v>46319</v>
       </c>
       <c r="B26" s="2" t="s">
         <v>141</v>
@@ -1768,8 +1759,8 @@
       <c r="H26" s="2"/>
     </row>
     <row r="27" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A27" s="38">
-        <v>46327</v>
+      <c r="A27" s="33">
+        <v>46350</v>
       </c>
       <c r="B27" s="2" t="s">
         <v>141</v>
@@ -1779,8 +1770,8 @@
       </c>
     </row>
     <row r="28" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A28" s="38">
-        <v>46357</v>
+      <c r="A28" s="34">
+        <v>46380</v>
       </c>
       <c r="B28" s="2" t="s">
         <v>141</v>
@@ -1790,8 +1781,8 @@
       </c>
     </row>
     <row r="29" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A29" s="38">
-        <v>46388</v>
+      <c r="A29" s="33">
+        <v>46411</v>
       </c>
       <c r="B29" s="2" t="s">
         <v>141</v>
@@ -1801,8 +1792,8 @@
       </c>
     </row>
     <row r="30" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A30" s="39">
-        <v>46419</v>
+      <c r="A30" s="34">
+        <v>46442</v>
       </c>
       <c r="B30" s="9" t="s">
         <v>141</v>
@@ -1851,16 +1842,16 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:8" ht="21.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A1" s="33" t="s">
+      <c r="A1" s="35" t="s">
         <v>151</v>
       </c>
-      <c r="B1" s="33"/>
-      <c r="C1" s="33"/>
-      <c r="D1" s="33"/>
-      <c r="E1" s="33"/>
-      <c r="F1" s="33"/>
-      <c r="G1" s="33"/>
-      <c r="H1" s="33"/>
+      <c r="B1" s="35"/>
+      <c r="C1" s="35"/>
+      <c r="D1" s="35"/>
+      <c r="E1" s="35"/>
+      <c r="F1" s="35"/>
+      <c r="G1" s="35"/>
+      <c r="H1" s="35"/>
     </row>
     <row r="2" spans="1:8" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A2" s="1" t="s">
@@ -1990,16 +1981,16 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:21" ht="21.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A1" s="33" t="s">
+      <c r="A1" s="35" t="s">
         <v>158</v>
       </c>
-      <c r="B1" s="33"/>
-      <c r="C1" s="33"/>
-      <c r="D1" s="33"/>
-      <c r="E1" s="33"/>
-      <c r="F1" s="33"/>
-      <c r="G1" s="33"/>
-      <c r="H1" s="33"/>
+      <c r="B1" s="35"/>
+      <c r="C1" s="35"/>
+      <c r="D1" s="35"/>
+      <c r="E1" s="35"/>
+      <c r="F1" s="35"/>
+      <c r="G1" s="35"/>
+      <c r="H1" s="35"/>
     </row>
     <row r="2" spans="1:21" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A2" s="1" t="s">
@@ -2319,16 +2310,16 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:8" ht="21.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A1" s="33" t="s">
+      <c r="A1" s="35" t="s">
         <v>167</v>
       </c>
-      <c r="B1" s="33"/>
-      <c r="C1" s="33"/>
-      <c r="D1" s="33"/>
-      <c r="E1" s="33"/>
-      <c r="F1" s="33"/>
-      <c r="G1" s="33"/>
-      <c r="H1" s="33"/>
+      <c r="B1" s="35"/>
+      <c r="C1" s="35"/>
+      <c r="D1" s="35"/>
+      <c r="E1" s="35"/>
+      <c r="F1" s="35"/>
+      <c r="G1" s="35"/>
+      <c r="H1" s="35"/>
     </row>
     <row r="2" spans="1:8" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A2" s="1" t="s">
@@ -2396,16 +2387,16 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:8" ht="21.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A1" s="33" t="s">
+      <c r="A1" s="35" t="s">
         <v>9</v>
       </c>
-      <c r="B1" s="33"/>
-      <c r="C1" s="33"/>
-      <c r="D1" s="33"/>
-      <c r="E1" s="33"/>
-      <c r="F1" s="33"/>
-      <c r="G1" s="33"/>
-      <c r="H1" s="33"/>
+      <c r="B1" s="35"/>
+      <c r="C1" s="35"/>
+      <c r="D1" s="35"/>
+      <c r="E1" s="35"/>
+      <c r="F1" s="35"/>
+      <c r="G1" s="35"/>
+      <c r="H1" s="35"/>
     </row>
     <row r="2" spans="1:8" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A2" s="1" t="s">
@@ -2513,16 +2504,16 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:8" ht="21.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A1" s="33" t="s">
+      <c r="A1" s="35" t="s">
         <v>22</v>
       </c>
-      <c r="B1" s="33"/>
-      <c r="C1" s="33"/>
-      <c r="D1" s="33"/>
-      <c r="E1" s="33"/>
-      <c r="F1" s="33"/>
-      <c r="G1" s="33"/>
-      <c r="H1" s="33"/>
+      <c r="B1" s="35"/>
+      <c r="C1" s="35"/>
+      <c r="D1" s="35"/>
+      <c r="E1" s="35"/>
+      <c r="F1" s="35"/>
+      <c r="G1" s="35"/>
+      <c r="H1" s="35"/>
     </row>
     <row r="2" spans="1:8" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A2" s="1" t="s">
@@ -2642,16 +2633,16 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:8" ht="21.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A1" s="33" t="s">
+      <c r="A1" s="35" t="s">
         <v>34</v>
       </c>
-      <c r="B1" s="33"/>
-      <c r="C1" s="33"/>
-      <c r="D1" s="33"/>
-      <c r="E1" s="33"/>
-      <c r="F1" s="33"/>
-      <c r="G1" s="33"/>
-      <c r="H1" s="33"/>
+      <c r="B1" s="35"/>
+      <c r="C1" s="35"/>
+      <c r="D1" s="35"/>
+      <c r="E1" s="35"/>
+      <c r="F1" s="35"/>
+      <c r="G1" s="35"/>
+      <c r="H1" s="35"/>
     </row>
     <row r="2" spans="1:8" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A2" s="1" t="s">
@@ -2793,16 +2784,16 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:8" ht="21.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A1" s="33" t="s">
+      <c r="A1" s="35" t="s">
         <v>46</v>
       </c>
-      <c r="B1" s="33"/>
-      <c r="C1" s="33"/>
-      <c r="D1" s="33"/>
-      <c r="E1" s="33"/>
-      <c r="F1" s="33"/>
-      <c r="G1" s="33"/>
-      <c r="H1" s="33"/>
+      <c r="B1" s="35"/>
+      <c r="C1" s="35"/>
+      <c r="D1" s="35"/>
+      <c r="E1" s="35"/>
+      <c r="F1" s="35"/>
+      <c r="G1" s="35"/>
+      <c r="H1" s="35"/>
     </row>
     <row r="2" spans="1:8" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A2" s="1" t="s">
@@ -2942,16 +2933,16 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:8" ht="21.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A1" s="33" t="s">
+      <c r="A1" s="35" t="s">
         <v>58</v>
       </c>
-      <c r="B1" s="33"/>
-      <c r="C1" s="33"/>
-      <c r="D1" s="33"/>
-      <c r="E1" s="33"/>
-      <c r="F1" s="33"/>
-      <c r="G1" s="33"/>
-      <c r="H1" s="33"/>
+      <c r="B1" s="35"/>
+      <c r="C1" s="35"/>
+      <c r="D1" s="35"/>
+      <c r="E1" s="35"/>
+      <c r="F1" s="35"/>
+      <c r="G1" s="35"/>
+      <c r="H1" s="35"/>
     </row>
     <row r="2" spans="1:8" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A2" s="1" t="s">
@@ -3047,24 +3038,24 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:8" ht="21.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A1" s="33" t="s">
+      <c r="A1" s="35" t="s">
         <v>70</v>
       </c>
-      <c r="B1" s="33"/>
-      <c r="C1" s="33"/>
-      <c r="D1" s="33"/>
-      <c r="E1" s="33"/>
-      <c r="F1" s="33"/>
-      <c r="G1" s="33"/>
-      <c r="H1" s="33"/>
+      <c r="B1" s="35"/>
+      <c r="C1" s="35"/>
+      <c r="D1" s="35"/>
+      <c r="E1" s="35"/>
+      <c r="F1" s="35"/>
+      <c r="G1" s="35"/>
+      <c r="H1" s="35"/>
     </row>
     <row r="2" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A2" s="34" t="s">
+      <c r="A2" s="36" t="s">
         <v>71</v>
       </c>
-      <c r="B2" s="34"/>
-      <c r="C2" s="34"/>
-      <c r="D2" s="34"/>
+      <c r="B2" s="36"/>
+      <c r="C2" s="36"/>
+      <c r="D2" s="36"/>
     </row>
     <row r="3" spans="1:8" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A3" s="1" t="s">
@@ -3130,12 +3121,12 @@
     </row>
     <row r="8" spans="1:8" ht="6" customHeight="1" x14ac:dyDescent="0.25"/>
     <row r="9" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A9" s="34" t="s">
+      <c r="A9" s="36" t="s">
         <v>80</v>
       </c>
-      <c r="B9" s="34"/>
-      <c r="C9" s="34"/>
-      <c r="D9" s="34"/>
+      <c r="B9" s="36"/>
+      <c r="C9" s="36"/>
+      <c r="D9" s="36"/>
     </row>
     <row r="10" spans="1:8" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A10" s="1" t="s">
@@ -3175,12 +3166,12 @@
     </row>
     <row r="13" spans="1:8" ht="6" customHeight="1" x14ac:dyDescent="0.25"/>
     <row r="14" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A14" s="34" t="s">
+      <c r="A14" s="36" t="s">
         <v>86</v>
       </c>
-      <c r="B14" s="34"/>
-      <c r="C14" s="34"/>
-      <c r="D14" s="34"/>
+      <c r="B14" s="36"/>
+      <c r="C14" s="36"/>
+      <c r="D14" s="36"/>
     </row>
     <row r="15" spans="1:8" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A15" s="1" t="s">
@@ -3302,16 +3293,16 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:8" ht="21.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A1" s="33" t="s">
+      <c r="A1" s="35" t="s">
         <v>101</v>
       </c>
-      <c r="B1" s="33"/>
-      <c r="C1" s="33"/>
-      <c r="D1" s="33"/>
-      <c r="E1" s="33"/>
-      <c r="F1" s="33"/>
-      <c r="G1" s="33"/>
-      <c r="H1" s="33"/>
+      <c r="B1" s="35"/>
+      <c r="C1" s="35"/>
+      <c r="D1" s="35"/>
+      <c r="E1" s="35"/>
+      <c r="F1" s="35"/>
+      <c r="G1" s="35"/>
+      <c r="H1" s="35"/>
     </row>
     <row r="2" spans="1:8" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A2" s="1" t="s">
@@ -3486,16 +3477,16 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:8" ht="21.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A1" s="33" t="s">
+      <c r="A1" s="35" t="s">
         <v>120</v>
       </c>
-      <c r="B1" s="33"/>
-      <c r="C1" s="33"/>
-      <c r="D1" s="33"/>
-      <c r="E1" s="33"/>
-      <c r="F1" s="33"/>
-      <c r="G1" s="33"/>
-      <c r="H1" s="33"/>
+      <c r="B1" s="35"/>
+      <c r="C1" s="35"/>
+      <c r="D1" s="35"/>
+      <c r="E1" s="35"/>
+      <c r="F1" s="35"/>
+      <c r="G1" s="35"/>
+      <c r="H1" s="35"/>
     </row>
     <row r="2" spans="1:8" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A2" s="1" t="s">

--- a/Dashboard_Data.xlsx
+++ b/Dashboard_Data.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://alfanargroup-my.sharepoint.com/personal/ahmed_abdelzaher_alfanar_com/Documents/SDCC Dashboard/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="196" documentId="14_{682A7E4B-1055-4B0F-805D-134F59E89DE5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{0F59A4CF-FCA6-4A64-ACA2-36A76E1298F0}"/>
+  <xr:revisionPtr revIDLastSave="212" documentId="14_{682A7E4B-1055-4B0F-805D-134F59E89DE5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{81FBB68A-9266-4B34-9684-0298CBA397A8}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" tabRatio="500" firstSheet="3" activeTab="9" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" tabRatio="500" firstSheet="5" activeTab="11" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Header" sheetId="1" r:id="rId1"/>
@@ -48,7 +48,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="340" uniqueCount="212">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="342" uniqueCount="211">
   <si>
     <t>HEADER — Dashboard Title &amp; PM</t>
   </si>
@@ -669,9 +669,6 @@
   </si>
   <si>
     <t>Fire Pumps</t>
-  </si>
-  <si>
-    <t>80%*</t>
   </si>
   <si>
     <t>Security System</t>
@@ -842,7 +839,7 @@
     <xf numFmtId="43" fontId="6" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="9" fontId="6" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="37">
+  <cellXfs count="38">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -942,6 +939,9 @@
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="9" fontId="3" fillId="6" borderId="1" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -1530,7 +1530,9 @@
       <c r="C13" s="2" t="s">
         <v>179</v>
       </c>
-      <c r="D13" s="2"/>
+      <c r="D13" s="2" t="s">
+        <v>145</v>
+      </c>
       <c r="E13" s="2" t="s">
         <v>141</v>
       </c>
@@ -1538,7 +1540,7 @@
       <c r="G13" s="2"/>
       <c r="H13" s="2"/>
     </row>
-    <row r="14" spans="1:8" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:8" ht="25.5" x14ac:dyDescent="0.25">
       <c r="A14" s="34">
         <v>45954</v>
       </c>
@@ -1548,7 +1550,9 @@
       <c r="C14" s="4" t="s">
         <v>180</v>
       </c>
-      <c r="D14" s="4"/>
+      <c r="D14" s="4" t="s">
+        <v>140</v>
+      </c>
       <c r="E14" s="4" t="s">
         <v>141</v>
       </c>
@@ -1584,7 +1588,9 @@
       <c r="C16" s="4" t="s">
         <v>181</v>
       </c>
-      <c r="D16" s="4"/>
+      <c r="D16" s="4" t="s">
+        <v>145</v>
+      </c>
       <c r="E16" s="4" t="s">
         <v>141</v>
       </c>
@@ -2031,13 +2037,13 @@
       <c r="D3" s="2" t="s">
         <v>165</v>
       </c>
-      <c r="E3" s="2">
+      <c r="E3" s="13">
         <v>1</v>
       </c>
-      <c r="F3" s="2">
+      <c r="F3" s="13">
         <v>1</v>
       </c>
-      <c r="G3" s="2">
+      <c r="G3" s="13">
         <v>1</v>
       </c>
       <c r="H3" s="11" t="s">
@@ -2057,13 +2063,13 @@
       <c r="D4" s="4" t="s">
         <v>165</v>
       </c>
-      <c r="E4" s="4">
+      <c r="E4" s="37">
         <v>1</v>
       </c>
-      <c r="F4" s="4">
+      <c r="F4" s="37">
         <v>1</v>
       </c>
-      <c r="G4" s="4">
+      <c r="G4" s="37">
         <v>1</v>
       </c>
       <c r="H4" s="11" t="s">
@@ -2083,13 +2089,13 @@
       <c r="D5" s="2" t="s">
         <v>165</v>
       </c>
-      <c r="E5" s="2">
+      <c r="E5" s="13">
         <v>1</v>
       </c>
-      <c r="F5" s="2">
+      <c r="F5" s="13">
         <v>1</v>
       </c>
-      <c r="G5" s="2">
+      <c r="G5" s="13">
         <v>1</v>
       </c>
       <c r="H5" s="11" t="s">
@@ -2109,13 +2115,13 @@
       <c r="D6" s="4" t="s">
         <v>165</v>
       </c>
-      <c r="E6" s="4">
+      <c r="E6" s="37">
         <v>1</v>
       </c>
-      <c r="F6" s="4">
+      <c r="F6" s="37">
         <v>1</v>
       </c>
-      <c r="G6" s="4">
+      <c r="G6" s="37">
         <v>1</v>
       </c>
       <c r="H6" s="11" t="s">
@@ -2135,13 +2141,13 @@
       <c r="D7" s="2" t="s">
         <v>165</v>
       </c>
-      <c r="E7" s="2">
+      <c r="E7" s="13">
         <v>1</v>
       </c>
-      <c r="F7" s="2">
+      <c r="F7" s="13">
         <v>0.9</v>
       </c>
-      <c r="G7" s="2">
+      <c r="G7" s="13">
         <v>0.9</v>
       </c>
       <c r="H7" s="10" t="s">
@@ -2161,13 +2167,13 @@
       <c r="D8" s="4" t="s">
         <v>165</v>
       </c>
-      <c r="E8" s="4">
+      <c r="E8" s="37">
         <v>1</v>
       </c>
-      <c r="F8" s="4">
+      <c r="F8" s="37">
         <v>0</v>
       </c>
-      <c r="G8" s="4">
+      <c r="G8" s="37">
         <v>0</v>
       </c>
       <c r="H8" s="10" t="s">
@@ -2187,13 +2193,13 @@
       <c r="D9" s="2" t="s">
         <v>165</v>
       </c>
-      <c r="E9" s="2" t="s">
-        <v>207</v>
-      </c>
-      <c r="F9" s="2">
+      <c r="E9" s="13">
+        <v>0.8</v>
+      </c>
+      <c r="F9" s="13">
         <v>0</v>
       </c>
-      <c r="G9" s="2">
+      <c r="G9" s="13">
         <v>0</v>
       </c>
       <c r="H9" s="10" t="s">
@@ -2205,21 +2211,21 @@
         <v>8</v>
       </c>
       <c r="B10" s="4" t="s">
+        <v>207</v>
+      </c>
+      <c r="C10" s="4" t="s">
         <v>208</v>
-      </c>
-      <c r="C10" s="4" t="s">
-        <v>209</v>
       </c>
       <c r="D10" s="4" t="s">
         <v>165</v>
       </c>
-      <c r="E10" s="4">
+      <c r="E10" s="37">
         <v>1</v>
       </c>
-      <c r="F10" s="4" t="s">
-        <v>210</v>
-      </c>
-      <c r="G10" s="4">
+      <c r="F10" s="37" t="s">
+        <v>209</v>
+      </c>
+      <c r="G10" s="37">
         <v>0.15</v>
       </c>
       <c r="H10" s="10" t="s">
@@ -2350,7 +2356,7 @@
         <v>171</v>
       </c>
       <c r="B5" s="3" t="s">
-        <v>211</v>
+        <v>210</v>
       </c>
     </row>
     <row r="6" spans="1:8" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">

--- a/Dashboard_Data.xlsx
+++ b/Dashboard_Data.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://alfanargroup-my.sharepoint.com/personal/ahmed_abdelzaher_alfanar_com/Documents/SDCC Dashboard/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="212" documentId="14_{682A7E4B-1055-4B0F-805D-134F59E89DE5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{81FBB68A-9266-4B34-9684-0298CBA397A8}"/>
+  <xr:revisionPtr revIDLastSave="217" documentId="14_{682A7E4B-1055-4B0F-805D-134F59E89DE5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{BC3D0E97-6939-4668-B388-BC9A3E0720B9}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" tabRatio="500" firstSheet="5" activeTab="11" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" tabRatio="500" firstSheet="5" activeTab="9" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Header" sheetId="1" r:id="rId1"/>
@@ -48,7 +48,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="342" uniqueCount="211">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="341" uniqueCount="211">
   <si>
     <t>HEADER — Dashboard Title &amp; PM</t>
   </si>
@@ -935,13 +935,13 @@
     <xf numFmtId="17" fontId="3" fillId="6" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="9" fontId="3" fillId="6" borderId="1" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="9" fontId="3" fillId="6" borderId="1" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -1221,16 +1221,16 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:8" ht="21.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A1" s="35" t="s">
+      <c r="A1" s="36" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="35"/>
-      <c r="C1" s="35"/>
-      <c r="D1" s="35"/>
-      <c r="E1" s="35"/>
-      <c r="F1" s="35"/>
-      <c r="G1" s="35"/>
-      <c r="H1" s="35"/>
+      <c r="B1" s="36"/>
+      <c r="C1" s="36"/>
+      <c r="D1" s="36"/>
+      <c r="E1" s="36"/>
+      <c r="F1" s="36"/>
+      <c r="G1" s="36"/>
+      <c r="H1" s="36"/>
     </row>
     <row r="2" spans="1:8" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A2" s="1" t="s">
@@ -1303,16 +1303,16 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:8" ht="21.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A1" s="35" t="s">
+      <c r="A1" s="36" t="s">
         <v>130</v>
       </c>
-      <c r="B1" s="35"/>
-      <c r="C1" s="35"/>
-      <c r="D1" s="35"/>
-      <c r="E1" s="35"/>
-      <c r="F1" s="35"/>
-      <c r="G1" s="35"/>
-      <c r="H1" s="35"/>
+      <c r="B1" s="36"/>
+      <c r="C1" s="36"/>
+      <c r="D1" s="36"/>
+      <c r="E1" s="36"/>
+      <c r="F1" s="36"/>
+      <c r="G1" s="36"/>
+      <c r="H1" s="36"/>
     </row>
     <row r="2" spans="1:8" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A2" s="1" t="s">
@@ -1525,7 +1525,7 @@
         <v>45924</v>
       </c>
       <c r="B13" s="2" t="s">
-        <v>141</v>
+        <v>138</v>
       </c>
       <c r="C13" s="2" t="s">
         <v>179</v>
@@ -1545,7 +1545,7 @@
         <v>45954</v>
       </c>
       <c r="B14" s="4" t="s">
-        <v>141</v>
+        <v>138</v>
       </c>
       <c r="C14" s="4" t="s">
         <v>180</v>
@@ -1565,12 +1565,10 @@
         <v>45985</v>
       </c>
       <c r="B15" s="2" t="s">
-        <v>138</v>
+        <v>141</v>
       </c>
       <c r="C15" s="2"/>
-      <c r="D15" s="2" t="s">
-        <v>140</v>
-      </c>
+      <c r="D15" s="2"/>
       <c r="E15" s="2" t="s">
         <v>141</v>
       </c>
@@ -1583,7 +1581,7 @@
         <v>46015</v>
       </c>
       <c r="B16" s="4" t="s">
-        <v>141</v>
+        <v>138</v>
       </c>
       <c r="C16" s="4" t="s">
         <v>181</v>
@@ -1848,16 +1846,16 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:8" ht="21.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A1" s="35" t="s">
+      <c r="A1" s="36" t="s">
         <v>151</v>
       </c>
-      <c r="B1" s="35"/>
-      <c r="C1" s="35"/>
-      <c r="D1" s="35"/>
-      <c r="E1" s="35"/>
-      <c r="F1" s="35"/>
-      <c r="G1" s="35"/>
-      <c r="H1" s="35"/>
+      <c r="B1" s="36"/>
+      <c r="C1" s="36"/>
+      <c r="D1" s="36"/>
+      <c r="E1" s="36"/>
+      <c r="F1" s="36"/>
+      <c r="G1" s="36"/>
+      <c r="H1" s="36"/>
     </row>
     <row r="2" spans="1:8" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A2" s="1" t="s">
@@ -1987,16 +1985,16 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:21" ht="21.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A1" s="35" t="s">
+      <c r="A1" s="36" t="s">
         <v>158</v>
       </c>
-      <c r="B1" s="35"/>
-      <c r="C1" s="35"/>
-      <c r="D1" s="35"/>
-      <c r="E1" s="35"/>
-      <c r="F1" s="35"/>
-      <c r="G1" s="35"/>
-      <c r="H1" s="35"/>
+      <c r="B1" s="36"/>
+      <c r="C1" s="36"/>
+      <c r="D1" s="36"/>
+      <c r="E1" s="36"/>
+      <c r="F1" s="36"/>
+      <c r="G1" s="36"/>
+      <c r="H1" s="36"/>
     </row>
     <row r="2" spans="1:21" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A2" s="1" t="s">
@@ -2063,13 +2061,13 @@
       <c r="D4" s="4" t="s">
         <v>165</v>
       </c>
-      <c r="E4" s="37">
+      <c r="E4" s="35">
         <v>1</v>
       </c>
-      <c r="F4" s="37">
+      <c r="F4" s="35">
         <v>1</v>
       </c>
-      <c r="G4" s="37">
+      <c r="G4" s="35">
         <v>1</v>
       </c>
       <c r="H4" s="11" t="s">
@@ -2115,13 +2113,13 @@
       <c r="D6" s="4" t="s">
         <v>165</v>
       </c>
-      <c r="E6" s="37">
+      <c r="E6" s="35">
         <v>1</v>
       </c>
-      <c r="F6" s="37">
+      <c r="F6" s="35">
         <v>1</v>
       </c>
-      <c r="G6" s="37">
+      <c r="G6" s="35">
         <v>1</v>
       </c>
       <c r="H6" s="11" t="s">
@@ -2167,13 +2165,13 @@
       <c r="D8" s="4" t="s">
         <v>165</v>
       </c>
-      <c r="E8" s="37">
+      <c r="E8" s="35">
         <v>1</v>
       </c>
-      <c r="F8" s="37">
+      <c r="F8" s="35">
         <v>0</v>
       </c>
-      <c r="G8" s="37">
+      <c r="G8" s="35">
         <v>0</v>
       </c>
       <c r="H8" s="10" t="s">
@@ -2219,13 +2217,13 @@
       <c r="D10" s="4" t="s">
         <v>165</v>
       </c>
-      <c r="E10" s="37">
+      <c r="E10" s="35">
         <v>1</v>
       </c>
-      <c r="F10" s="37" t="s">
+      <c r="F10" s="35" t="s">
         <v>209</v>
       </c>
-      <c r="G10" s="37">
+      <c r="G10" s="35">
         <v>0.15</v>
       </c>
       <c r="H10" s="10" t="s">
@@ -2316,16 +2314,16 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:8" ht="21.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A1" s="35" t="s">
+      <c r="A1" s="36" t="s">
         <v>167</v>
       </c>
-      <c r="B1" s="35"/>
-      <c r="C1" s="35"/>
-      <c r="D1" s="35"/>
-      <c r="E1" s="35"/>
-      <c r="F1" s="35"/>
-      <c r="G1" s="35"/>
-      <c r="H1" s="35"/>
+      <c r="B1" s="36"/>
+      <c r="C1" s="36"/>
+      <c r="D1" s="36"/>
+      <c r="E1" s="36"/>
+      <c r="F1" s="36"/>
+      <c r="G1" s="36"/>
+      <c r="H1" s="36"/>
     </row>
     <row r="2" spans="1:8" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A2" s="1" t="s">
@@ -2393,16 +2391,16 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:8" ht="21.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A1" s="35" t="s">
+      <c r="A1" s="36" t="s">
         <v>9</v>
       </c>
-      <c r="B1" s="35"/>
-      <c r="C1" s="35"/>
-      <c r="D1" s="35"/>
-      <c r="E1" s="35"/>
-      <c r="F1" s="35"/>
-      <c r="G1" s="35"/>
-      <c r="H1" s="35"/>
+      <c r="B1" s="36"/>
+      <c r="C1" s="36"/>
+      <c r="D1" s="36"/>
+      <c r="E1" s="36"/>
+      <c r="F1" s="36"/>
+      <c r="G1" s="36"/>
+      <c r="H1" s="36"/>
     </row>
     <row r="2" spans="1:8" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A2" s="1" t="s">
@@ -2510,16 +2508,16 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:8" ht="21.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A1" s="35" t="s">
+      <c r="A1" s="36" t="s">
         <v>22</v>
       </c>
-      <c r="B1" s="35"/>
-      <c r="C1" s="35"/>
-      <c r="D1" s="35"/>
-      <c r="E1" s="35"/>
-      <c r="F1" s="35"/>
-      <c r="G1" s="35"/>
-      <c r="H1" s="35"/>
+      <c r="B1" s="36"/>
+      <c r="C1" s="36"/>
+      <c r="D1" s="36"/>
+      <c r="E1" s="36"/>
+      <c r="F1" s="36"/>
+      <c r="G1" s="36"/>
+      <c r="H1" s="36"/>
     </row>
     <row r="2" spans="1:8" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A2" s="1" t="s">
@@ -2639,16 +2637,16 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:8" ht="21.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A1" s="35" t="s">
+      <c r="A1" s="36" t="s">
         <v>34</v>
       </c>
-      <c r="B1" s="35"/>
-      <c r="C1" s="35"/>
-      <c r="D1" s="35"/>
-      <c r="E1" s="35"/>
-      <c r="F1" s="35"/>
-      <c r="G1" s="35"/>
-      <c r="H1" s="35"/>
+      <c r="B1" s="36"/>
+      <c r="C1" s="36"/>
+      <c r="D1" s="36"/>
+      <c r="E1" s="36"/>
+      <c r="F1" s="36"/>
+      <c r="G1" s="36"/>
+      <c r="H1" s="36"/>
     </row>
     <row r="2" spans="1:8" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A2" s="1" t="s">
@@ -2790,16 +2788,16 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:8" ht="21.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A1" s="35" t="s">
+      <c r="A1" s="36" t="s">
         <v>46</v>
       </c>
-      <c r="B1" s="35"/>
-      <c r="C1" s="35"/>
-      <c r="D1" s="35"/>
-      <c r="E1" s="35"/>
-      <c r="F1" s="35"/>
-      <c r="G1" s="35"/>
-      <c r="H1" s="35"/>
+      <c r="B1" s="36"/>
+      <c r="C1" s="36"/>
+      <c r="D1" s="36"/>
+      <c r="E1" s="36"/>
+      <c r="F1" s="36"/>
+      <c r="G1" s="36"/>
+      <c r="H1" s="36"/>
     </row>
     <row r="2" spans="1:8" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A2" s="1" t="s">
@@ -2939,16 +2937,16 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:8" ht="21.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A1" s="35" t="s">
+      <c r="A1" s="36" t="s">
         <v>58</v>
       </c>
-      <c r="B1" s="35"/>
-      <c r="C1" s="35"/>
-      <c r="D1" s="35"/>
-      <c r="E1" s="35"/>
-      <c r="F1" s="35"/>
-      <c r="G1" s="35"/>
-      <c r="H1" s="35"/>
+      <c r="B1" s="36"/>
+      <c r="C1" s="36"/>
+      <c r="D1" s="36"/>
+      <c r="E1" s="36"/>
+      <c r="F1" s="36"/>
+      <c r="G1" s="36"/>
+      <c r="H1" s="36"/>
     </row>
     <row r="2" spans="1:8" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A2" s="1" t="s">
@@ -3044,24 +3042,24 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:8" ht="21.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A1" s="35" t="s">
+      <c r="A1" s="36" t="s">
         <v>70</v>
       </c>
-      <c r="B1" s="35"/>
-      <c r="C1" s="35"/>
-      <c r="D1" s="35"/>
-      <c r="E1" s="35"/>
-      <c r="F1" s="35"/>
-      <c r="G1" s="35"/>
-      <c r="H1" s="35"/>
+      <c r="B1" s="36"/>
+      <c r="C1" s="36"/>
+      <c r="D1" s="36"/>
+      <c r="E1" s="36"/>
+      <c r="F1" s="36"/>
+      <c r="G1" s="36"/>
+      <c r="H1" s="36"/>
     </row>
     <row r="2" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A2" s="36" t="s">
+      <c r="A2" s="37" t="s">
         <v>71</v>
       </c>
-      <c r="B2" s="36"/>
-      <c r="C2" s="36"/>
-      <c r="D2" s="36"/>
+      <c r="B2" s="37"/>
+      <c r="C2" s="37"/>
+      <c r="D2" s="37"/>
     </row>
     <row r="3" spans="1:8" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A3" s="1" t="s">
@@ -3127,12 +3125,12 @@
     </row>
     <row r="8" spans="1:8" ht="6" customHeight="1" x14ac:dyDescent="0.25"/>
     <row r="9" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A9" s="36" t="s">
+      <c r="A9" s="37" t="s">
         <v>80</v>
       </c>
-      <c r="B9" s="36"/>
-      <c r="C9" s="36"/>
-      <c r="D9" s="36"/>
+      <c r="B9" s="37"/>
+      <c r="C9" s="37"/>
+      <c r="D9" s="37"/>
     </row>
     <row r="10" spans="1:8" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A10" s="1" t="s">
@@ -3172,12 +3170,12 @@
     </row>
     <row r="13" spans="1:8" ht="6" customHeight="1" x14ac:dyDescent="0.25"/>
     <row r="14" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A14" s="36" t="s">
+      <c r="A14" s="37" t="s">
         <v>86</v>
       </c>
-      <c r="B14" s="36"/>
-      <c r="C14" s="36"/>
-      <c r="D14" s="36"/>
+      <c r="B14" s="37"/>
+      <c r="C14" s="37"/>
+      <c r="D14" s="37"/>
     </row>
     <row r="15" spans="1:8" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A15" s="1" t="s">
@@ -3299,16 +3297,16 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:8" ht="21.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A1" s="35" t="s">
+      <c r="A1" s="36" t="s">
         <v>101</v>
       </c>
-      <c r="B1" s="35"/>
-      <c r="C1" s="35"/>
-      <c r="D1" s="35"/>
-      <c r="E1" s="35"/>
-      <c r="F1" s="35"/>
-      <c r="G1" s="35"/>
-      <c r="H1" s="35"/>
+      <c r="B1" s="36"/>
+      <c r="C1" s="36"/>
+      <c r="D1" s="36"/>
+      <c r="E1" s="36"/>
+      <c r="F1" s="36"/>
+      <c r="G1" s="36"/>
+      <c r="H1" s="36"/>
     </row>
     <row r="2" spans="1:8" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A2" s="1" t="s">
@@ -3483,16 +3481,16 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:8" ht="21.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A1" s="35" t="s">
+      <c r="A1" s="36" t="s">
         <v>120</v>
       </c>
-      <c r="B1" s="35"/>
-      <c r="C1" s="35"/>
-      <c r="D1" s="35"/>
-      <c r="E1" s="35"/>
-      <c r="F1" s="35"/>
-      <c r="G1" s="35"/>
-      <c r="H1" s="35"/>
+      <c r="B1" s="36"/>
+      <c r="C1" s="36"/>
+      <c r="D1" s="36"/>
+      <c r="E1" s="36"/>
+      <c r="F1" s="36"/>
+      <c r="G1" s="36"/>
+      <c r="H1" s="36"/>
     </row>
     <row r="2" spans="1:8" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A2" s="1" t="s">

--- a/Dashboard_Data.xlsx
+++ b/Dashboard_Data.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://alfanargroup-my.sharepoint.com/personal/ahmed_abdelzaher_alfanar_com/Documents/SDCC Dashboard/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="217" documentId="14_{682A7E4B-1055-4B0F-805D-134F59E89DE5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{BC3D0E97-6939-4668-B388-BC9A3E0720B9}"/>
+  <xr:revisionPtr revIDLastSave="231" documentId="14_{682A7E4B-1055-4B0F-805D-134F59E89DE5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{0564E0F5-59BA-4BB6-B474-1457848E431B}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" tabRatio="500" firstSheet="5" activeTab="9" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="17520" tabRatio="500" firstSheet="5" activeTab="5" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Header" sheetId="1" r:id="rId1"/>
@@ -687,10 +687,9 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <numFmts count="4">
+  <numFmts count="3">
     <numFmt numFmtId="43" formatCode="_(* #,##0.00_);_(* \(#,##0.00\);_(* &quot;-&quot;??_);_(@_)"/>
     <numFmt numFmtId="164" formatCode="[$-409]d\-mmm\-yy;@"/>
-    <numFmt numFmtId="165" formatCode="0.0%"/>
     <numFmt numFmtId="166" formatCode="0.0"/>
   </numFmts>
   <fonts count="8" x14ac:knownFonts="1">
@@ -915,9 +914,6 @@
     <xf numFmtId="10" fontId="3" fillId="5" borderId="1" xfId="2" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="165" fontId="3" fillId="4" borderId="1" xfId="2" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="166" fontId="3" fillId="4" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
@@ -942,6 +938,9 @@
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="166" fontId="3" fillId="5" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -1221,16 +1220,16 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:8" ht="21.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A1" s="36" t="s">
+      <c r="A1" s="35" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="36"/>
-      <c r="C1" s="36"/>
-      <c r="D1" s="36"/>
-      <c r="E1" s="36"/>
-      <c r="F1" s="36"/>
-      <c r="G1" s="36"/>
-      <c r="H1" s="36"/>
+      <c r="B1" s="35"/>
+      <c r="C1" s="35"/>
+      <c r="D1" s="35"/>
+      <c r="E1" s="35"/>
+      <c r="F1" s="35"/>
+      <c r="G1" s="35"/>
+      <c r="H1" s="35"/>
     </row>
     <row r="2" spans="1:8" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A2" s="1" t="s">
@@ -1303,16 +1302,16 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:8" ht="21.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A1" s="36" t="s">
+      <c r="A1" s="35" t="s">
         <v>130</v>
       </c>
-      <c r="B1" s="36"/>
-      <c r="C1" s="36"/>
-      <c r="D1" s="36"/>
-      <c r="E1" s="36"/>
-      <c r="F1" s="36"/>
-      <c r="G1" s="36"/>
-      <c r="H1" s="36"/>
+      <c r="B1" s="35"/>
+      <c r="C1" s="35"/>
+      <c r="D1" s="35"/>
+      <c r="E1" s="35"/>
+      <c r="F1" s="35"/>
+      <c r="G1" s="35"/>
+      <c r="H1" s="35"/>
     </row>
     <row r="2" spans="1:8" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A2" s="1" t="s">
@@ -1341,7 +1340,7 @@
       </c>
     </row>
     <row r="3" spans="1:8" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A3" s="33">
+      <c r="A3" s="32">
         <v>45620</v>
       </c>
       <c r="B3" s="2" t="s">
@@ -1363,7 +1362,7 @@
       </c>
     </row>
     <row r="4" spans="1:8" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A4" s="34">
+      <c r="A4" s="33">
         <v>45650</v>
       </c>
       <c r="B4" s="4" t="s">
@@ -1379,7 +1378,7 @@
       <c r="H4" s="4"/>
     </row>
     <row r="5" spans="1:8" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A5" s="33">
+      <c r="A5" s="32">
         <v>45681</v>
       </c>
       <c r="B5" s="2" t="s">
@@ -1395,7 +1394,7 @@
       <c r="H5" s="2"/>
     </row>
     <row r="6" spans="1:8" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A6" s="34">
+      <c r="A6" s="33">
         <v>45712</v>
       </c>
       <c r="B6" s="4" t="s">
@@ -1411,7 +1410,7 @@
       <c r="H6" s="4"/>
     </row>
     <row r="7" spans="1:8" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A7" s="33">
+      <c r="A7" s="32">
         <v>45740</v>
       </c>
       <c r="B7" s="2" t="s">
@@ -1431,7 +1430,7 @@
       <c r="H7" s="2"/>
     </row>
     <row r="8" spans="1:8" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A8" s="34">
+      <c r="A8" s="33">
         <v>45771</v>
       </c>
       <c r="B8" s="4" t="s">
@@ -1453,7 +1452,7 @@
       </c>
     </row>
     <row r="9" spans="1:8" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A9" s="33">
+      <c r="A9" s="32">
         <v>45801</v>
       </c>
       <c r="B9" s="2" t="s">
@@ -1469,7 +1468,7 @@
       <c r="H9" s="2"/>
     </row>
     <row r="10" spans="1:8" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A10" s="34">
+      <c r="A10" s="33">
         <v>45832</v>
       </c>
       <c r="B10" s="4" t="s">
@@ -1489,7 +1488,7 @@
       <c r="H10" s="4"/>
     </row>
     <row r="11" spans="1:8" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A11" s="33">
+      <c r="A11" s="32">
         <v>45862</v>
       </c>
       <c r="B11" s="2" t="s">
@@ -1505,7 +1504,7 @@
       <c r="H11" s="2"/>
     </row>
     <row r="12" spans="1:8" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A12" s="34">
+      <c r="A12" s="33">
         <v>45893</v>
       </c>
       <c r="B12" s="4" t="s">
@@ -1521,7 +1520,7 @@
       <c r="H12" s="4"/>
     </row>
     <row r="13" spans="1:8" ht="25.5" x14ac:dyDescent="0.25">
-      <c r="A13" s="33">
+      <c r="A13" s="32">
         <v>45924</v>
       </c>
       <c r="B13" s="2" t="s">
@@ -1541,7 +1540,7 @@
       <c r="H13" s="2"/>
     </row>
     <row r="14" spans="1:8" ht="25.5" x14ac:dyDescent="0.25">
-      <c r="A14" s="34">
+      <c r="A14" s="33">
         <v>45954</v>
       </c>
       <c r="B14" s="4" t="s">
@@ -1561,7 +1560,7 @@
       <c r="H14" s="4"/>
     </row>
     <row r="15" spans="1:8" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A15" s="33">
+      <c r="A15" s="32">
         <v>45985</v>
       </c>
       <c r="B15" s="2" t="s">
@@ -1577,7 +1576,7 @@
       <c r="H15" s="2"/>
     </row>
     <row r="16" spans="1:8" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A16" s="34">
+      <c r="A16" s="33">
         <v>46015</v>
       </c>
       <c r="B16" s="4" t="s">
@@ -1597,7 +1596,7 @@
       <c r="H16" s="4"/>
     </row>
     <row r="17" spans="1:8" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A17" s="33">
+      <c r="A17" s="32">
         <v>46046</v>
       </c>
       <c r="B17" s="2" t="s">
@@ -1613,7 +1612,7 @@
       <c r="H17" s="2"/>
     </row>
     <row r="18" spans="1:8" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A18" s="34">
+      <c r="A18" s="33">
         <v>46077</v>
       </c>
       <c r="B18" s="4" t="s">
@@ -1629,7 +1628,7 @@
       <c r="H18" s="4"/>
     </row>
     <row r="19" spans="1:8" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A19" s="33">
+      <c r="A19" s="32">
         <v>46105</v>
       </c>
       <c r="B19" s="2" t="s">
@@ -1645,7 +1644,7 @@
       <c r="H19" s="2"/>
     </row>
     <row r="20" spans="1:8" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A20" s="34">
+      <c r="A20" s="33">
         <v>46136</v>
       </c>
       <c r="B20" s="2" t="s">
@@ -1661,7 +1660,7 @@
       <c r="H20" s="2"/>
     </row>
     <row r="21" spans="1:8" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A21" s="33">
+      <c r="A21" s="32">
         <v>46166</v>
       </c>
       <c r="B21" s="2" t="s">
@@ -1677,7 +1676,7 @@
       <c r="H21" s="2"/>
     </row>
     <row r="22" spans="1:8" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A22" s="34">
+      <c r="A22" s="33">
         <v>46197</v>
       </c>
       <c r="B22" s="2" t="s">
@@ -1693,7 +1692,7 @@
       <c r="H22" s="2"/>
     </row>
     <row r="23" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A23" s="33">
+      <c r="A23" s="32">
         <v>46227</v>
       </c>
       <c r="B23" s="8" t="s">
@@ -1715,7 +1714,7 @@
       </c>
     </row>
     <row r="24" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A24" s="34">
+      <c r="A24" s="33">
         <v>46258</v>
       </c>
       <c r="B24" s="2" t="s">
@@ -1731,7 +1730,7 @@
       <c r="H24" s="2"/>
     </row>
     <row r="25" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A25" s="33">
+      <c r="A25" s="32">
         <v>46289</v>
       </c>
       <c r="B25" s="2" t="s">
@@ -1747,7 +1746,7 @@
       <c r="H25" s="2"/>
     </row>
     <row r="26" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A26" s="34">
+      <c r="A26" s="33">
         <v>46319</v>
       </c>
       <c r="B26" s="2" t="s">
@@ -1763,7 +1762,7 @@
       <c r="H26" s="2"/>
     </row>
     <row r="27" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A27" s="33">
+      <c r="A27" s="32">
         <v>46350</v>
       </c>
       <c r="B27" s="2" t="s">
@@ -1774,7 +1773,7 @@
       </c>
     </row>
     <row r="28" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A28" s="34">
+      <c r="A28" s="33">
         <v>46380</v>
       </c>
       <c r="B28" s="2" t="s">
@@ -1785,7 +1784,7 @@
       </c>
     </row>
     <row r="29" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A29" s="33">
+      <c r="A29" s="32">
         <v>46411</v>
       </c>
       <c r="B29" s="2" t="s">
@@ -1796,7 +1795,7 @@
       </c>
     </row>
     <row r="30" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A30" s="34">
+      <c r="A30" s="33">
         <v>46442</v>
       </c>
       <c r="B30" s="9" t="s">
@@ -1810,7 +1809,7 @@
       <c r="F30" s="9" t="s">
         <v>149</v>
       </c>
-      <c r="G30" s="30">
+      <c r="G30" s="29">
         <v>46435</v>
       </c>
       <c r="H30" s="9" t="s">
@@ -1846,16 +1845,16 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:8" ht="21.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A1" s="36" t="s">
+      <c r="A1" s="35" t="s">
         <v>151</v>
       </c>
-      <c r="B1" s="36"/>
-      <c r="C1" s="36"/>
-      <c r="D1" s="36"/>
-      <c r="E1" s="36"/>
-      <c r="F1" s="36"/>
-      <c r="G1" s="36"/>
-      <c r="H1" s="36"/>
+      <c r="B1" s="35"/>
+      <c r="C1" s="35"/>
+      <c r="D1" s="35"/>
+      <c r="E1" s="35"/>
+      <c r="F1" s="35"/>
+      <c r="G1" s="35"/>
+      <c r="H1" s="35"/>
     </row>
     <row r="2" spans="1:8" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A2" s="1" t="s">
@@ -1985,16 +1984,16 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:21" ht="21.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A1" s="36" t="s">
+      <c r="A1" s="35" t="s">
         <v>158</v>
       </c>
-      <c r="B1" s="36"/>
-      <c r="C1" s="36"/>
-      <c r="D1" s="36"/>
-      <c r="E1" s="36"/>
-      <c r="F1" s="36"/>
-      <c r="G1" s="36"/>
-      <c r="H1" s="36"/>
+      <c r="B1" s="35"/>
+      <c r="C1" s="35"/>
+      <c r="D1" s="35"/>
+      <c r="E1" s="35"/>
+      <c r="F1" s="35"/>
+      <c r="G1" s="35"/>
+      <c r="H1" s="35"/>
     </row>
     <row r="2" spans="1:21" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A2" s="1" t="s">
@@ -2061,13 +2060,13 @@
       <c r="D4" s="4" t="s">
         <v>165</v>
       </c>
-      <c r="E4" s="35">
+      <c r="E4" s="34">
         <v>1</v>
       </c>
-      <c r="F4" s="35">
+      <c r="F4" s="34">
         <v>1</v>
       </c>
-      <c r="G4" s="35">
+      <c r="G4" s="34">
         <v>1</v>
       </c>
       <c r="H4" s="11" t="s">
@@ -2113,13 +2112,13 @@
       <c r="D6" s="4" t="s">
         <v>165</v>
       </c>
-      <c r="E6" s="35">
+      <c r="E6" s="34">
         <v>1</v>
       </c>
-      <c r="F6" s="35">
+      <c r="F6" s="34">
         <v>1</v>
       </c>
-      <c r="G6" s="35">
+      <c r="G6" s="34">
         <v>1</v>
       </c>
       <c r="H6" s="11" t="s">
@@ -2165,13 +2164,13 @@
       <c r="D8" s="4" t="s">
         <v>165</v>
       </c>
-      <c r="E8" s="35">
+      <c r="E8" s="34">
         <v>1</v>
       </c>
-      <c r="F8" s="35">
+      <c r="F8" s="34">
         <v>0</v>
       </c>
-      <c r="G8" s="35">
+      <c r="G8" s="34">
         <v>0</v>
       </c>
       <c r="H8" s="10" t="s">
@@ -2217,13 +2216,13 @@
       <c r="D10" s="4" t="s">
         <v>165</v>
       </c>
-      <c r="E10" s="35">
+      <c r="E10" s="34">
         <v>1</v>
       </c>
-      <c r="F10" s="35" t="s">
+      <c r="F10" s="34" t="s">
         <v>209</v>
       </c>
-      <c r="G10" s="35">
+      <c r="G10" s="34">
         <v>0.15</v>
       </c>
       <c r="H10" s="10" t="s">
@@ -2231,63 +2230,63 @@
       </c>
     </row>
     <row r="11" spans="1:21" x14ac:dyDescent="0.25">
-      <c r="S11" s="32"/>
-      <c r="T11" s="32"/>
-      <c r="U11" s="32"/>
+      <c r="S11" s="31"/>
+      <c r="T11" s="31"/>
+      <c r="U11" s="31"/>
     </row>
     <row r="12" spans="1:21" x14ac:dyDescent="0.25">
-      <c r="S12" s="32"/>
-      <c r="T12" s="32"/>
-      <c r="U12" s="32"/>
+      <c r="S12" s="31"/>
+      <c r="T12" s="31"/>
+      <c r="U12" s="31"/>
     </row>
     <row r="13" spans="1:21" x14ac:dyDescent="0.25">
-      <c r="S13" s="32"/>
-      <c r="T13" s="32"/>
-      <c r="U13" s="32"/>
+      <c r="S13" s="31"/>
+      <c r="T13" s="31"/>
+      <c r="U13" s="31"/>
     </row>
     <row r="14" spans="1:21" x14ac:dyDescent="0.25">
-      <c r="S14" s="32"/>
-      <c r="T14" s="32"/>
-      <c r="U14" s="32"/>
+      <c r="S14" s="31"/>
+      <c r="T14" s="31"/>
+      <c r="U14" s="31"/>
     </row>
     <row r="15" spans="1:21" x14ac:dyDescent="0.25">
-      <c r="S15" s="32"/>
-      <c r="T15" s="32"/>
-      <c r="U15" s="32"/>
+      <c r="S15" s="31"/>
+      <c r="T15" s="31"/>
+      <c r="U15" s="31"/>
     </row>
     <row r="16" spans="1:21" x14ac:dyDescent="0.25">
-      <c r="S16" s="32"/>
-      <c r="T16" s="32"/>
-      <c r="U16" s="32"/>
+      <c r="S16" s="31"/>
+      <c r="T16" s="31"/>
+      <c r="U16" s="31"/>
     </row>
     <row r="17" spans="19:21" x14ac:dyDescent="0.25">
-      <c r="T17" s="32"/>
-      <c r="U17" s="32"/>
+      <c r="T17" s="31"/>
+      <c r="U17" s="31"/>
     </row>
     <row r="18" spans="19:21" x14ac:dyDescent="0.25">
-      <c r="S18" s="32"/>
-      <c r="U18" s="32"/>
+      <c r="S18" s="31"/>
+      <c r="U18" s="31"/>
     </row>
     <row r="19" spans="19:21" x14ac:dyDescent="0.25">
-      <c r="S19" s="31"/>
+      <c r="S19" s="30"/>
     </row>
     <row r="20" spans="19:21" x14ac:dyDescent="0.25">
-      <c r="S20" s="31"/>
+      <c r="S20" s="30"/>
     </row>
     <row r="21" spans="19:21" x14ac:dyDescent="0.25">
-      <c r="S21" s="31"/>
+      <c r="S21" s="30"/>
     </row>
     <row r="22" spans="19:21" x14ac:dyDescent="0.25">
-      <c r="S22" s="31"/>
+      <c r="S22" s="30"/>
     </row>
     <row r="23" spans="19:21" x14ac:dyDescent="0.25">
-      <c r="S23" s="31"/>
+      <c r="S23" s="30"/>
     </row>
     <row r="24" spans="19:21" x14ac:dyDescent="0.25">
-      <c r="S24" s="31"/>
+      <c r="S24" s="30"/>
     </row>
     <row r="25" spans="19:21" x14ac:dyDescent="0.25">
-      <c r="S25" s="31"/>
+      <c r="S25" s="30"/>
     </row>
   </sheetData>
   <mergeCells count="1">
@@ -2314,16 +2313,16 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:8" ht="21.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A1" s="36" t="s">
+      <c r="A1" s="35" t="s">
         <v>167</v>
       </c>
-      <c r="B1" s="36"/>
-      <c r="C1" s="36"/>
-      <c r="D1" s="36"/>
-      <c r="E1" s="36"/>
-      <c r="F1" s="36"/>
-      <c r="G1" s="36"/>
-      <c r="H1" s="36"/>
+      <c r="B1" s="35"/>
+      <c r="C1" s="35"/>
+      <c r="D1" s="35"/>
+      <c r="E1" s="35"/>
+      <c r="F1" s="35"/>
+      <c r="G1" s="35"/>
+      <c r="H1" s="35"/>
     </row>
     <row r="2" spans="1:8" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A2" s="1" t="s">
@@ -2391,16 +2390,16 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:8" ht="21.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A1" s="36" t="s">
+      <c r="A1" s="35" t="s">
         <v>9</v>
       </c>
-      <c r="B1" s="36"/>
-      <c r="C1" s="36"/>
-      <c r="D1" s="36"/>
-      <c r="E1" s="36"/>
-      <c r="F1" s="36"/>
-      <c r="G1" s="36"/>
-      <c r="H1" s="36"/>
+      <c r="B1" s="35"/>
+      <c r="C1" s="35"/>
+      <c r="D1" s="35"/>
+      <c r="E1" s="35"/>
+      <c r="F1" s="35"/>
+      <c r="G1" s="35"/>
+      <c r="H1" s="35"/>
     </row>
     <row r="2" spans="1:8" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A2" s="1" t="s">
@@ -2508,16 +2507,16 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:8" ht="21.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A1" s="36" t="s">
+      <c r="A1" s="35" t="s">
         <v>22</v>
       </c>
-      <c r="B1" s="36"/>
-      <c r="C1" s="36"/>
-      <c r="D1" s="36"/>
-      <c r="E1" s="36"/>
-      <c r="F1" s="36"/>
-      <c r="G1" s="36"/>
-      <c r="H1" s="36"/>
+      <c r="B1" s="35"/>
+      <c r="C1" s="35"/>
+      <c r="D1" s="35"/>
+      <c r="E1" s="35"/>
+      <c r="F1" s="35"/>
+      <c r="G1" s="35"/>
+      <c r="H1" s="35"/>
     </row>
     <row r="2" spans="1:8" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A2" s="1" t="s">
@@ -2637,16 +2636,16 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:8" ht="21.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A1" s="36" t="s">
+      <c r="A1" s="35" t="s">
         <v>34</v>
       </c>
-      <c r="B1" s="36"/>
-      <c r="C1" s="36"/>
-      <c r="D1" s="36"/>
-      <c r="E1" s="36"/>
-      <c r="F1" s="36"/>
-      <c r="G1" s="36"/>
-      <c r="H1" s="36"/>
+      <c r="B1" s="35"/>
+      <c r="C1" s="35"/>
+      <c r="D1" s="35"/>
+      <c r="E1" s="35"/>
+      <c r="F1" s="35"/>
+      <c r="G1" s="35"/>
+      <c r="H1" s="35"/>
     </row>
     <row r="2" spans="1:8" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A2" s="1" t="s">
@@ -2703,10 +2702,7 @@
       <c r="B6" s="19">
         <v>0.40899999999999997</v>
       </c>
-      <c r="C6" s="22">
-        <f>B4-B6</f>
-        <v>0.59099999999999997</v>
-      </c>
+      <c r="C6" s="22"/>
       <c r="D6" s="2" t="s">
         <v>41</v>
       </c>
@@ -2788,16 +2784,16 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:8" ht="21.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A1" s="36" t="s">
+      <c r="A1" s="35" t="s">
         <v>46</v>
       </c>
-      <c r="B1" s="36"/>
-      <c r="C1" s="36"/>
-      <c r="D1" s="36"/>
-      <c r="E1" s="36"/>
-      <c r="F1" s="36"/>
-      <c r="G1" s="36"/>
-      <c r="H1" s="36"/>
+      <c r="B1" s="35"/>
+      <c r="C1" s="35"/>
+      <c r="D1" s="35"/>
+      <c r="E1" s="35"/>
+      <c r="F1" s="35"/>
+      <c r="G1" s="35"/>
+      <c r="H1" s="35"/>
     </row>
     <row r="2" spans="1:8" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A2" s="1" t="s">
@@ -2937,16 +2933,16 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:8" ht="21.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A1" s="36" t="s">
+      <c r="A1" s="35" t="s">
         <v>58</v>
       </c>
-      <c r="B1" s="36"/>
-      <c r="C1" s="36"/>
-      <c r="D1" s="36"/>
-      <c r="E1" s="36"/>
-      <c r="F1" s="36"/>
-      <c r="G1" s="36"/>
-      <c r="H1" s="36"/>
+      <c r="B1" s="35"/>
+      <c r="C1" s="35"/>
+      <c r="D1" s="35"/>
+      <c r="E1" s="35"/>
+      <c r="F1" s="35"/>
+      <c r="G1" s="35"/>
+      <c r="H1" s="35"/>
     </row>
     <row r="2" spans="1:8" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A2" s="1" t="s">
@@ -2993,9 +2989,9 @@
       <c r="B5" s="3">
         <v>68</v>
       </c>
-      <c r="C5" s="27">
-        <f>B5/B6</f>
-        <v>0.52631578947368429</v>
+      <c r="C5" s="37">
+        <f>(B5/B6)*100</f>
+        <v>52.631578947368432</v>
       </c>
       <c r="D5" s="2" t="s">
         <v>67</v>
@@ -3042,24 +3038,24 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:8" ht="21.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A1" s="36" t="s">
+      <c r="A1" s="35" t="s">
         <v>70</v>
       </c>
-      <c r="B1" s="36"/>
-      <c r="C1" s="36"/>
-      <c r="D1" s="36"/>
-      <c r="E1" s="36"/>
-      <c r="F1" s="36"/>
-      <c r="G1" s="36"/>
-      <c r="H1" s="36"/>
+      <c r="B1" s="35"/>
+      <c r="C1" s="35"/>
+      <c r="D1" s="35"/>
+      <c r="E1" s="35"/>
+      <c r="F1" s="35"/>
+      <c r="G1" s="35"/>
+      <c r="H1" s="35"/>
     </row>
     <row r="2" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A2" s="37" t="s">
+      <c r="A2" s="36" t="s">
         <v>71</v>
       </c>
-      <c r="B2" s="37"/>
-      <c r="C2" s="37"/>
-      <c r="D2" s="37"/>
+      <c r="B2" s="36"/>
+      <c r="C2" s="36"/>
+      <c r="D2" s="36"/>
     </row>
     <row r="3" spans="1:8" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A3" s="1" t="s">
@@ -3125,12 +3121,12 @@
     </row>
     <row r="8" spans="1:8" ht="6" customHeight="1" x14ac:dyDescent="0.25"/>
     <row r="9" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A9" s="37" t="s">
+      <c r="A9" s="36" t="s">
         <v>80</v>
       </c>
-      <c r="B9" s="37"/>
-      <c r="C9" s="37"/>
-      <c r="D9" s="37"/>
+      <c r="B9" s="36"/>
+      <c r="C9" s="36"/>
+      <c r="D9" s="36"/>
     </row>
     <row r="10" spans="1:8" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A10" s="1" t="s">
@@ -3170,12 +3166,12 @@
     </row>
     <row r="13" spans="1:8" ht="6" customHeight="1" x14ac:dyDescent="0.25"/>
     <row r="14" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A14" s="37" t="s">
+      <c r="A14" s="36" t="s">
         <v>86</v>
       </c>
-      <c r="B14" s="37"/>
-      <c r="C14" s="37"/>
-      <c r="D14" s="37"/>
+      <c r="B14" s="36"/>
+      <c r="C14" s="36"/>
+      <c r="D14" s="36"/>
     </row>
     <row r="15" spans="1:8" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A15" s="1" t="s">
@@ -3297,16 +3293,16 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:8" ht="21.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A1" s="36" t="s">
+      <c r="A1" s="35" t="s">
         <v>101</v>
       </c>
-      <c r="B1" s="36"/>
-      <c r="C1" s="36"/>
-      <c r="D1" s="36"/>
-      <c r="E1" s="36"/>
-      <c r="F1" s="36"/>
-      <c r="G1" s="36"/>
-      <c r="H1" s="36"/>
+      <c r="B1" s="35"/>
+      <c r="C1" s="35"/>
+      <c r="D1" s="35"/>
+      <c r="E1" s="35"/>
+      <c r="F1" s="35"/>
+      <c r="G1" s="35"/>
+      <c r="H1" s="35"/>
     </row>
     <row r="2" spans="1:8" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A2" s="1" t="s">
@@ -3332,10 +3328,10 @@
       <c r="A3" s="2" t="s">
         <v>107</v>
       </c>
-      <c r="B3" s="28">
+      <c r="B3" s="27">
         <v>92.78</v>
       </c>
-      <c r="C3" s="28">
+      <c r="C3" s="27">
         <v>84.28</v>
       </c>
       <c r="D3" s="5">
@@ -3353,10 +3349,10 @@
       <c r="A4" s="4" t="s">
         <v>110</v>
       </c>
-      <c r="B4" s="29">
+      <c r="B4" s="28">
         <v>100</v>
       </c>
-      <c r="C4" s="29">
+      <c r="C4" s="28">
         <v>99.25</v>
       </c>
       <c r="D4" s="6">
@@ -3374,10 +3370,10 @@
       <c r="A5" s="2" t="s">
         <v>113</v>
       </c>
-      <c r="B5" s="28">
+      <c r="B5" s="27">
         <v>100</v>
       </c>
-      <c r="C5" s="28">
+      <c r="C5" s="27">
         <v>95.54</v>
       </c>
       <c r="D5" s="5">
@@ -3395,10 +3391,10 @@
       <c r="A6" s="4" t="s">
         <v>116</v>
       </c>
-      <c r="B6" s="29">
+      <c r="B6" s="28">
         <v>95.92</v>
       </c>
-      <c r="C6" s="29">
+      <c r="C6" s="28">
         <v>90.82</v>
       </c>
       <c r="D6" s="6">
@@ -3416,10 +3412,10 @@
       <c r="A7" s="2" t="s">
         <v>117</v>
       </c>
-      <c r="B7" s="28">
+      <c r="B7" s="27">
         <v>100</v>
       </c>
-      <c r="C7" s="28">
+      <c r="C7" s="27">
         <v>93.32</v>
       </c>
       <c r="D7" s="5">
@@ -3437,10 +3433,10 @@
       <c r="A8" s="4" t="s">
         <v>118</v>
       </c>
-      <c r="B8" s="29">
+      <c r="B8" s="28">
         <v>68.05</v>
       </c>
-      <c r="C8" s="29">
+      <c r="C8" s="28">
         <v>22.08</v>
       </c>
       <c r="D8" s="6">
@@ -3481,16 +3477,16 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:8" ht="21.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A1" s="36" t="s">
+      <c r="A1" s="35" t="s">
         <v>120</v>
       </c>
-      <c r="B1" s="36"/>
-      <c r="C1" s="36"/>
-      <c r="D1" s="36"/>
-      <c r="E1" s="36"/>
-      <c r="F1" s="36"/>
-      <c r="G1" s="36"/>
-      <c r="H1" s="36"/>
+      <c r="B1" s="35"/>
+      <c r="C1" s="35"/>
+      <c r="D1" s="35"/>
+      <c r="E1" s="35"/>
+      <c r="F1" s="35"/>
+      <c r="G1" s="35"/>
+      <c r="H1" s="35"/>
     </row>
     <row r="2" spans="1:8" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A2" s="1" t="s">

--- a/Dashboard_Data.xlsx
+++ b/Dashboard_Data.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://alfanargroup-my.sharepoint.com/personal/ahmed_abdelzaher_alfanar_com/Documents/SDCC Dashboard/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="231" documentId="14_{682A7E4B-1055-4B0F-805D-134F59E89DE5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{0564E0F5-59BA-4BB6-B474-1457848E431B}"/>
+  <xr:revisionPtr revIDLastSave="234" documentId="14_{682A7E4B-1055-4B0F-805D-134F59E89DE5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{F841B871-84DB-4F72-930D-35CA20AE1320}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="17520" tabRatio="500" firstSheet="5" activeTab="5" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -690,7 +690,7 @@
   <numFmts count="3">
     <numFmt numFmtId="43" formatCode="_(* #,##0.00_);_(* \(#,##0.00\);_(* &quot;-&quot;??_);_(@_)"/>
     <numFmt numFmtId="164" formatCode="[$-409]d\-mmm\-yy;@"/>
-    <numFmt numFmtId="166" formatCode="0.0"/>
+    <numFmt numFmtId="165" formatCode="0.0"/>
   </numFmts>
   <fonts count="8" x14ac:knownFonts="1">
     <font>
@@ -914,10 +914,10 @@
     <xf numFmtId="10" fontId="3" fillId="5" borderId="1" xfId="2" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="166" fontId="3" fillId="4" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="165" fontId="3" fillId="4" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="166" fontId="3" fillId="6" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="165" fontId="3" fillId="6" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="15" fontId="3" fillId="8" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -934,13 +934,13 @@
     <xf numFmtId="9" fontId="3" fillId="6" borderId="1" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="165" fontId="3" fillId="5" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="166" fontId="3" fillId="5" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -1220,16 +1220,16 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:8" ht="21.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A1" s="35" t="s">
+      <c r="A1" s="36" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="35"/>
-      <c r="C1" s="35"/>
-      <c r="D1" s="35"/>
-      <c r="E1" s="35"/>
-      <c r="F1" s="35"/>
-      <c r="G1" s="35"/>
-      <c r="H1" s="35"/>
+      <c r="B1" s="36"/>
+      <c r="C1" s="36"/>
+      <c r="D1" s="36"/>
+      <c r="E1" s="36"/>
+      <c r="F1" s="36"/>
+      <c r="G1" s="36"/>
+      <c r="H1" s="36"/>
     </row>
     <row r="2" spans="1:8" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A2" s="1" t="s">
@@ -1302,16 +1302,16 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:8" ht="21.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A1" s="35" t="s">
+      <c r="A1" s="36" t="s">
         <v>130</v>
       </c>
-      <c r="B1" s="35"/>
-      <c r="C1" s="35"/>
-      <c r="D1" s="35"/>
-      <c r="E1" s="35"/>
-      <c r="F1" s="35"/>
-      <c r="G1" s="35"/>
-      <c r="H1" s="35"/>
+      <c r="B1" s="36"/>
+      <c r="C1" s="36"/>
+      <c r="D1" s="36"/>
+      <c r="E1" s="36"/>
+      <c r="F1" s="36"/>
+      <c r="G1" s="36"/>
+      <c r="H1" s="36"/>
     </row>
     <row r="2" spans="1:8" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A2" s="1" t="s">
@@ -1845,16 +1845,16 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:8" ht="21.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A1" s="35" t="s">
+      <c r="A1" s="36" t="s">
         <v>151</v>
       </c>
-      <c r="B1" s="35"/>
-      <c r="C1" s="35"/>
-      <c r="D1" s="35"/>
-      <c r="E1" s="35"/>
-      <c r="F1" s="35"/>
-      <c r="G1" s="35"/>
-      <c r="H1" s="35"/>
+      <c r="B1" s="36"/>
+      <c r="C1" s="36"/>
+      <c r="D1" s="36"/>
+      <c r="E1" s="36"/>
+      <c r="F1" s="36"/>
+      <c r="G1" s="36"/>
+      <c r="H1" s="36"/>
     </row>
     <row r="2" spans="1:8" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A2" s="1" t="s">
@@ -1984,16 +1984,16 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:21" ht="21.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A1" s="35" t="s">
+      <c r="A1" s="36" t="s">
         <v>158</v>
       </c>
-      <c r="B1" s="35"/>
-      <c r="C1" s="35"/>
-      <c r="D1" s="35"/>
-      <c r="E1" s="35"/>
-      <c r="F1" s="35"/>
-      <c r="G1" s="35"/>
-      <c r="H1" s="35"/>
+      <c r="B1" s="36"/>
+      <c r="C1" s="36"/>
+      <c r="D1" s="36"/>
+      <c r="E1" s="36"/>
+      <c r="F1" s="36"/>
+      <c r="G1" s="36"/>
+      <c r="H1" s="36"/>
     </row>
     <row r="2" spans="1:21" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A2" s="1" t="s">
@@ -2313,16 +2313,16 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:8" ht="21.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A1" s="35" t="s">
+      <c r="A1" s="36" t="s">
         <v>167</v>
       </c>
-      <c r="B1" s="35"/>
-      <c r="C1" s="35"/>
-      <c r="D1" s="35"/>
-      <c r="E1" s="35"/>
-      <c r="F1" s="35"/>
-      <c r="G1" s="35"/>
-      <c r="H1" s="35"/>
+      <c r="B1" s="36"/>
+      <c r="C1" s="36"/>
+      <c r="D1" s="36"/>
+      <c r="E1" s="36"/>
+      <c r="F1" s="36"/>
+      <c r="G1" s="36"/>
+      <c r="H1" s="36"/>
     </row>
     <row r="2" spans="1:8" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A2" s="1" t="s">
@@ -2390,16 +2390,16 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:8" ht="21.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A1" s="35" t="s">
+      <c r="A1" s="36" t="s">
         <v>9</v>
       </c>
-      <c r="B1" s="35"/>
-      <c r="C1" s="35"/>
-      <c r="D1" s="35"/>
-      <c r="E1" s="35"/>
-      <c r="F1" s="35"/>
-      <c r="G1" s="35"/>
-      <c r="H1" s="35"/>
+      <c r="B1" s="36"/>
+      <c r="C1" s="36"/>
+      <c r="D1" s="36"/>
+      <c r="E1" s="36"/>
+      <c r="F1" s="36"/>
+      <c r="G1" s="36"/>
+      <c r="H1" s="36"/>
     </row>
     <row r="2" spans="1:8" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A2" s="1" t="s">
@@ -2507,16 +2507,16 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:8" ht="21.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A1" s="35" t="s">
+      <c r="A1" s="36" t="s">
         <v>22</v>
       </c>
-      <c r="B1" s="35"/>
-      <c r="C1" s="35"/>
-      <c r="D1" s="35"/>
-      <c r="E1" s="35"/>
-      <c r="F1" s="35"/>
-      <c r="G1" s="35"/>
-      <c r="H1" s="35"/>
+      <c r="B1" s="36"/>
+      <c r="C1" s="36"/>
+      <c r="D1" s="36"/>
+      <c r="E1" s="36"/>
+      <c r="F1" s="36"/>
+      <c r="G1" s="36"/>
+      <c r="H1" s="36"/>
     </row>
     <row r="2" spans="1:8" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A2" s="1" t="s">
@@ -2636,16 +2636,16 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:8" ht="21.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A1" s="35" t="s">
+      <c r="A1" s="36" t="s">
         <v>34</v>
       </c>
-      <c r="B1" s="35"/>
-      <c r="C1" s="35"/>
-      <c r="D1" s="35"/>
-      <c r="E1" s="35"/>
-      <c r="F1" s="35"/>
-      <c r="G1" s="35"/>
-      <c r="H1" s="35"/>
+      <c r="B1" s="36"/>
+      <c r="C1" s="36"/>
+      <c r="D1" s="36"/>
+      <c r="E1" s="36"/>
+      <c r="F1" s="36"/>
+      <c r="G1" s="36"/>
+      <c r="H1" s="36"/>
     </row>
     <row r="2" spans="1:8" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A2" s="1" t="s">
@@ -2784,16 +2784,16 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:8" ht="21.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A1" s="35" t="s">
+      <c r="A1" s="36" t="s">
         <v>46</v>
       </c>
-      <c r="B1" s="35"/>
-      <c r="C1" s="35"/>
-      <c r="D1" s="35"/>
-      <c r="E1" s="35"/>
-      <c r="F1" s="35"/>
-      <c r="G1" s="35"/>
-      <c r="H1" s="35"/>
+      <c r="B1" s="36"/>
+      <c r="C1" s="36"/>
+      <c r="D1" s="36"/>
+      <c r="E1" s="36"/>
+      <c r="F1" s="36"/>
+      <c r="G1" s="36"/>
+      <c r="H1" s="36"/>
     </row>
     <row r="2" spans="1:8" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A2" s="1" t="s">
@@ -2933,16 +2933,16 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:8" ht="21.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A1" s="35" t="s">
+      <c r="A1" s="36" t="s">
         <v>58</v>
       </c>
-      <c r="B1" s="35"/>
-      <c r="C1" s="35"/>
-      <c r="D1" s="35"/>
-      <c r="E1" s="35"/>
-      <c r="F1" s="35"/>
-      <c r="G1" s="35"/>
-      <c r="H1" s="35"/>
+      <c r="B1" s="36"/>
+      <c r="C1" s="36"/>
+      <c r="D1" s="36"/>
+      <c r="E1" s="36"/>
+      <c r="F1" s="36"/>
+      <c r="G1" s="36"/>
+      <c r="H1" s="36"/>
     </row>
     <row r="2" spans="1:8" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A2" s="1" t="s">
@@ -2963,12 +2963,16 @@
         <v>61</v>
       </c>
       <c r="B3" s="3">
-        <v>-61.1</v>
+        <f>B5-B6</f>
+        <v>5.8000000000000114</v>
       </c>
       <c r="C3" s="2"/>
       <c r="D3" s="2" t="s">
         <v>62</v>
       </c>
+      <c r="F3">
+        <v>-61.1</v>
+      </c>
     </row>
     <row r="4" spans="1:8" ht="27" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A4" s="4" t="s">
@@ -2981,20 +2985,26 @@
       <c r="D4" s="4" t="s">
         <v>65</v>
       </c>
+      <c r="F4">
+        <v>68</v>
+      </c>
     </row>
     <row r="5" spans="1:8" ht="27" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A5" s="2" t="s">
         <v>66</v>
       </c>
       <c r="B5" s="3">
-        <v>68</v>
-      </c>
-      <c r="C5" s="37">
+        <v>135</v>
+      </c>
+      <c r="C5" s="35">
         <f>(B5/B6)*100</f>
-        <v>52.631578947368432</v>
+        <v>104.48916408668731</v>
       </c>
       <c r="D5" s="2" t="s">
         <v>67</v>
+      </c>
+      <c r="F5">
+        <v>129.19999999999999</v>
       </c>
     </row>
     <row r="6" spans="1:8" ht="27" customHeight="1" x14ac:dyDescent="0.25">
@@ -3038,24 +3048,24 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:8" ht="21.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A1" s="35" t="s">
+      <c r="A1" s="36" t="s">
         <v>70</v>
       </c>
-      <c r="B1" s="35"/>
-      <c r="C1" s="35"/>
-      <c r="D1" s="35"/>
-      <c r="E1" s="35"/>
-      <c r="F1" s="35"/>
-      <c r="G1" s="35"/>
-      <c r="H1" s="35"/>
+      <c r="B1" s="36"/>
+      <c r="C1" s="36"/>
+      <c r="D1" s="36"/>
+      <c r="E1" s="36"/>
+      <c r="F1" s="36"/>
+      <c r="G1" s="36"/>
+      <c r="H1" s="36"/>
     </row>
     <row r="2" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A2" s="36" t="s">
+      <c r="A2" s="37" t="s">
         <v>71</v>
       </c>
-      <c r="B2" s="36"/>
-      <c r="C2" s="36"/>
-      <c r="D2" s="36"/>
+      <c r="B2" s="37"/>
+      <c r="C2" s="37"/>
+      <c r="D2" s="37"/>
     </row>
     <row r="3" spans="1:8" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A3" s="1" t="s">
@@ -3121,12 +3131,12 @@
     </row>
     <row r="8" spans="1:8" ht="6" customHeight="1" x14ac:dyDescent="0.25"/>
     <row r="9" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A9" s="36" t="s">
+      <c r="A9" s="37" t="s">
         <v>80</v>
       </c>
-      <c r="B9" s="36"/>
-      <c r="C9" s="36"/>
-      <c r="D9" s="36"/>
+      <c r="B9" s="37"/>
+      <c r="C9" s="37"/>
+      <c r="D9" s="37"/>
     </row>
     <row r="10" spans="1:8" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A10" s="1" t="s">
@@ -3166,12 +3176,12 @@
     </row>
     <row r="13" spans="1:8" ht="6" customHeight="1" x14ac:dyDescent="0.25"/>
     <row r="14" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A14" s="36" t="s">
+      <c r="A14" s="37" t="s">
         <v>86</v>
       </c>
-      <c r="B14" s="36"/>
-      <c r="C14" s="36"/>
-      <c r="D14" s="36"/>
+      <c r="B14" s="37"/>
+      <c r="C14" s="37"/>
+      <c r="D14" s="37"/>
     </row>
     <row r="15" spans="1:8" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A15" s="1" t="s">
@@ -3293,16 +3303,16 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:8" ht="21.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A1" s="35" t="s">
+      <c r="A1" s="36" t="s">
         <v>101</v>
       </c>
-      <c r="B1" s="35"/>
-      <c r="C1" s="35"/>
-      <c r="D1" s="35"/>
-      <c r="E1" s="35"/>
-      <c r="F1" s="35"/>
-      <c r="G1" s="35"/>
-      <c r="H1" s="35"/>
+      <c r="B1" s="36"/>
+      <c r="C1" s="36"/>
+      <c r="D1" s="36"/>
+      <c r="E1" s="36"/>
+      <c r="F1" s="36"/>
+      <c r="G1" s="36"/>
+      <c r="H1" s="36"/>
     </row>
     <row r="2" spans="1:8" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A2" s="1" t="s">
@@ -3477,16 +3487,16 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:8" ht="21.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A1" s="35" t="s">
+      <c r="A1" s="36" t="s">
         <v>120</v>
       </c>
-      <c r="B1" s="35"/>
-      <c r="C1" s="35"/>
-      <c r="D1" s="35"/>
-      <c r="E1" s="35"/>
-      <c r="F1" s="35"/>
-      <c r="G1" s="35"/>
-      <c r="H1" s="35"/>
+      <c r="B1" s="36"/>
+      <c r="C1" s="36"/>
+      <c r="D1" s="36"/>
+      <c r="E1" s="36"/>
+      <c r="F1" s="36"/>
+      <c r="G1" s="36"/>
+      <c r="H1" s="36"/>
     </row>
     <row r="2" spans="1:8" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A2" s="1" t="s">

--- a/Dashboard_Data.xlsx
+++ b/Dashboard_Data.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://alfanargroup-my.sharepoint.com/personal/ahmed_abdelzaher_alfanar_com/Documents/SDCC Dashboard/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="234" documentId="14_{682A7E4B-1055-4B0F-805D-134F59E89DE5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{F841B871-84DB-4F72-930D-35CA20AE1320}"/>
+  <xr:revisionPtr revIDLastSave="236" documentId="14_{682A7E4B-1055-4B0F-805D-134F59E89DE5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{3D90A536-7096-4170-A405-93798882EF3C}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="17520" tabRatio="500" firstSheet="5" activeTab="5" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -2964,15 +2964,12 @@
       </c>
       <c r="B3" s="3">
         <f>B5-B6</f>
-        <v>5.8000000000000114</v>
+        <v>-61.199999999999989</v>
       </c>
       <c r="C3" s="2"/>
       <c r="D3" s="2" t="s">
         <v>62</v>
       </c>
-      <c r="F3">
-        <v>-61.1</v>
-      </c>
     </row>
     <row r="4" spans="1:8" ht="27" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A4" s="4" t="s">
@@ -2985,26 +2982,20 @@
       <c r="D4" s="4" t="s">
         <v>65</v>
       </c>
-      <c r="F4">
-        <v>68</v>
-      </c>
     </row>
     <row r="5" spans="1:8" ht="27" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A5" s="2" t="s">
         <v>66</v>
       </c>
       <c r="B5" s="3">
-        <v>135</v>
+        <v>68</v>
       </c>
       <c r="C5" s="35">
         <f>(B5/B6)*100</f>
-        <v>104.48916408668731</v>
+        <v>52.631578947368432</v>
       </c>
       <c r="D5" s="2" t="s">
         <v>67</v>
-      </c>
-      <c r="F5">
-        <v>129.19999999999999</v>
       </c>
     </row>
     <row r="6" spans="1:8" ht="27" customHeight="1" x14ac:dyDescent="0.25">

--- a/Dashboard_Data.xlsx
+++ b/Dashboard_Data.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://alfanargroup-my.sharepoint.com/personal/ahmed_abdelzaher_alfanar_com/Documents/SDCC Dashboard/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="236" documentId="14_{682A7E4B-1055-4B0F-805D-134F59E89DE5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{3D90A536-7096-4170-A405-93798882EF3C}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{08402470-AB39-479E-9F56-A762705072E3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="17520" tabRatio="500" firstSheet="5" activeTab="5" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" tabRatio="500" firstSheet="4" activeTab="5" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Header" sheetId="1" r:id="rId1"/>
@@ -27,8 +27,11 @@
     <sheet name="Equipment_Status" sheetId="12" r:id="rId12"/>
     <sheet name="Footer" sheetId="13" r:id="rId13"/>
   </sheets>
-  <calcPr calcId="191029"/>
+  <calcPr calcId="191028"/>
   <extLst>
+    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
+      <x15:workbookPr chartTrackingRefBase="1"/>
+    </ext>
     <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
       <xcalcf:calcFeatures>
         <xcalcf:feature name="microsoft.com:RD"/>
@@ -62,6 +65,9 @@
     <t>Dashboard Title</t>
   </si>
   <si>
+    <t>WESTERN &amp; SOUTHERN REGION SDCC PROJECT DASHBOARD | PE-286</t>
+  </si>
+  <si>
     <t>Project Code</t>
   </si>
   <si>
@@ -71,6 +77,9 @@
     <t>Region</t>
   </si>
   <si>
+    <t>Western &amp; SOUTHERN Region</t>
+  </si>
+  <si>
     <t>Project Manager</t>
   </si>
   <si>
@@ -104,396 +113,414 @@
     <t>Contractual TCC</t>
   </si>
   <si>
+    <t>Highlighted orange in dashboard</t>
+  </si>
+  <si>
+    <t>Expected TCC</t>
+  </si>
+  <si>
+    <t>Highlighted red in dashboard — delayed</t>
+  </si>
+  <si>
+    <t>COMMERCIAL INFO (SAR)</t>
+  </si>
+  <si>
+    <t>Value (SAR)</t>
+  </si>
+  <si>
+    <t>Tag / Badge</t>
+  </si>
+  <si>
+    <t>Org. Contract Value</t>
+  </si>
+  <si>
+    <t>Cont. Adv. Payment</t>
+  </si>
+  <si>
+    <t>Change Orders</t>
+  </si>
+  <si>
+    <t>Sub. Cost Claim</t>
+  </si>
+  <si>
+    <t>Expected Cont. Value</t>
+  </si>
+  <si>
+    <t>Equals Org. Contract Value + Change Orders</t>
+  </si>
+  <si>
+    <t>Org. Contingency</t>
+  </si>
+  <si>
+    <t>Rem. Contingency</t>
+  </si>
+  <si>
+    <t>Badge shown in amber/red in dashboard</t>
+  </si>
+  <si>
+    <t>BUDGETARY INFO</t>
+  </si>
+  <si>
+    <t>Rev. Budget Amount</t>
+  </si>
+  <si>
+    <t>SAR</t>
+  </si>
+  <si>
+    <t>Target POC 2026</t>
+  </si>
+  <si>
+    <t>100%</t>
+  </si>
+  <si>
+    <t>Percentage</t>
+  </si>
+  <si>
+    <t>Planned POC</t>
+  </si>
+  <si>
+    <t>Actual POC Till Date</t>
+  </si>
+  <si>
+    <t>Red in dashboard; badge shows gap vs target</t>
+  </si>
+  <si>
+    <t>Contingency Used</t>
+  </si>
+  <si>
+    <t>Amber in dashboard</t>
+  </si>
+  <si>
+    <t>EOT Status</t>
+  </si>
+  <si>
+    <t>Submitted</t>
+  </si>
+  <si>
+    <t>Red in dashboard</t>
+  </si>
+  <si>
+    <t>COLLECTION INFO (SAR)</t>
+  </si>
+  <si>
+    <t>Tag %</t>
+  </si>
+  <si>
+    <t>Color in Dashboard</t>
+  </si>
+  <si>
+    <t>Invoiceable Amount</t>
+  </si>
+  <si>
+    <t>Green</t>
+  </si>
+  <si>
+    <t>Submitted Invoices</t>
+  </si>
+  <si>
+    <t>Amber</t>
+  </si>
+  <si>
+    <t>Approved Invoices</t>
+  </si>
+  <si>
+    <t>Collected Adv.</t>
+  </si>
+  <si>
+    <t>Normal</t>
+  </si>
+  <si>
+    <t>Col. Amount Inc Adv</t>
+  </si>
+  <si>
+    <t>Billing vs Actual POC</t>
+  </si>
+  <si>
+    <t>Text field — shown as-is</t>
+  </si>
+  <si>
+    <t>CASH FLOW STATUS (SAR Millions)</t>
+  </si>
+  <si>
+    <t>Value (SAR M)</t>
+  </si>
+  <si>
+    <t>Bar Width %</t>
+  </si>
+  <si>
+    <t>Net Cash Position</t>
+  </si>
+  <si>
+    <t>Shown as hero figure; red background</t>
+  </si>
+  <si>
+    <t>Hero Sub-label</t>
+  </si>
+  <si>
+    <t>Outflow exceeds inflow · negative position</t>
+  </si>
+  <si>
+    <t>Descriptive text under the big number</t>
+  </si>
+  <si>
+    <t>Cash In</t>
+  </si>
+  <si>
+    <t>Green bar; relative to Cash Out (max)</t>
+  </si>
+  <si>
+    <t>Cash Out</t>
+  </si>
+  <si>
+    <t>Orange bar; this is the 100% reference</t>
+  </si>
+  <si>
+    <t>MANPOWER STATUS</t>
+  </si>
+  <si>
+    <t>A — Totals</t>
+  </si>
+  <si>
+    <t>Total Manpower</t>
+  </si>
+  <si>
+    <t>Hero figure — orange background</t>
+  </si>
+  <si>
+    <t>Direct Labor</t>
+  </si>
+  <si>
+    <t>Green segment in donut</t>
+  </si>
+  <si>
+    <t>Indirect</t>
+  </si>
+  <si>
+    <t>Orange segment in donut</t>
+  </si>
+  <si>
+    <t>Direct Share %</t>
+  </si>
+  <si>
+    <t>Shown as green text</t>
+  </si>
+  <si>
+    <t>B — Direct Labor Breakdown</t>
+  </si>
+  <si>
+    <t>Category</t>
+  </si>
+  <si>
+    <t>Count</t>
+  </si>
+  <si>
+    <t>ALF (Alfanar direct)</t>
+  </si>
+  <si>
+    <t>Shown as sub-label under Direct Labor</t>
+  </si>
+  <si>
+    <t>SC (Subcontractor)</t>
+  </si>
+  <si>
+    <t>C — Donut Chart SVG Parameters (auto-calculated from counts above)</t>
+  </si>
+  <si>
+    <t>Parameter</t>
+  </si>
+  <si>
+    <t>Formula / Notes</t>
+  </si>
+  <si>
+    <t>Direct % of Total</t>
+  </si>
+  <si>
+    <t>e.g. 79.6  → used for green arc dasharray</t>
+  </si>
+  <si>
+    <t>Indirect % of Total</t>
+  </si>
+  <si>
+    <t>e.g. 20.4  → used for orange arc dasharray</t>
+  </si>
+  <si>
+    <t>Green arc dasharray part1</t>
+  </si>
+  <si>
+    <t>stroke-dasharray first value (green)</t>
+  </si>
+  <si>
+    <t>Green arc dasharray part2</t>
+  </si>
+  <si>
+    <t>stroke-dasharray second value (green)</t>
+  </si>
+  <si>
+    <t>Orange arc dasharray part1</t>
+  </si>
+  <si>
+    <t>stroke-dasharray first value (orange)</t>
+  </si>
+  <si>
+    <t>Orange arc dasharray part2</t>
+  </si>
+  <si>
+    <t>stroke-dasharray second value (orange)</t>
+  </si>
+  <si>
+    <t>PROJECT PHASES — Plan vs Actual (%)</t>
+  </si>
+  <si>
+    <t>Phase</t>
+  </si>
+  <si>
+    <t>Plan %</t>
+  </si>
+  <si>
+    <t>Actual %</t>
+  </si>
+  <si>
+    <t>Delta</t>
+  </si>
+  <si>
+    <t>Delta Color</t>
+  </si>
+  <si>
+    <t>Overall</t>
+  </si>
+  <si>
+    <t>warn</t>
+  </si>
+  <si>
+    <t>Red badge</t>
+  </si>
+  <si>
+    <t>Engineering</t>
+  </si>
+  <si>
+    <t>good</t>
+  </si>
+  <si>
+    <t>Green badge</t>
+  </si>
+  <si>
+    <t>Equipment</t>
+  </si>
+  <si>
+    <t>mild</t>
+  </si>
+  <si>
+    <t>Amber badge</t>
+  </si>
+  <si>
+    <t>Construction</t>
+  </si>
+  <si>
+    <t>Installation</t>
+  </si>
+  <si>
+    <t>Testing &amp; Commissioning</t>
+  </si>
+  <si>
+    <t>Red badge; actual bar uses tiny style</t>
+  </si>
+  <si>
+    <t>PROGRESS PER CITY — Plan vs Actual (%)</t>
+  </si>
+  <si>
+    <t>City</t>
+  </si>
+  <si>
+    <t>Madinah</t>
+  </si>
+  <si>
+    <t>Abha</t>
+  </si>
+  <si>
+    <t>Jizan</t>
+  </si>
+  <si>
+    <t>Trails plan the most</t>
+  </si>
+  <si>
+    <t>Jeddah</t>
+  </si>
+  <si>
+    <t>Makkah</t>
+  </si>
+  <si>
+    <t>Leads on actual completion</t>
+  </si>
+  <si>
+    <t>Footer Note (italic text shown below chart)</t>
+  </si>
+  <si>
+    <t>PROJECTS TIMELINE — Monthly Milestones</t>
+  </si>
+  <si>
+    <t>Month Label</t>
+  </si>
+  <si>
+    <t>Has Milestone</t>
+  </si>
+  <si>
+    <t>Milestone Text</t>
+  </si>
+  <si>
+    <t>Flag Position</t>
+  </si>
+  <si>
+    <t>Is TCC Cell</t>
+  </si>
+  <si>
+    <t>TCC Box Label</t>
+  </si>
+  <si>
+    <t>TCC Box Date</t>
+  </si>
+  <si>
+    <t>YES</t>
+  </si>
+  <si>
+    <t>Project Start</t>
+  </si>
+  <si>
+    <t>above</t>
+  </si>
+  <si>
+    <t>NO</t>
+  </si>
+  <si>
+    <t>First month</t>
+  </si>
+  <si>
+    <t>MADINAH P.C.</t>
+  </si>
+  <si>
+    <t>ABHA P.C.</t>
+  </si>
+  <si>
+    <t>below</t>
+  </si>
+  <si>
+    <t>Flag goes below bar</t>
+  </si>
+  <si>
+    <t>JIZAN P.C.</t>
+  </si>
+  <si>
+    <t>MAD&amp; ABH Structur Completed</t>
+  </si>
+  <si>
+    <t>Jizan Structure Completed</t>
+  </si>
+  <si>
+    <t>CET Equip. Delivery</t>
+  </si>
+  <si>
     <t>24-Jul-26</t>
   </si>
   <si>
-    <t>Highlighted orange in dashboard</t>
-  </si>
-  <si>
-    <t>Expected TCC</t>
-  </si>
-  <si>
-    <t>Highlighted red in dashboard — delayed</t>
-  </si>
-  <si>
-    <t>COMMERCIAL INFO (SAR)</t>
-  </si>
-  <si>
-    <t>Value (SAR)</t>
-  </si>
-  <si>
-    <t>Tag / Badge</t>
-  </si>
-  <si>
-    <t>Org. Contract Value</t>
-  </si>
-  <si>
-    <t>Cont. Adv. Payment</t>
-  </si>
-  <si>
-    <t>Change Orders</t>
-  </si>
-  <si>
-    <t>Sub. Cost Claim</t>
-  </si>
-  <si>
-    <t>Expected Cont. Value</t>
-  </si>
-  <si>
-    <t>Equals Org. Contract Value + Change Orders</t>
-  </si>
-  <si>
-    <t>Org. Contingency</t>
-  </si>
-  <si>
-    <t>Rem. Contingency</t>
-  </si>
-  <si>
-    <t>Badge shown in amber/red in dashboard</t>
-  </si>
-  <si>
-    <t>BUDGETARY INFO</t>
-  </si>
-  <si>
-    <t>Rev. Budget Amount</t>
-  </si>
-  <si>
-    <t>SAR</t>
-  </si>
-  <si>
-    <t>Target POC 2026</t>
-  </si>
-  <si>
-    <t>100%</t>
-  </si>
-  <si>
-    <t>Percentage</t>
-  </si>
-  <si>
-    <t>Actual POC Till Date</t>
-  </si>
-  <si>
-    <t>Red in dashboard; badge shows gap vs target</t>
-  </si>
-  <si>
-    <t>Contingency Used</t>
-  </si>
-  <si>
-    <t>Amber in dashboard</t>
-  </si>
-  <si>
-    <t>EOT Status</t>
-  </si>
-  <si>
-    <t>Red in dashboard</t>
-  </si>
-  <si>
-    <t>COLLECTION INFO (SAR)</t>
-  </si>
-  <si>
-    <t>Tag %</t>
-  </si>
-  <si>
-    <t>Color in Dashboard</t>
-  </si>
-  <si>
-    <t>Invoiceable Amount</t>
-  </si>
-  <si>
-    <t>Green</t>
-  </si>
-  <si>
-    <t>Submitted Invoices</t>
-  </si>
-  <si>
-    <t>Amber</t>
-  </si>
-  <si>
-    <t>Approved Invoices</t>
-  </si>
-  <si>
-    <t>Collected Adv.</t>
-  </si>
-  <si>
-    <t>Normal</t>
-  </si>
-  <si>
-    <t>Col. Amount Inc Adv</t>
-  </si>
-  <si>
-    <t>Text field — shown as-is</t>
-  </si>
-  <si>
-    <t>CASH FLOW STATUS (SAR Millions)</t>
-  </si>
-  <si>
-    <t>Value (SAR M)</t>
-  </si>
-  <si>
-    <t>Bar Width %</t>
-  </si>
-  <si>
-    <t>Net Cash Position</t>
-  </si>
-  <si>
-    <t>Shown as hero figure; red background</t>
-  </si>
-  <si>
-    <t>Hero Sub-label</t>
-  </si>
-  <si>
-    <t>Outflow exceeds inflow · negative position</t>
-  </si>
-  <si>
-    <t>Descriptive text under the big number</t>
-  </si>
-  <si>
-    <t>Cash In</t>
-  </si>
-  <si>
-    <t>Green bar; relative to Cash Out (max)</t>
-  </si>
-  <si>
-    <t>Cash Out</t>
-  </si>
-  <si>
-    <t>Orange bar; this is the 100% reference</t>
-  </si>
-  <si>
-    <t>MANPOWER STATUS</t>
-  </si>
-  <si>
-    <t>A — Totals</t>
-  </si>
-  <si>
-    <t>Total Manpower</t>
-  </si>
-  <si>
-    <t>Hero figure — orange background</t>
-  </si>
-  <si>
-    <t>Direct Labor</t>
-  </si>
-  <si>
-    <t>Green segment in donut</t>
-  </si>
-  <si>
-    <t>Indirect</t>
-  </si>
-  <si>
-    <t>Orange segment in donut</t>
-  </si>
-  <si>
-    <t>Direct Share %</t>
-  </si>
-  <si>
-    <t>Shown as green text</t>
-  </si>
-  <si>
-    <t>B — Direct Labor Breakdown</t>
-  </si>
-  <si>
-    <t>Category</t>
-  </si>
-  <si>
-    <t>Count</t>
-  </si>
-  <si>
-    <t>ALF (Alfanar direct)</t>
-  </si>
-  <si>
-    <t>Shown as sub-label under Direct Labor</t>
-  </si>
-  <si>
-    <t>SC (Subcontractor)</t>
-  </si>
-  <si>
-    <t>C — Donut Chart SVG Parameters (auto-calculated from counts above)</t>
-  </si>
-  <si>
-    <t>Parameter</t>
-  </si>
-  <si>
-    <t>Formula / Notes</t>
-  </si>
-  <si>
-    <t>Direct % of Total</t>
-  </si>
-  <si>
-    <t>e.g. 79.6  → used for green arc dasharray</t>
-  </si>
-  <si>
-    <t>Indirect % of Total</t>
-  </si>
-  <si>
-    <t>e.g. 20.4  → used for orange arc dasharray</t>
-  </si>
-  <si>
-    <t>Green arc dasharray part1</t>
-  </si>
-  <si>
-    <t>stroke-dasharray first value (green)</t>
-  </si>
-  <si>
-    <t>Green arc dasharray part2</t>
-  </si>
-  <si>
-    <t>stroke-dasharray second value (green)</t>
-  </si>
-  <si>
-    <t>Orange arc dasharray part1</t>
-  </si>
-  <si>
-    <t>stroke-dasharray first value (orange)</t>
-  </si>
-  <si>
-    <t>Orange arc dasharray part2</t>
-  </si>
-  <si>
-    <t>stroke-dasharray second value (orange)</t>
-  </si>
-  <si>
-    <t>PROJECT PHASES — Plan vs Actual (%)</t>
-  </si>
-  <si>
-    <t>Phase</t>
-  </si>
-  <si>
-    <t>Plan %</t>
-  </si>
-  <si>
-    <t>Actual %</t>
-  </si>
-  <si>
-    <t>Delta</t>
-  </si>
-  <si>
-    <t>Delta Color</t>
-  </si>
-  <si>
-    <t>Overall</t>
-  </si>
-  <si>
-    <t>warn</t>
-  </si>
-  <si>
-    <t>Red badge</t>
-  </si>
-  <si>
-    <t>Engineering</t>
-  </si>
-  <si>
-    <t>good</t>
-  </si>
-  <si>
-    <t>Green badge</t>
-  </si>
-  <si>
-    <t>Equipment</t>
-  </si>
-  <si>
-    <t>mild</t>
-  </si>
-  <si>
-    <t>Amber badge</t>
-  </si>
-  <si>
-    <t>Construction</t>
-  </si>
-  <si>
-    <t>Installation</t>
-  </si>
-  <si>
-    <t>Testing &amp; Commissioning</t>
-  </si>
-  <si>
-    <t>Red badge; actual bar uses tiny style</t>
-  </si>
-  <si>
-    <t>PROGRESS PER CITY — Plan vs Actual (%)</t>
-  </si>
-  <si>
-    <t>City</t>
-  </si>
-  <si>
-    <t>Madinah</t>
-  </si>
-  <si>
-    <t>Abha</t>
-  </si>
-  <si>
-    <t>Jizan</t>
-  </si>
-  <si>
-    <t>Trails plan the most</t>
-  </si>
-  <si>
-    <t>Jeddah</t>
-  </si>
-  <si>
-    <t>Makkah</t>
-  </si>
-  <si>
-    <t>Leads on actual completion</t>
-  </si>
-  <si>
-    <t>Footer Note (italic text shown below chart)</t>
-  </si>
-  <si>
-    <t>PROJECTS TIMELINE — Monthly Milestones</t>
-  </si>
-  <si>
-    <t>Month Label</t>
-  </si>
-  <si>
-    <t>Has Milestone</t>
-  </si>
-  <si>
-    <t>Milestone Text</t>
-  </si>
-  <si>
-    <t>Flag Position</t>
-  </si>
-  <si>
-    <t>Is TCC Cell</t>
-  </si>
-  <si>
-    <t>TCC Box Label</t>
-  </si>
-  <si>
-    <t>TCC Box Date</t>
-  </si>
-  <si>
-    <t>YES</t>
-  </si>
-  <si>
-    <t>Project Start</t>
-  </si>
-  <si>
-    <t>above</t>
-  </si>
-  <si>
-    <t>NO</t>
-  </si>
-  <si>
-    <t>First month</t>
-  </si>
-  <si>
-    <t>MADINAH P.C.</t>
-  </si>
-  <si>
-    <t>ABHA P.C.</t>
-  </si>
-  <si>
-    <t>below</t>
-  </si>
-  <si>
-    <t>Flag goes below bar</t>
-  </si>
-  <si>
-    <t>JIZAN P.C.</t>
-  </si>
-  <si>
     <t>Orange cell</t>
   </si>
   <si>
@@ -524,6 +551,45 @@
     <t>Priority</t>
   </si>
   <si>
+    <t>Delay Delivery of Low Current 3rd Fix Materials</t>
+  </si>
+  <si>
+    <t>Procurement</t>
+  </si>
+  <si>
+    <t>Supplier (Digital Era)</t>
+  </si>
+  <si>
+    <t>PM to arrange a meeting with supplier top management to enhance the current delivery forecast dates to meet the TCC contractual date.</t>
+  </si>
+  <si>
+    <t>High</t>
+  </si>
+  <si>
+    <t>Delay Approval of Jockey Pumps (Fire Pumps Package)</t>
+  </si>
+  <si>
+    <t>Engineering / Procurement</t>
+  </si>
+  <si>
+    <t>SE</t>
+  </si>
+  <si>
+    <t>SE to expedite the approval of Jockey Pumps to start manufacturing of materials and fulfill the supplied flow USA.</t>
+  </si>
+  <si>
+    <t>Delay Approval of LAN/WAN (M6 Routers) Which Fulfill Contract Requirements</t>
+  </si>
+  <si>
+    <t>Approved design is to use (M14 routers), delivery duration 20–24 weeks.SE to approve Alfanar proposal to deliver (M6 routers) which have a delivery duration of 6–8 weeks.</t>
+  </si>
+  <si>
+    <t>Delay Delivery of DWDM (PO Issued to AES) – Waiting for Final Confirmation of Recent Traffic Plan</t>
+  </si>
+  <si>
+    <t>SE to expedite providing the confirmed recent traffic plan to start manufacturing materials of DWDM.</t>
+  </si>
+  <si>
     <t>EQUIPMENT STATUS</t>
   </si>
   <si>
@@ -545,12 +611,57 @@
     <t>Status</t>
   </si>
   <si>
+    <t>ADMS/DERMS Servers</t>
+  </si>
+  <si>
+    <t>CET</t>
+  </si>
+  <si>
     <t>Issued</t>
   </si>
   <si>
     <t>OK</t>
   </si>
   <si>
+    <t>CRAC / PACU Units</t>
+  </si>
+  <si>
+    <t>Zamil</t>
+  </si>
+  <si>
+    <t>FM-200 Cylinders</t>
+  </si>
+  <si>
+    <t>DDC Panels</t>
+  </si>
+  <si>
+    <t>Marine</t>
+  </si>
+  <si>
+    <t>AC/DC Panels</t>
+  </si>
+  <si>
+    <t>AES</t>
+  </si>
+  <si>
+    <t>Delayed</t>
+  </si>
+  <si>
+    <t>48 VDC System</t>
+  </si>
+  <si>
+    <t>Fire Pumps</t>
+  </si>
+  <si>
+    <t>Security System</t>
+  </si>
+  <si>
+    <t>ITC</t>
+  </si>
+  <si>
+    <t>N/A</t>
+  </si>
+  <si>
     <t>FOOTER — Classification &amp; Branding</t>
   </si>
   <si>
@@ -566,121 +677,13 @@
     <t>Department</t>
   </si>
   <si>
+    <t>Control Center</t>
+  </si>
+  <si>
     <t>Brand Name</t>
   </si>
   <si>
     <t>alfanar</t>
-  </si>
-  <si>
-    <t>WESTERN &amp; SOUTHERN REGION SDCC PROJECT DASHBOARD | PE-286</t>
-  </si>
-  <si>
-    <t>Western &amp; SOUTHERN Region</t>
-  </si>
-  <si>
-    <t>Submitted</t>
-  </si>
-  <si>
-    <t>Billing vs Actual POC</t>
-  </si>
-  <si>
-    <t>Planned POC</t>
-  </si>
-  <si>
-    <t>MAD&amp; ABH Structur Completed</t>
-  </si>
-  <si>
-    <t>Jizan Structure Completed</t>
-  </si>
-  <si>
-    <t>CET Equip. Delivery</t>
-  </si>
-  <si>
-    <t>High</t>
-  </si>
-  <si>
-    <t>Supplier (Digital Era)</t>
-  </si>
-  <si>
-    <t>Procurement</t>
-  </si>
-  <si>
-    <t>SE</t>
-  </si>
-  <si>
-    <t>Engineering / Procurement</t>
-  </si>
-  <si>
-    <t>Delay Delivery of Low Current 3rd Fix Materials</t>
-  </si>
-  <si>
-    <t>PM to arrange a meeting with supplier top management to enhance the current delivery forecast dates to meet the TCC contractual date.</t>
-  </si>
-  <si>
-    <t>Delay Approval of Jockey Pumps (Fire Pumps Package)</t>
-  </si>
-  <si>
-    <t>SE to expedite the approval of Jockey Pumps to start manufacturing of materials and fulfill the supplied flow USA.</t>
-  </si>
-  <si>
-    <t>Delay Approval of LAN/WAN (M6 Routers) Which Fulfill Contract Requirements</t>
-  </si>
-  <si>
-    <t>Delay Delivery of DWDM (PO Issued to AES) – Waiting for Final Confirmation of Recent Traffic Plan</t>
-  </si>
-  <si>
-    <t>SE to expedite providing the confirmed recent traffic plan to start manufacturing materials of DWDM.</t>
-  </si>
-  <si>
-    <t>Approved design is to use (M14 routers), delivery duration 20–24 weeks.SE to approve Alfanar proposal to deliver (M6 routers) which have a delivery duration of 6–8 weeks.</t>
-  </si>
-  <si>
-    <t>48 VDC System</t>
-  </si>
-  <si>
-    <t>ADMS/DERMS Servers</t>
-  </si>
-  <si>
-    <t>CET</t>
-  </si>
-  <si>
-    <t>CRAC / PACU Units</t>
-  </si>
-  <si>
-    <t>Zamil</t>
-  </si>
-  <si>
-    <t>FM-200 Cylinders</t>
-  </si>
-  <si>
-    <t>DDC Panels</t>
-  </si>
-  <si>
-    <t>Marine</t>
-  </si>
-  <si>
-    <t>AC/DC Panels</t>
-  </si>
-  <si>
-    <t>AES</t>
-  </si>
-  <si>
-    <t>Delayed</t>
-  </si>
-  <si>
-    <t>Fire Pumps</t>
-  </si>
-  <si>
-    <t>Security System</t>
-  </si>
-  <si>
-    <t>ITC</t>
-  </si>
-  <si>
-    <t>N/A</t>
-  </si>
-  <si>
-    <t>Control Center</t>
   </si>
 </sst>
 </file>
@@ -838,7 +841,7 @@
     <xf numFmtId="43" fontId="6" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="9" fontId="6" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="38">
+  <cellXfs count="39">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -937,6 +940,7 @@
     <xf numFmtId="165" fontId="3" fillId="5" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="3" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
@@ -1220,16 +1224,16 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:8" ht="21.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A1" s="36" t="s">
+      <c r="A1" s="37" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="36"/>
-      <c r="C1" s="36"/>
-      <c r="D1" s="36"/>
-      <c r="E1" s="36"/>
-      <c r="F1" s="36"/>
-      <c r="G1" s="36"/>
-      <c r="H1" s="36"/>
+      <c r="B1" s="37"/>
+      <c r="C1" s="37"/>
+      <c r="D1" s="37"/>
+      <c r="E1" s="37"/>
+      <c r="F1" s="37"/>
+      <c r="G1" s="37"/>
+      <c r="H1" s="37"/>
     </row>
     <row r="2" spans="1:8" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A2" s="1" t="s">
@@ -1244,31 +1248,31 @@
         <v>3</v>
       </c>
       <c r="B3" s="3" t="s">
-        <v>174</v>
+        <v>4</v>
       </c>
     </row>
     <row r="4" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A4" s="4" t="s">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="B4" s="3" t="s">
-        <v>5</v>
+        <v>6</v>
       </c>
     </row>
     <row r="5" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A5" s="2" t="s">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="B5" s="3" t="s">
-        <v>175</v>
+        <v>8</v>
       </c>
     </row>
     <row r="6" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A6" s="4" t="s">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="B6" s="3" t="s">
-        <v>8</v>
+        <v>10</v>
       </c>
     </row>
   </sheetData>
@@ -1302,41 +1306,41 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:8" ht="21.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A1" s="36" t="s">
-        <v>130</v>
-      </c>
-      <c r="B1" s="36"/>
-      <c r="C1" s="36"/>
-      <c r="D1" s="36"/>
-      <c r="E1" s="36"/>
-      <c r="F1" s="36"/>
-      <c r="G1" s="36"/>
-      <c r="H1" s="36"/>
+      <c r="A1" s="37" t="s">
+        <v>134</v>
+      </c>
+      <c r="B1" s="37"/>
+      <c r="C1" s="37"/>
+      <c r="D1" s="37"/>
+      <c r="E1" s="37"/>
+      <c r="F1" s="37"/>
+      <c r="G1" s="37"/>
+      <c r="H1" s="37"/>
     </row>
     <row r="2" spans="1:8" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A2" s="1" t="s">
-        <v>131</v>
+        <v>135</v>
       </c>
       <c r="B2" s="1" t="s">
-        <v>132</v>
+        <v>136</v>
       </c>
       <c r="C2" s="1" t="s">
-        <v>133</v>
+        <v>137</v>
       </c>
       <c r="D2" s="1" t="s">
-        <v>134</v>
+        <v>138</v>
       </c>
       <c r="E2" s="1" t="s">
-        <v>135</v>
+        <v>139</v>
       </c>
       <c r="F2" s="1" t="s">
-        <v>136</v>
+        <v>140</v>
       </c>
       <c r="G2" s="1" t="s">
-        <v>137</v>
+        <v>141</v>
       </c>
       <c r="H2" s="1" t="s">
-        <v>11</v>
+        <v>13</v>
       </c>
     </row>
     <row r="3" spans="1:8" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
@@ -1344,21 +1348,21 @@
         <v>45620</v>
       </c>
       <c r="B3" s="2" t="s">
-        <v>138</v>
+        <v>142</v>
       </c>
       <c r="C3" s="2" t="s">
-        <v>139</v>
+        <v>143</v>
       </c>
       <c r="D3" s="2" t="s">
-        <v>140</v>
+        <v>144</v>
       </c>
       <c r="E3" s="2" t="s">
-        <v>141</v>
+        <v>145</v>
       </c>
       <c r="F3" s="2"/>
       <c r="G3" s="2"/>
       <c r="H3" s="2" t="s">
-        <v>142</v>
+        <v>146</v>
       </c>
     </row>
     <row r="4" spans="1:8" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
@@ -1366,12 +1370,12 @@
         <v>45650</v>
       </c>
       <c r="B4" s="4" t="s">
-        <v>141</v>
+        <v>145</v>
       </c>
       <c r="C4" s="4"/>
       <c r="D4" s="4"/>
       <c r="E4" s="4" t="s">
-        <v>141</v>
+        <v>145</v>
       </c>
       <c r="F4" s="4"/>
       <c r="G4" s="4"/>
@@ -1382,12 +1386,12 @@
         <v>45681</v>
       </c>
       <c r="B5" s="2" t="s">
-        <v>141</v>
+        <v>145</v>
       </c>
       <c r="C5" s="2"/>
       <c r="D5" s="2"/>
       <c r="E5" s="2" t="s">
-        <v>141</v>
+        <v>145</v>
       </c>
       <c r="F5" s="2"/>
       <c r="G5" s="2"/>
@@ -1398,12 +1402,12 @@
         <v>45712</v>
       </c>
       <c r="B6" s="4" t="s">
-        <v>141</v>
+        <v>145</v>
       </c>
       <c r="C6" s="4"/>
       <c r="D6" s="4"/>
       <c r="E6" s="4" t="s">
-        <v>141</v>
+        <v>145</v>
       </c>
       <c r="F6" s="4"/>
       <c r="G6" s="4"/>
@@ -1414,16 +1418,16 @@
         <v>45740</v>
       </c>
       <c r="B7" s="2" t="s">
-        <v>138</v>
+        <v>142</v>
       </c>
       <c r="C7" s="2" t="s">
-        <v>143</v>
+        <v>147</v>
       </c>
       <c r="D7" s="2" t="s">
-        <v>140</v>
+        <v>144</v>
       </c>
       <c r="E7" s="2" t="s">
-        <v>141</v>
+        <v>145</v>
       </c>
       <c r="F7" s="2"/>
       <c r="G7" s="2"/>
@@ -1434,21 +1438,21 @@
         <v>45771</v>
       </c>
       <c r="B8" s="4" t="s">
-        <v>138</v>
+        <v>142</v>
       </c>
       <c r="C8" s="4" t="s">
-        <v>144</v>
+        <v>148</v>
       </c>
       <c r="D8" s="4" t="s">
-        <v>145</v>
+        <v>149</v>
       </c>
       <c r="E8" s="4" t="s">
-        <v>141</v>
+        <v>145</v>
       </c>
       <c r="F8" s="4"/>
       <c r="G8" s="4"/>
       <c r="H8" s="4" t="s">
-        <v>146</v>
+        <v>150</v>
       </c>
     </row>
     <row r="9" spans="1:8" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
@@ -1456,12 +1460,12 @@
         <v>45801</v>
       </c>
       <c r="B9" s="2" t="s">
-        <v>141</v>
+        <v>145</v>
       </c>
       <c r="C9" s="2"/>
       <c r="D9" s="2"/>
       <c r="E9" s="2" t="s">
-        <v>141</v>
+        <v>145</v>
       </c>
       <c r="F9" s="2"/>
       <c r="G9" s="2"/>
@@ -1472,16 +1476,16 @@
         <v>45832</v>
       </c>
       <c r="B10" s="4" t="s">
-        <v>138</v>
+        <v>142</v>
       </c>
       <c r="C10" s="4" t="s">
-        <v>147</v>
+        <v>151</v>
       </c>
       <c r="D10" s="4" t="s">
-        <v>140</v>
+        <v>144</v>
       </c>
       <c r="E10" s="4" t="s">
-        <v>141</v>
+        <v>145</v>
       </c>
       <c r="F10" s="4"/>
       <c r="G10" s="4"/>
@@ -1492,12 +1496,12 @@
         <v>45862</v>
       </c>
       <c r="B11" s="2" t="s">
-        <v>141</v>
+        <v>145</v>
       </c>
       <c r="C11" s="2"/>
       <c r="D11" s="2"/>
       <c r="E11" s="2" t="s">
-        <v>141</v>
+        <v>145</v>
       </c>
       <c r="F11" s="2"/>
       <c r="G11" s="2"/>
@@ -1508,12 +1512,12 @@
         <v>45893</v>
       </c>
       <c r="B12" s="4" t="s">
-        <v>141</v>
+        <v>145</v>
       </c>
       <c r="C12" s="4"/>
       <c r="D12" s="4"/>
       <c r="E12" s="4" t="s">
-        <v>141</v>
+        <v>145</v>
       </c>
       <c r="F12" s="4"/>
       <c r="G12" s="4"/>
@@ -1524,16 +1528,16 @@
         <v>45924</v>
       </c>
       <c r="B13" s="2" t="s">
-        <v>138</v>
+        <v>142</v>
       </c>
       <c r="C13" s="2" t="s">
-        <v>179</v>
+        <v>152</v>
       </c>
       <c r="D13" s="2" t="s">
-        <v>145</v>
+        <v>149</v>
       </c>
       <c r="E13" s="2" t="s">
-        <v>141</v>
+        <v>145</v>
       </c>
       <c r="F13" s="2"/>
       <c r="G13" s="2"/>
@@ -1544,16 +1548,16 @@
         <v>45954</v>
       </c>
       <c r="B14" s="4" t="s">
-        <v>138</v>
+        <v>142</v>
       </c>
       <c r="C14" s="4" t="s">
-        <v>180</v>
+        <v>153</v>
       </c>
       <c r="D14" s="4" t="s">
-        <v>140</v>
+        <v>144</v>
       </c>
       <c r="E14" s="4" t="s">
-        <v>141</v>
+        <v>145</v>
       </c>
       <c r="F14" s="4"/>
       <c r="G14" s="4"/>
@@ -1564,12 +1568,12 @@
         <v>45985</v>
       </c>
       <c r="B15" s="2" t="s">
-        <v>141</v>
+        <v>145</v>
       </c>
       <c r="C15" s="2"/>
       <c r="D15" s="2"/>
       <c r="E15" s="2" t="s">
-        <v>141</v>
+        <v>145</v>
       </c>
       <c r="F15" s="2"/>
       <c r="G15" s="2"/>
@@ -1580,16 +1584,16 @@
         <v>46015</v>
       </c>
       <c r="B16" s="4" t="s">
-        <v>138</v>
+        <v>142</v>
       </c>
       <c r="C16" s="4" t="s">
-        <v>181</v>
+        <v>154</v>
       </c>
       <c r="D16" s="4" t="s">
-        <v>145</v>
+        <v>149</v>
       </c>
       <c r="E16" s="4" t="s">
-        <v>141</v>
+        <v>145</v>
       </c>
       <c r="F16" s="4"/>
       <c r="G16" s="4"/>
@@ -1600,12 +1604,12 @@
         <v>46046</v>
       </c>
       <c r="B17" s="2" t="s">
-        <v>141</v>
+        <v>145</v>
       </c>
       <c r="C17" s="2"/>
       <c r="D17" s="2"/>
       <c r="E17" s="2" t="s">
-        <v>141</v>
+        <v>145</v>
       </c>
       <c r="F17" s="2"/>
       <c r="G17" s="2"/>
@@ -1616,12 +1620,12 @@
         <v>46077</v>
       </c>
       <c r="B18" s="4" t="s">
-        <v>141</v>
+        <v>145</v>
       </c>
       <c r="C18" s="4"/>
       <c r="D18" s="4"/>
       <c r="E18" s="4" t="s">
-        <v>141</v>
+        <v>145</v>
       </c>
       <c r="F18" s="4"/>
       <c r="G18" s="4"/>
@@ -1632,12 +1636,12 @@
         <v>46105</v>
       </c>
       <c r="B19" s="2" t="s">
-        <v>141</v>
+        <v>145</v>
       </c>
       <c r="C19" s="2"/>
       <c r="D19" s="2"/>
       <c r="E19" s="2" t="s">
-        <v>141</v>
+        <v>145</v>
       </c>
       <c r="F19" s="2"/>
       <c r="G19" s="2"/>
@@ -1648,12 +1652,12 @@
         <v>46136</v>
       </c>
       <c r="B20" s="2" t="s">
-        <v>141</v>
+        <v>145</v>
       </c>
       <c r="C20" s="2"/>
       <c r="D20" s="2"/>
       <c r="E20" s="2" t="s">
-        <v>141</v>
+        <v>145</v>
       </c>
       <c r="F20" s="2"/>
       <c r="G20" s="2"/>
@@ -1664,12 +1668,12 @@
         <v>46166</v>
       </c>
       <c r="B21" s="2" t="s">
-        <v>141</v>
+        <v>145</v>
       </c>
       <c r="C21" s="2"/>
       <c r="D21" s="2"/>
       <c r="E21" s="2" t="s">
-        <v>141</v>
+        <v>145</v>
       </c>
       <c r="F21" s="2"/>
       <c r="G21" s="2"/>
@@ -1680,12 +1684,12 @@
         <v>46197</v>
       </c>
       <c r="B22" s="2" t="s">
-        <v>141</v>
+        <v>145</v>
       </c>
       <c r="C22" s="2"/>
       <c r="D22" s="2"/>
       <c r="E22" s="2" t="s">
-        <v>138</v>
+        <v>142</v>
       </c>
       <c r="F22" s="2"/>
       <c r="G22" s="2"/>
@@ -1696,21 +1700,21 @@
         <v>46227</v>
       </c>
       <c r="B23" s="8" t="s">
-        <v>141</v>
+        <v>145</v>
       </c>
       <c r="C23" s="8"/>
       <c r="D23" s="8"/>
       <c r="E23" s="8" t="s">
-        <v>138</v>
+        <v>142</v>
       </c>
       <c r="F23" s="8" t="s">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="G23" s="8" t="s">
-        <v>18</v>
+        <v>155</v>
       </c>
       <c r="H23" s="8" t="s">
-        <v>148</v>
+        <v>156</v>
       </c>
     </row>
     <row r="24" spans="1:8" x14ac:dyDescent="0.25">
@@ -1718,12 +1722,12 @@
         <v>46258</v>
       </c>
       <c r="B24" s="2" t="s">
-        <v>141</v>
+        <v>145</v>
       </c>
       <c r="C24" s="2"/>
       <c r="D24" s="2"/>
       <c r="E24" s="2" t="s">
-        <v>141</v>
+        <v>145</v>
       </c>
       <c r="F24" s="2"/>
       <c r="G24" s="2"/>
@@ -1734,12 +1738,12 @@
         <v>46289</v>
       </c>
       <c r="B25" s="2" t="s">
-        <v>141</v>
+        <v>145</v>
       </c>
       <c r="C25" s="2"/>
       <c r="D25" s="2"/>
       <c r="E25" s="2" t="s">
-        <v>141</v>
+        <v>145</v>
       </c>
       <c r="F25" s="2"/>
       <c r="G25" s="2"/>
@@ -1750,12 +1754,12 @@
         <v>46319</v>
       </c>
       <c r="B26" s="2" t="s">
-        <v>141</v>
+        <v>145</v>
       </c>
       <c r="C26" s="2"/>
       <c r="D26" s="2"/>
       <c r="E26" s="2" t="s">
-        <v>141</v>
+        <v>145</v>
       </c>
       <c r="F26" s="2"/>
       <c r="G26" s="2"/>
@@ -1766,10 +1770,10 @@
         <v>46350</v>
       </c>
       <c r="B27" s="2" t="s">
-        <v>141</v>
+        <v>145</v>
       </c>
       <c r="E27" s="2" t="s">
-        <v>141</v>
+        <v>145</v>
       </c>
     </row>
     <row r="28" spans="1:8" x14ac:dyDescent="0.25">
@@ -1777,10 +1781,10 @@
         <v>46380</v>
       </c>
       <c r="B28" s="2" t="s">
-        <v>141</v>
+        <v>145</v>
       </c>
       <c r="E28" s="2" t="s">
-        <v>141</v>
+        <v>145</v>
       </c>
     </row>
     <row r="29" spans="1:8" x14ac:dyDescent="0.25">
@@ -1788,10 +1792,10 @@
         <v>46411</v>
       </c>
       <c r="B29" s="2" t="s">
-        <v>141</v>
+        <v>145</v>
       </c>
       <c r="E29" s="2" t="s">
-        <v>141</v>
+        <v>145</v>
       </c>
     </row>
     <row r="30" spans="1:8" x14ac:dyDescent="0.25">
@@ -1799,21 +1803,21 @@
         <v>46442</v>
       </c>
       <c r="B30" s="9" t="s">
-        <v>141</v>
+        <v>145</v>
       </c>
       <c r="C30" s="9"/>
       <c r="D30" s="9"/>
       <c r="E30" s="9" t="s">
-        <v>138</v>
+        <v>142</v>
       </c>
       <c r="F30" s="9" t="s">
-        <v>149</v>
+        <v>157</v>
       </c>
       <c r="G30" s="29">
         <v>46435</v>
       </c>
       <c r="H30" s="9" t="s">
-        <v>150</v>
+        <v>158</v>
       </c>
     </row>
   </sheetData>
@@ -1845,35 +1849,35 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:8" ht="21.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A1" s="36" t="s">
-        <v>151</v>
-      </c>
-      <c r="B1" s="36"/>
-      <c r="C1" s="36"/>
-      <c r="D1" s="36"/>
-      <c r="E1" s="36"/>
-      <c r="F1" s="36"/>
-      <c r="G1" s="36"/>
-      <c r="H1" s="36"/>
+      <c r="A1" s="37" t="s">
+        <v>159</v>
+      </c>
+      <c r="B1" s="37"/>
+      <c r="C1" s="37"/>
+      <c r="D1" s="37"/>
+      <c r="E1" s="37"/>
+      <c r="F1" s="37"/>
+      <c r="G1" s="37"/>
+      <c r="H1" s="37"/>
     </row>
     <row r="2" spans="1:8" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A2" s="1" t="s">
-        <v>152</v>
+        <v>160</v>
       </c>
       <c r="B2" s="1" t="s">
-        <v>153</v>
+        <v>161</v>
       </c>
       <c r="C2" s="1" t="s">
-        <v>154</v>
+        <v>162</v>
       </c>
       <c r="D2" s="1" t="s">
-        <v>155</v>
+        <v>163</v>
       </c>
       <c r="E2" s="1" t="s">
-        <v>156</v>
+        <v>164</v>
       </c>
       <c r="F2" s="1" t="s">
-        <v>157</v>
+        <v>165</v>
       </c>
     </row>
     <row r="3" spans="1:8" ht="38.25" x14ac:dyDescent="0.25">
@@ -1881,19 +1885,19 @@
         <v>1</v>
       </c>
       <c r="B3" s="2" t="s">
-        <v>187</v>
+        <v>166</v>
       </c>
       <c r="C3" s="2" t="s">
-        <v>184</v>
+        <v>167</v>
       </c>
       <c r="D3" s="2" t="s">
-        <v>183</v>
+        <v>168</v>
       </c>
       <c r="E3" s="2" t="s">
-        <v>188</v>
+        <v>169</v>
       </c>
       <c r="F3" s="10" t="s">
-        <v>182</v>
+        <v>170</v>
       </c>
     </row>
     <row r="4" spans="1:8" ht="25.5" x14ac:dyDescent="0.25">
@@ -1901,19 +1905,19 @@
         <v>2</v>
       </c>
       <c r="B4" s="4" t="s">
-        <v>189</v>
+        <v>171</v>
       </c>
       <c r="C4" s="4" t="s">
-        <v>186</v>
+        <v>172</v>
       </c>
       <c r="D4" s="4" t="s">
-        <v>185</v>
+        <v>173</v>
       </c>
       <c r="E4" s="4" t="s">
-        <v>190</v>
+        <v>174</v>
       </c>
       <c r="F4" s="10" t="s">
-        <v>182</v>
+        <v>170</v>
       </c>
     </row>
     <row r="5" spans="1:8" ht="38.25" x14ac:dyDescent="0.25">
@@ -1921,19 +1925,19 @@
         <v>3</v>
       </c>
       <c r="B5" s="2" t="s">
-        <v>191</v>
+        <v>175</v>
       </c>
       <c r="C5" s="2" t="s">
-        <v>186</v>
+        <v>172</v>
       </c>
       <c r="D5" s="2" t="s">
-        <v>185</v>
+        <v>173</v>
       </c>
       <c r="E5" s="2" t="s">
-        <v>194</v>
+        <v>176</v>
       </c>
       <c r="F5" s="10" t="s">
-        <v>182</v>
+        <v>170</v>
       </c>
     </row>
     <row r="6" spans="1:8" ht="38.25" x14ac:dyDescent="0.25">
@@ -1941,19 +1945,19 @@
         <v>4</v>
       </c>
       <c r="B6" s="2" t="s">
-        <v>192</v>
+        <v>177</v>
       </c>
       <c r="C6" s="2" t="s">
-        <v>186</v>
+        <v>172</v>
       </c>
       <c r="D6" s="2" t="s">
-        <v>185</v>
+        <v>173</v>
       </c>
       <c r="E6" s="2" t="s">
-        <v>193</v>
+        <v>178</v>
       </c>
       <c r="F6" s="10" t="s">
-        <v>182</v>
+        <v>170</v>
       </c>
     </row>
   </sheetData>
@@ -1984,41 +1988,41 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:21" ht="21.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A1" s="36" t="s">
-        <v>158</v>
-      </c>
-      <c r="B1" s="36"/>
-      <c r="C1" s="36"/>
-      <c r="D1" s="36"/>
-      <c r="E1" s="36"/>
-      <c r="F1" s="36"/>
-      <c r="G1" s="36"/>
-      <c r="H1" s="36"/>
+      <c r="A1" s="37" t="s">
+        <v>179</v>
+      </c>
+      <c r="B1" s="37"/>
+      <c r="C1" s="37"/>
+      <c r="D1" s="37"/>
+      <c r="E1" s="37"/>
+      <c r="F1" s="37"/>
+      <c r="G1" s="37"/>
+      <c r="H1" s="37"/>
     </row>
     <row r="2" spans="1:21" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A2" s="1" t="s">
-        <v>152</v>
+        <v>160</v>
       </c>
       <c r="B2" s="1" t="s">
-        <v>113</v>
+        <v>117</v>
       </c>
       <c r="C2" s="1" t="s">
-        <v>159</v>
+        <v>180</v>
       </c>
       <c r="D2" s="1" t="s">
-        <v>160</v>
+        <v>181</v>
       </c>
       <c r="E2" s="1" t="s">
-        <v>161</v>
+        <v>182</v>
       </c>
       <c r="F2" s="1" t="s">
-        <v>162</v>
+        <v>183</v>
       </c>
       <c r="G2" s="1" t="s">
-        <v>163</v>
+        <v>184</v>
       </c>
       <c r="H2" s="1" t="s">
-        <v>164</v>
+        <v>185</v>
       </c>
     </row>
     <row r="3" spans="1:21" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
@@ -2026,13 +2030,13 @@
         <v>1</v>
       </c>
       <c r="B3" s="2" t="s">
-        <v>196</v>
+        <v>186</v>
       </c>
       <c r="C3" s="2" t="s">
-        <v>197</v>
+        <v>187</v>
       </c>
       <c r="D3" s="2" t="s">
-        <v>165</v>
+        <v>188</v>
       </c>
       <c r="E3" s="13">
         <v>1</v>
@@ -2044,7 +2048,7 @@
         <v>1</v>
       </c>
       <c r="H3" s="11" t="s">
-        <v>166</v>
+        <v>189</v>
       </c>
     </row>
     <row r="4" spans="1:21" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
@@ -2052,13 +2056,13 @@
         <v>2</v>
       </c>
       <c r="B4" s="4" t="s">
-        <v>198</v>
+        <v>190</v>
       </c>
       <c r="C4" s="4" t="s">
-        <v>199</v>
+        <v>191</v>
       </c>
       <c r="D4" s="4" t="s">
-        <v>165</v>
+        <v>188</v>
       </c>
       <c r="E4" s="34">
         <v>1</v>
@@ -2070,7 +2074,7 @@
         <v>1</v>
       </c>
       <c r="H4" s="11" t="s">
-        <v>166</v>
+        <v>189</v>
       </c>
     </row>
     <row r="5" spans="1:21" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
@@ -2078,13 +2082,13 @@
         <v>3</v>
       </c>
       <c r="B5" s="2" t="s">
-        <v>200</v>
+        <v>192</v>
       </c>
       <c r="C5" s="2" t="s">
-        <v>199</v>
+        <v>191</v>
       </c>
       <c r="D5" s="2" t="s">
-        <v>165</v>
+        <v>188</v>
       </c>
       <c r="E5" s="13">
         <v>1</v>
@@ -2096,7 +2100,7 @@
         <v>1</v>
       </c>
       <c r="H5" s="11" t="s">
-        <v>166</v>
+        <v>189</v>
       </c>
     </row>
     <row r="6" spans="1:21" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
@@ -2104,13 +2108,13 @@
         <v>4</v>
       </c>
       <c r="B6" s="4" t="s">
-        <v>201</v>
+        <v>193</v>
       </c>
       <c r="C6" s="4" t="s">
-        <v>202</v>
+        <v>194</v>
       </c>
       <c r="D6" s="4" t="s">
-        <v>165</v>
+        <v>188</v>
       </c>
       <c r="E6" s="34">
         <v>1</v>
@@ -2122,7 +2126,7 @@
         <v>1</v>
       </c>
       <c r="H6" s="11" t="s">
-        <v>166</v>
+        <v>189</v>
       </c>
     </row>
     <row r="7" spans="1:21" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
@@ -2130,13 +2134,13 @@
         <v>5</v>
       </c>
       <c r="B7" s="2" t="s">
-        <v>203</v>
+        <v>195</v>
       </c>
       <c r="C7" s="2" t="s">
-        <v>204</v>
+        <v>196</v>
       </c>
       <c r="D7" s="2" t="s">
-        <v>165</v>
+        <v>188</v>
       </c>
       <c r="E7" s="13">
         <v>1</v>
@@ -2148,7 +2152,7 @@
         <v>0.9</v>
       </c>
       <c r="H7" s="10" t="s">
-        <v>205</v>
+        <v>197</v>
       </c>
     </row>
     <row r="8" spans="1:21" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
@@ -2156,13 +2160,13 @@
         <v>6</v>
       </c>
       <c r="B8" s="4" t="s">
-        <v>195</v>
+        <v>198</v>
       </c>
       <c r="C8" s="4" t="s">
-        <v>204</v>
+        <v>196</v>
       </c>
       <c r="D8" s="4" t="s">
-        <v>165</v>
+        <v>188</v>
       </c>
       <c r="E8" s="34">
         <v>1</v>
@@ -2174,7 +2178,7 @@
         <v>0</v>
       </c>
       <c r="H8" s="10" t="s">
-        <v>205</v>
+        <v>197</v>
       </c>
     </row>
     <row r="9" spans="1:21" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
@@ -2182,13 +2186,13 @@
         <v>7</v>
       </c>
       <c r="B9" s="2" t="s">
-        <v>206</v>
+        <v>199</v>
       </c>
       <c r="C9" s="2" t="s">
-        <v>199</v>
+        <v>191</v>
       </c>
       <c r="D9" s="2" t="s">
-        <v>165</v>
+        <v>188</v>
       </c>
       <c r="E9" s="13">
         <v>0.8</v>
@@ -2200,7 +2204,7 @@
         <v>0</v>
       </c>
       <c r="H9" s="10" t="s">
-        <v>205</v>
+        <v>197</v>
       </c>
     </row>
     <row r="10" spans="1:21" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
@@ -2208,25 +2212,25 @@
         <v>8</v>
       </c>
       <c r="B10" s="4" t="s">
-        <v>207</v>
+        <v>200</v>
       </c>
       <c r="C10" s="4" t="s">
-        <v>208</v>
+        <v>201</v>
       </c>
       <c r="D10" s="4" t="s">
-        <v>165</v>
+        <v>188</v>
       </c>
       <c r="E10" s="34">
         <v>1</v>
       </c>
       <c r="F10" s="34" t="s">
-        <v>209</v>
+        <v>202</v>
       </c>
       <c r="G10" s="34">
         <v>0.15</v>
       </c>
       <c r="H10" s="10" t="s">
-        <v>205</v>
+        <v>197</v>
       </c>
     </row>
     <row r="11" spans="1:21" x14ac:dyDescent="0.25">
@@ -2313,16 +2317,16 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:8" ht="21.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A1" s="36" t="s">
-        <v>167</v>
-      </c>
-      <c r="B1" s="36"/>
-      <c r="C1" s="36"/>
-      <c r="D1" s="36"/>
-      <c r="E1" s="36"/>
-      <c r="F1" s="36"/>
-      <c r="G1" s="36"/>
-      <c r="H1" s="36"/>
+      <c r="A1" s="37" t="s">
+        <v>203</v>
+      </c>
+      <c r="B1" s="37"/>
+      <c r="C1" s="37"/>
+      <c r="D1" s="37"/>
+      <c r="E1" s="37"/>
+      <c r="F1" s="37"/>
+      <c r="G1" s="37"/>
+      <c r="H1" s="37"/>
     </row>
     <row r="2" spans="1:8" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A2" s="1" t="s">
@@ -2334,15 +2338,15 @@
     </row>
     <row r="3" spans="1:8" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A3" s="2" t="s">
-        <v>168</v>
+        <v>204</v>
       </c>
       <c r="B3" s="3" t="s">
-        <v>169</v>
+        <v>205</v>
       </c>
     </row>
     <row r="4" spans="1:8" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A4" s="4" t="s">
-        <v>170</v>
+        <v>206</v>
       </c>
       <c r="B4" s="12">
         <v>46176</v>
@@ -2350,18 +2354,18 @@
     </row>
     <row r="5" spans="1:8" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A5" s="2" t="s">
-        <v>171</v>
+        <v>207</v>
       </c>
       <c r="B5" s="3" t="s">
-        <v>210</v>
+        <v>208</v>
       </c>
     </row>
     <row r="6" spans="1:8" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A6" s="4" t="s">
-        <v>172</v>
+        <v>209</v>
       </c>
       <c r="B6" s="3" t="s">
-        <v>173</v>
+        <v>210</v>
       </c>
     </row>
   </sheetData>
@@ -2390,31 +2394,31 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:8" ht="21.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A1" s="36" t="s">
-        <v>9</v>
-      </c>
-      <c r="B1" s="36"/>
-      <c r="C1" s="36"/>
-      <c r="D1" s="36"/>
-      <c r="E1" s="36"/>
-      <c r="F1" s="36"/>
-      <c r="G1" s="36"/>
-      <c r="H1" s="36"/>
+      <c r="A1" s="37" t="s">
+        <v>11</v>
+      </c>
+      <c r="B1" s="37"/>
+      <c r="C1" s="37"/>
+      <c r="D1" s="37"/>
+      <c r="E1" s="37"/>
+      <c r="F1" s="37"/>
+      <c r="G1" s="37"/>
+      <c r="H1" s="37"/>
     </row>
     <row r="2" spans="1:8" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A2" s="1" t="s">
         <v>1</v>
       </c>
       <c r="B2" s="1" t="s">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="C2" s="1" t="s">
-        <v>11</v>
+        <v>13</v>
       </c>
     </row>
     <row r="3" spans="1:8" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A3" s="2" t="s">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="B3" s="16">
         <v>45497</v>
@@ -2423,7 +2427,7 @@
     </row>
     <row r="4" spans="1:8" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A4" s="4" t="s">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="B4" s="16">
         <v>45530</v>
@@ -2432,7 +2436,7 @@
     </row>
     <row r="5" spans="1:8" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A5" s="2" t="s">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="B5" s="16">
         <v>45571</v>
@@ -2441,7 +2445,7 @@
     </row>
     <row r="6" spans="1:8" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A6" s="4" t="s">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="B6" s="16">
         <v>45718</v>
@@ -2450,7 +2454,7 @@
     </row>
     <row r="7" spans="1:8" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A7" s="2" t="s">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="B7" s="16">
         <v>45830</v>
@@ -2459,24 +2463,24 @@
     </row>
     <row r="8" spans="1:8" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A8" s="4" t="s">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="B8" s="16">
         <v>46227</v>
       </c>
       <c r="C8" s="4" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
     </row>
     <row r="9" spans="1:8" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A9" s="2" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="B9" s="16">
         <v>46435</v>
       </c>
       <c r="C9" s="2" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
     </row>
   </sheetData>
@@ -2507,34 +2511,34 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:8" ht="21.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A1" s="36" t="s">
-        <v>22</v>
-      </c>
-      <c r="B1" s="36"/>
-      <c r="C1" s="36"/>
-      <c r="D1" s="36"/>
-      <c r="E1" s="36"/>
-      <c r="F1" s="36"/>
-      <c r="G1" s="36"/>
-      <c r="H1" s="36"/>
+      <c r="A1" s="37" t="s">
+        <v>23</v>
+      </c>
+      <c r="B1" s="37"/>
+      <c r="C1" s="37"/>
+      <c r="D1" s="37"/>
+      <c r="E1" s="37"/>
+      <c r="F1" s="37"/>
+      <c r="G1" s="37"/>
+      <c r="H1" s="37"/>
     </row>
     <row r="2" spans="1:8" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A2" s="1" t="s">
         <v>1</v>
       </c>
       <c r="B2" s="1" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="C2" s="1" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="D2" s="1" t="s">
-        <v>11</v>
+        <v>13</v>
       </c>
     </row>
     <row r="3" spans="1:8" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A3" s="2" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="B3" s="15">
         <v>388016486</v>
@@ -2544,7 +2548,7 @@
     </row>
     <row r="4" spans="1:8" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A4" s="4" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="B4" s="15">
         <v>0</v>
@@ -2554,7 +2558,7 @@
     </row>
     <row r="5" spans="1:8" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A5" s="2" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="B5" s="15">
         <v>0</v>
@@ -2564,7 +2568,7 @@
     </row>
     <row r="6" spans="1:8" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A6" s="4" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="B6" s="15">
         <v>0</v>
@@ -2574,19 +2578,19 @@
     </row>
     <row r="7" spans="1:8" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A7" s="2" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="B7" s="15">
         <v>388016486</v>
       </c>
       <c r="C7" s="2"/>
       <c r="D7" s="2" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
     </row>
     <row r="8" spans="1:8" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A8" s="4" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="B8" s="15">
         <v>34426811</v>
@@ -2596,7 +2600,7 @@
     </row>
     <row r="9" spans="1:8" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A9" s="2" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="B9" s="15">
         <v>15596872</v>
@@ -2606,7 +2610,7 @@
         <v>0.45304434384003794</v>
       </c>
       <c r="D9" s="2" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
     </row>
   </sheetData>
@@ -2636,16 +2640,16 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:8" ht="21.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A1" s="36" t="s">
-        <v>34</v>
-      </c>
-      <c r="B1" s="36"/>
-      <c r="C1" s="36"/>
-      <c r="D1" s="36"/>
-      <c r="E1" s="36"/>
-      <c r="F1" s="36"/>
-      <c r="G1" s="36"/>
-      <c r="H1" s="36"/>
+      <c r="A1" s="37" t="s">
+        <v>35</v>
+      </c>
+      <c r="B1" s="37"/>
+      <c r="C1" s="37"/>
+      <c r="D1" s="37"/>
+      <c r="E1" s="37"/>
+      <c r="F1" s="37"/>
+      <c r="G1" s="37"/>
+      <c r="H1" s="37"/>
     </row>
     <row r="2" spans="1:8" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A2" s="1" t="s">
@@ -2655,85 +2659,85 @@
         <v>2</v>
       </c>
       <c r="C2" s="1" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="D2" s="1" t="s">
-        <v>11</v>
+        <v>13</v>
       </c>
     </row>
     <row r="3" spans="1:8" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A3" s="2" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="B3" s="18">
         <v>355587125</v>
       </c>
       <c r="C3" s="20"/>
       <c r="D3" s="2" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
     </row>
     <row r="4" spans="1:8" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A4" s="4" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="B4" s="19" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="C4" s="21"/>
       <c r="D4" s="4" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
     </row>
     <row r="5" spans="1:8" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A5" s="4" t="s">
-        <v>178</v>
+        <v>41</v>
       </c>
       <c r="B5" s="19">
-        <v>0.68799999999999994</v>
+        <v>0.75600000000000001</v>
       </c>
       <c r="C5" s="21"/>
       <c r="D5" s="4"/>
     </row>
     <row r="6" spans="1:8" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A6" s="2" t="s">
-        <v>40</v>
+        <v>42</v>
       </c>
       <c r="B6" s="19">
-        <v>0.40899999999999997</v>
+        <v>0.45900000000000002</v>
       </c>
       <c r="C6" s="22"/>
       <c r="D6" s="2" t="s">
-        <v>41</v>
+        <v>43</v>
       </c>
     </row>
     <row r="7" spans="1:8" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A7" s="4" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="B7" s="18">
         <v>34426811</v>
       </c>
       <c r="C7" s="21"/>
       <c r="D7" s="4" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
     </row>
     <row r="8" spans="1:8" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A8" s="2" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="B8" s="18">
         <v>15596872</v>
       </c>
       <c r="C8" s="20"/>
       <c r="D8" s="2" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
     </row>
     <row r="9" spans="1:8" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A9" s="4" t="s">
-        <v>42</v>
+        <v>44</v>
       </c>
       <c r="B9" s="19">
         <f>(B7-B8)/B7</f>
@@ -2741,19 +2745,19 @@
       </c>
       <c r="C9" s="21"/>
       <c r="D9" s="4" t="s">
-        <v>43</v>
+        <v>45</v>
       </c>
     </row>
     <row r="10" spans="1:8" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A10" s="2" t="s">
-        <v>44</v>
+        <v>46</v>
       </c>
       <c r="B10" s="17" t="s">
-        <v>176</v>
+        <v>47</v>
       </c>
       <c r="C10" s="20"/>
       <c r="D10" s="2" t="s">
-        <v>45</v>
+        <v>48</v>
       </c>
     </row>
   </sheetData>
@@ -2773,7 +2777,7 @@
   <sheetPr>
     <tabColor rgb="FFE87722"/>
   </sheetPr>
-  <dimension ref="A1:H8"/>
+  <dimension ref="A1:H16"/>
   <sheetFormatPr defaultColWidth="8.7109375" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="32" customWidth="1"/>
@@ -2784,70 +2788,70 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:8" ht="21.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A1" s="36" t="s">
-        <v>46</v>
-      </c>
-      <c r="B1" s="36"/>
-      <c r="C1" s="36"/>
-      <c r="D1" s="36"/>
-      <c r="E1" s="36"/>
-      <c r="F1" s="36"/>
-      <c r="G1" s="36"/>
-      <c r="H1" s="36"/>
+      <c r="A1" s="37" t="s">
+        <v>49</v>
+      </c>
+      <c r="B1" s="37"/>
+      <c r="C1" s="37"/>
+      <c r="D1" s="37"/>
+      <c r="E1" s="37"/>
+      <c r="F1" s="37"/>
+      <c r="G1" s="37"/>
+      <c r="H1" s="37"/>
     </row>
     <row r="2" spans="1:8" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A2" s="1" t="s">
         <v>1</v>
       </c>
       <c r="B2" s="1" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="C2" s="1" t="s">
-        <v>47</v>
+        <v>50</v>
       </c>
       <c r="D2" s="1" t="s">
-        <v>48</v>
+        <v>51</v>
       </c>
       <c r="E2" s="1" t="s">
-        <v>11</v>
+        <v>13</v>
       </c>
     </row>
     <row r="3" spans="1:8" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A3" s="2" t="s">
-        <v>49</v>
+        <v>52</v>
       </c>
       <c r="B3" s="14">
-        <v>204059236</v>
+        <v>223311139</v>
       </c>
       <c r="C3" s="13">
         <f>B3/Commercial_Info!$B$3</f>
-        <v>0.52590352050144595</v>
+        <v>0.57551971902554677</v>
       </c>
       <c r="D3" s="2" t="s">
-        <v>50</v>
+        <v>53</v>
       </c>
       <c r="E3" s="2"/>
       <c r="G3" s="24"/>
     </row>
     <row r="4" spans="1:8" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A4" s="4" t="s">
-        <v>51</v>
+        <v>54</v>
       </c>
       <c r="B4" s="14">
-        <v>152961744</v>
+        <v>204095236</v>
       </c>
       <c r="C4" s="13">
         <f>B4/Commercial_Info!$B$3</f>
-        <v>0.39421454891481078</v>
+        <v>0.52599630006442566</v>
       </c>
       <c r="D4" s="4" t="s">
-        <v>52</v>
+        <v>55</v>
       </c>
       <c r="E4" s="4"/>
     </row>
     <row r="5" spans="1:8" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A5" s="2" t="s">
-        <v>53</v>
+        <v>56</v>
       </c>
       <c r="B5" s="14">
         <v>152961744</v>
@@ -2857,26 +2861,26 @@
         <v>0.39421454891481078</v>
       </c>
       <c r="D5" s="2" t="s">
-        <v>52</v>
+        <v>55</v>
       </c>
       <c r="E5" s="2"/>
     </row>
     <row r="6" spans="1:8" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A6" s="4" t="s">
-        <v>54</v>
+        <v>57</v>
       </c>
       <c r="B6" s="14">
         <v>0</v>
       </c>
       <c r="C6" s="4"/>
       <c r="D6" s="4" t="s">
-        <v>55</v>
+        <v>58</v>
       </c>
       <c r="E6" s="4"/>
     </row>
     <row r="7" spans="1:8" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A7" s="2" t="s">
-        <v>56</v>
+        <v>59</v>
       </c>
       <c r="B7" s="14">
         <v>68039022</v>
@@ -2886,25 +2890,34 @@
         <v>0.17535085352017749</v>
       </c>
       <c r="D7" s="2" t="s">
-        <v>52</v>
+        <v>55</v>
       </c>
       <c r="E7" s="2"/>
     </row>
     <row r="8" spans="1:8" ht="28.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A8" s="4" t="s">
-        <v>177</v>
+        <v>60</v>
       </c>
       <c r="B8" s="26" t="str">
         <f>ROUNDUP(C4*100,0)&amp;"%"&amp;" / "&amp;ROUNDUP(Budgetary_Info!B6*100,0)&amp;"%"</f>
-        <v>40% / 41%</v>
+        <v>53% / 46%</v>
       </c>
       <c r="C8" s="4"/>
       <c r="D8" s="4" t="s">
-        <v>55</v>
+        <v>58</v>
       </c>
       <c r="E8" s="4" t="s">
-        <v>57</v>
-      </c>
+        <v>61</v>
+      </c>
+    </row>
+    <row r="14" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="E14" s="36"/>
+    </row>
+    <row r="15" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="E15" s="36"/>
+    </row>
+    <row r="16" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="E16" s="36"/>
     </row>
   </sheetData>
   <mergeCells count="1">
@@ -2933,83 +2946,82 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:8" ht="21.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A1" s="36" t="s">
-        <v>58</v>
-      </c>
-      <c r="B1" s="36"/>
-      <c r="C1" s="36"/>
-      <c r="D1" s="36"/>
-      <c r="E1" s="36"/>
-      <c r="F1" s="36"/>
-      <c r="G1" s="36"/>
-      <c r="H1" s="36"/>
+      <c r="A1" s="37" t="s">
+        <v>62</v>
+      </c>
+      <c r="B1" s="37"/>
+      <c r="C1" s="37"/>
+      <c r="D1" s="37"/>
+      <c r="E1" s="37"/>
+      <c r="F1" s="37"/>
+      <c r="G1" s="37"/>
+      <c r="H1" s="37"/>
     </row>
     <row r="2" spans="1:8" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A2" s="1" t="s">
         <v>1</v>
       </c>
       <c r="B2" s="1" t="s">
-        <v>59</v>
+        <v>63</v>
       </c>
       <c r="C2" s="1" t="s">
-        <v>60</v>
+        <v>64</v>
       </c>
       <c r="D2" s="1" t="s">
-        <v>11</v>
+        <v>13</v>
       </c>
     </row>
     <row r="3" spans="1:8" ht="27" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A3" s="2" t="s">
-        <v>61</v>
+        <v>65</v>
       </c>
       <c r="B3" s="3">
-        <f>B5-B6</f>
-        <v>-61.199999999999989</v>
+        <v>-70.3</v>
       </c>
       <c r="C3" s="2"/>
       <c r="D3" s="2" t="s">
-        <v>62</v>
-      </c>
-    </row>
-    <row r="4" spans="1:8" ht="27" customHeight="1" x14ac:dyDescent="0.25">
+        <v>66</v>
+      </c>
+    </row>
+    <row r="4" spans="1:8" ht="46.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A4" s="4" t="s">
-        <v>63</v>
+        <v>67</v>
       </c>
       <c r="B4" s="3" t="s">
-        <v>64</v>
+        <v>68</v>
       </c>
       <c r="C4" s="4"/>
       <c r="D4" s="4" t="s">
-        <v>65</v>
+        <v>69</v>
       </c>
     </row>
     <row r="5" spans="1:8" ht="27" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A5" s="2" t="s">
-        <v>66</v>
+        <v>70</v>
       </c>
       <c r="B5" s="3">
         <v>68</v>
       </c>
       <c r="C5" s="35">
         <f>(B5/B6)*100</f>
-        <v>52.631578947368432</v>
+        <v>49.132947976878611</v>
       </c>
       <c r="D5" s="2" t="s">
-        <v>67</v>
+        <v>71</v>
       </c>
     </row>
     <row r="6" spans="1:8" ht="27" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A6" s="4" t="s">
-        <v>68</v>
+        <v>72</v>
       </c>
       <c r="B6" s="3">
-        <v>129.19999999999999</v>
+        <v>138.4</v>
       </c>
       <c r="C6" s="4" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="D6" s="4" t="s">
-        <v>69</v>
+        <v>73</v>
       </c>
     </row>
   </sheetData>
@@ -3039,24 +3051,24 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:8" ht="21.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A1" s="36" t="s">
-        <v>70</v>
-      </c>
-      <c r="B1" s="36"/>
-      <c r="C1" s="36"/>
-      <c r="D1" s="36"/>
-      <c r="E1" s="36"/>
-      <c r="F1" s="36"/>
-      <c r="G1" s="36"/>
-      <c r="H1" s="36"/>
+      <c r="A1" s="37" t="s">
+        <v>74</v>
+      </c>
+      <c r="B1" s="37"/>
+      <c r="C1" s="37"/>
+      <c r="D1" s="37"/>
+      <c r="E1" s="37"/>
+      <c r="F1" s="37"/>
+      <c r="G1" s="37"/>
+      <c r="H1" s="37"/>
     </row>
     <row r="2" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A2" s="37" t="s">
-        <v>71</v>
-      </c>
-      <c r="B2" s="37"/>
-      <c r="C2" s="37"/>
-      <c r="D2" s="37"/>
+      <c r="A2" s="38" t="s">
+        <v>75</v>
+      </c>
+      <c r="B2" s="38"/>
+      <c r="C2" s="38"/>
+      <c r="D2" s="38"/>
     </row>
     <row r="3" spans="1:8" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A3" s="1" t="s">
@@ -3066,201 +3078,201 @@
         <v>2</v>
       </c>
       <c r="C3" s="1" t="s">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="D3" s="1"/>
     </row>
     <row r="4" spans="1:8" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A4" s="4" t="s">
-        <v>72</v>
+        <v>76</v>
       </c>
       <c r="B4" s="3">
         <f>B5+B6</f>
         <v>751</v>
       </c>
       <c r="C4" s="4" t="s">
-        <v>73</v>
+        <v>77</v>
       </c>
       <c r="D4" s="4"/>
     </row>
     <row r="5" spans="1:8" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A5" s="2" t="s">
-        <v>74</v>
+        <v>78</v>
       </c>
       <c r="B5" s="3">
         <v>654</v>
       </c>
       <c r="C5" s="2" t="s">
-        <v>75</v>
+        <v>79</v>
       </c>
       <c r="D5" s="2"/>
     </row>
     <row r="6" spans="1:8" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A6" s="4" t="s">
-        <v>76</v>
+        <v>80</v>
       </c>
       <c r="B6" s="3">
         <v>97</v>
       </c>
       <c r="C6" s="4" t="s">
-        <v>77</v>
+        <v>81</v>
       </c>
       <c r="D6" s="4"/>
     </row>
     <row r="7" spans="1:8" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A7" s="2" t="s">
-        <v>78</v>
+        <v>82</v>
       </c>
       <c r="B7" s="25">
         <f>B5/B4</f>
         <v>0.87083888149134492</v>
       </c>
       <c r="C7" s="2" t="s">
-        <v>79</v>
+        <v>83</v>
       </c>
       <c r="D7" s="2"/>
     </row>
     <row r="8" spans="1:8" ht="6" customHeight="1" x14ac:dyDescent="0.25"/>
     <row r="9" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A9" s="37" t="s">
-        <v>80</v>
-      </c>
-      <c r="B9" s="37"/>
-      <c r="C9" s="37"/>
-      <c r="D9" s="37"/>
+      <c r="A9" s="38" t="s">
+        <v>84</v>
+      </c>
+      <c r="B9" s="38"/>
+      <c r="C9" s="38"/>
+      <c r="D9" s="38"/>
     </row>
     <row r="10" spans="1:8" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A10" s="1" t="s">
-        <v>81</v>
+        <v>85</v>
       </c>
       <c r="B10" s="1" t="s">
-        <v>82</v>
+        <v>86</v>
       </c>
       <c r="C10" s="1" t="s">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="D10" s="1"/>
     </row>
     <row r="11" spans="1:8" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A11" s="2" t="s">
-        <v>83</v>
+        <v>87</v>
       </c>
       <c r="B11" s="3">
         <v>386</v>
       </c>
       <c r="C11" s="2" t="s">
-        <v>84</v>
+        <v>88</v>
       </c>
       <c r="D11" s="2"/>
     </row>
     <row r="12" spans="1:8" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A12" s="4" t="s">
-        <v>85</v>
+        <v>89</v>
       </c>
       <c r="B12" s="3">
         <v>268</v>
       </c>
       <c r="C12" s="4" t="s">
-        <v>84</v>
+        <v>88</v>
       </c>
       <c r="D12" s="4"/>
     </row>
     <row r="13" spans="1:8" ht="6" customHeight="1" x14ac:dyDescent="0.25"/>
     <row r="14" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A14" s="37" t="s">
-        <v>86</v>
-      </c>
-      <c r="B14" s="37"/>
-      <c r="C14" s="37"/>
-      <c r="D14" s="37"/>
+      <c r="A14" s="38" t="s">
+        <v>90</v>
+      </c>
+      <c r="B14" s="38"/>
+      <c r="C14" s="38"/>
+      <c r="D14" s="38"/>
     </row>
     <row r="15" spans="1:8" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A15" s="1" t="s">
-        <v>87</v>
+        <v>91</v>
       </c>
       <c r="B15" s="1" t="s">
         <v>2</v>
       </c>
       <c r="C15" s="1" t="s">
-        <v>88</v>
+        <v>92</v>
       </c>
       <c r="D15" s="1"/>
     </row>
     <row r="16" spans="1:8" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A16" s="4" t="s">
-        <v>89</v>
+        <v>93</v>
       </c>
       <c r="B16" s="3">
         <f>B4/B5*100</f>
         <v>114.83180428134557</v>
       </c>
       <c r="C16" s="4" t="s">
-        <v>90</v>
+        <v>94</v>
       </c>
       <c r="D16" s="4"/>
     </row>
     <row r="17" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A17" s="2" t="s">
-        <v>91</v>
+        <v>95</v>
       </c>
       <c r="B17" s="3">
         <f>B6/B5*100</f>
         <v>14.831804281345565</v>
       </c>
       <c r="C17" s="2" t="s">
-        <v>92</v>
+        <v>96</v>
       </c>
       <c r="D17" s="2"/>
     </row>
     <row r="18" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A18" s="4" t="s">
-        <v>93</v>
+        <v>97</v>
       </c>
       <c r="B18" s="3">
         <f>B16</f>
         <v>114.83180428134557</v>
       </c>
       <c r="C18" s="4" t="s">
-        <v>94</v>
+        <v>98</v>
       </c>
       <c r="D18" s="4"/>
     </row>
     <row r="19" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A19" s="2" t="s">
-        <v>95</v>
+        <v>99</v>
       </c>
       <c r="B19" s="3">
         <f>100-B16</f>
         <v>-14.831804281345569</v>
       </c>
       <c r="C19" s="2" t="s">
-        <v>96</v>
+        <v>100</v>
       </c>
       <c r="D19" s="2"/>
     </row>
     <row r="20" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A20" s="4" t="s">
-        <v>97</v>
+        <v>101</v>
       </c>
       <c r="B20" s="3">
         <f>B17</f>
         <v>14.831804281345565</v>
       </c>
       <c r="C20" s="4" t="s">
-        <v>98</v>
+        <v>102</v>
       </c>
       <c r="D20" s="4"/>
     </row>
     <row r="21" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A21" s="2" t="s">
-        <v>99</v>
+        <v>103</v>
       </c>
       <c r="B21" s="3">
         <f>100-B17</f>
         <v>85.168195718654431</v>
       </c>
       <c r="C21" s="2" t="s">
-        <v>100</v>
+        <v>104</v>
       </c>
       <c r="D21" s="2"/>
     </row>
@@ -3294,40 +3306,40 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:8" ht="21.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A1" s="36" t="s">
-        <v>101</v>
-      </c>
-      <c r="B1" s="36"/>
-      <c r="C1" s="36"/>
-      <c r="D1" s="36"/>
-      <c r="E1" s="36"/>
-      <c r="F1" s="36"/>
-      <c r="G1" s="36"/>
-      <c r="H1" s="36"/>
+      <c r="A1" s="37" t="s">
+        <v>105</v>
+      </c>
+      <c r="B1" s="37"/>
+      <c r="C1" s="37"/>
+      <c r="D1" s="37"/>
+      <c r="E1" s="37"/>
+      <c r="F1" s="37"/>
+      <c r="G1" s="37"/>
+      <c r="H1" s="37"/>
     </row>
     <row r="2" spans="1:8" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A2" s="1" t="s">
-        <v>102</v>
+        <v>106</v>
       </c>
       <c r="B2" s="1" t="s">
-        <v>103</v>
+        <v>107</v>
       </c>
       <c r="C2" s="1" t="s">
-        <v>104</v>
+        <v>108</v>
       </c>
       <c r="D2" s="1" t="s">
-        <v>105</v>
+        <v>109</v>
       </c>
       <c r="E2" s="1" t="s">
-        <v>106</v>
+        <v>110</v>
       </c>
       <c r="F2" s="1" t="s">
-        <v>11</v>
+        <v>13</v>
       </c>
     </row>
     <row r="3" spans="1:8" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A3" s="2" t="s">
-        <v>107</v>
+        <v>111</v>
       </c>
       <c r="B3" s="27">
         <v>92.78</v>
@@ -3340,15 +3352,15 @@
         <v>8.5</v>
       </c>
       <c r="E3" s="2" t="s">
-        <v>108</v>
+        <v>112</v>
       </c>
       <c r="F3" s="2" t="s">
-        <v>109</v>
+        <v>113</v>
       </c>
     </row>
     <row r="4" spans="1:8" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A4" s="4" t="s">
-        <v>110</v>
+        <v>114</v>
       </c>
       <c r="B4" s="28">
         <v>100</v>
@@ -3361,15 +3373,15 @@
         <v>0.75</v>
       </c>
       <c r="E4" s="4" t="s">
-        <v>111</v>
+        <v>115</v>
       </c>
       <c r="F4" s="4" t="s">
-        <v>112</v>
+        <v>116</v>
       </c>
     </row>
     <row r="5" spans="1:8" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A5" s="2" t="s">
-        <v>113</v>
+        <v>117</v>
       </c>
       <c r="B5" s="27">
         <v>100</v>
@@ -3382,15 +3394,15 @@
         <v>4.4599999999999937</v>
       </c>
       <c r="E5" s="2" t="s">
-        <v>114</v>
+        <v>118</v>
       </c>
       <c r="F5" s="2" t="s">
-        <v>115</v>
+        <v>119</v>
       </c>
     </row>
     <row r="6" spans="1:8" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A6" s="4" t="s">
-        <v>116</v>
+        <v>120</v>
       </c>
       <c r="B6" s="28">
         <v>95.92</v>
@@ -3403,15 +3415,15 @@
         <v>5.1000000000000085</v>
       </c>
       <c r="E6" s="4" t="s">
-        <v>108</v>
+        <v>112</v>
       </c>
       <c r="F6" s="4" t="s">
-        <v>109</v>
+        <v>113</v>
       </c>
     </row>
     <row r="7" spans="1:8" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A7" s="2" t="s">
-        <v>117</v>
+        <v>121</v>
       </c>
       <c r="B7" s="27">
         <v>100</v>
@@ -3424,15 +3436,15 @@
         <v>6.6800000000000068</v>
       </c>
       <c r="E7" s="2" t="s">
-        <v>114</v>
+        <v>118</v>
       </c>
       <c r="F7" s="2" t="s">
-        <v>115</v>
+        <v>119</v>
       </c>
     </row>
     <row r="8" spans="1:8" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A8" s="4" t="s">
-        <v>118</v>
+        <v>122</v>
       </c>
       <c r="B8" s="28">
         <v>68.05</v>
@@ -3445,10 +3457,10 @@
         <v>45.97</v>
       </c>
       <c r="E8" s="4" t="s">
-        <v>108</v>
+        <v>112</v>
       </c>
       <c r="F8" s="4" t="s">
-        <v>119</v>
+        <v>123</v>
       </c>
     </row>
   </sheetData>
@@ -3478,40 +3490,40 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:8" ht="21.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A1" s="36" t="s">
-        <v>120</v>
-      </c>
-      <c r="B1" s="36"/>
-      <c r="C1" s="36"/>
-      <c r="D1" s="36"/>
-      <c r="E1" s="36"/>
-      <c r="F1" s="36"/>
-      <c r="G1" s="36"/>
-      <c r="H1" s="36"/>
+      <c r="A1" s="37" t="s">
+        <v>124</v>
+      </c>
+      <c r="B1" s="37"/>
+      <c r="C1" s="37"/>
+      <c r="D1" s="37"/>
+      <c r="E1" s="37"/>
+      <c r="F1" s="37"/>
+      <c r="G1" s="37"/>
+      <c r="H1" s="37"/>
     </row>
     <row r="2" spans="1:8" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A2" s="1" t="s">
-        <v>121</v>
+        <v>125</v>
       </c>
       <c r="B2" s="1" t="s">
-        <v>103</v>
+        <v>107</v>
       </c>
       <c r="C2" s="1" t="s">
-        <v>104</v>
+        <v>108</v>
       </c>
       <c r="D2" s="1" t="s">
-        <v>105</v>
+        <v>109</v>
       </c>
       <c r="E2" s="1" t="s">
-        <v>106</v>
+        <v>110</v>
       </c>
       <c r="F2" s="1" t="s">
-        <v>11</v>
+        <v>13</v>
       </c>
     </row>
     <row r="3" spans="1:8" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A3" s="2" t="s">
-        <v>122</v>
+        <v>126</v>
       </c>
       <c r="B3" s="2">
         <v>92.88</v>
@@ -3524,13 +3536,13 @@
         <v>9.0999999999999943</v>
       </c>
       <c r="E3" s="2" t="s">
-        <v>108</v>
+        <v>112</v>
       </c>
       <c r="F3" s="2"/>
     </row>
     <row r="4" spans="1:8" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A4" s="4" t="s">
-        <v>123</v>
+        <v>127</v>
       </c>
       <c r="B4" s="4">
         <v>92.15</v>
@@ -3543,13 +3555,13 @@
         <v>7.8200000000000074</v>
       </c>
       <c r="E4" s="4" t="s">
-        <v>114</v>
+        <v>118</v>
       </c>
       <c r="F4" s="4"/>
     </row>
     <row r="5" spans="1:8" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A5" s="2" t="s">
-        <v>124</v>
+        <v>128</v>
       </c>
       <c r="B5" s="2">
         <v>90.96</v>
@@ -3562,15 +3574,15 @@
         <v>9.5899999999999892</v>
       </c>
       <c r="E5" s="2" t="s">
-        <v>108</v>
+        <v>112</v>
       </c>
       <c r="F5" s="2" t="s">
-        <v>125</v>
+        <v>129</v>
       </c>
     </row>
     <row r="6" spans="1:8" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A6" s="4" t="s">
-        <v>126</v>
+        <v>130</v>
       </c>
       <c r="B6" s="4">
         <v>95.89</v>
@@ -3583,13 +3595,13 @@
         <v>9.7900000000000063</v>
       </c>
       <c r="E6" s="4" t="s">
-        <v>108</v>
+        <v>112</v>
       </c>
       <c r="F6" s="4"/>
     </row>
     <row r="7" spans="1:8" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A7" s="2" t="s">
-        <v>127</v>
+        <v>131</v>
       </c>
       <c r="B7" s="2">
         <v>95.71</v>
@@ -3602,15 +3614,15 @@
         <v>4.6799999999999926</v>
       </c>
       <c r="E7" s="2" t="s">
-        <v>114</v>
+        <v>118</v>
       </c>
       <c r="F7" s="2" t="s">
-        <v>128</v>
+        <v>132</v>
       </c>
     </row>
     <row r="8" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A8" s="7" t="s">
-        <v>129</v>
+        <v>133</v>
       </c>
       <c r="B8" s="7"/>
       <c r="C8" s="7"/>

--- a/Dashboard_Data.xlsx
+++ b/Dashboard_Data.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29929"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30210"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://alfanargroup-my.sharepoint.com/personal/ahmed_abdelzaher_alfanar_com/Documents/SDCC Dashboard/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{08402470-AB39-479E-9F56-A762705072E3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="40" documentId="8_{08402470-AB39-479E-9F56-A762705072E3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{1D450DF2-80C7-4DE4-876E-55C772860178}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" tabRatio="500" firstSheet="4" activeTab="5" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" tabRatio="500" firstSheet="5" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Header" sheetId="1" r:id="rId1"/>
@@ -695,7 +695,7 @@
     <numFmt numFmtId="164" formatCode="[$-409]d\-mmm\-yy;@"/>
     <numFmt numFmtId="165" formatCode="0.0"/>
   </numFmts>
-  <fonts count="8" x14ac:knownFonts="1">
+  <fonts count="8">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -841,7 +841,7 @@
     <xf numFmtId="43" fontId="6" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="9" fontId="6" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="39">
+  <cellXfs count="41">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -945,6 +945,10 @@
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="43" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="43" fontId="3" fillId="5" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -1217,13 +1221,13 @@
     <tabColor rgb="FFE87722"/>
   </sheetPr>
   <dimension ref="A1:H6"/>
-  <sheetFormatPr defaultColWidth="8.7109375" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultColWidth="8.7109375" defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="30" customWidth="1"/>
     <col min="2" max="2" width="40" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:8" ht="21.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:8" ht="21.75" customHeight="1">
       <c r="A1" s="37" t="s">
         <v>0</v>
       </c>
@@ -1235,7 +1239,7 @@
       <c r="G1" s="37"/>
       <c r="H1" s="37"/>
     </row>
-    <row r="2" spans="1:8" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:8" ht="18" customHeight="1">
       <c r="A2" s="1" t="s">
         <v>1</v>
       </c>
@@ -1243,7 +1247,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="3" spans="1:8" ht="25.5" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:8" ht="25.5">
       <c r="A3" s="2" t="s">
         <v>3</v>
       </c>
@@ -1251,7 +1255,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="4" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:8">
       <c r="A4" s="4" t="s">
         <v>5</v>
       </c>
@@ -1259,7 +1263,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="5" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:8">
       <c r="A5" s="2" t="s">
         <v>7</v>
       </c>
@@ -1267,7 +1271,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="6" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:8">
       <c r="A6" s="4" t="s">
         <v>9</v>
       </c>
@@ -1293,7 +1297,7 @@
     <tabColor rgb="FFE87722"/>
   </sheetPr>
   <dimension ref="A1:H30"/>
-  <sheetFormatPr defaultColWidth="8.7109375" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultColWidth="8.7109375" defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="12" customWidth="1"/>
     <col min="2" max="2" width="14" customWidth="1"/>
@@ -1305,7 +1309,7 @@
     <col min="8" max="8" width="30" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:8" ht="21.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:8" ht="21.75" customHeight="1">
       <c r="A1" s="37" t="s">
         <v>134</v>
       </c>
@@ -1317,7 +1321,7 @@
       <c r="G1" s="37"/>
       <c r="H1" s="37"/>
     </row>
-    <row r="2" spans="1:8" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:8" ht="18" customHeight="1">
       <c r="A2" s="1" t="s">
         <v>135</v>
       </c>
@@ -1343,7 +1347,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="3" spans="1:8" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:8" ht="15.75" customHeight="1">
       <c r="A3" s="32">
         <v>45620</v>
       </c>
@@ -1365,7 +1369,7 @@
         <v>146</v>
       </c>
     </row>
-    <row r="4" spans="1:8" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:8" ht="15.75" customHeight="1">
       <c r="A4" s="33">
         <v>45650</v>
       </c>
@@ -1381,7 +1385,7 @@
       <c r="G4" s="4"/>
       <c r="H4" s="4"/>
     </row>
-    <row r="5" spans="1:8" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:8" ht="15.75" customHeight="1">
       <c r="A5" s="32">
         <v>45681</v>
       </c>
@@ -1397,7 +1401,7 @@
       <c r="G5" s="2"/>
       <c r="H5" s="2"/>
     </row>
-    <row r="6" spans="1:8" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:8" ht="15.75" customHeight="1">
       <c r="A6" s="33">
         <v>45712</v>
       </c>
@@ -1413,7 +1417,7 @@
       <c r="G6" s="4"/>
       <c r="H6" s="4"/>
     </row>
-    <row r="7" spans="1:8" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:8" ht="15.75" customHeight="1">
       <c r="A7" s="32">
         <v>45740</v>
       </c>
@@ -1433,7 +1437,7 @@
       <c r="G7" s="2"/>
       <c r="H7" s="2"/>
     </row>
-    <row r="8" spans="1:8" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:8" ht="15.75" customHeight="1">
       <c r="A8" s="33">
         <v>45771</v>
       </c>
@@ -1455,7 +1459,7 @@
         <v>150</v>
       </c>
     </row>
-    <row r="9" spans="1:8" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:8" ht="15.75" customHeight="1">
       <c r="A9" s="32">
         <v>45801</v>
       </c>
@@ -1471,7 +1475,7 @@
       <c r="G9" s="2"/>
       <c r="H9" s="2"/>
     </row>
-    <row r="10" spans="1:8" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:8" ht="15.75" customHeight="1">
       <c r="A10" s="33">
         <v>45832</v>
       </c>
@@ -1491,7 +1495,7 @@
       <c r="G10" s="4"/>
       <c r="H10" s="4"/>
     </row>
-    <row r="11" spans="1:8" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:8" ht="15.75" customHeight="1">
       <c r="A11" s="32">
         <v>45862</v>
       </c>
@@ -1507,7 +1511,7 @@
       <c r="G11" s="2"/>
       <c r="H11" s="2"/>
     </row>
-    <row r="12" spans="1:8" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:8" ht="15.75" customHeight="1">
       <c r="A12" s="33">
         <v>45893</v>
       </c>
@@ -1523,7 +1527,7 @@
       <c r="G12" s="4"/>
       <c r="H12" s="4"/>
     </row>
-    <row r="13" spans="1:8" ht="25.5" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:8" ht="25.5">
       <c r="A13" s="32">
         <v>45924</v>
       </c>
@@ -1543,7 +1547,7 @@
       <c r="G13" s="2"/>
       <c r="H13" s="2"/>
     </row>
-    <row r="14" spans="1:8" ht="25.5" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:8" ht="25.5">
       <c r="A14" s="33">
         <v>45954</v>
       </c>
@@ -1563,7 +1567,7 @@
       <c r="G14" s="4"/>
       <c r="H14" s="4"/>
     </row>
-    <row r="15" spans="1:8" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:8" ht="15.75" customHeight="1">
       <c r="A15" s="32">
         <v>45985</v>
       </c>
@@ -1579,7 +1583,7 @@
       <c r="G15" s="2"/>
       <c r="H15" s="2"/>
     </row>
-    <row r="16" spans="1:8" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:8" ht="15.75" customHeight="1">
       <c r="A16" s="33">
         <v>46015</v>
       </c>
@@ -1599,7 +1603,7 @@
       <c r="G16" s="4"/>
       <c r="H16" s="4"/>
     </row>
-    <row r="17" spans="1:8" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:8" ht="15.75" customHeight="1">
       <c r="A17" s="32">
         <v>46046</v>
       </c>
@@ -1615,7 +1619,7 @@
       <c r="G17" s="2"/>
       <c r="H17" s="2"/>
     </row>
-    <row r="18" spans="1:8" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:8" ht="15.75" customHeight="1">
       <c r="A18" s="33">
         <v>46077</v>
       </c>
@@ -1631,7 +1635,7 @@
       <c r="G18" s="4"/>
       <c r="H18" s="4"/>
     </row>
-    <row r="19" spans="1:8" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:8" ht="15.75" customHeight="1">
       <c r="A19" s="32">
         <v>46105</v>
       </c>
@@ -1647,7 +1651,7 @@
       <c r="G19" s="2"/>
       <c r="H19" s="2"/>
     </row>
-    <row r="20" spans="1:8" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:8" ht="15.75" customHeight="1">
       <c r="A20" s="33">
         <v>46136</v>
       </c>
@@ -1663,7 +1667,7 @@
       <c r="G20" s="2"/>
       <c r="H20" s="2"/>
     </row>
-    <row r="21" spans="1:8" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:8" ht="15.75" customHeight="1">
       <c r="A21" s="32">
         <v>46166</v>
       </c>
@@ -1679,7 +1683,7 @@
       <c r="G21" s="2"/>
       <c r="H21" s="2"/>
     </row>
-    <row r="22" spans="1:8" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:8" ht="15.75" customHeight="1">
       <c r="A22" s="33">
         <v>46197</v>
       </c>
@@ -1695,7 +1699,7 @@
       <c r="G22" s="2"/>
       <c r="H22" s="2"/>
     </row>
-    <row r="23" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:8">
       <c r="A23" s="32">
         <v>46227</v>
       </c>
@@ -1717,7 +1721,7 @@
         <v>156</v>
       </c>
     </row>
-    <row r="24" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:8">
       <c r="A24" s="33">
         <v>46258</v>
       </c>
@@ -1733,7 +1737,7 @@
       <c r="G24" s="2"/>
       <c r="H24" s="2"/>
     </row>
-    <row r="25" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="25" spans="1:8">
       <c r="A25" s="32">
         <v>46289</v>
       </c>
@@ -1749,7 +1753,7 @@
       <c r="G25" s="2"/>
       <c r="H25" s="2"/>
     </row>
-    <row r="26" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="26" spans="1:8">
       <c r="A26" s="33">
         <v>46319</v>
       </c>
@@ -1765,7 +1769,7 @@
       <c r="G26" s="2"/>
       <c r="H26" s="2"/>
     </row>
-    <row r="27" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="27" spans="1:8">
       <c r="A27" s="32">
         <v>46350</v>
       </c>
@@ -1776,7 +1780,7 @@
         <v>145</v>
       </c>
     </row>
-    <row r="28" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="28" spans="1:8">
       <c r="A28" s="33">
         <v>46380</v>
       </c>
@@ -1787,7 +1791,7 @@
         <v>145</v>
       </c>
     </row>
-    <row r="29" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="29" spans="1:8">
       <c r="A29" s="32">
         <v>46411</v>
       </c>
@@ -1798,7 +1802,7 @@
         <v>145</v>
       </c>
     </row>
-    <row r="30" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="30" spans="1:8">
       <c r="A30" s="33">
         <v>46442</v>
       </c>
@@ -1838,7 +1842,7 @@
     <tabColor rgb="FFE87722"/>
   </sheetPr>
   <dimension ref="A1:H6"/>
-  <sheetFormatPr defaultColWidth="8.7109375" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultColWidth="8.7109375" defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="4" customWidth="1"/>
     <col min="2" max="2" width="38" customWidth="1"/>
@@ -1848,7 +1852,7 @@
     <col min="6" max="6" width="10" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:8" ht="21.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:8" ht="21.75" customHeight="1">
       <c r="A1" s="37" t="s">
         <v>159</v>
       </c>
@@ -1860,7 +1864,7 @@
       <c r="G1" s="37"/>
       <c r="H1" s="37"/>
     </row>
-    <row r="2" spans="1:8" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:8" ht="18" customHeight="1">
       <c r="A2" s="1" t="s">
         <v>160</v>
       </c>
@@ -1880,7 +1884,7 @@
         <v>165</v>
       </c>
     </row>
-    <row r="3" spans="1:8" ht="38.25" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:8" ht="38.25">
       <c r="A3" s="2">
         <v>1</v>
       </c>
@@ -1900,7 +1904,7 @@
         <v>170</v>
       </c>
     </row>
-    <row r="4" spans="1:8" ht="25.5" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:8" ht="25.5">
       <c r="A4" s="4">
         <v>2</v>
       </c>
@@ -1920,7 +1924,7 @@
         <v>170</v>
       </c>
     </row>
-    <row r="5" spans="1:8" ht="38.25" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:8" ht="38.25">
       <c r="A5" s="2">
         <v>3</v>
       </c>
@@ -1940,7 +1944,7 @@
         <v>170</v>
       </c>
     </row>
-    <row r="6" spans="1:8" ht="38.25" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:8" ht="38.25">
       <c r="A6" s="2">
         <v>4</v>
       </c>
@@ -1978,7 +1982,7 @@
     <tabColor rgb="FFE87722"/>
   </sheetPr>
   <dimension ref="A1:U25"/>
-  <sheetFormatPr defaultColWidth="8.7109375" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultColWidth="8.7109375" defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="4" customWidth="1"/>
     <col min="2" max="2" width="26" customWidth="1"/>
@@ -1987,7 +1991,7 @@
     <col min="8" max="8" width="12" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:21" ht="21.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:21" ht="21.75" customHeight="1">
       <c r="A1" s="37" t="s">
         <v>179</v>
       </c>
@@ -1999,7 +2003,7 @@
       <c r="G1" s="37"/>
       <c r="H1" s="37"/>
     </row>
-    <row r="2" spans="1:21" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:21" ht="18" customHeight="1">
       <c r="A2" s="1" t="s">
         <v>160</v>
       </c>
@@ -2025,7 +2029,7 @@
         <v>185</v>
       </c>
     </row>
-    <row r="3" spans="1:21" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:21" ht="15.75" customHeight="1">
       <c r="A3" s="2">
         <v>1</v>
       </c>
@@ -2051,7 +2055,7 @@
         <v>189</v>
       </c>
     </row>
-    <row r="4" spans="1:21" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:21" ht="15.75" customHeight="1">
       <c r="A4" s="4">
         <v>2</v>
       </c>
@@ -2077,7 +2081,7 @@
         <v>189</v>
       </c>
     </row>
-    <row r="5" spans="1:21" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:21" ht="15.75" customHeight="1">
       <c r="A5" s="2">
         <v>3</v>
       </c>
@@ -2103,7 +2107,7 @@
         <v>189</v>
       </c>
     </row>
-    <row r="6" spans="1:21" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:21" ht="15.75" customHeight="1">
       <c r="A6" s="4">
         <v>4</v>
       </c>
@@ -2129,7 +2133,7 @@
         <v>189</v>
       </c>
     </row>
-    <row r="7" spans="1:21" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:21" ht="15.75" customHeight="1">
       <c r="A7" s="2">
         <v>5</v>
       </c>
@@ -2155,7 +2159,7 @@
         <v>197</v>
       </c>
     </row>
-    <row r="8" spans="1:21" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:21" ht="15.75" customHeight="1">
       <c r="A8" s="4">
         <v>6</v>
       </c>
@@ -2181,7 +2185,7 @@
         <v>197</v>
       </c>
     </row>
-    <row r="9" spans="1:21" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:21" ht="15.75" customHeight="1">
       <c r="A9" s="2">
         <v>7</v>
       </c>
@@ -2207,7 +2211,7 @@
         <v>197</v>
       </c>
     </row>
-    <row r="10" spans="1:21" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:21" ht="15.75" customHeight="1">
       <c r="A10" s="4">
         <v>8</v>
       </c>
@@ -2233,63 +2237,63 @@
         <v>197</v>
       </c>
     </row>
-    <row r="11" spans="1:21" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:21">
       <c r="S11" s="31"/>
       <c r="T11" s="31"/>
       <c r="U11" s="31"/>
     </row>
-    <row r="12" spans="1:21" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:21">
       <c r="S12" s="31"/>
       <c r="T12" s="31"/>
       <c r="U12" s="31"/>
     </row>
-    <row r="13" spans="1:21" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:21">
       <c r="S13" s="31"/>
       <c r="T13" s="31"/>
       <c r="U13" s="31"/>
     </row>
-    <row r="14" spans="1:21" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:21">
       <c r="S14" s="31"/>
       <c r="T14" s="31"/>
       <c r="U14" s="31"/>
     </row>
-    <row r="15" spans="1:21" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:21">
       <c r="S15" s="31"/>
       <c r="T15" s="31"/>
       <c r="U15" s="31"/>
     </row>
-    <row r="16" spans="1:21" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:21">
       <c r="S16" s="31"/>
       <c r="T16" s="31"/>
       <c r="U16" s="31"/>
     </row>
-    <row r="17" spans="19:21" x14ac:dyDescent="0.25">
+    <row r="17" spans="19:21">
       <c r="T17" s="31"/>
       <c r="U17" s="31"/>
     </row>
-    <row r="18" spans="19:21" x14ac:dyDescent="0.25">
+    <row r="18" spans="19:21">
       <c r="S18" s="31"/>
       <c r="U18" s="31"/>
     </row>
-    <row r="19" spans="19:21" x14ac:dyDescent="0.25">
+    <row r="19" spans="19:21">
       <c r="S19" s="30"/>
     </row>
-    <row r="20" spans="19:21" x14ac:dyDescent="0.25">
+    <row r="20" spans="19:21">
       <c r="S20" s="30"/>
     </row>
-    <row r="21" spans="19:21" x14ac:dyDescent="0.25">
+    <row r="21" spans="19:21">
       <c r="S21" s="30"/>
     </row>
-    <row r="22" spans="19:21" x14ac:dyDescent="0.25">
+    <row r="22" spans="19:21">
       <c r="S22" s="30"/>
     </row>
-    <row r="23" spans="19:21" x14ac:dyDescent="0.25">
+    <row r="23" spans="19:21">
       <c r="S23" s="30"/>
     </row>
-    <row r="24" spans="19:21" x14ac:dyDescent="0.25">
+    <row r="24" spans="19:21">
       <c r="S24" s="30"/>
     </row>
-    <row r="25" spans="19:21" x14ac:dyDescent="0.25">
+    <row r="25" spans="19:21">
       <c r="S25" s="30"/>
     </row>
   </sheetData>
@@ -2310,13 +2314,13 @@
     <tabColor rgb="FFE87722"/>
   </sheetPr>
   <dimension ref="A1:H6"/>
-  <sheetFormatPr defaultColWidth="8.7109375" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultColWidth="8.7109375" defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="30" customWidth="1"/>
     <col min="2" max="2" width="50" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:8" ht="21.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:8" ht="21.75" customHeight="1">
       <c r="A1" s="37" t="s">
         <v>203</v>
       </c>
@@ -2328,7 +2332,7 @@
       <c r="G1" s="37"/>
       <c r="H1" s="37"/>
     </row>
-    <row r="2" spans="1:8" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:8" ht="18" customHeight="1">
       <c r="A2" s="1" t="s">
         <v>1</v>
       </c>
@@ -2336,7 +2340,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="3" spans="1:8" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:8" ht="15.75" customHeight="1">
       <c r="A3" s="2" t="s">
         <v>204</v>
       </c>
@@ -2344,7 +2348,7 @@
         <v>205</v>
       </c>
     </row>
-    <row r="4" spans="1:8" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:8" ht="15.75" customHeight="1">
       <c r="A4" s="4" t="s">
         <v>206</v>
       </c>
@@ -2352,7 +2356,7 @@
         <v>46176</v>
       </c>
     </row>
-    <row r="5" spans="1:8" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:8" ht="15.75" customHeight="1">
       <c r="A5" s="2" t="s">
         <v>207</v>
       </c>
@@ -2360,7 +2364,7 @@
         <v>208</v>
       </c>
     </row>
-    <row r="6" spans="1:8" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:8" ht="15.75" customHeight="1">
       <c r="A6" s="4" t="s">
         <v>209</v>
       </c>
@@ -2386,14 +2390,14 @@
     <tabColor rgb="FFE87722"/>
   </sheetPr>
   <dimension ref="A1:H9"/>
-  <sheetFormatPr defaultColWidth="8.7109375" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultColWidth="8.7109375" defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="32" customWidth="1"/>
     <col min="2" max="2" width="18" customWidth="1"/>
     <col min="3" max="3" width="40" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:8" ht="21.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:8" ht="21.75" customHeight="1">
       <c r="A1" s="37" t="s">
         <v>11</v>
       </c>
@@ -2405,7 +2409,7 @@
       <c r="G1" s="37"/>
       <c r="H1" s="37"/>
     </row>
-    <row r="2" spans="1:8" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:8" ht="18" customHeight="1">
       <c r="A2" s="1" t="s">
         <v>1</v>
       </c>
@@ -2416,7 +2420,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="3" spans="1:8" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:8" ht="15.75" customHeight="1">
       <c r="A3" s="2" t="s">
         <v>14</v>
       </c>
@@ -2425,7 +2429,7 @@
       </c>
       <c r="C3" s="2"/>
     </row>
-    <row r="4" spans="1:8" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:8" ht="15.75" customHeight="1">
       <c r="A4" s="4" t="s">
         <v>15</v>
       </c>
@@ -2434,7 +2438,7 @@
       </c>
       <c r="C4" s="4"/>
     </row>
-    <row r="5" spans="1:8" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:8" ht="15.75" customHeight="1">
       <c r="A5" s="2" t="s">
         <v>16</v>
       </c>
@@ -2443,7 +2447,7 @@
       </c>
       <c r="C5" s="2"/>
     </row>
-    <row r="6" spans="1:8" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:8" ht="15.75" customHeight="1">
       <c r="A6" s="4" t="s">
         <v>17</v>
       </c>
@@ -2452,7 +2456,7 @@
       </c>
       <c r="C6" s="4"/>
     </row>
-    <row r="7" spans="1:8" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:8" ht="15.75" customHeight="1">
       <c r="A7" s="2" t="s">
         <v>18</v>
       </c>
@@ -2461,7 +2465,7 @@
       </c>
       <c r="C7" s="2"/>
     </row>
-    <row r="8" spans="1:8" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:8" ht="15.75" customHeight="1">
       <c r="A8" s="4" t="s">
         <v>19</v>
       </c>
@@ -2472,7 +2476,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="9" spans="1:8" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:8" ht="15.75" customHeight="1">
       <c r="A9" s="2" t="s">
         <v>21</v>
       </c>
@@ -2502,7 +2506,7 @@
     <tabColor rgb="FFE87722"/>
   </sheetPr>
   <dimension ref="A1:H9"/>
-  <sheetFormatPr defaultColWidth="8.7109375" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultColWidth="8.7109375" defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="32" customWidth="1"/>
     <col min="2" max="2" width="22" customWidth="1"/>
@@ -2510,7 +2514,7 @@
     <col min="4" max="4" width="40" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:8" ht="21.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:8" ht="21.75" customHeight="1">
       <c r="A1" s="37" t="s">
         <v>23</v>
       </c>
@@ -2522,7 +2526,7 @@
       <c r="G1" s="37"/>
       <c r="H1" s="37"/>
     </row>
-    <row r="2" spans="1:8" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:8" ht="18" customHeight="1">
       <c r="A2" s="1" t="s">
         <v>1</v>
       </c>
@@ -2536,7 +2540,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="3" spans="1:8" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:8" ht="15.75" customHeight="1">
       <c r="A3" s="2" t="s">
         <v>26</v>
       </c>
@@ -2546,7 +2550,7 @@
       <c r="C3" s="2"/>
       <c r="D3" s="2"/>
     </row>
-    <row r="4" spans="1:8" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:8" ht="15.75" customHeight="1">
       <c r="A4" s="4" t="s">
         <v>27</v>
       </c>
@@ -2556,7 +2560,7 @@
       <c r="C4" s="4"/>
       <c r="D4" s="4"/>
     </row>
-    <row r="5" spans="1:8" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:8" ht="15.75" customHeight="1">
       <c r="A5" s="2" t="s">
         <v>28</v>
       </c>
@@ -2566,7 +2570,7 @@
       <c r="C5" s="2"/>
       <c r="D5" s="2"/>
     </row>
-    <row r="6" spans="1:8" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:8" ht="15.75" customHeight="1">
       <c r="A6" s="4" t="s">
         <v>29</v>
       </c>
@@ -2576,7 +2580,7 @@
       <c r="C6" s="4"/>
       <c r="D6" s="4"/>
     </row>
-    <row r="7" spans="1:8" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:8" ht="15.75" customHeight="1">
       <c r="A7" s="2" t="s">
         <v>30</v>
       </c>
@@ -2588,7 +2592,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="8" spans="1:8" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:8" ht="15.75" customHeight="1">
       <c r="A8" s="4" t="s">
         <v>32</v>
       </c>
@@ -2598,7 +2602,7 @@
       <c r="C8" s="4"/>
       <c r="D8" s="4"/>
     </row>
-    <row r="9" spans="1:8" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:8" ht="15.75" customHeight="1">
       <c r="A9" s="2" t="s">
         <v>33</v>
       </c>
@@ -2631,7 +2635,7 @@
     <tabColor rgb="FFE87722"/>
   </sheetPr>
   <dimension ref="A1:H10"/>
-  <sheetFormatPr defaultColWidth="8.7109375" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultColWidth="8.7109375" defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="32" customWidth="1"/>
     <col min="2" max="2" width="22" customWidth="1"/>
@@ -2639,7 +2643,7 @@
     <col min="4" max="4" width="40" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:8" ht="21.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:8" ht="21.75" customHeight="1">
       <c r="A1" s="37" t="s">
         <v>35</v>
       </c>
@@ -2651,7 +2655,7 @@
       <c r="G1" s="37"/>
       <c r="H1" s="37"/>
     </row>
-    <row r="2" spans="1:8" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:8" ht="18" customHeight="1">
       <c r="A2" s="1" t="s">
         <v>1</v>
       </c>
@@ -2665,7 +2669,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="3" spans="1:8" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:8" ht="15.75" customHeight="1">
       <c r="A3" s="2" t="s">
         <v>36</v>
       </c>
@@ -2677,7 +2681,7 @@
         <v>37</v>
       </c>
     </row>
-    <row r="4" spans="1:8" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:8" ht="15.75" customHeight="1">
       <c r="A4" s="4" t="s">
         <v>38</v>
       </c>
@@ -2689,29 +2693,29 @@
         <v>40</v>
       </c>
     </row>
-    <row r="5" spans="1:8" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:8" ht="15.75" customHeight="1">
       <c r="A5" s="4" t="s">
         <v>41</v>
       </c>
       <c r="B5" s="19">
-        <v>0.75600000000000001</v>
+        <v>0.78249999999999997</v>
       </c>
       <c r="C5" s="21"/>
       <c r="D5" s="4"/>
     </row>
-    <row r="6" spans="1:8" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:8" ht="15.75" customHeight="1">
       <c r="A6" s="2" t="s">
         <v>42</v>
       </c>
       <c r="B6" s="19">
-        <v>0.45900000000000002</v>
+        <v>0.46589999999999998</v>
       </c>
       <c r="C6" s="22"/>
       <c r="D6" s="2" t="s">
         <v>43</v>
       </c>
     </row>
-    <row r="7" spans="1:8" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:8" ht="15.75" customHeight="1">
       <c r="A7" s="4" t="s">
         <v>32</v>
       </c>
@@ -2723,7 +2727,7 @@
         <v>37</v>
       </c>
     </row>
-    <row r="8" spans="1:8" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:8" ht="15.75" customHeight="1">
       <c r="A8" s="2" t="s">
         <v>33</v>
       </c>
@@ -2735,7 +2739,7 @@
         <v>37</v>
       </c>
     </row>
-    <row r="9" spans="1:8" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:8" ht="15.75" customHeight="1">
       <c r="A9" s="4" t="s">
         <v>44</v>
       </c>
@@ -2748,7 +2752,7 @@
         <v>45</v>
       </c>
     </row>
-    <row r="10" spans="1:8" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:8" ht="15.75" customHeight="1">
       <c r="A10" s="2" t="s">
         <v>46</v>
       </c>
@@ -2778,7 +2782,7 @@
     <tabColor rgb="FFE87722"/>
   </sheetPr>
   <dimension ref="A1:H16"/>
-  <sheetFormatPr defaultColWidth="8.7109375" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultColWidth="8.7109375" defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="32" customWidth="1"/>
     <col min="2" max="2" width="22" customWidth="1"/>
@@ -2787,7 +2791,7 @@
     <col min="5" max="5" width="35" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:8" ht="21.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:8" ht="21.75" customHeight="1">
       <c r="A1" s="37" t="s">
         <v>49</v>
       </c>
@@ -2799,7 +2803,7 @@
       <c r="G1" s="37"/>
       <c r="H1" s="37"/>
     </row>
-    <row r="2" spans="1:8" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:8" ht="18" customHeight="1">
       <c r="A2" s="1" t="s">
         <v>1</v>
       </c>
@@ -2816,7 +2820,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="3" spans="1:8" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:8" ht="15.75" customHeight="1">
       <c r="A3" s="2" t="s">
         <v>52</v>
       </c>
@@ -2833,7 +2837,7 @@
       <c r="E3" s="2"/>
       <c r="G3" s="24"/>
     </row>
-    <row r="4" spans="1:8" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:8" ht="15.75" customHeight="1">
       <c r="A4" s="4" t="s">
         <v>54</v>
       </c>
@@ -2849,7 +2853,7 @@
       </c>
       <c r="E4" s="4"/>
     </row>
-    <row r="5" spans="1:8" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:8" ht="15.75" customHeight="1">
       <c r="A5" s="2" t="s">
         <v>56</v>
       </c>
@@ -2865,7 +2869,7 @@
       </c>
       <c r="E5" s="2"/>
     </row>
-    <row r="6" spans="1:8" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:8" ht="15.75" customHeight="1">
       <c r="A6" s="4" t="s">
         <v>57</v>
       </c>
@@ -2878,29 +2882,29 @@
       </c>
       <c r="E6" s="4"/>
     </row>
-    <row r="7" spans="1:8" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:8" ht="15.75" customHeight="1">
       <c r="A7" s="2" t="s">
         <v>59</v>
       </c>
       <c r="B7" s="14">
-        <v>68039022</v>
+        <v>152961744</v>
       </c>
       <c r="C7" s="13">
         <f>B7/Commercial_Info!$B$3</f>
-        <v>0.17535085352017749</v>
+        <v>0.39421454891481078</v>
       </c>
       <c r="D7" s="2" t="s">
         <v>55</v>
       </c>
       <c r="E7" s="2"/>
     </row>
-    <row r="8" spans="1:8" ht="28.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:8" ht="28.5" customHeight="1">
       <c r="A8" s="4" t="s">
         <v>60</v>
       </c>
       <c r="B8" s="26" t="str">
         <f>ROUNDUP(C4*100,0)&amp;"%"&amp;" / "&amp;ROUNDUP(Budgetary_Info!B6*100,0)&amp;"%"</f>
-        <v>53% / 46%</v>
+        <v>53% / 47%</v>
       </c>
       <c r="C8" s="4"/>
       <c r="D8" s="4" t="s">
@@ -2910,13 +2914,16 @@
         <v>61</v>
       </c>
     </row>
-    <row r="14" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:8">
+      <c r="B10" s="39"/>
+    </row>
+    <row r="14" spans="1:8">
       <c r="E14" s="36"/>
     </row>
-    <row r="15" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:8">
       <c r="E15" s="36"/>
     </row>
-    <row r="16" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:8">
       <c r="E16" s="36"/>
     </row>
   </sheetData>
@@ -2936,8 +2943,8 @@
   <sheetPr>
     <tabColor rgb="FFE87722"/>
   </sheetPr>
-  <dimension ref="A1:H6"/>
-  <sheetFormatPr defaultColWidth="8.7109375" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <dimension ref="A1:H9"/>
+  <sheetFormatPr defaultColWidth="8.7109375" defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="30" customWidth="1"/>
     <col min="2" max="2" width="20" customWidth="1"/>
@@ -2945,7 +2952,7 @@
     <col min="4" max="4" width="40" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:8" ht="21.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:8" ht="21.75" customHeight="1">
       <c r="A1" s="37" t="s">
         <v>62</v>
       </c>
@@ -2957,7 +2964,7 @@
       <c r="G1" s="37"/>
       <c r="H1" s="37"/>
     </row>
-    <row r="2" spans="1:8" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:8" ht="18" customHeight="1">
       <c r="A2" s="1" t="s">
         <v>1</v>
       </c>
@@ -2971,19 +2978,19 @@
         <v>13</v>
       </c>
     </row>
-    <row r="3" spans="1:8" ht="27" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:8" ht="27" customHeight="1">
       <c r="A3" s="2" t="s">
         <v>65</v>
       </c>
-      <c r="B3" s="3">
-        <v>-70.3</v>
+      <c r="B3" s="40">
+        <v>14.58</v>
       </c>
       <c r="C3" s="2"/>
       <c r="D3" s="2" t="s">
         <v>66</v>
       </c>
     </row>
-    <row r="4" spans="1:8" ht="46.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:8" ht="46.5" customHeight="1">
       <c r="A4" s="4" t="s">
         <v>67</v>
       </c>
@@ -2995,22 +3002,22 @@
         <v>69</v>
       </c>
     </row>
-    <row r="5" spans="1:8" ht="27" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:8" ht="27" customHeight="1">
       <c r="A5" s="2" t="s">
         <v>70</v>
       </c>
       <c r="B5" s="3">
-        <v>68</v>
+        <v>152.6</v>
       </c>
       <c r="C5" s="35">
         <f>(B5/B6)*100</f>
-        <v>49.132947976878611</v>
+        <v>110.26011560693641</v>
       </c>
       <c r="D5" s="2" t="s">
         <v>71</v>
       </c>
     </row>
-    <row r="6" spans="1:8" ht="27" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:8" ht="27" customHeight="1">
       <c r="A6" s="4" t="s">
         <v>72</v>
       </c>
@@ -3023,6 +3030,9 @@
       <c r="D6" s="4" t="s">
         <v>73</v>
       </c>
+    </row>
+    <row r="9" spans="1:8">
+      <c r="B9" s="39"/>
     </row>
   </sheetData>
   <mergeCells count="1">
@@ -3042,7 +3052,7 @@
     <tabColor rgb="FFE87722"/>
   </sheetPr>
   <dimension ref="A1:H21"/>
-  <sheetFormatPr defaultColWidth="8.7109375" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultColWidth="8.7109375" defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="28" customWidth="1"/>
     <col min="2" max="2" width="16" customWidth="1"/>
@@ -3050,7 +3060,7 @@
     <col min="4" max="4" width="10" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:8" ht="21.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:8" ht="21.75" customHeight="1">
       <c r="A1" s="37" t="s">
         <v>74</v>
       </c>
@@ -3062,7 +3072,7 @@
       <c r="G1" s="37"/>
       <c r="H1" s="37"/>
     </row>
-    <row r="2" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:8" ht="15" customHeight="1">
       <c r="A2" s="38" t="s">
         <v>75</v>
       </c>
@@ -3070,7 +3080,7 @@
       <c r="C2" s="38"/>
       <c r="D2" s="38"/>
     </row>
-    <row r="3" spans="1:8" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:8" ht="18" customHeight="1">
       <c r="A3" s="1" t="s">
         <v>1</v>
       </c>
@@ -3082,58 +3092,58 @@
       </c>
       <c r="D3" s="1"/>
     </row>
-    <row r="4" spans="1:8" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:8" ht="15.75" customHeight="1">
       <c r="A4" s="4" t="s">
         <v>76</v>
       </c>
       <c r="B4" s="3">
         <f>B5+B6</f>
-        <v>751</v>
+        <v>712</v>
       </c>
       <c r="C4" s="4" t="s">
         <v>77</v>
       </c>
       <c r="D4" s="4"/>
     </row>
-    <row r="5" spans="1:8" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:8" ht="15.75" customHeight="1">
       <c r="A5" s="2" t="s">
         <v>78</v>
       </c>
       <c r="B5" s="3">
-        <v>654</v>
+        <v>599</v>
       </c>
       <c r="C5" s="2" t="s">
         <v>79</v>
       </c>
       <c r="D5" s="2"/>
     </row>
-    <row r="6" spans="1:8" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:8" ht="15.75" customHeight="1">
       <c r="A6" s="4" t="s">
         <v>80</v>
       </c>
       <c r="B6" s="3">
-        <v>97</v>
+        <v>113</v>
       </c>
       <c r="C6" s="4" t="s">
         <v>81</v>
       </c>
       <c r="D6" s="4"/>
     </row>
-    <row r="7" spans="1:8" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:8" ht="15.75" customHeight="1">
       <c r="A7" s="2" t="s">
         <v>82</v>
       </c>
       <c r="B7" s="25">
         <f>B5/B4</f>
-        <v>0.87083888149134492</v>
+        <v>0.8412921348314607</v>
       </c>
       <c r="C7" s="2" t="s">
         <v>83</v>
       </c>
       <c r="D7" s="2"/>
     </row>
-    <row r="8" spans="1:8" ht="6" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="9" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:8" ht="6" customHeight="1"/>
+    <row r="9" spans="1:8" ht="15" customHeight="1">
       <c r="A9" s="38" t="s">
         <v>84</v>
       </c>
@@ -3141,7 +3151,7 @@
       <c r="C9" s="38"/>
       <c r="D9" s="38"/>
     </row>
-    <row r="10" spans="1:8" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:8" ht="18" customHeight="1">
       <c r="A10" s="1" t="s">
         <v>85</v>
       </c>
@@ -3153,32 +3163,32 @@
       </c>
       <c r="D10" s="1"/>
     </row>
-    <row r="11" spans="1:8" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:8" ht="15.75" customHeight="1">
       <c r="A11" s="2" t="s">
         <v>87</v>
       </c>
       <c r="B11" s="3">
-        <v>386</v>
+        <v>388</v>
       </c>
       <c r="C11" s="2" t="s">
         <v>88</v>
       </c>
       <c r="D11" s="2"/>
     </row>
-    <row r="12" spans="1:8" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:8" ht="15.75" customHeight="1">
       <c r="A12" s="4" t="s">
         <v>89</v>
       </c>
       <c r="B12" s="3">
-        <v>268</v>
+        <v>211</v>
       </c>
       <c r="C12" s="4" t="s">
         <v>88</v>
       </c>
       <c r="D12" s="4"/>
     </row>
-    <row r="13" spans="1:8" ht="6" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="14" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:8" ht="6" customHeight="1"/>
+    <row r="14" spans="1:8" ht="15" customHeight="1">
       <c r="A14" s="38" t="s">
         <v>90</v>
       </c>
@@ -3186,7 +3196,7 @@
       <c r="C14" s="38"/>
       <c r="D14" s="38"/>
     </row>
-    <row r="15" spans="1:8" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:8" ht="18" customHeight="1">
       <c r="A15" s="1" t="s">
         <v>91</v>
       </c>
@@ -3198,78 +3208,78 @@
       </c>
       <c r="D15" s="1"/>
     </row>
-    <row r="16" spans="1:8" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:8" ht="15.75" customHeight="1">
       <c r="A16" s="4" t="s">
         <v>93</v>
       </c>
       <c r="B16" s="3">
         <f>B4/B5*100</f>
-        <v>114.83180428134557</v>
+        <v>118.86477462437395</v>
       </c>
       <c r="C16" s="4" t="s">
         <v>94</v>
       </c>
       <c r="D16" s="4"/>
     </row>
-    <row r="17" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:4" ht="15.75" customHeight="1">
       <c r="A17" s="2" t="s">
         <v>95</v>
       </c>
       <c r="B17" s="3">
         <f>B6/B5*100</f>
-        <v>14.831804281345565</v>
+        <v>18.864774624373958</v>
       </c>
       <c r="C17" s="2" t="s">
         <v>96</v>
       </c>
       <c r="D17" s="2"/>
     </row>
-    <row r="18" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:4" ht="15.75" customHeight="1">
       <c r="A18" s="4" t="s">
         <v>97</v>
       </c>
       <c r="B18" s="3">
         <f>B16</f>
-        <v>114.83180428134557</v>
+        <v>118.86477462437395</v>
       </c>
       <c r="C18" s="4" t="s">
         <v>98</v>
       </c>
       <c r="D18" s="4"/>
     </row>
-    <row r="19" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:4" ht="15.75" customHeight="1">
       <c r="A19" s="2" t="s">
         <v>99</v>
       </c>
       <c r="B19" s="3">
         <f>100-B16</f>
-        <v>-14.831804281345569</v>
+        <v>-18.86477462437395</v>
       </c>
       <c r="C19" s="2" t="s">
         <v>100</v>
       </c>
       <c r="D19" s="2"/>
     </row>
-    <row r="20" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:4" ht="15.75" customHeight="1">
       <c r="A20" s="4" t="s">
         <v>101</v>
       </c>
       <c r="B20" s="3">
         <f>B17</f>
-        <v>14.831804281345565</v>
+        <v>18.864774624373958</v>
       </c>
       <c r="C20" s="4" t="s">
         <v>102</v>
       </c>
       <c r="D20" s="4"/>
     </row>
-    <row r="21" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:4" ht="15.75" customHeight="1">
       <c r="A21" s="2" t="s">
         <v>103</v>
       </c>
       <c r="B21" s="3">
         <f>100-B17</f>
-        <v>85.168195718654431</v>
+        <v>81.13522537562605</v>
       </c>
       <c r="C21" s="2" t="s">
         <v>104</v>
@@ -3297,7 +3307,7 @@
     <tabColor rgb="FFE87722"/>
   </sheetPr>
   <dimension ref="A1:H8"/>
-  <sheetFormatPr defaultColWidth="8.7109375" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultColWidth="8.7109375" defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="28" customWidth="1"/>
     <col min="2" max="4" width="10" customWidth="1"/>
@@ -3305,7 +3315,7 @@
     <col min="6" max="6" width="35" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:8" ht="21.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:8" ht="21.75" customHeight="1">
       <c r="A1" s="37" t="s">
         <v>105</v>
       </c>
@@ -3317,7 +3327,7 @@
       <c r="G1" s="37"/>
       <c r="H1" s="37"/>
     </row>
-    <row r="2" spans="1:8" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:8" ht="18" customHeight="1">
       <c r="A2" s="1" t="s">
         <v>106</v>
       </c>
@@ -3337,19 +3347,19 @@
         <v>13</v>
       </c>
     </row>
-    <row r="3" spans="1:8" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:8" ht="15.75" customHeight="1">
       <c r="A3" s="2" t="s">
         <v>111</v>
       </c>
       <c r="B3" s="27">
-        <v>92.78</v>
+        <v>93.23</v>
       </c>
       <c r="C3" s="27">
-        <v>84.28</v>
+        <v>84.78</v>
       </c>
       <c r="D3" s="5">
         <f t="shared" ref="D3:D8" si="0">-C3+B3</f>
-        <v>8.5</v>
+        <v>8.4500000000000028</v>
       </c>
       <c r="E3" s="2" t="s">
         <v>112</v>
@@ -3358,7 +3368,7 @@
         <v>113</v>
       </c>
     </row>
-    <row r="4" spans="1:8" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:8" ht="15.75" customHeight="1">
       <c r="A4" s="4" t="s">
         <v>114</v>
       </c>
@@ -3379,7 +3389,7 @@
         <v>116</v>
       </c>
     </row>
-    <row r="5" spans="1:8" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:8" ht="15.75" customHeight="1">
       <c r="A5" s="2" t="s">
         <v>117</v>
       </c>
@@ -3387,11 +3397,11 @@
         <v>100</v>
       </c>
       <c r="C5" s="27">
-        <v>95.54</v>
+        <v>95.69</v>
       </c>
       <c r="D5" s="5">
         <f t="shared" si="0"/>
-        <v>4.4599999999999937</v>
+        <v>4.3100000000000023</v>
       </c>
       <c r="E5" s="2" t="s">
         <v>118</v>
@@ -3400,19 +3410,19 @@
         <v>119</v>
       </c>
     </row>
-    <row r="6" spans="1:8" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:8" ht="15.75" customHeight="1">
       <c r="A6" s="4" t="s">
         <v>120</v>
       </c>
       <c r="B6" s="28">
-        <v>95.92</v>
+        <v>96.41</v>
       </c>
       <c r="C6" s="28">
-        <v>90.82</v>
+        <v>91.53</v>
       </c>
       <c r="D6" s="6">
         <f t="shared" si="0"/>
-        <v>5.1000000000000085</v>
+        <v>4.8799999999999955</v>
       </c>
       <c r="E6" s="4" t="s">
         <v>112</v>
@@ -3421,7 +3431,7 @@
         <v>113</v>
       </c>
     </row>
-    <row r="7" spans="1:8" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:8" ht="15.75" customHeight="1">
       <c r="A7" s="2" t="s">
         <v>121</v>
       </c>
@@ -3442,19 +3452,19 @@
         <v>119</v>
       </c>
     </row>
-    <row r="8" spans="1:8" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:8" ht="15.75" customHeight="1">
       <c r="A8" s="4" t="s">
         <v>122</v>
       </c>
       <c r="B8" s="28">
-        <v>68.05</v>
+        <v>71.23</v>
       </c>
       <c r="C8" s="28">
-        <v>22.08</v>
+        <v>24.82</v>
       </c>
       <c r="D8" s="6">
         <f t="shared" si="0"/>
-        <v>45.97</v>
+        <v>46.410000000000004</v>
       </c>
       <c r="E8" s="4" t="s">
         <v>112</v>
@@ -3481,7 +3491,7 @@
     <tabColor rgb="FFE87722"/>
   </sheetPr>
   <dimension ref="A1:H8"/>
-  <sheetFormatPr defaultColWidth="8.7109375" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultColWidth="8.7109375" defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="18" customWidth="1"/>
     <col min="2" max="4" width="10" customWidth="1"/>
@@ -3489,7 +3499,7 @@
     <col min="6" max="6" width="40" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:8" ht="21.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:8" ht="21.75" customHeight="1">
       <c r="A1" s="37" t="s">
         <v>124</v>
       </c>
@@ -3501,7 +3511,7 @@
       <c r="G1" s="37"/>
       <c r="H1" s="37"/>
     </row>
-    <row r="2" spans="1:8" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:8" ht="18" customHeight="1">
       <c r="A2" s="1" t="s">
         <v>125</v>
       </c>
@@ -3521,57 +3531,57 @@
         <v>13</v>
       </c>
     </row>
-    <row r="3" spans="1:8" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:8" ht="15.75" customHeight="1">
       <c r="A3" s="2" t="s">
         <v>126</v>
       </c>
       <c r="B3" s="2">
-        <v>92.88</v>
+        <v>93.23</v>
       </c>
       <c r="C3" s="2">
-        <v>83.78</v>
+        <v>84.22</v>
       </c>
       <c r="D3" s="5">
         <f>-C3+B3</f>
-        <v>9.0999999999999943</v>
+        <v>9.0100000000000051</v>
       </c>
       <c r="E3" s="2" t="s">
         <v>112</v>
       </c>
       <c r="F3" s="2"/>
     </row>
-    <row r="4" spans="1:8" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:8" ht="15.75" customHeight="1">
       <c r="A4" s="4" t="s">
         <v>127</v>
       </c>
       <c r="B4" s="4">
-        <v>92.15</v>
+        <v>92.64</v>
       </c>
       <c r="C4" s="4">
-        <v>84.33</v>
+        <v>84.89</v>
       </c>
       <c r="D4" s="6">
         <f>-C4+B4</f>
-        <v>7.8200000000000074</v>
+        <v>7.75</v>
       </c>
       <c r="E4" s="4" t="s">
         <v>118</v>
       </c>
       <c r="F4" s="4"/>
     </row>
-    <row r="5" spans="1:8" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:8" ht="15.75" customHeight="1">
       <c r="A5" s="2" t="s">
         <v>128</v>
       </c>
       <c r="B5" s="2">
-        <v>90.96</v>
+        <v>91.73</v>
       </c>
       <c r="C5" s="2">
-        <v>81.37</v>
+        <v>81.89</v>
       </c>
       <c r="D5" s="5">
         <f>-C5+B5</f>
-        <v>9.5899999999999892</v>
+        <v>9.8400000000000034</v>
       </c>
       <c r="E5" s="2" t="s">
         <v>112</v>
@@ -3580,38 +3590,38 @@
         <v>129</v>
       </c>
     </row>
-    <row r="6" spans="1:8" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:8" ht="15.75" customHeight="1">
       <c r="A6" s="4" t="s">
         <v>130</v>
       </c>
       <c r="B6" s="4">
-        <v>95.89</v>
+        <v>95.99</v>
       </c>
       <c r="C6" s="4">
-        <v>86.1</v>
+        <v>84.87</v>
       </c>
       <c r="D6" s="6">
         <f>-C6+B6</f>
-        <v>9.7900000000000063</v>
+        <v>11.11999999999999</v>
       </c>
       <c r="E6" s="4" t="s">
         <v>112</v>
       </c>
       <c r="F6" s="4"/>
     </row>
-    <row r="7" spans="1:8" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:8" ht="15.75" customHeight="1">
       <c r="A7" s="2" t="s">
         <v>131</v>
       </c>
       <c r="B7" s="2">
-        <v>95.71</v>
+        <v>95.79</v>
       </c>
       <c r="C7" s="2">
-        <v>91.03</v>
+        <v>91.27</v>
       </c>
       <c r="D7" s="5">
         <f>-C7+B7</f>
-        <v>4.6799999999999926</v>
+        <v>4.5200000000000102</v>
       </c>
       <c r="E7" s="2" t="s">
         <v>118</v>
@@ -3620,7 +3630,7 @@
         <v>132</v>
       </c>
     </row>
-    <row r="8" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:8" ht="15" customHeight="1">
       <c r="A8" s="7" t="s">
         <v>133</v>
       </c>

--- a/Dashboard_Data.xlsx
+++ b/Dashboard_Data.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30210"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29929"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://alfanargroup-my.sharepoint.com/personal/ahmed_abdelzaher_alfanar_com/Documents/SDCC Dashboard/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="40" documentId="8_{08402470-AB39-479E-9F56-A762705072E3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{1D450DF2-80C7-4DE4-876E-55C772860178}"/>
+  <xr:revisionPtr revIDLastSave="143" documentId="8_{08402470-AB39-479E-9F56-A762705072E3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{C8FD466D-7510-48FC-8F0E-8B6E74B27236}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" tabRatio="500" firstSheet="5" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" tabRatio="500" firstSheet="5" activeTab="5" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Header" sheetId="1" r:id="rId1"/>
@@ -51,7 +51,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="341" uniqueCount="211">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="391" uniqueCount="233">
   <si>
     <t>HEADER — Dashboard Title &amp; PM</t>
   </si>
@@ -257,9 +257,6 @@
     <t>Hero Sub-label</t>
   </si>
   <si>
-    <t>Outflow exceeds inflow · negative position</t>
-  </si>
-  <si>
     <t>Descriptive text under the big number</t>
   </si>
   <si>
@@ -684,6 +681,76 @@
   </si>
   <si>
     <t>alfanar</t>
+  </si>
+  <si>
+    <t>Delay in Telecom Rediness due to T&amp;C Delay from TNDT</t>
+  </si>
+  <si>
+    <t>T&amp;C</t>
+  </si>
+  <si>
+    <t>Delay in BMS Delivery</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Delay in Validation of SLD </t>
+  </si>
+  <si>
+    <t>CET/SE</t>
+  </si>
+  <si>
+    <t xml:space="preserve">CET &amp; SE to Expedite Validation of SLD </t>
+  </si>
+  <si>
+    <t>Delay in DERMS software Installation</t>
+  </si>
+  <si>
+    <t>CET to mobilize Derms team ASAP</t>
+  </si>
+  <si>
+    <t>medium</t>
+  </si>
+  <si>
+    <t>Low</t>
+  </si>
+  <si>
+    <t>Delay in starting Migration Activities</t>
+  </si>
+  <si>
+    <t>CET to start Activities of Migration Activity</t>
+  </si>
+  <si>
+    <t>Delay in Start Training</t>
+  </si>
+  <si>
+    <t>Alfanar / CET</t>
+  </si>
+  <si>
+    <t>Alfanar to Expedite Training room rediness
+CET to Expedite Avaialbility of Instructor Team</t>
+  </si>
+  <si>
+    <t xml:space="preserve">SE to push TNDT to proceed in T&amp;C </t>
+  </si>
+  <si>
+    <t>SETRA</t>
+  </si>
+  <si>
+    <t>Degital Era</t>
+  </si>
+  <si>
+    <t>DWDM</t>
+  </si>
+  <si>
+    <t>BMS Systems</t>
+  </si>
+  <si>
+    <t>LAN/WAN</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Low Current </t>
+  </si>
+  <si>
+    <t>Fire Alarm</t>
   </si>
 </sst>
 </file>
@@ -695,7 +762,7 @@
     <numFmt numFmtId="164" formatCode="[$-409]d\-mmm\-yy;@"/>
     <numFmt numFmtId="165" formatCode="0.0"/>
   </numFmts>
-  <fonts count="8">
+  <fonts count="8" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -812,7 +879,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="2">
+  <borders count="3">
     <border>
       <left/>
       <right/>
@@ -835,13 +902,24 @@
       </bottom>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin">
+        <color rgb="FFAAAAAA"/>
+      </left>
+      <right style="thin">
+        <color rgb="FFAAAAAA"/>
+      </right>
+      <top/>
+      <bottom/>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="3">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="43" fontId="6" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="9" fontId="6" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="41">
+  <cellXfs count="45">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -941,14 +1019,26 @@
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="3" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="43" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="43" fontId="3" fillId="5" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="4" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="9" fontId="3" fillId="4" borderId="2" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="6" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="9" fontId="3" fillId="6" borderId="2" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="43" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
-    <xf numFmtId="43" fontId="3" fillId="5" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -1221,25 +1311,25 @@
     <tabColor rgb="FFE87722"/>
   </sheetPr>
   <dimension ref="A1:H6"/>
-  <sheetFormatPr defaultColWidth="8.7109375" defaultRowHeight="15"/>
+  <sheetFormatPr defaultColWidth="8.7109375" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="30" customWidth="1"/>
     <col min="2" max="2" width="40" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:8" ht="21.75" customHeight="1">
-      <c r="A1" s="37" t="s">
+    <row r="1" spans="1:8" ht="21.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A1" s="43" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="37"/>
-      <c r="C1" s="37"/>
-      <c r="D1" s="37"/>
-      <c r="E1" s="37"/>
-      <c r="F1" s="37"/>
-      <c r="G1" s="37"/>
-      <c r="H1" s="37"/>
-    </row>
-    <row r="2" spans="1:8" ht="18" customHeight="1">
+      <c r="B1" s="43"/>
+      <c r="C1" s="43"/>
+      <c r="D1" s="43"/>
+      <c r="E1" s="43"/>
+      <c r="F1" s="43"/>
+      <c r="G1" s="43"/>
+      <c r="H1" s="43"/>
+    </row>
+    <row r="2" spans="1:8" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A2" s="1" t="s">
         <v>1</v>
       </c>
@@ -1247,7 +1337,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="3" spans="1:8" ht="25.5">
+    <row r="3" spans="1:8" ht="25.5" x14ac:dyDescent="0.25">
       <c r="A3" s="2" t="s">
         <v>3</v>
       </c>
@@ -1255,7 +1345,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="4" spans="1:8">
+    <row r="4" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A4" s="4" t="s">
         <v>5</v>
       </c>
@@ -1263,7 +1353,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="5" spans="1:8">
+    <row r="5" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A5" s="2" t="s">
         <v>7</v>
       </c>
@@ -1271,7 +1361,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="6" spans="1:8">
+    <row r="6" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A6" s="4" t="s">
         <v>9</v>
       </c>
@@ -1297,7 +1387,7 @@
     <tabColor rgb="FFE87722"/>
   </sheetPr>
   <dimension ref="A1:H30"/>
-  <sheetFormatPr defaultColWidth="8.7109375" defaultRowHeight="15"/>
+  <sheetFormatPr defaultColWidth="8.7109375" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="12" customWidth="1"/>
     <col min="2" max="2" width="14" customWidth="1"/>
@@ -1309,519 +1399,519 @@
     <col min="8" max="8" width="30" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:8" ht="21.75" customHeight="1">
-      <c r="A1" s="37" t="s">
+    <row r="1" spans="1:8" ht="21.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A1" s="43" t="s">
+        <v>133</v>
+      </c>
+      <c r="B1" s="43"/>
+      <c r="C1" s="43"/>
+      <c r="D1" s="43"/>
+      <c r="E1" s="43"/>
+      <c r="F1" s="43"/>
+      <c r="G1" s="43"/>
+      <c r="H1" s="43"/>
+    </row>
+    <row r="2" spans="1:8" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A2" s="1" t="s">
         <v>134</v>
       </c>
-      <c r="B1" s="37"/>
-      <c r="C1" s="37"/>
-      <c r="D1" s="37"/>
-      <c r="E1" s="37"/>
-      <c r="F1" s="37"/>
-      <c r="G1" s="37"/>
-      <c r="H1" s="37"/>
-    </row>
-    <row r="2" spans="1:8" ht="18" customHeight="1">
-      <c r="A2" s="1" t="s">
+      <c r="B2" s="1" t="s">
         <v>135</v>
       </c>
-      <c r="B2" s="1" t="s">
+      <c r="C2" s="1" t="s">
         <v>136</v>
       </c>
-      <c r="C2" s="1" t="s">
+      <c r="D2" s="1" t="s">
         <v>137</v>
       </c>
-      <c r="D2" s="1" t="s">
+      <c r="E2" s="1" t="s">
         <v>138</v>
       </c>
-      <c r="E2" s="1" t="s">
+      <c r="F2" s="1" t="s">
         <v>139</v>
       </c>
-      <c r="F2" s="1" t="s">
+      <c r="G2" s="1" t="s">
         <v>140</v>
-      </c>
-      <c r="G2" s="1" t="s">
-        <v>141</v>
       </c>
       <c r="H2" s="1" t="s">
         <v>13</v>
       </c>
     </row>
-    <row r="3" spans="1:8" ht="15.75" customHeight="1">
+    <row r="3" spans="1:8" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A3" s="32">
         <v>45620</v>
       </c>
       <c r="B3" s="2" t="s">
+        <v>141</v>
+      </c>
+      <c r="C3" s="2" t="s">
         <v>142</v>
       </c>
-      <c r="C3" s="2" t="s">
+      <c r="D3" s="2" t="s">
         <v>143</v>
       </c>
-      <c r="D3" s="2" t="s">
-        <v>144</v>
-      </c>
       <c r="E3" s="2" t="s">
-        <v>145</v>
+        <v>144</v>
       </c>
       <c r="F3" s="2"/>
       <c r="G3" s="2"/>
       <c r="H3" s="2" t="s">
-        <v>146</v>
-      </c>
-    </row>
-    <row r="4" spans="1:8" ht="15.75" customHeight="1">
+        <v>145</v>
+      </c>
+    </row>
+    <row r="4" spans="1:8" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A4" s="33">
         <v>45650</v>
       </c>
       <c r="B4" s="4" t="s">
-        <v>145</v>
+        <v>144</v>
       </c>
       <c r="C4" s="4"/>
       <c r="D4" s="4"/>
       <c r="E4" s="4" t="s">
-        <v>145</v>
+        <v>144</v>
       </c>
       <c r="F4" s="4"/>
       <c r="G4" s="4"/>
       <c r="H4" s="4"/>
     </row>
-    <row r="5" spans="1:8" ht="15.75" customHeight="1">
+    <row r="5" spans="1:8" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A5" s="32">
         <v>45681</v>
       </c>
       <c r="B5" s="2" t="s">
-        <v>145</v>
+        <v>144</v>
       </c>
       <c r="C5" s="2"/>
       <c r="D5" s="2"/>
       <c r="E5" s="2" t="s">
-        <v>145</v>
+        <v>144</v>
       </c>
       <c r="F5" s="2"/>
       <c r="G5" s="2"/>
       <c r="H5" s="2"/>
     </row>
-    <row r="6" spans="1:8" ht="15.75" customHeight="1">
+    <row r="6" spans="1:8" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A6" s="33">
         <v>45712</v>
       </c>
       <c r="B6" s="4" t="s">
-        <v>145</v>
+        <v>144</v>
       </c>
       <c r="C6" s="4"/>
       <c r="D6" s="4"/>
       <c r="E6" s="4" t="s">
-        <v>145</v>
+        <v>144</v>
       </c>
       <c r="F6" s="4"/>
       <c r="G6" s="4"/>
       <c r="H6" s="4"/>
     </row>
-    <row r="7" spans="1:8" ht="15.75" customHeight="1">
+    <row r="7" spans="1:8" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A7" s="32">
         <v>45740</v>
       </c>
       <c r="B7" s="2" t="s">
-        <v>142</v>
+        <v>141</v>
       </c>
       <c r="C7" s="2" t="s">
-        <v>147</v>
+        <v>146</v>
       </c>
       <c r="D7" s="2" t="s">
-        <v>144</v>
+        <v>143</v>
       </c>
       <c r="E7" s="2" t="s">
-        <v>145</v>
+        <v>144</v>
       </c>
       <c r="F7" s="2"/>
       <c r="G7" s="2"/>
       <c r="H7" s="2"/>
     </row>
-    <row r="8" spans="1:8" ht="15.75" customHeight="1">
+    <row r="8" spans="1:8" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A8" s="33">
         <v>45771</v>
       </c>
       <c r="B8" s="4" t="s">
-        <v>142</v>
+        <v>141</v>
       </c>
       <c r="C8" s="4" t="s">
+        <v>147</v>
+      </c>
+      <c r="D8" s="4" t="s">
         <v>148</v>
       </c>
-      <c r="D8" s="4" t="s">
-        <v>149</v>
-      </c>
       <c r="E8" s="4" t="s">
-        <v>145</v>
+        <v>144</v>
       </c>
       <c r="F8" s="4"/>
       <c r="G8" s="4"/>
       <c r="H8" s="4" t="s">
-        <v>150</v>
-      </c>
-    </row>
-    <row r="9" spans="1:8" ht="15.75" customHeight="1">
+        <v>149</v>
+      </c>
+    </row>
+    <row r="9" spans="1:8" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A9" s="32">
         <v>45801</v>
       </c>
       <c r="B9" s="2" t="s">
-        <v>145</v>
+        <v>144</v>
       </c>
       <c r="C9" s="2"/>
       <c r="D9" s="2"/>
       <c r="E9" s="2" t="s">
-        <v>145</v>
+        <v>144</v>
       </c>
       <c r="F9" s="2"/>
       <c r="G9" s="2"/>
       <c r="H9" s="2"/>
     </row>
-    <row r="10" spans="1:8" ht="15.75" customHeight="1">
+    <row r="10" spans="1:8" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A10" s="33">
         <v>45832</v>
       </c>
       <c r="B10" s="4" t="s">
-        <v>142</v>
+        <v>141</v>
       </c>
       <c r="C10" s="4" t="s">
-        <v>151</v>
+        <v>150</v>
       </c>
       <c r="D10" s="4" t="s">
-        <v>144</v>
+        <v>143</v>
       </c>
       <c r="E10" s="4" t="s">
-        <v>145</v>
+        <v>144</v>
       </c>
       <c r="F10" s="4"/>
       <c r="G10" s="4"/>
       <c r="H10" s="4"/>
     </row>
-    <row r="11" spans="1:8" ht="15.75" customHeight="1">
+    <row r="11" spans="1:8" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A11" s="32">
         <v>45862</v>
       </c>
       <c r="B11" s="2" t="s">
-        <v>145</v>
+        <v>144</v>
       </c>
       <c r="C11" s="2"/>
       <c r="D11" s="2"/>
       <c r="E11" s="2" t="s">
-        <v>145</v>
+        <v>144</v>
       </c>
       <c r="F11" s="2"/>
       <c r="G11" s="2"/>
       <c r="H11" s="2"/>
     </row>
-    <row r="12" spans="1:8" ht="15.75" customHeight="1">
+    <row r="12" spans="1:8" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A12" s="33">
         <v>45893</v>
       </c>
       <c r="B12" s="4" t="s">
-        <v>145</v>
+        <v>144</v>
       </c>
       <c r="C12" s="4"/>
       <c r="D12" s="4"/>
       <c r="E12" s="4" t="s">
-        <v>145</v>
+        <v>144</v>
       </c>
       <c r="F12" s="4"/>
       <c r="G12" s="4"/>
       <c r="H12" s="4"/>
     </row>
-    <row r="13" spans="1:8" ht="25.5">
+    <row r="13" spans="1:8" ht="25.5" x14ac:dyDescent="0.25">
       <c r="A13" s="32">
         <v>45924</v>
       </c>
       <c r="B13" s="2" t="s">
-        <v>142</v>
+        <v>141</v>
       </c>
       <c r="C13" s="2" t="s">
-        <v>152</v>
+        <v>151</v>
       </c>
       <c r="D13" s="2" t="s">
-        <v>149</v>
+        <v>148</v>
       </c>
       <c r="E13" s="2" t="s">
-        <v>145</v>
+        <v>144</v>
       </c>
       <c r="F13" s="2"/>
       <c r="G13" s="2"/>
       <c r="H13" s="2"/>
     </row>
-    <row r="14" spans="1:8" ht="25.5">
+    <row r="14" spans="1:8" ht="25.5" x14ac:dyDescent="0.25">
       <c r="A14" s="33">
         <v>45954</v>
       </c>
       <c r="B14" s="4" t="s">
-        <v>142</v>
+        <v>141</v>
       </c>
       <c r="C14" s="4" t="s">
-        <v>153</v>
+        <v>152</v>
       </c>
       <c r="D14" s="4" t="s">
-        <v>144</v>
+        <v>143</v>
       </c>
       <c r="E14" s="4" t="s">
-        <v>145</v>
+        <v>144</v>
       </c>
       <c r="F14" s="4"/>
       <c r="G14" s="4"/>
       <c r="H14" s="4"/>
     </row>
-    <row r="15" spans="1:8" ht="15.75" customHeight="1">
+    <row r="15" spans="1:8" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A15" s="32">
         <v>45985</v>
       </c>
       <c r="B15" s="2" t="s">
-        <v>145</v>
+        <v>144</v>
       </c>
       <c r="C15" s="2"/>
       <c r="D15" s="2"/>
       <c r="E15" s="2" t="s">
-        <v>145</v>
+        <v>144</v>
       </c>
       <c r="F15" s="2"/>
       <c r="G15" s="2"/>
       <c r="H15" s="2"/>
     </row>
-    <row r="16" spans="1:8" ht="15.75" customHeight="1">
+    <row r="16" spans="1:8" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A16" s="33">
         <v>46015</v>
       </c>
       <c r="B16" s="4" t="s">
-        <v>142</v>
+        <v>141</v>
       </c>
       <c r="C16" s="4" t="s">
-        <v>154</v>
+        <v>153</v>
       </c>
       <c r="D16" s="4" t="s">
-        <v>149</v>
+        <v>148</v>
       </c>
       <c r="E16" s="4" t="s">
-        <v>145</v>
+        <v>144</v>
       </c>
       <c r="F16" s="4"/>
       <c r="G16" s="4"/>
       <c r="H16" s="4"/>
     </row>
-    <row r="17" spans="1:8" ht="15.75" customHeight="1">
+    <row r="17" spans="1:8" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A17" s="32">
         <v>46046</v>
       </c>
       <c r="B17" s="2" t="s">
-        <v>145</v>
+        <v>144</v>
       </c>
       <c r="C17" s="2"/>
       <c r="D17" s="2"/>
       <c r="E17" s="2" t="s">
-        <v>145</v>
+        <v>144</v>
       </c>
       <c r="F17" s="2"/>
       <c r="G17" s="2"/>
       <c r="H17" s="2"/>
     </row>
-    <row r="18" spans="1:8" ht="15.75" customHeight="1">
+    <row r="18" spans="1:8" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A18" s="33">
         <v>46077</v>
       </c>
       <c r="B18" s="4" t="s">
-        <v>145</v>
+        <v>144</v>
       </c>
       <c r="C18" s="4"/>
       <c r="D18" s="4"/>
       <c r="E18" s="4" t="s">
-        <v>145</v>
+        <v>144</v>
       </c>
       <c r="F18" s="4"/>
       <c r="G18" s="4"/>
       <c r="H18" s="4"/>
     </row>
-    <row r="19" spans="1:8" ht="15.75" customHeight="1">
+    <row r="19" spans="1:8" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A19" s="32">
         <v>46105</v>
       </c>
       <c r="B19" s="2" t="s">
-        <v>145</v>
+        <v>144</v>
       </c>
       <c r="C19" s="2"/>
       <c r="D19" s="2"/>
       <c r="E19" s="2" t="s">
-        <v>145</v>
+        <v>144</v>
       </c>
       <c r="F19" s="2"/>
       <c r="G19" s="2"/>
       <c r="H19" s="2"/>
     </row>
-    <row r="20" spans="1:8" ht="15.75" customHeight="1">
+    <row r="20" spans="1:8" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A20" s="33">
         <v>46136</v>
       </c>
       <c r="B20" s="2" t="s">
-        <v>145</v>
+        <v>144</v>
       </c>
       <c r="C20" s="2"/>
       <c r="D20" s="2"/>
       <c r="E20" s="2" t="s">
-        <v>145</v>
+        <v>144</v>
       </c>
       <c r="F20" s="2"/>
       <c r="G20" s="2"/>
       <c r="H20" s="2"/>
     </row>
-    <row r="21" spans="1:8" ht="15.75" customHeight="1">
+    <row r="21" spans="1:8" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A21" s="32">
         <v>46166</v>
       </c>
       <c r="B21" s="2" t="s">
-        <v>145</v>
+        <v>144</v>
       </c>
       <c r="C21" s="2"/>
       <c r="D21" s="2"/>
       <c r="E21" s="2" t="s">
-        <v>145</v>
+        <v>144</v>
       </c>
       <c r="F21" s="2"/>
       <c r="G21" s="2"/>
       <c r="H21" s="2"/>
     </row>
-    <row r="22" spans="1:8" ht="15.75" customHeight="1">
+    <row r="22" spans="1:8" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A22" s="33">
         <v>46197</v>
       </c>
       <c r="B22" s="2" t="s">
-        <v>145</v>
+        <v>144</v>
       </c>
       <c r="C22" s="2"/>
       <c r="D22" s="2"/>
       <c r="E22" s="2" t="s">
-        <v>142</v>
+        <v>141</v>
       </c>
       <c r="F22" s="2"/>
       <c r="G22" s="2"/>
       <c r="H22" s="2"/>
     </row>
-    <row r="23" spans="1:8">
+    <row r="23" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A23" s="32">
         <v>46227</v>
       </c>
       <c r="B23" s="8" t="s">
-        <v>145</v>
+        <v>144</v>
       </c>
       <c r="C23" s="8"/>
       <c r="D23" s="8"/>
       <c r="E23" s="8" t="s">
-        <v>142</v>
+        <v>141</v>
       </c>
       <c r="F23" s="8" t="s">
         <v>19</v>
       </c>
       <c r="G23" s="8" t="s">
+        <v>154</v>
+      </c>
+      <c r="H23" s="8" t="s">
         <v>155</v>
       </c>
-      <c r="H23" s="8" t="s">
-        <v>156</v>
-      </c>
-    </row>
-    <row r="24" spans="1:8">
+    </row>
+    <row r="24" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A24" s="33">
         <v>46258</v>
       </c>
       <c r="B24" s="2" t="s">
-        <v>145</v>
+        <v>144</v>
       </c>
       <c r="C24" s="2"/>
       <c r="D24" s="2"/>
       <c r="E24" s="2" t="s">
-        <v>145</v>
+        <v>144</v>
       </c>
       <c r="F24" s="2"/>
       <c r="G24" s="2"/>
       <c r="H24" s="2"/>
     </row>
-    <row r="25" spans="1:8">
+    <row r="25" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A25" s="32">
         <v>46289</v>
       </c>
       <c r="B25" s="2" t="s">
-        <v>145</v>
+        <v>144</v>
       </c>
       <c r="C25" s="2"/>
       <c r="D25" s="2"/>
       <c r="E25" s="2" t="s">
-        <v>145</v>
+        <v>144</v>
       </c>
       <c r="F25" s="2"/>
       <c r="G25" s="2"/>
       <c r="H25" s="2"/>
     </row>
-    <row r="26" spans="1:8">
+    <row r="26" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A26" s="33">
         <v>46319</v>
       </c>
       <c r="B26" s="2" t="s">
-        <v>145</v>
+        <v>144</v>
       </c>
       <c r="C26" s="2"/>
       <c r="D26" s="2"/>
       <c r="E26" s="2" t="s">
-        <v>145</v>
+        <v>144</v>
       </c>
       <c r="F26" s="2"/>
       <c r="G26" s="2"/>
       <c r="H26" s="2"/>
     </row>
-    <row r="27" spans="1:8">
+    <row r="27" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A27" s="32">
         <v>46350</v>
       </c>
       <c r="B27" s="2" t="s">
-        <v>145</v>
+        <v>144</v>
       </c>
       <c r="E27" s="2" t="s">
-        <v>145</v>
-      </c>
-    </row>
-    <row r="28" spans="1:8">
+        <v>144</v>
+      </c>
+    </row>
+    <row r="28" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A28" s="33">
         <v>46380</v>
       </c>
       <c r="B28" s="2" t="s">
-        <v>145</v>
+        <v>144</v>
       </c>
       <c r="E28" s="2" t="s">
-        <v>145</v>
-      </c>
-    </row>
-    <row r="29" spans="1:8">
+        <v>144</v>
+      </c>
+    </row>
+    <row r="29" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A29" s="32">
         <v>46411</v>
       </c>
       <c r="B29" s="2" t="s">
-        <v>145</v>
+        <v>144</v>
       </c>
       <c r="E29" s="2" t="s">
-        <v>145</v>
-      </c>
-    </row>
-    <row r="30" spans="1:8">
+        <v>144</v>
+      </c>
+    </row>
+    <row r="30" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A30" s="33">
         <v>46442</v>
       </c>
       <c r="B30" s="9" t="s">
-        <v>145</v>
+        <v>144</v>
       </c>
       <c r="C30" s="9"/>
       <c r="D30" s="9"/>
       <c r="E30" s="9" t="s">
-        <v>142</v>
+        <v>141</v>
       </c>
       <c r="F30" s="9" t="s">
-        <v>157</v>
+        <v>156</v>
       </c>
       <c r="G30" s="29">
         <v>46435</v>
       </c>
       <c r="H30" s="9" t="s">
-        <v>158</v>
+        <v>157</v>
       </c>
     </row>
   </sheetData>
@@ -1841,8 +1931,8 @@
   <sheetPr>
     <tabColor rgb="FFE87722"/>
   </sheetPr>
-  <dimension ref="A1:H6"/>
-  <sheetFormatPr defaultColWidth="8.7109375" defaultRowHeight="15"/>
+  <dimension ref="A1:H12"/>
+  <sheetFormatPr defaultColWidth="8.7109375" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="4" customWidth="1"/>
     <col min="2" max="2" width="38" customWidth="1"/>
@@ -1852,116 +1942,234 @@
     <col min="6" max="6" width="10" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:8" ht="21.75" customHeight="1">
-      <c r="A1" s="37" t="s">
+    <row r="1" spans="1:8" ht="21.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A1" s="43" t="s">
+        <v>158</v>
+      </c>
+      <c r="B1" s="43"/>
+      <c r="C1" s="43"/>
+      <c r="D1" s="43"/>
+      <c r="E1" s="43"/>
+      <c r="F1" s="43"/>
+      <c r="G1" s="43"/>
+      <c r="H1" s="43"/>
+    </row>
+    <row r="2" spans="1:8" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A2" s="1" t="s">
         <v>159</v>
       </c>
-      <c r="B1" s="37"/>
-      <c r="C1" s="37"/>
-      <c r="D1" s="37"/>
-      <c r="E1" s="37"/>
-      <c r="F1" s="37"/>
-      <c r="G1" s="37"/>
-      <c r="H1" s="37"/>
-    </row>
-    <row r="2" spans="1:8" ht="18" customHeight="1">
-      <c r="A2" s="1" t="s">
+      <c r="B2" s="1" t="s">
         <v>160</v>
       </c>
-      <c r="B2" s="1" t="s">
+      <c r="C2" s="1" t="s">
         <v>161</v>
       </c>
-      <c r="C2" s="1" t="s">
+      <c r="D2" s="1" t="s">
         <v>162</v>
       </c>
-      <c r="D2" s="1" t="s">
+      <c r="E2" s="1" t="s">
         <v>163</v>
       </c>
-      <c r="E2" s="1" t="s">
+      <c r="F2" s="1" t="s">
         <v>164</v>
       </c>
-      <c r="F2" s="1" t="s">
-        <v>165</v>
-      </c>
-    </row>
-    <row r="3" spans="1:8" ht="38.25">
+    </row>
+    <row r="3" spans="1:8" ht="38.25" x14ac:dyDescent="0.25">
       <c r="A3" s="2">
         <v>1</v>
       </c>
       <c r="B3" s="2" t="s">
+        <v>165</v>
+      </c>
+      <c r="C3" s="2" t="s">
         <v>166</v>
       </c>
-      <c r="C3" s="2" t="s">
+      <c r="D3" s="2" t="s">
         <v>167</v>
       </c>
-      <c r="D3" s="2" t="s">
+      <c r="E3" s="2" t="s">
         <v>168</v>
       </c>
-      <c r="E3" s="2" t="s">
+      <c r="F3" s="10" t="s">
         <v>169</v>
       </c>
-      <c r="F3" s="10" t="s">
-        <v>170</v>
-      </c>
-    </row>
-    <row r="4" spans="1:8" ht="25.5">
+    </row>
+    <row r="4" spans="1:8" ht="25.5" x14ac:dyDescent="0.25">
       <c r="A4" s="4">
         <v>2</v>
       </c>
       <c r="B4" s="4" t="s">
+        <v>170</v>
+      </c>
+      <c r="C4" s="4" t="s">
         <v>171</v>
       </c>
-      <c r="C4" s="4" t="s">
+      <c r="D4" s="4" t="s">
         <v>172</v>
       </c>
-      <c r="D4" s="4" t="s">
+      <c r="E4" s="4" t="s">
         <v>173</v>
       </c>
-      <c r="E4" s="4" t="s">
-        <v>174</v>
-      </c>
       <c r="F4" s="10" t="s">
-        <v>170</v>
-      </c>
-    </row>
-    <row r="5" spans="1:8" ht="38.25">
+        <v>169</v>
+      </c>
+    </row>
+    <row r="5" spans="1:8" ht="38.25" x14ac:dyDescent="0.25">
       <c r="A5" s="2">
         <v>3</v>
       </c>
       <c r="B5" s="2" t="s">
+        <v>174</v>
+      </c>
+      <c r="C5" s="2" t="s">
+        <v>171</v>
+      </c>
+      <c r="D5" s="2" t="s">
+        <v>172</v>
+      </c>
+      <c r="E5" s="2" t="s">
         <v>175</v>
       </c>
-      <c r="C5" s="2" t="s">
-        <v>172</v>
-      </c>
-      <c r="D5" s="2" t="s">
-        <v>173</v>
-      </c>
-      <c r="E5" s="2" t="s">
-        <v>176</v>
-      </c>
       <c r="F5" s="10" t="s">
-        <v>170</v>
-      </c>
-    </row>
-    <row r="6" spans="1:8" ht="38.25">
+        <v>169</v>
+      </c>
+    </row>
+    <row r="6" spans="1:8" ht="38.25" x14ac:dyDescent="0.25">
       <c r="A6" s="2">
         <v>4</v>
       </c>
       <c r="B6" s="2" t="s">
+        <v>176</v>
+      </c>
+      <c r="C6" s="2" t="s">
+        <v>171</v>
+      </c>
+      <c r="D6" s="2" t="s">
+        <v>172</v>
+      </c>
+      <c r="E6" s="2" t="s">
         <v>177</v>
       </c>
-      <c r="C6" s="2" t="s">
+      <c r="F6" s="10" t="s">
+        <v>169</v>
+      </c>
+    </row>
+    <row r="7" spans="1:8" ht="25.5" x14ac:dyDescent="0.25">
+      <c r="A7" s="2">
+        <v>5</v>
+      </c>
+      <c r="B7" s="2" t="s">
+        <v>210</v>
+      </c>
+      <c r="C7" s="2" t="s">
+        <v>211</v>
+      </c>
+      <c r="D7" s="2" t="s">
         <v>172</v>
       </c>
-      <c r="D6" s="2" t="s">
-        <v>173</v>
-      </c>
-      <c r="E6" s="2" t="s">
-        <v>178</v>
-      </c>
-      <c r="F6" s="10" t="s">
-        <v>170</v>
+      <c r="E7" s="2" t="s">
+        <v>225</v>
+      </c>
+      <c r="F7" s="10" t="s">
+        <v>169</v>
+      </c>
+    </row>
+    <row r="8" spans="1:8" ht="25.5" x14ac:dyDescent="0.25">
+      <c r="A8" s="2">
+        <v>6</v>
+      </c>
+      <c r="B8" s="2" t="s">
+        <v>212</v>
+      </c>
+      <c r="C8" s="2" t="s">
+        <v>171</v>
+      </c>
+      <c r="D8" s="2" t="s">
+        <v>226</v>
+      </c>
+      <c r="E8" s="2"/>
+      <c r="F8" s="10" t="s">
+        <v>218</v>
+      </c>
+    </row>
+    <row r="9" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A9" s="2">
+        <v>7</v>
+      </c>
+      <c r="B9" s="2" t="s">
+        <v>213</v>
+      </c>
+      <c r="C9" s="2" t="s">
+        <v>211</v>
+      </c>
+      <c r="D9" s="2" t="s">
+        <v>214</v>
+      </c>
+      <c r="E9" s="2" t="s">
+        <v>215</v>
+      </c>
+      <c r="F9" s="10" t="s">
+        <v>169</v>
+      </c>
+    </row>
+    <row r="10" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A10" s="2">
+        <v>8</v>
+      </c>
+      <c r="B10" s="2" t="s">
+        <v>216</v>
+      </c>
+      <c r="C10" s="2" t="s">
+        <v>211</v>
+      </c>
+      <c r="D10" s="2" t="s">
+        <v>214</v>
+      </c>
+      <c r="E10" s="2" t="s">
+        <v>217</v>
+      </c>
+      <c r="F10" s="10" t="s">
+        <v>219</v>
+      </c>
+    </row>
+    <row r="11" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A11" s="2">
+        <v>9</v>
+      </c>
+      <c r="B11" s="2" t="s">
+        <v>220</v>
+      </c>
+      <c r="C11" s="2" t="s">
+        <v>211</v>
+      </c>
+      <c r="D11" s="2" t="s">
+        <v>214</v>
+      </c>
+      <c r="E11" s="2" t="s">
+        <v>221</v>
+      </c>
+      <c r="F11" s="10" t="s">
+        <v>169</v>
+      </c>
+    </row>
+    <row r="12" spans="1:8" ht="25.5" x14ac:dyDescent="0.25">
+      <c r="A12" s="2">
+        <v>10</v>
+      </c>
+      <c r="B12" s="2" t="s">
+        <v>222</v>
+      </c>
+      <c r="C12" s="2" t="s">
+        <v>211</v>
+      </c>
+      <c r="D12" s="2" t="s">
+        <v>223</v>
+      </c>
+      <c r="E12" s="2" t="s">
+        <v>224</v>
+      </c>
+      <c r="F12" s="10" t="s">
+        <v>218</v>
       </c>
     </row>
   </sheetData>
@@ -1981,8 +2189,8 @@
   <sheetPr>
     <tabColor rgb="FFE87722"/>
   </sheetPr>
-  <dimension ref="A1:U25"/>
-  <sheetFormatPr defaultColWidth="8.7109375" defaultRowHeight="15"/>
+  <dimension ref="A1:U28"/>
+  <sheetFormatPr defaultColWidth="8.7109375" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="4" customWidth="1"/>
     <col min="2" max="2" width="26" customWidth="1"/>
@@ -1991,56 +2199,56 @@
     <col min="8" max="8" width="12" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:21" ht="21.75" customHeight="1">
-      <c r="A1" s="37" t="s">
+    <row r="1" spans="1:21" ht="21.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A1" s="43" t="s">
+        <v>178</v>
+      </c>
+      <c r="B1" s="43"/>
+      <c r="C1" s="43"/>
+      <c r="D1" s="43"/>
+      <c r="E1" s="43"/>
+      <c r="F1" s="43"/>
+      <c r="G1" s="43"/>
+      <c r="H1" s="43"/>
+    </row>
+    <row r="2" spans="1:21" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A2" s="1" t="s">
+        <v>159</v>
+      </c>
+      <c r="B2" s="1" t="s">
+        <v>116</v>
+      </c>
+      <c r="C2" s="1" t="s">
         <v>179</v>
       </c>
-      <c r="B1" s="37"/>
-      <c r="C1" s="37"/>
-      <c r="D1" s="37"/>
-      <c r="E1" s="37"/>
-      <c r="F1" s="37"/>
-      <c r="G1" s="37"/>
-      <c r="H1" s="37"/>
-    </row>
-    <row r="2" spans="1:21" ht="18" customHeight="1">
-      <c r="A2" s="1" t="s">
-        <v>160</v>
-      </c>
-      <c r="B2" s="1" t="s">
-        <v>117</v>
-      </c>
-      <c r="C2" s="1" t="s">
+      <c r="D2" s="1" t="s">
         <v>180</v>
       </c>
-      <c r="D2" s="1" t="s">
+      <c r="E2" s="1" t="s">
         <v>181</v>
       </c>
-      <c r="E2" s="1" t="s">
+      <c r="F2" s="1" t="s">
         <v>182</v>
       </c>
-      <c r="F2" s="1" t="s">
+      <c r="G2" s="1" t="s">
         <v>183</v>
       </c>
-      <c r="G2" s="1" t="s">
+      <c r="H2" s="1" t="s">
         <v>184</v>
       </c>
-      <c r="H2" s="1" t="s">
-        <v>185</v>
-      </c>
-    </row>
-    <row r="3" spans="1:21" ht="15.75" customHeight="1">
+    </row>
+    <row r="3" spans="1:21" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A3" s="2">
         <v>1</v>
       </c>
       <c r="B3" s="2" t="s">
+        <v>185</v>
+      </c>
+      <c r="C3" s="2" t="s">
         <v>186</v>
       </c>
-      <c r="C3" s="2" t="s">
+      <c r="D3" s="2" t="s">
         <v>187</v>
-      </c>
-      <c r="D3" s="2" t="s">
-        <v>188</v>
       </c>
       <c r="E3" s="13">
         <v>1</v>
@@ -2049,24 +2257,24 @@
         <v>1</v>
       </c>
       <c r="G3" s="13">
-        <v>1</v>
-      </c>
-      <c r="H3" s="11" t="s">
-        <v>189</v>
-      </c>
-    </row>
-    <row r="4" spans="1:21" ht="15.75" customHeight="1">
+        <v>0.95</v>
+      </c>
+      <c r="H3" s="10" t="s">
+        <v>196</v>
+      </c>
+    </row>
+    <row r="4" spans="1:21" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A4" s="4">
         <v>2</v>
       </c>
       <c r="B4" s="4" t="s">
+        <v>189</v>
+      </c>
+      <c r="C4" s="4" t="s">
         <v>190</v>
       </c>
-      <c r="C4" s="4" t="s">
-        <v>191</v>
-      </c>
       <c r="D4" s="4" t="s">
-        <v>188</v>
+        <v>187</v>
       </c>
       <c r="E4" s="34">
         <v>1</v>
@@ -2078,21 +2286,21 @@
         <v>1</v>
       </c>
       <c r="H4" s="11" t="s">
-        <v>189</v>
-      </c>
-    </row>
-    <row r="5" spans="1:21" ht="15.75" customHeight="1">
+        <v>188</v>
+      </c>
+    </row>
+    <row r="5" spans="1:21" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A5" s="2">
         <v>3</v>
       </c>
       <c r="B5" s="2" t="s">
-        <v>192</v>
+        <v>191</v>
       </c>
       <c r="C5" s="2" t="s">
-        <v>191</v>
+        <v>190</v>
       </c>
       <c r="D5" s="2" t="s">
-        <v>188</v>
+        <v>187</v>
       </c>
       <c r="E5" s="13">
         <v>1</v>
@@ -2104,21 +2312,21 @@
         <v>1</v>
       </c>
       <c r="H5" s="11" t="s">
-        <v>189</v>
-      </c>
-    </row>
-    <row r="6" spans="1:21" ht="15.75" customHeight="1">
+        <v>188</v>
+      </c>
+    </row>
+    <row r="6" spans="1:21" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A6" s="4">
         <v>4</v>
       </c>
       <c r="B6" s="4" t="s">
+        <v>192</v>
+      </c>
+      <c r="C6" s="4" t="s">
         <v>193</v>
       </c>
-      <c r="C6" s="4" t="s">
-        <v>194</v>
-      </c>
       <c r="D6" s="4" t="s">
-        <v>188</v>
+        <v>187</v>
       </c>
       <c r="E6" s="34">
         <v>1</v>
@@ -2130,171 +2338,297 @@
         <v>1</v>
       </c>
       <c r="H6" s="11" t="s">
-        <v>189</v>
-      </c>
-    </row>
-    <row r="7" spans="1:21" ht="15.75" customHeight="1">
+        <v>188</v>
+      </c>
+    </row>
+    <row r="7" spans="1:21" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A7" s="2">
         <v>5</v>
       </c>
-      <c r="B7" s="2" t="s">
-        <v>195</v>
+      <c r="B7" s="4" t="s">
+        <v>232</v>
       </c>
       <c r="C7" s="2" t="s">
-        <v>196</v>
-      </c>
-      <c r="D7" s="2" t="s">
+        <v>190</v>
+      </c>
+      <c r="D7" s="4" t="s">
+        <v>187</v>
+      </c>
+      <c r="E7" s="34">
+        <v>1</v>
+      </c>
+      <c r="F7" s="34">
+        <v>1</v>
+      </c>
+      <c r="G7" s="34">
+        <v>1</v>
+      </c>
+      <c r="H7" s="11" t="s">
         <v>188</v>
       </c>
-      <c r="E7" s="13">
-        <v>1</v>
-      </c>
-      <c r="F7" s="13">
-        <v>0.9</v>
-      </c>
-      <c r="G7" s="13">
-        <v>0.9</v>
-      </c>
-      <c r="H7" s="10" t="s">
-        <v>197</v>
-      </c>
-    </row>
-    <row r="8" spans="1:21" ht="15.75" customHeight="1">
+    </row>
+    <row r="8" spans="1:21" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A8" s="4">
         <v>6</v>
       </c>
-      <c r="B8" s="4" t="s">
-        <v>198</v>
-      </c>
-      <c r="C8" s="4" t="s">
+      <c r="B8" s="2" t="s">
+        <v>194</v>
+      </c>
+      <c r="C8" s="2" t="s">
+        <v>195</v>
+      </c>
+      <c r="D8" s="2" t="s">
+        <v>187</v>
+      </c>
+      <c r="E8" s="13">
+        <v>1</v>
+      </c>
+      <c r="F8" s="13">
+        <v>0.9</v>
+      </c>
+      <c r="G8" s="13">
+        <v>0.9</v>
+      </c>
+      <c r="H8" s="10" t="s">
         <v>196</v>
       </c>
-      <c r="D8" s="4" t="s">
-        <v>188</v>
-      </c>
-      <c r="E8" s="34">
-        <v>1</v>
-      </c>
-      <c r="F8" s="34">
-        <v>0</v>
-      </c>
-      <c r="G8" s="34">
-        <v>0</v>
-      </c>
-      <c r="H8" s="10" t="s">
-        <v>197</v>
-      </c>
-    </row>
-    <row r="9" spans="1:21" ht="15.75" customHeight="1">
+    </row>
+    <row r="9" spans="1:21" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A9" s="2">
         <v>7</v>
       </c>
-      <c r="B9" s="2" t="s">
-        <v>199</v>
-      </c>
-      <c r="C9" s="2" t="s">
-        <v>191</v>
-      </c>
-      <c r="D9" s="2" t="s">
-        <v>188</v>
-      </c>
-      <c r="E9" s="13">
-        <v>0.8</v>
-      </c>
-      <c r="F9" s="13">
+      <c r="B9" s="4" t="s">
+        <v>197</v>
+      </c>
+      <c r="C9" s="4" t="s">
+        <v>195</v>
+      </c>
+      <c r="D9" s="4" t="s">
+        <v>187</v>
+      </c>
+      <c r="E9" s="34">
+        <v>1</v>
+      </c>
+      <c r="F9" s="34">
         <v>0</v>
       </c>
-      <c r="G9" s="13">
+      <c r="G9" s="34">
         <v>0</v>
       </c>
       <c r="H9" s="10" t="s">
-        <v>197</v>
-      </c>
-    </row>
-    <row r="10" spans="1:21" ht="15.75" customHeight="1">
+        <v>196</v>
+      </c>
+    </row>
+    <row r="10" spans="1:21" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A10" s="4">
         <v>8</v>
       </c>
       <c r="B10" s="4" t="s">
+        <v>230</v>
+      </c>
+      <c r="C10" s="4" t="s">
+        <v>195</v>
+      </c>
+      <c r="D10" s="4" t="s">
+        <v>187</v>
+      </c>
+      <c r="E10" s="34">
+        <v>0</v>
+      </c>
+      <c r="F10" s="34">
+        <v>0</v>
+      </c>
+      <c r="G10" s="34">
+        <v>0</v>
+      </c>
+      <c r="H10" s="10" t="s">
+        <v>196</v>
+      </c>
+    </row>
+    <row r="11" spans="1:21" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A11" s="2">
+        <v>9</v>
+      </c>
+      <c r="B11" s="4" t="s">
+        <v>228</v>
+      </c>
+      <c r="C11" s="4" t="s">
+        <v>195</v>
+      </c>
+      <c r="D11" s="4" t="s">
+        <v>187</v>
+      </c>
+      <c r="E11" s="34">
+        <v>1</v>
+      </c>
+      <c r="F11" s="34">
+        <v>0</v>
+      </c>
+      <c r="G11" s="34">
+        <v>0</v>
+      </c>
+      <c r="H11" s="10" t="s">
+        <v>196</v>
+      </c>
+    </row>
+    <row r="12" spans="1:21" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A12" s="4">
+        <v>10</v>
+      </c>
+      <c r="B12" s="2" t="s">
+        <v>198</v>
+      </c>
+      <c r="C12" s="2" t="s">
+        <v>190</v>
+      </c>
+      <c r="D12" s="2" t="s">
+        <v>187</v>
+      </c>
+      <c r="E12" s="13">
+        <v>0.8</v>
+      </c>
+      <c r="F12" s="13">
+        <v>0</v>
+      </c>
+      <c r="G12" s="13">
+        <v>0</v>
+      </c>
+      <c r="H12" s="10" t="s">
+        <v>196</v>
+      </c>
+    </row>
+    <row r="13" spans="1:21" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A13" s="2">
+        <v>11</v>
+      </c>
+      <c r="B13" s="4" t="s">
+        <v>199</v>
+      </c>
+      <c r="C13" s="4" t="s">
         <v>200</v>
       </c>
-      <c r="C10" s="4" t="s">
+      <c r="D13" s="4" t="s">
+        <v>187</v>
+      </c>
+      <c r="E13" s="34">
+        <v>1</v>
+      </c>
+      <c r="F13" s="34" t="s">
         <v>201</v>
       </c>
-      <c r="D10" s="4" t="s">
-        <v>188</v>
-      </c>
-      <c r="E10" s="34">
+      <c r="G13" s="34">
+        <v>0.15</v>
+      </c>
+      <c r="H13" s="10" t="s">
+        <v>196</v>
+      </c>
+    </row>
+    <row r="14" spans="1:21" x14ac:dyDescent="0.25">
+      <c r="A14" s="4">
+        <v>12</v>
+      </c>
+      <c r="B14" s="39" t="s">
+        <v>231</v>
+      </c>
+      <c r="C14" s="39" t="s">
+        <v>227</v>
+      </c>
+      <c r="D14" s="39" t="s">
+        <v>187</v>
+      </c>
+      <c r="E14" s="40">
         <v>1</v>
       </c>
-      <c r="F10" s="34" t="s">
-        <v>202</v>
-      </c>
-      <c r="G10" s="34">
-        <v>0.15</v>
-      </c>
-      <c r="H10" s="10" t="s">
-        <v>197</v>
-      </c>
-    </row>
-    <row r="11" spans="1:21">
-      <c r="S11" s="31"/>
-      <c r="T11" s="31"/>
-      <c r="U11" s="31"/>
-    </row>
-    <row r="12" spans="1:21">
-      <c r="S12" s="31"/>
-      <c r="T12" s="31"/>
-      <c r="U12" s="31"/>
-    </row>
-    <row r="13" spans="1:21">
-      <c r="S13" s="31"/>
-      <c r="T13" s="31"/>
-      <c r="U13" s="31"/>
-    </row>
-    <row r="14" spans="1:21">
+      <c r="F14" s="39" t="s">
+        <v>201</v>
+      </c>
+      <c r="G14" s="42">
+        <v>0.4</v>
+      </c>
+      <c r="H14" s="10" t="s">
+        <v>196</v>
+      </c>
       <c r="S14" s="31"/>
       <c r="T14" s="31"/>
       <c r="U14" s="31"/>
     </row>
-    <row r="15" spans="1:21">
+    <row r="15" spans="1:21" x14ac:dyDescent="0.25">
+      <c r="A15" s="2">
+        <v>13</v>
+      </c>
+      <c r="B15" s="41" t="s">
+        <v>229</v>
+      </c>
+      <c r="C15" s="41" t="s">
+        <v>226</v>
+      </c>
+      <c r="D15" s="41" t="s">
+        <v>187</v>
+      </c>
+      <c r="E15" s="42">
+        <v>1</v>
+      </c>
+      <c r="F15" s="42" t="s">
+        <v>201</v>
+      </c>
+      <c r="G15" s="42">
+        <v>0</v>
+      </c>
+      <c r="H15" s="10" t="s">
+        <v>196</v>
+      </c>
       <c r="S15" s="31"/>
       <c r="T15" s="31"/>
       <c r="U15" s="31"/>
     </row>
-    <row r="16" spans="1:21">
+    <row r="16" spans="1:21" x14ac:dyDescent="0.25">
       <c r="S16" s="31"/>
       <c r="T16" s="31"/>
       <c r="U16" s="31"/>
     </row>
-    <row r="17" spans="19:21">
+    <row r="17" spans="19:21" x14ac:dyDescent="0.25">
+      <c r="S17" s="31"/>
       <c r="T17" s="31"/>
       <c r="U17" s="31"/>
     </row>
-    <row r="18" spans="19:21">
+    <row r="18" spans="19:21" x14ac:dyDescent="0.25">
       <c r="S18" s="31"/>
+      <c r="T18" s="31"/>
       <c r="U18" s="31"/>
     </row>
-    <row r="19" spans="19:21">
-      <c r="S19" s="30"/>
-    </row>
-    <row r="20" spans="19:21">
-      <c r="S20" s="30"/>
-    </row>
-    <row r="21" spans="19:21">
-      <c r="S21" s="30"/>
-    </row>
-    <row r="22" spans="19:21">
+    <row r="19" spans="19:21" x14ac:dyDescent="0.25">
+      <c r="S19" s="31"/>
+      <c r="T19" s="31"/>
+      <c r="U19" s="31"/>
+    </row>
+    <row r="20" spans="19:21" x14ac:dyDescent="0.25">
+      <c r="T20" s="31"/>
+      <c r="U20" s="31"/>
+    </row>
+    <row r="21" spans="19:21" x14ac:dyDescent="0.25">
+      <c r="S21" s="31"/>
+      <c r="U21" s="31"/>
+    </row>
+    <row r="22" spans="19:21" x14ac:dyDescent="0.25">
       <c r="S22" s="30"/>
     </row>
-    <row r="23" spans="19:21">
+    <row r="23" spans="19:21" x14ac:dyDescent="0.25">
       <c r="S23" s="30"/>
     </row>
-    <row r="24" spans="19:21">
+    <row r="24" spans="19:21" x14ac:dyDescent="0.25">
       <c r="S24" s="30"/>
     </row>
-    <row r="25" spans="19:21">
+    <row r="25" spans="19:21" x14ac:dyDescent="0.25">
       <c r="S25" s="30"/>
+    </row>
+    <row r="26" spans="19:21" x14ac:dyDescent="0.25">
+      <c r="S26" s="30"/>
+    </row>
+    <row r="27" spans="19:21" x14ac:dyDescent="0.25">
+      <c r="S27" s="30"/>
+    </row>
+    <row r="28" spans="19:21" x14ac:dyDescent="0.25">
+      <c r="S28" s="30"/>
     </row>
   </sheetData>
   <mergeCells count="1">
@@ -2314,25 +2648,25 @@
     <tabColor rgb="FFE87722"/>
   </sheetPr>
   <dimension ref="A1:H6"/>
-  <sheetFormatPr defaultColWidth="8.7109375" defaultRowHeight="15"/>
+  <sheetFormatPr defaultColWidth="8.7109375" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="30" customWidth="1"/>
     <col min="2" max="2" width="50" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:8" ht="21.75" customHeight="1">
-      <c r="A1" s="37" t="s">
-        <v>203</v>
-      </c>
-      <c r="B1" s="37"/>
-      <c r="C1" s="37"/>
-      <c r="D1" s="37"/>
-      <c r="E1" s="37"/>
-      <c r="F1" s="37"/>
-      <c r="G1" s="37"/>
-      <c r="H1" s="37"/>
-    </row>
-    <row r="2" spans="1:8" ht="18" customHeight="1">
+    <row r="1" spans="1:8" ht="21.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A1" s="43" t="s">
+        <v>202</v>
+      </c>
+      <c r="B1" s="43"/>
+      <c r="C1" s="43"/>
+      <c r="D1" s="43"/>
+      <c r="E1" s="43"/>
+      <c r="F1" s="43"/>
+      <c r="G1" s="43"/>
+      <c r="H1" s="43"/>
+    </row>
+    <row r="2" spans="1:8" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A2" s="1" t="s">
         <v>1</v>
       </c>
@@ -2340,36 +2674,36 @@
         <v>2</v>
       </c>
     </row>
-    <row r="3" spans="1:8" ht="15.75" customHeight="1">
+    <row r="3" spans="1:8" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A3" s="2" t="s">
+        <v>203</v>
+      </c>
+      <c r="B3" s="3" t="s">
         <v>204</v>
       </c>
-      <c r="B3" s="3" t="s">
+    </row>
+    <row r="4" spans="1:8" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A4" s="4" t="s">
         <v>205</v>
-      </c>
-    </row>
-    <row r="4" spans="1:8" ht="15.75" customHeight="1">
-      <c r="A4" s="4" t="s">
-        <v>206</v>
       </c>
       <c r="B4" s="12">
         <v>46176</v>
       </c>
     </row>
-    <row r="5" spans="1:8" ht="15.75" customHeight="1">
+    <row r="5" spans="1:8" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A5" s="2" t="s">
+        <v>206</v>
+      </c>
+      <c r="B5" s="3" t="s">
         <v>207</v>
       </c>
-      <c r="B5" s="3" t="s">
+    </row>
+    <row r="6" spans="1:8" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A6" s="4" t="s">
         <v>208</v>
       </c>
-    </row>
-    <row r="6" spans="1:8" ht="15.75" customHeight="1">
-      <c r="A6" s="4" t="s">
+      <c r="B6" s="3" t="s">
         <v>209</v>
-      </c>
-      <c r="B6" s="3" t="s">
-        <v>210</v>
       </c>
     </row>
   </sheetData>
@@ -2390,26 +2724,26 @@
     <tabColor rgb="FFE87722"/>
   </sheetPr>
   <dimension ref="A1:H9"/>
-  <sheetFormatPr defaultColWidth="8.7109375" defaultRowHeight="15"/>
+  <sheetFormatPr defaultColWidth="8.7109375" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="32" customWidth="1"/>
     <col min="2" max="2" width="18" customWidth="1"/>
     <col min="3" max="3" width="40" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:8" ht="21.75" customHeight="1">
-      <c r="A1" s="37" t="s">
+    <row r="1" spans="1:8" ht="21.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A1" s="43" t="s">
         <v>11</v>
       </c>
-      <c r="B1" s="37"/>
-      <c r="C1" s="37"/>
-      <c r="D1" s="37"/>
-      <c r="E1" s="37"/>
-      <c r="F1" s="37"/>
-      <c r="G1" s="37"/>
-      <c r="H1" s="37"/>
-    </row>
-    <row r="2" spans="1:8" ht="18" customHeight="1">
+      <c r="B1" s="43"/>
+      <c r="C1" s="43"/>
+      <c r="D1" s="43"/>
+      <c r="E1" s="43"/>
+      <c r="F1" s="43"/>
+      <c r="G1" s="43"/>
+      <c r="H1" s="43"/>
+    </row>
+    <row r="2" spans="1:8" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A2" s="1" t="s">
         <v>1</v>
       </c>
@@ -2420,7 +2754,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="3" spans="1:8" ht="15.75" customHeight="1">
+    <row r="3" spans="1:8" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A3" s="2" t="s">
         <v>14</v>
       </c>
@@ -2429,7 +2763,7 @@
       </c>
       <c r="C3" s="2"/>
     </row>
-    <row r="4" spans="1:8" ht="15.75" customHeight="1">
+    <row r="4" spans="1:8" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A4" s="4" t="s">
         <v>15</v>
       </c>
@@ -2438,7 +2772,7 @@
       </c>
       <c r="C4" s="4"/>
     </row>
-    <row r="5" spans="1:8" ht="15.75" customHeight="1">
+    <row r="5" spans="1:8" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A5" s="2" t="s">
         <v>16</v>
       </c>
@@ -2447,7 +2781,7 @@
       </c>
       <c r="C5" s="2"/>
     </row>
-    <row r="6" spans="1:8" ht="15.75" customHeight="1">
+    <row r="6" spans="1:8" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A6" s="4" t="s">
         <v>17</v>
       </c>
@@ -2456,7 +2790,7 @@
       </c>
       <c r="C6" s="4"/>
     </row>
-    <row r="7" spans="1:8" ht="15.75" customHeight="1">
+    <row r="7" spans="1:8" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A7" s="2" t="s">
         <v>18</v>
       </c>
@@ -2465,7 +2799,7 @@
       </c>
       <c r="C7" s="2"/>
     </row>
-    <row r="8" spans="1:8" ht="15.75" customHeight="1">
+    <row r="8" spans="1:8" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A8" s="4" t="s">
         <v>19</v>
       </c>
@@ -2476,7 +2810,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="9" spans="1:8" ht="15.75" customHeight="1">
+    <row r="9" spans="1:8" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A9" s="2" t="s">
         <v>21</v>
       </c>
@@ -2506,7 +2840,7 @@
     <tabColor rgb="FFE87722"/>
   </sheetPr>
   <dimension ref="A1:H9"/>
-  <sheetFormatPr defaultColWidth="8.7109375" defaultRowHeight="15"/>
+  <sheetFormatPr defaultColWidth="8.7109375" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="32" customWidth="1"/>
     <col min="2" max="2" width="22" customWidth="1"/>
@@ -2514,19 +2848,19 @@
     <col min="4" max="4" width="40" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:8" ht="21.75" customHeight="1">
-      <c r="A1" s="37" t="s">
+    <row r="1" spans="1:8" ht="21.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A1" s="43" t="s">
         <v>23</v>
       </c>
-      <c r="B1" s="37"/>
-      <c r="C1" s="37"/>
-      <c r="D1" s="37"/>
-      <c r="E1" s="37"/>
-      <c r="F1" s="37"/>
-      <c r="G1" s="37"/>
-      <c r="H1" s="37"/>
-    </row>
-    <row r="2" spans="1:8" ht="18" customHeight="1">
+      <c r="B1" s="43"/>
+      <c r="C1" s="43"/>
+      <c r="D1" s="43"/>
+      <c r="E1" s="43"/>
+      <c r="F1" s="43"/>
+      <c r="G1" s="43"/>
+      <c r="H1" s="43"/>
+    </row>
+    <row r="2" spans="1:8" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A2" s="1" t="s">
         <v>1</v>
       </c>
@@ -2540,7 +2874,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="3" spans="1:8" ht="15.75" customHeight="1">
+    <row r="3" spans="1:8" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A3" s="2" t="s">
         <v>26</v>
       </c>
@@ -2550,7 +2884,7 @@
       <c r="C3" s="2"/>
       <c r="D3" s="2"/>
     </row>
-    <row r="4" spans="1:8" ht="15.75" customHeight="1">
+    <row r="4" spans="1:8" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A4" s="4" t="s">
         <v>27</v>
       </c>
@@ -2560,7 +2894,7 @@
       <c r="C4" s="4"/>
       <c r="D4" s="4"/>
     </row>
-    <row r="5" spans="1:8" ht="15.75" customHeight="1">
+    <row r="5" spans="1:8" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A5" s="2" t="s">
         <v>28</v>
       </c>
@@ -2570,7 +2904,7 @@
       <c r="C5" s="2"/>
       <c r="D5" s="2"/>
     </row>
-    <row r="6" spans="1:8" ht="15.75" customHeight="1">
+    <row r="6" spans="1:8" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A6" s="4" t="s">
         <v>29</v>
       </c>
@@ -2580,7 +2914,7 @@
       <c r="C6" s="4"/>
       <c r="D6" s="4"/>
     </row>
-    <row r="7" spans="1:8" ht="15.75" customHeight="1">
+    <row r="7" spans="1:8" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A7" s="2" t="s">
         <v>30</v>
       </c>
@@ -2592,7 +2926,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="8" spans="1:8" ht="15.75" customHeight="1">
+    <row r="8" spans="1:8" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A8" s="4" t="s">
         <v>32</v>
       </c>
@@ -2602,7 +2936,7 @@
       <c r="C8" s="4"/>
       <c r="D8" s="4"/>
     </row>
-    <row r="9" spans="1:8" ht="15.75" customHeight="1">
+    <row r="9" spans="1:8" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A9" s="2" t="s">
         <v>33</v>
       </c>
@@ -2635,7 +2969,7 @@
     <tabColor rgb="FFE87722"/>
   </sheetPr>
   <dimension ref="A1:H10"/>
-  <sheetFormatPr defaultColWidth="8.7109375" defaultRowHeight="15"/>
+  <sheetFormatPr defaultColWidth="8.7109375" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="32" customWidth="1"/>
     <col min="2" max="2" width="22" customWidth="1"/>
@@ -2643,19 +2977,19 @@
     <col min="4" max="4" width="40" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:8" ht="21.75" customHeight="1">
-      <c r="A1" s="37" t="s">
+    <row r="1" spans="1:8" ht="21.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A1" s="43" t="s">
         <v>35</v>
       </c>
-      <c r="B1" s="37"/>
-      <c r="C1" s="37"/>
-      <c r="D1" s="37"/>
-      <c r="E1" s="37"/>
-      <c r="F1" s="37"/>
-      <c r="G1" s="37"/>
-      <c r="H1" s="37"/>
-    </row>
-    <row r="2" spans="1:8" ht="18" customHeight="1">
+      <c r="B1" s="43"/>
+      <c r="C1" s="43"/>
+      <c r="D1" s="43"/>
+      <c r="E1" s="43"/>
+      <c r="F1" s="43"/>
+      <c r="G1" s="43"/>
+      <c r="H1" s="43"/>
+    </row>
+    <row r="2" spans="1:8" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A2" s="1" t="s">
         <v>1</v>
       </c>
@@ -2669,7 +3003,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="3" spans="1:8" ht="15.75" customHeight="1">
+    <row r="3" spans="1:8" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A3" s="2" t="s">
         <v>36</v>
       </c>
@@ -2681,7 +3015,7 @@
         <v>37</v>
       </c>
     </row>
-    <row r="4" spans="1:8" ht="15.75" customHeight="1">
+    <row r="4" spans="1:8" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A4" s="4" t="s">
         <v>38</v>
       </c>
@@ -2693,7 +3027,7 @@
         <v>40</v>
       </c>
     </row>
-    <row r="5" spans="1:8" ht="15.75" customHeight="1">
+    <row r="5" spans="1:8" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A5" s="4" t="s">
         <v>41</v>
       </c>
@@ -2703,7 +3037,7 @@
       <c r="C5" s="21"/>
       <c r="D5" s="4"/>
     </row>
-    <row r="6" spans="1:8" ht="15.75" customHeight="1">
+    <row r="6" spans="1:8" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A6" s="2" t="s">
         <v>42</v>
       </c>
@@ -2715,7 +3049,7 @@
         <v>43</v>
       </c>
     </row>
-    <row r="7" spans="1:8" ht="15.75" customHeight="1">
+    <row r="7" spans="1:8" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A7" s="4" t="s">
         <v>32</v>
       </c>
@@ -2727,7 +3061,7 @@
         <v>37</v>
       </c>
     </row>
-    <row r="8" spans="1:8" ht="15.75" customHeight="1">
+    <row r="8" spans="1:8" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A8" s="2" t="s">
         <v>33</v>
       </c>
@@ -2739,7 +3073,7 @@
         <v>37</v>
       </c>
     </row>
-    <row r="9" spans="1:8" ht="15.75" customHeight="1">
+    <row r="9" spans="1:8" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A9" s="4" t="s">
         <v>44</v>
       </c>
@@ -2752,7 +3086,7 @@
         <v>45</v>
       </c>
     </row>
-    <row r="10" spans="1:8" ht="15.75" customHeight="1">
+    <row r="10" spans="1:8" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A10" s="2" t="s">
         <v>46</v>
       </c>
@@ -2782,7 +3116,7 @@
     <tabColor rgb="FFE87722"/>
   </sheetPr>
   <dimension ref="A1:H16"/>
-  <sheetFormatPr defaultColWidth="8.7109375" defaultRowHeight="15"/>
+  <sheetFormatPr defaultColWidth="8.7109375" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="32" customWidth="1"/>
     <col min="2" max="2" width="22" customWidth="1"/>
@@ -2791,19 +3125,19 @@
     <col min="5" max="5" width="35" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:8" ht="21.75" customHeight="1">
-      <c r="A1" s="37" t="s">
+    <row r="1" spans="1:8" ht="21.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A1" s="43" t="s">
         <v>49</v>
       </c>
-      <c r="B1" s="37"/>
-      <c r="C1" s="37"/>
-      <c r="D1" s="37"/>
-      <c r="E1" s="37"/>
-      <c r="F1" s="37"/>
-      <c r="G1" s="37"/>
-      <c r="H1" s="37"/>
-    </row>
-    <row r="2" spans="1:8" ht="18" customHeight="1">
+      <c r="B1" s="43"/>
+      <c r="C1" s="43"/>
+      <c r="D1" s="43"/>
+      <c r="E1" s="43"/>
+      <c r="F1" s="43"/>
+      <c r="G1" s="43"/>
+      <c r="H1" s="43"/>
+    </row>
+    <row r="2" spans="1:8" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A2" s="1" t="s">
         <v>1</v>
       </c>
@@ -2820,7 +3154,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="3" spans="1:8" ht="15.75" customHeight="1">
+    <row r="3" spans="1:8" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A3" s="2" t="s">
         <v>52</v>
       </c>
@@ -2837,7 +3171,7 @@
       <c r="E3" s="2"/>
       <c r="G3" s="24"/>
     </row>
-    <row r="4" spans="1:8" ht="15.75" customHeight="1">
+    <row r="4" spans="1:8" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A4" s="4" t="s">
         <v>54</v>
       </c>
@@ -2853,7 +3187,7 @@
       </c>
       <c r="E4" s="4"/>
     </row>
-    <row r="5" spans="1:8" ht="15.75" customHeight="1">
+    <row r="5" spans="1:8" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A5" s="2" t="s">
         <v>56</v>
       </c>
@@ -2869,7 +3203,7 @@
       </c>
       <c r="E5" s="2"/>
     </row>
-    <row r="6" spans="1:8" ht="15.75" customHeight="1">
+    <row r="6" spans="1:8" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A6" s="4" t="s">
         <v>57</v>
       </c>
@@ -2882,7 +3216,7 @@
       </c>
       <c r="E6" s="4"/>
     </row>
-    <row r="7" spans="1:8" ht="15.75" customHeight="1">
+    <row r="7" spans="1:8" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A7" s="2" t="s">
         <v>59</v>
       </c>
@@ -2898,7 +3232,7 @@
       </c>
       <c r="E7" s="2"/>
     </row>
-    <row r="8" spans="1:8" ht="28.5" customHeight="1">
+    <row r="8" spans="1:8" ht="28.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A8" s="4" t="s">
         <v>60</v>
       </c>
@@ -2914,16 +3248,16 @@
         <v>61</v>
       </c>
     </row>
-    <row r="10" spans="1:8">
-      <c r="B10" s="39"/>
-    </row>
-    <row r="14" spans="1:8">
+    <row r="10" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="B10" s="37"/>
+    </row>
+    <row r="14" spans="1:8" x14ac:dyDescent="0.25">
       <c r="E14" s="36"/>
     </row>
-    <row r="15" spans="1:8">
+    <row r="15" spans="1:8" x14ac:dyDescent="0.25">
       <c r="E15" s="36"/>
     </row>
-    <row r="16" spans="1:8">
+    <row r="16" spans="1:8" x14ac:dyDescent="0.25">
       <c r="E16" s="36"/>
     </row>
   </sheetData>
@@ -2944,7 +3278,7 @@
     <tabColor rgb="FFE87722"/>
   </sheetPr>
   <dimension ref="A1:H9"/>
-  <sheetFormatPr defaultColWidth="8.7109375" defaultRowHeight="15"/>
+  <sheetFormatPr defaultColWidth="8.7109375" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="30" customWidth="1"/>
     <col min="2" max="2" width="20" customWidth="1"/>
@@ -2952,19 +3286,19 @@
     <col min="4" max="4" width="40" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:8" ht="21.75" customHeight="1">
-      <c r="A1" s="37" t="s">
+    <row r="1" spans="1:8" ht="21.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A1" s="43" t="s">
         <v>62</v>
       </c>
-      <c r="B1" s="37"/>
-      <c r="C1" s="37"/>
-      <c r="D1" s="37"/>
-      <c r="E1" s="37"/>
-      <c r="F1" s="37"/>
-      <c r="G1" s="37"/>
-      <c r="H1" s="37"/>
-    </row>
-    <row r="2" spans="1:8" ht="18" customHeight="1">
+      <c r="B1" s="43"/>
+      <c r="C1" s="43"/>
+      <c r="D1" s="43"/>
+      <c r="E1" s="43"/>
+      <c r="F1" s="43"/>
+      <c r="G1" s="43"/>
+      <c r="H1" s="43"/>
+    </row>
+    <row r="2" spans="1:8" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A2" s="1" t="s">
         <v>1</v>
       </c>
@@ -2978,11 +3312,11 @@
         <v>13</v>
       </c>
     </row>
-    <row r="3" spans="1:8" ht="27" customHeight="1">
+    <row r="3" spans="1:8" ht="27" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A3" s="2" t="s">
         <v>65</v>
       </c>
-      <c r="B3" s="40">
+      <c r="B3" s="38">
         <v>14.58</v>
       </c>
       <c r="C3" s="2"/>
@@ -2990,21 +3324,22 @@
         <v>66</v>
       </c>
     </row>
-    <row r="4" spans="1:8" ht="46.5" customHeight="1">
+    <row r="4" spans="1:8" ht="46.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A4" s="4" t="s">
         <v>67</v>
       </c>
-      <c r="B4" s="3" t="s">
-        <v>68</v>
+      <c r="B4" s="3" t="str">
+        <f>IF(B3&gt;0,"Inflow exceeds outflow · positive position","Outflow exceeds inflow · negative position")</f>
+        <v>Inflow exceeds outflow · positive position</v>
       </c>
       <c r="C4" s="4"/>
       <c r="D4" s="4" t="s">
+        <v>68</v>
+      </c>
+    </row>
+    <row r="5" spans="1:8" ht="27" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A5" s="2" t="s">
         <v>69</v>
-      </c>
-    </row>
-    <row r="5" spans="1:8" ht="27" customHeight="1">
-      <c r="A5" s="2" t="s">
-        <v>70</v>
       </c>
       <c r="B5" s="3">
         <v>152.6</v>
@@ -3014,12 +3349,12 @@
         <v>110.26011560693641</v>
       </c>
       <c r="D5" s="2" t="s">
+        <v>70</v>
+      </c>
+    </row>
+    <row r="6" spans="1:8" ht="27" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A6" s="4" t="s">
         <v>71</v>
-      </c>
-    </row>
-    <row r="6" spans="1:8" ht="27" customHeight="1">
-      <c r="A6" s="4" t="s">
-        <v>72</v>
       </c>
       <c r="B6" s="3">
         <v>138.4</v>
@@ -3028,11 +3363,11 @@
         <v>39</v>
       </c>
       <c r="D6" s="4" t="s">
-        <v>73</v>
-      </c>
-    </row>
-    <row r="9" spans="1:8">
-      <c r="B9" s="39"/>
+        <v>72</v>
+      </c>
+    </row>
+    <row r="9" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="B9" s="37"/>
     </row>
   </sheetData>
   <mergeCells count="1">
@@ -3052,7 +3387,7 @@
     <tabColor rgb="FFE87722"/>
   </sheetPr>
   <dimension ref="A1:H21"/>
-  <sheetFormatPr defaultColWidth="8.7109375" defaultRowHeight="15"/>
+  <sheetFormatPr defaultColWidth="8.7109375" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="28" customWidth="1"/>
     <col min="2" max="2" width="16" customWidth="1"/>
@@ -3060,27 +3395,27 @@
     <col min="4" max="4" width="10" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:8" ht="21.75" customHeight="1">
-      <c r="A1" s="37" t="s">
+    <row r="1" spans="1:8" ht="21.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A1" s="43" t="s">
+        <v>73</v>
+      </c>
+      <c r="B1" s="43"/>
+      <c r="C1" s="43"/>
+      <c r="D1" s="43"/>
+      <c r="E1" s="43"/>
+      <c r="F1" s="43"/>
+      <c r="G1" s="43"/>
+      <c r="H1" s="43"/>
+    </row>
+    <row r="2" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A2" s="44" t="s">
         <v>74</v>
       </c>
-      <c r="B1" s="37"/>
-      <c r="C1" s="37"/>
-      <c r="D1" s="37"/>
-      <c r="E1" s="37"/>
-      <c r="F1" s="37"/>
-      <c r="G1" s="37"/>
-      <c r="H1" s="37"/>
-    </row>
-    <row r="2" spans="1:8" ht="15" customHeight="1">
-      <c r="A2" s="38" t="s">
-        <v>75</v>
-      </c>
-      <c r="B2" s="38"/>
-      <c r="C2" s="38"/>
-      <c r="D2" s="38"/>
-    </row>
-    <row r="3" spans="1:8" ht="18" customHeight="1">
+      <c r="B2" s="44"/>
+      <c r="C2" s="44"/>
+      <c r="D2" s="44"/>
+    </row>
+    <row r="3" spans="1:8" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A3" s="1" t="s">
         <v>1</v>
       </c>
@@ -3092,197 +3427,197 @@
       </c>
       <c r="D3" s="1"/>
     </row>
-    <row r="4" spans="1:8" ht="15.75" customHeight="1">
+    <row r="4" spans="1:8" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A4" s="4" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="B4" s="3">
         <f>B5+B6</f>
         <v>712</v>
       </c>
       <c r="C4" s="4" t="s">
+        <v>76</v>
+      </c>
+      <c r="D4" s="4"/>
+    </row>
+    <row r="5" spans="1:8" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A5" s="2" t="s">
         <v>77</v>
-      </c>
-      <c r="D4" s="4"/>
-    </row>
-    <row r="5" spans="1:8" ht="15.75" customHeight="1">
-      <c r="A5" s="2" t="s">
-        <v>78</v>
       </c>
       <c r="B5" s="3">
         <v>599</v>
       </c>
       <c r="C5" s="2" t="s">
+        <v>78</v>
+      </c>
+      <c r="D5" s="2"/>
+    </row>
+    <row r="6" spans="1:8" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A6" s="4" t="s">
         <v>79</v>
-      </c>
-      <c r="D5" s="2"/>
-    </row>
-    <row r="6" spans="1:8" ht="15.75" customHeight="1">
-      <c r="A6" s="4" t="s">
-        <v>80</v>
       </c>
       <c r="B6" s="3">
         <v>113</v>
       </c>
       <c r="C6" s="4" t="s">
+        <v>80</v>
+      </c>
+      <c r="D6" s="4"/>
+    </row>
+    <row r="7" spans="1:8" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A7" s="2" t="s">
         <v>81</v>
-      </c>
-      <c r="D6" s="4"/>
-    </row>
-    <row r="7" spans="1:8" ht="15.75" customHeight="1">
-      <c r="A7" s="2" t="s">
-        <v>82</v>
       </c>
       <c r="B7" s="25">
         <f>B5/B4</f>
         <v>0.8412921348314607</v>
       </c>
       <c r="C7" s="2" t="s">
+        <v>82</v>
+      </c>
+      <c r="D7" s="2"/>
+    </row>
+    <row r="8" spans="1:8" ht="6" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="9" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A9" s="44" t="s">
         <v>83</v>
       </c>
-      <c r="D7" s="2"/>
-    </row>
-    <row r="8" spans="1:8" ht="6" customHeight="1"/>
-    <row r="9" spans="1:8" ht="15" customHeight="1">
-      <c r="A9" s="38" t="s">
+      <c r="B9" s="44"/>
+      <c r="C9" s="44"/>
+      <c r="D9" s="44"/>
+    </row>
+    <row r="10" spans="1:8" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A10" s="1" t="s">
         <v>84</v>
       </c>
-      <c r="B9" s="38"/>
-      <c r="C9" s="38"/>
-      <c r="D9" s="38"/>
-    </row>
-    <row r="10" spans="1:8" ht="18" customHeight="1">
-      <c r="A10" s="1" t="s">
+      <c r="B10" s="1" t="s">
         <v>85</v>
-      </c>
-      <c r="B10" s="1" t="s">
-        <v>86</v>
       </c>
       <c r="C10" s="1" t="s">
         <v>13</v>
       </c>
       <c r="D10" s="1"/>
     </row>
-    <row r="11" spans="1:8" ht="15.75" customHeight="1">
+    <row r="11" spans="1:8" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A11" s="2" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="B11" s="3">
         <v>388</v>
       </c>
       <c r="C11" s="2" t="s">
+        <v>87</v>
+      </c>
+      <c r="D11" s="2"/>
+    </row>
+    <row r="12" spans="1:8" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A12" s="4" t="s">
         <v>88</v>
-      </c>
-      <c r="D11" s="2"/>
-    </row>
-    <row r="12" spans="1:8" ht="15.75" customHeight="1">
-      <c r="A12" s="4" t="s">
-        <v>89</v>
       </c>
       <c r="B12" s="3">
         <v>211</v>
       </c>
       <c r="C12" s="4" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="D12" s="4"/>
     </row>
-    <row r="13" spans="1:8" ht="6" customHeight="1"/>
-    <row r="14" spans="1:8" ht="15" customHeight="1">
-      <c r="A14" s="38" t="s">
+    <row r="13" spans="1:8" ht="6" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="14" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A14" s="44" t="s">
+        <v>89</v>
+      </c>
+      <c r="B14" s="44"/>
+      <c r="C14" s="44"/>
+      <c r="D14" s="44"/>
+    </row>
+    <row r="15" spans="1:8" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A15" s="1" t="s">
         <v>90</v>
-      </c>
-      <c r="B14" s="38"/>
-      <c r="C14" s="38"/>
-      <c r="D14" s="38"/>
-    </row>
-    <row r="15" spans="1:8" ht="18" customHeight="1">
-      <c r="A15" s="1" t="s">
-        <v>91</v>
       </c>
       <c r="B15" s="1" t="s">
         <v>2</v>
       </c>
       <c r="C15" s="1" t="s">
+        <v>91</v>
+      </c>
+      <c r="D15" s="1"/>
+    </row>
+    <row r="16" spans="1:8" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A16" s="4" t="s">
         <v>92</v>
-      </c>
-      <c r="D15" s="1"/>
-    </row>
-    <row r="16" spans="1:8" ht="15.75" customHeight="1">
-      <c r="A16" s="4" t="s">
-        <v>93</v>
       </c>
       <c r="B16" s="3">
         <f>B4/B5*100</f>
         <v>118.86477462437395</v>
       </c>
       <c r="C16" s="4" t="s">
+        <v>93</v>
+      </c>
+      <c r="D16" s="4"/>
+    </row>
+    <row r="17" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A17" s="2" t="s">
         <v>94</v>
-      </c>
-      <c r="D16" s="4"/>
-    </row>
-    <row r="17" spans="1:4" ht="15.75" customHeight="1">
-      <c r="A17" s="2" t="s">
-        <v>95</v>
       </c>
       <c r="B17" s="3">
         <f>B6/B5*100</f>
         <v>18.864774624373958</v>
       </c>
       <c r="C17" s="2" t="s">
+        <v>95</v>
+      </c>
+      <c r="D17" s="2"/>
+    </row>
+    <row r="18" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A18" s="4" t="s">
         <v>96</v>
-      </c>
-      <c r="D17" s="2"/>
-    </row>
-    <row r="18" spans="1:4" ht="15.75" customHeight="1">
-      <c r="A18" s="4" t="s">
-        <v>97</v>
       </c>
       <c r="B18" s="3">
         <f>B16</f>
         <v>118.86477462437395</v>
       </c>
       <c r="C18" s="4" t="s">
+        <v>97</v>
+      </c>
+      <c r="D18" s="4"/>
+    </row>
+    <row r="19" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A19" s="2" t="s">
         <v>98</v>
-      </c>
-      <c r="D18" s="4"/>
-    </row>
-    <row r="19" spans="1:4" ht="15.75" customHeight="1">
-      <c r="A19" s="2" t="s">
-        <v>99</v>
       </c>
       <c r="B19" s="3">
         <f>100-B16</f>
         <v>-18.86477462437395</v>
       </c>
       <c r="C19" s="2" t="s">
+        <v>99</v>
+      </c>
+      <c r="D19" s="2"/>
+    </row>
+    <row r="20" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A20" s="4" t="s">
         <v>100</v>
-      </c>
-      <c r="D19" s="2"/>
-    </row>
-    <row r="20" spans="1:4" ht="15.75" customHeight="1">
-      <c r="A20" s="4" t="s">
-        <v>101</v>
       </c>
       <c r="B20" s="3">
         <f>B17</f>
         <v>18.864774624373958</v>
       </c>
       <c r="C20" s="4" t="s">
+        <v>101</v>
+      </c>
+      <c r="D20" s="4"/>
+    </row>
+    <row r="21" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A21" s="2" t="s">
         <v>102</v>
-      </c>
-      <c r="D20" s="4"/>
-    </row>
-    <row r="21" spans="1:4" ht="15.75" customHeight="1">
-      <c r="A21" s="2" t="s">
-        <v>103</v>
       </c>
       <c r="B21" s="3">
         <f>100-B17</f>
         <v>81.13522537562605</v>
       </c>
       <c r="C21" s="2" t="s">
-        <v>104</v>
+        <v>103</v>
       </c>
       <c r="D21" s="2"/>
     </row>
@@ -3307,7 +3642,7 @@
     <tabColor rgb="FFE87722"/>
   </sheetPr>
   <dimension ref="A1:H8"/>
-  <sheetFormatPr defaultColWidth="8.7109375" defaultRowHeight="15"/>
+  <sheetFormatPr defaultColWidth="8.7109375" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="28" customWidth="1"/>
     <col min="2" max="4" width="10" customWidth="1"/>
@@ -3315,41 +3650,41 @@
     <col min="6" max="6" width="35" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:8" ht="21.75" customHeight="1">
-      <c r="A1" s="37" t="s">
+    <row r="1" spans="1:8" ht="21.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A1" s="43" t="s">
+        <v>104</v>
+      </c>
+      <c r="B1" s="43"/>
+      <c r="C1" s="43"/>
+      <c r="D1" s="43"/>
+      <c r="E1" s="43"/>
+      <c r="F1" s="43"/>
+      <c r="G1" s="43"/>
+      <c r="H1" s="43"/>
+    </row>
+    <row r="2" spans="1:8" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A2" s="1" t="s">
         <v>105</v>
       </c>
-      <c r="B1" s="37"/>
-      <c r="C1" s="37"/>
-      <c r="D1" s="37"/>
-      <c r="E1" s="37"/>
-      <c r="F1" s="37"/>
-      <c r="G1" s="37"/>
-      <c r="H1" s="37"/>
-    </row>
-    <row r="2" spans="1:8" ht="18" customHeight="1">
-      <c r="A2" s="1" t="s">
+      <c r="B2" s="1" t="s">
         <v>106</v>
       </c>
-      <c r="B2" s="1" t="s">
+      <c r="C2" s="1" t="s">
         <v>107</v>
       </c>
-      <c r="C2" s="1" t="s">
+      <c r="D2" s="1" t="s">
         <v>108</v>
       </c>
-      <c r="D2" s="1" t="s">
+      <c r="E2" s="1" t="s">
         <v>109</v>
-      </c>
-      <c r="E2" s="1" t="s">
-        <v>110</v>
       </c>
       <c r="F2" s="1" t="s">
         <v>13</v>
       </c>
     </row>
-    <row r="3" spans="1:8" ht="15.75" customHeight="1">
+    <row r="3" spans="1:8" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A3" s="2" t="s">
-        <v>111</v>
+        <v>110</v>
       </c>
       <c r="B3" s="27">
         <v>93.23</v>
@@ -3362,15 +3697,15 @@
         <v>8.4500000000000028</v>
       </c>
       <c r="E3" s="2" t="s">
+        <v>111</v>
+      </c>
+      <c r="F3" s="2" t="s">
         <v>112</v>
       </c>
-      <c r="F3" s="2" t="s">
+    </row>
+    <row r="4" spans="1:8" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A4" s="4" t="s">
         <v>113</v>
-      </c>
-    </row>
-    <row r="4" spans="1:8" ht="15.75" customHeight="1">
-      <c r="A4" s="4" t="s">
-        <v>114</v>
       </c>
       <c r="B4" s="28">
         <v>100</v>
@@ -3383,15 +3718,15 @@
         <v>0.75</v>
       </c>
       <c r="E4" s="4" t="s">
+        <v>114</v>
+      </c>
+      <c r="F4" s="4" t="s">
         <v>115</v>
       </c>
-      <c r="F4" s="4" t="s">
+    </row>
+    <row r="5" spans="1:8" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A5" s="2" t="s">
         <v>116</v>
-      </c>
-    </row>
-    <row r="5" spans="1:8" ht="15.75" customHeight="1">
-      <c r="A5" s="2" t="s">
-        <v>117</v>
       </c>
       <c r="B5" s="27">
         <v>100</v>
@@ -3404,15 +3739,15 @@
         <v>4.3100000000000023</v>
       </c>
       <c r="E5" s="2" t="s">
+        <v>117</v>
+      </c>
+      <c r="F5" s="2" t="s">
         <v>118</v>
       </c>
-      <c r="F5" s="2" t="s">
+    </row>
+    <row r="6" spans="1:8" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A6" s="4" t="s">
         <v>119</v>
-      </c>
-    </row>
-    <row r="6" spans="1:8" ht="15.75" customHeight="1">
-      <c r="A6" s="4" t="s">
-        <v>120</v>
       </c>
       <c r="B6" s="28">
         <v>96.41</v>
@@ -3425,15 +3760,15 @@
         <v>4.8799999999999955</v>
       </c>
       <c r="E6" s="4" t="s">
+        <v>111</v>
+      </c>
+      <c r="F6" s="4" t="s">
         <v>112</v>
       </c>
-      <c r="F6" s="4" t="s">
-        <v>113</v>
-      </c>
-    </row>
-    <row r="7" spans="1:8" ht="15.75" customHeight="1">
+    </row>
+    <row r="7" spans="1:8" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A7" s="2" t="s">
-        <v>121</v>
+        <v>120</v>
       </c>
       <c r="B7" s="27">
         <v>100</v>
@@ -3446,15 +3781,15 @@
         <v>6.6800000000000068</v>
       </c>
       <c r="E7" s="2" t="s">
+        <v>117</v>
+      </c>
+      <c r="F7" s="2" t="s">
         <v>118</v>
       </c>
-      <c r="F7" s="2" t="s">
-        <v>119</v>
-      </c>
-    </row>
-    <row r="8" spans="1:8" ht="15.75" customHeight="1">
+    </row>
+    <row r="8" spans="1:8" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A8" s="4" t="s">
-        <v>122</v>
+        <v>121</v>
       </c>
       <c r="B8" s="28">
         <v>71.23</v>
@@ -3467,10 +3802,10 @@
         <v>46.410000000000004</v>
       </c>
       <c r="E8" s="4" t="s">
-        <v>112</v>
+        <v>111</v>
       </c>
       <c r="F8" s="4" t="s">
-        <v>123</v>
+        <v>122</v>
       </c>
     </row>
   </sheetData>
@@ -3491,7 +3826,7 @@
     <tabColor rgb="FFE87722"/>
   </sheetPr>
   <dimension ref="A1:H8"/>
-  <sheetFormatPr defaultColWidth="8.7109375" defaultRowHeight="15"/>
+  <sheetFormatPr defaultColWidth="8.7109375" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="18" customWidth="1"/>
     <col min="2" max="4" width="10" customWidth="1"/>
@@ -3499,41 +3834,41 @@
     <col min="6" max="6" width="40" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:8" ht="21.75" customHeight="1">
-      <c r="A1" s="37" t="s">
+    <row r="1" spans="1:8" ht="21.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A1" s="43" t="s">
+        <v>123</v>
+      </c>
+      <c r="B1" s="43"/>
+      <c r="C1" s="43"/>
+      <c r="D1" s="43"/>
+      <c r="E1" s="43"/>
+      <c r="F1" s="43"/>
+      <c r="G1" s="43"/>
+      <c r="H1" s="43"/>
+    </row>
+    <row r="2" spans="1:8" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A2" s="1" t="s">
         <v>124</v>
       </c>
-      <c r="B1" s="37"/>
-      <c r="C1" s="37"/>
-      <c r="D1" s="37"/>
-      <c r="E1" s="37"/>
-      <c r="F1" s="37"/>
-      <c r="G1" s="37"/>
-      <c r="H1" s="37"/>
-    </row>
-    <row r="2" spans="1:8" ht="18" customHeight="1">
-      <c r="A2" s="1" t="s">
-        <v>125</v>
-      </c>
       <c r="B2" s="1" t="s">
+        <v>106</v>
+      </c>
+      <c r="C2" s="1" t="s">
         <v>107</v>
       </c>
-      <c r="C2" s="1" t="s">
+      <c r="D2" s="1" t="s">
         <v>108</v>
       </c>
-      <c r="D2" s="1" t="s">
+      <c r="E2" s="1" t="s">
         <v>109</v>
-      </c>
-      <c r="E2" s="1" t="s">
-        <v>110</v>
       </c>
       <c r="F2" s="1" t="s">
         <v>13</v>
       </c>
     </row>
-    <row r="3" spans="1:8" ht="15.75" customHeight="1">
+    <row r="3" spans="1:8" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A3" s="2" t="s">
-        <v>126</v>
+        <v>125</v>
       </c>
       <c r="B3" s="2">
         <v>93.23</v>
@@ -3546,13 +3881,13 @@
         <v>9.0100000000000051</v>
       </c>
       <c r="E3" s="2" t="s">
-        <v>112</v>
+        <v>111</v>
       </c>
       <c r="F3" s="2"/>
     </row>
-    <row r="4" spans="1:8" ht="15.75" customHeight="1">
+    <row r="4" spans="1:8" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A4" s="4" t="s">
-        <v>127</v>
+        <v>126</v>
       </c>
       <c r="B4" s="4">
         <v>92.64</v>
@@ -3565,13 +3900,13 @@
         <v>7.75</v>
       </c>
       <c r="E4" s="4" t="s">
-        <v>118</v>
+        <v>117</v>
       </c>
       <c r="F4" s="4"/>
     </row>
-    <row r="5" spans="1:8" ht="15.75" customHeight="1">
+    <row r="5" spans="1:8" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A5" s="2" t="s">
-        <v>128</v>
+        <v>127</v>
       </c>
       <c r="B5" s="2">
         <v>91.73</v>
@@ -3584,15 +3919,15 @@
         <v>9.8400000000000034</v>
       </c>
       <c r="E5" s="2" t="s">
-        <v>112</v>
+        <v>111</v>
       </c>
       <c r="F5" s="2" t="s">
+        <v>128</v>
+      </c>
+    </row>
+    <row r="6" spans="1:8" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A6" s="4" t="s">
         <v>129</v>
-      </c>
-    </row>
-    <row r="6" spans="1:8" ht="15.75" customHeight="1">
-      <c r="A6" s="4" t="s">
-        <v>130</v>
       </c>
       <c r="B6" s="4">
         <v>95.99</v>
@@ -3605,13 +3940,13 @@
         <v>11.11999999999999</v>
       </c>
       <c r="E6" s="4" t="s">
-        <v>112</v>
+        <v>111</v>
       </c>
       <c r="F6" s="4"/>
     </row>
-    <row r="7" spans="1:8" ht="15.75" customHeight="1">
+    <row r="7" spans="1:8" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A7" s="2" t="s">
-        <v>131</v>
+        <v>130</v>
       </c>
       <c r="B7" s="2">
         <v>95.79</v>
@@ -3624,15 +3959,15 @@
         <v>4.5200000000000102</v>
       </c>
       <c r="E7" s="2" t="s">
-        <v>118</v>
+        <v>117</v>
       </c>
       <c r="F7" s="2" t="s">
+        <v>131</v>
+      </c>
+    </row>
+    <row r="8" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A8" s="7" t="s">
         <v>132</v>
-      </c>
-    </row>
-    <row r="8" spans="1:8" ht="15" customHeight="1">
-      <c r="A8" s="7" t="s">
-        <v>133</v>
       </c>
       <c r="B8" s="7"/>
       <c r="C8" s="7"/>

--- a/Dashboard_Data.xlsx
+++ b/Dashboard_Data.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://alfanargroup-my.sharepoint.com/personal/ahmed_abdelzaher_alfanar_com/Documents/SDCC Dashboard/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="143" documentId="8_{08402470-AB39-479E-9F56-A762705072E3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{C8FD466D-7510-48FC-8F0E-8B6E74B27236}"/>
+  <xr:revisionPtr revIDLastSave="145" documentId="8_{08402470-AB39-479E-9F56-A762705072E3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{54652C20-332C-41D5-A479-78F6DFB84EB6}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" tabRatio="500" firstSheet="5" activeTab="5" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" tabRatio="500" firstSheet="5" activeTab="10" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Header" sheetId="1" r:id="rId1"/>
@@ -51,7 +51,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="391" uniqueCount="233">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="392" uniqueCount="234">
   <si>
     <t>HEADER — Dashboard Title &amp; PM</t>
   </si>
@@ -751,6 +751,9 @@
   </si>
   <si>
     <t>Fire Alarm</t>
+  </si>
+  <si>
+    <t>Push SETRA to give a Confirmation date for Delivery and Installation Plan</t>
   </si>
 </sst>
 </file>
@@ -2087,7 +2090,9 @@
       <c r="D8" s="2" t="s">
         <v>226</v>
       </c>
-      <c r="E8" s="2"/>
+      <c r="E8" s="2" t="s">
+        <v>233</v>
+      </c>
       <c r="F8" s="10" t="s">
         <v>218</v>
       </c>

--- a/Dashboard_Data.xlsx
+++ b/Dashboard_Data.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://alfanargroup-my.sharepoint.com/personal/ahmed_abdelzaher_alfanar_com/Documents/SDCC Dashboard/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="145" documentId="8_{08402470-AB39-479E-9F56-A762705072E3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{54652C20-332C-41D5-A479-78F6DFB84EB6}"/>
+  <xr:revisionPtr revIDLastSave="147" documentId="8_{08402470-AB39-479E-9F56-A762705072E3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{05EE1967-3FE0-495E-8284-EE7BD15252EC}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" tabRatio="500" firstSheet="5" activeTab="10" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" tabRatio="500" firstSheet="1" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Header" sheetId="1" r:id="rId1"/>
@@ -1911,7 +1911,7 @@
         <v>156</v>
       </c>
       <c r="G30" s="29">
-        <v>46435</v>
+        <v>46442</v>
       </c>
       <c r="H30" s="9" t="s">
         <v>157</v>
@@ -2820,7 +2820,7 @@
         <v>21</v>
       </c>
       <c r="B9" s="16">
-        <v>46435</v>
+        <v>46442</v>
       </c>
       <c r="C9" s="2" t="s">
         <v>22</v>

--- a/Dashboard_Data.xlsx
+++ b/Dashboard_Data.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29929"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30215"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://alfanargroup-my.sharepoint.com/personal/ahmed_abdelzaher_alfanar_com/Documents/SDCC Dashboard/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="147" documentId="8_{08402470-AB39-479E-9F56-A762705072E3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{05EE1967-3FE0-495E-8284-EE7BD15252EC}"/>
+  <xr:revisionPtr revIDLastSave="149" documentId="8_{08402470-AB39-479E-9F56-A762705072E3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{76A02C64-34C4-46A9-A1A7-154C55A78CFF}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" tabRatio="500" firstSheet="1" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" tabRatio="500" firstSheet="1" activeTab="4" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Header" sheetId="1" r:id="rId1"/>
@@ -587,111 +587,27 @@
     <t>SE to expedite providing the confirmed recent traffic plan to start manufacturing materials of DWDM.</t>
   </si>
   <si>
-    <t>EQUIPMENT STATUS</t>
-  </si>
-  <si>
-    <t>Vendor</t>
-  </si>
-  <si>
-    <t>PO</t>
-  </si>
-  <si>
-    <t>GAFM</t>
-  </si>
-  <si>
-    <t>FAT</t>
-  </si>
-  <si>
-    <t>Delivery</t>
-  </si>
-  <si>
-    <t>Status</t>
-  </si>
-  <si>
-    <t>ADMS/DERMS Servers</t>
-  </si>
-  <si>
-    <t>CET</t>
-  </si>
-  <si>
-    <t>Issued</t>
-  </si>
-  <si>
-    <t>OK</t>
-  </si>
-  <si>
-    <t>CRAC / PACU Units</t>
-  </si>
-  <si>
-    <t>Zamil</t>
-  </si>
-  <si>
-    <t>FM-200 Cylinders</t>
-  </si>
-  <si>
-    <t>DDC Panels</t>
-  </si>
-  <si>
-    <t>Marine</t>
-  </si>
-  <si>
-    <t>AC/DC Panels</t>
-  </si>
-  <si>
-    <t>AES</t>
-  </si>
-  <si>
-    <t>Delayed</t>
-  </si>
-  <si>
-    <t>48 VDC System</t>
-  </si>
-  <si>
-    <t>Fire Pumps</t>
-  </si>
-  <si>
-    <t>Security System</t>
-  </si>
-  <si>
-    <t>ITC</t>
-  </si>
-  <si>
-    <t>N/A</t>
-  </si>
-  <si>
-    <t>FOOTER — Classification &amp; Branding</t>
-  </si>
-  <si>
-    <t>Classification</t>
-  </si>
-  <si>
-    <t>Public</t>
-  </si>
-  <si>
-    <t>Prepared Date</t>
-  </si>
-  <si>
-    <t>Department</t>
-  </si>
-  <si>
-    <t>Control Center</t>
-  </si>
-  <si>
-    <t>Brand Name</t>
-  </si>
-  <si>
-    <t>alfanar</t>
-  </si>
-  <si>
     <t>Delay in Telecom Rediness due to T&amp;C Delay from TNDT</t>
   </si>
   <si>
     <t>T&amp;C</t>
   </si>
   <si>
+    <t xml:space="preserve">SE to push TNDT to proceed in T&amp;C </t>
+  </si>
+  <si>
     <t>Delay in BMS Delivery</t>
   </si>
   <si>
+    <t>SETRA</t>
+  </si>
+  <si>
+    <t>Push SETRA to give a Confirmation date for Delivery and Installation Plan</t>
+  </si>
+  <si>
+    <t>medium</t>
+  </si>
+  <si>
     <t xml:space="preserve">Delay in Validation of SLD </t>
   </si>
   <si>
@@ -705,9 +621,6 @@
   </si>
   <si>
     <t>CET to mobilize Derms team ASAP</t>
-  </si>
-  <si>
-    <t>medium</t>
   </si>
   <si>
     <t>Low</t>
@@ -729,31 +642,118 @@
 CET to Expedite Avaialbility of Instructor Team</t>
   </si>
   <si>
-    <t xml:space="preserve">SE to push TNDT to proceed in T&amp;C </t>
-  </si>
-  <si>
-    <t>SETRA</t>
+    <t>EQUIPMENT STATUS</t>
+  </si>
+  <si>
+    <t>Vendor</t>
+  </si>
+  <si>
+    <t>PO</t>
+  </si>
+  <si>
+    <t>GAFM</t>
+  </si>
+  <si>
+    <t>FAT</t>
+  </si>
+  <si>
+    <t>Delivery</t>
+  </si>
+  <si>
+    <t>Status</t>
+  </si>
+  <si>
+    <t>ADMS/DERMS Servers</t>
+  </si>
+  <si>
+    <t>CET</t>
+  </si>
+  <si>
+    <t>Issued</t>
+  </si>
+  <si>
+    <t>Delayed</t>
+  </si>
+  <si>
+    <t>CRAC / PACU Units</t>
+  </si>
+  <si>
+    <t>Zamil</t>
+  </si>
+  <si>
+    <t>OK</t>
+  </si>
+  <si>
+    <t>FM-200 Cylinders</t>
+  </si>
+  <si>
+    <t>DDC Panels</t>
+  </si>
+  <si>
+    <t>Marine</t>
+  </si>
+  <si>
+    <t>Fire Alarm</t>
+  </si>
+  <si>
+    <t>AC/DC Panels</t>
+  </si>
+  <si>
+    <t>AES</t>
+  </si>
+  <si>
+    <t>48 VDC System</t>
+  </si>
+  <si>
+    <t>LAN/WAN</t>
+  </si>
+  <si>
+    <t>DWDM</t>
+  </si>
+  <si>
+    <t>Fire Pumps</t>
+  </si>
+  <si>
+    <t>Security System</t>
+  </si>
+  <si>
+    <t>ITC</t>
+  </si>
+  <si>
+    <t>N/A</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Low Current </t>
   </si>
   <si>
     <t>Degital Era</t>
   </si>
   <si>
-    <t>DWDM</t>
-  </si>
-  <si>
     <t>BMS Systems</t>
   </si>
   <si>
-    <t>LAN/WAN</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Low Current </t>
-  </si>
-  <si>
-    <t>Fire Alarm</t>
-  </si>
-  <si>
-    <t>Push SETRA to give a Confirmation date for Delivery and Installation Plan</t>
+    <t>FOOTER — Classification &amp; Branding</t>
+  </si>
+  <si>
+    <t>Classification</t>
+  </si>
+  <si>
+    <t>Public</t>
+  </si>
+  <si>
+    <t>Prepared Date</t>
+  </si>
+  <si>
+    <t>Department</t>
+  </si>
+  <si>
+    <t>Control Center</t>
+  </si>
+  <si>
+    <t>Brand Name</t>
+  </si>
+  <si>
+    <t>alfanar</t>
   </si>
 </sst>
 </file>
@@ -765,7 +765,7 @@
     <numFmt numFmtId="164" formatCode="[$-409]d\-mmm\-yy;@"/>
     <numFmt numFmtId="165" formatCode="0.0"/>
   </numFmts>
-  <fonts count="8" x14ac:knownFonts="1">
+  <fonts count="8">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -922,7 +922,7 @@
     <xf numFmtId="43" fontId="6" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="9" fontId="6" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="45">
+  <cellXfs count="46">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -1043,6 +1043,9 @@
     </xf>
     <xf numFmtId="0" fontId="2" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="9" fontId="3" fillId="4" borderId="1" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="3">
@@ -1314,13 +1317,13 @@
     <tabColor rgb="FFE87722"/>
   </sheetPr>
   <dimension ref="A1:H6"/>
-  <sheetFormatPr defaultColWidth="8.7109375" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultColWidth="8.7109375" defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="30" customWidth="1"/>
     <col min="2" max="2" width="40" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:8" ht="21.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:8" ht="21.75" customHeight="1">
       <c r="A1" s="43" t="s">
         <v>0</v>
       </c>
@@ -1332,7 +1335,7 @@
       <c r="G1" s="43"/>
       <c r="H1" s="43"/>
     </row>
-    <row r="2" spans="1:8" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:8" ht="18" customHeight="1">
       <c r="A2" s="1" t="s">
         <v>1</v>
       </c>
@@ -1340,7 +1343,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="3" spans="1:8" ht="25.5" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:8" ht="25.5">
       <c r="A3" s="2" t="s">
         <v>3</v>
       </c>
@@ -1348,7 +1351,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="4" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:8">
       <c r="A4" s="4" t="s">
         <v>5</v>
       </c>
@@ -1356,7 +1359,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="5" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:8">
       <c r="A5" s="2" t="s">
         <v>7</v>
       </c>
@@ -1364,7 +1367,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="6" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:8">
       <c r="A6" s="4" t="s">
         <v>9</v>
       </c>
@@ -1390,7 +1393,7 @@
     <tabColor rgb="FFE87722"/>
   </sheetPr>
   <dimension ref="A1:H30"/>
-  <sheetFormatPr defaultColWidth="8.7109375" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultColWidth="8.7109375" defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="12" customWidth="1"/>
     <col min="2" max="2" width="14" customWidth="1"/>
@@ -1402,7 +1405,7 @@
     <col min="8" max="8" width="30" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:8" ht="21.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:8" ht="21.75" customHeight="1">
       <c r="A1" s="43" t="s">
         <v>133</v>
       </c>
@@ -1414,7 +1417,7 @@
       <c r="G1" s="43"/>
       <c r="H1" s="43"/>
     </row>
-    <row r="2" spans="1:8" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:8" ht="18" customHeight="1">
       <c r="A2" s="1" t="s">
         <v>134</v>
       </c>
@@ -1440,7 +1443,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="3" spans="1:8" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:8" ht="15.75" customHeight="1">
       <c r="A3" s="32">
         <v>45620</v>
       </c>
@@ -1462,7 +1465,7 @@
         <v>145</v>
       </c>
     </row>
-    <row r="4" spans="1:8" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:8" ht="15.75" customHeight="1">
       <c r="A4" s="33">
         <v>45650</v>
       </c>
@@ -1478,7 +1481,7 @@
       <c r="G4" s="4"/>
       <c r="H4" s="4"/>
     </row>
-    <row r="5" spans="1:8" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:8" ht="15.75" customHeight="1">
       <c r="A5" s="32">
         <v>45681</v>
       </c>
@@ -1494,7 +1497,7 @@
       <c r="G5" s="2"/>
       <c r="H5" s="2"/>
     </row>
-    <row r="6" spans="1:8" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:8" ht="15.75" customHeight="1">
       <c r="A6" s="33">
         <v>45712</v>
       </c>
@@ -1510,7 +1513,7 @@
       <c r="G6" s="4"/>
       <c r="H6" s="4"/>
     </row>
-    <row r="7" spans="1:8" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:8" ht="15.75" customHeight="1">
       <c r="A7" s="32">
         <v>45740</v>
       </c>
@@ -1530,7 +1533,7 @@
       <c r="G7" s="2"/>
       <c r="H7" s="2"/>
     </row>
-    <row r="8" spans="1:8" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:8" ht="15.75" customHeight="1">
       <c r="A8" s="33">
         <v>45771</v>
       </c>
@@ -1552,7 +1555,7 @@
         <v>149</v>
       </c>
     </row>
-    <row r="9" spans="1:8" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:8" ht="15.75" customHeight="1">
       <c r="A9" s="32">
         <v>45801</v>
       </c>
@@ -1568,7 +1571,7 @@
       <c r="G9" s="2"/>
       <c r="H9" s="2"/>
     </row>
-    <row r="10" spans="1:8" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:8" ht="15.75" customHeight="1">
       <c r="A10" s="33">
         <v>45832</v>
       </c>
@@ -1588,7 +1591,7 @@
       <c r="G10" s="4"/>
       <c r="H10" s="4"/>
     </row>
-    <row r="11" spans="1:8" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:8" ht="15.75" customHeight="1">
       <c r="A11" s="32">
         <v>45862</v>
       </c>
@@ -1604,7 +1607,7 @@
       <c r="G11" s="2"/>
       <c r="H11" s="2"/>
     </row>
-    <row r="12" spans="1:8" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:8" ht="15.75" customHeight="1">
       <c r="A12" s="33">
         <v>45893</v>
       </c>
@@ -1620,7 +1623,7 @@
       <c r="G12" s="4"/>
       <c r="H12" s="4"/>
     </row>
-    <row r="13" spans="1:8" ht="25.5" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:8" ht="25.5">
       <c r="A13" s="32">
         <v>45924</v>
       </c>
@@ -1640,7 +1643,7 @@
       <c r="G13" s="2"/>
       <c r="H13" s="2"/>
     </row>
-    <row r="14" spans="1:8" ht="25.5" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:8" ht="25.5">
       <c r="A14" s="33">
         <v>45954</v>
       </c>
@@ -1660,7 +1663,7 @@
       <c r="G14" s="4"/>
       <c r="H14" s="4"/>
     </row>
-    <row r="15" spans="1:8" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:8" ht="15.75" customHeight="1">
       <c r="A15" s="32">
         <v>45985</v>
       </c>
@@ -1676,7 +1679,7 @@
       <c r="G15" s="2"/>
       <c r="H15" s="2"/>
     </row>
-    <row r="16" spans="1:8" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:8" ht="15.75" customHeight="1">
       <c r="A16" s="33">
         <v>46015</v>
       </c>
@@ -1696,7 +1699,7 @@
       <c r="G16" s="4"/>
       <c r="H16" s="4"/>
     </row>
-    <row r="17" spans="1:8" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:8" ht="15.75" customHeight="1">
       <c r="A17" s="32">
         <v>46046</v>
       </c>
@@ -1712,7 +1715,7 @@
       <c r="G17" s="2"/>
       <c r="H17" s="2"/>
     </row>
-    <row r="18" spans="1:8" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:8" ht="15.75" customHeight="1">
       <c r="A18" s="33">
         <v>46077</v>
       </c>
@@ -1728,7 +1731,7 @@
       <c r="G18" s="4"/>
       <c r="H18" s="4"/>
     </row>
-    <row r="19" spans="1:8" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:8" ht="15.75" customHeight="1">
       <c r="A19" s="32">
         <v>46105</v>
       </c>
@@ -1744,7 +1747,7 @@
       <c r="G19" s="2"/>
       <c r="H19" s="2"/>
     </row>
-    <row r="20" spans="1:8" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:8" ht="15.75" customHeight="1">
       <c r="A20" s="33">
         <v>46136</v>
       </c>
@@ -1760,7 +1763,7 @@
       <c r="G20" s="2"/>
       <c r="H20" s="2"/>
     </row>
-    <row r="21" spans="1:8" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:8" ht="15.75" customHeight="1">
       <c r="A21" s="32">
         <v>46166</v>
       </c>
@@ -1776,7 +1779,7 @@
       <c r="G21" s="2"/>
       <c r="H21" s="2"/>
     </row>
-    <row r="22" spans="1:8" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:8" ht="15.75" customHeight="1">
       <c r="A22" s="33">
         <v>46197</v>
       </c>
@@ -1792,7 +1795,7 @@
       <c r="G22" s="2"/>
       <c r="H22" s="2"/>
     </row>
-    <row r="23" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:8">
       <c r="A23" s="32">
         <v>46227</v>
       </c>
@@ -1814,7 +1817,7 @@
         <v>155</v>
       </c>
     </row>
-    <row r="24" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:8">
       <c r="A24" s="33">
         <v>46258</v>
       </c>
@@ -1830,7 +1833,7 @@
       <c r="G24" s="2"/>
       <c r="H24" s="2"/>
     </row>
-    <row r="25" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="25" spans="1:8">
       <c r="A25" s="32">
         <v>46289</v>
       </c>
@@ -1846,7 +1849,7 @@
       <c r="G25" s="2"/>
       <c r="H25" s="2"/>
     </row>
-    <row r="26" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="26" spans="1:8">
       <c r="A26" s="33">
         <v>46319</v>
       </c>
@@ -1862,7 +1865,7 @@
       <c r="G26" s="2"/>
       <c r="H26" s="2"/>
     </row>
-    <row r="27" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="27" spans="1:8">
       <c r="A27" s="32">
         <v>46350</v>
       </c>
@@ -1873,7 +1876,7 @@
         <v>144</v>
       </c>
     </row>
-    <row r="28" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="28" spans="1:8">
       <c r="A28" s="33">
         <v>46380</v>
       </c>
@@ -1884,7 +1887,7 @@
         <v>144</v>
       </c>
     </row>
-    <row r="29" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="29" spans="1:8">
       <c r="A29" s="32">
         <v>46411</v>
       </c>
@@ -1895,7 +1898,7 @@
         <v>144</v>
       </c>
     </row>
-    <row r="30" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="30" spans="1:8">
       <c r="A30" s="33">
         <v>46442</v>
       </c>
@@ -1935,7 +1938,7 @@
     <tabColor rgb="FFE87722"/>
   </sheetPr>
   <dimension ref="A1:H12"/>
-  <sheetFormatPr defaultColWidth="8.7109375" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultColWidth="8.7109375" defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="4" customWidth="1"/>
     <col min="2" max="2" width="38" customWidth="1"/>
@@ -1945,7 +1948,7 @@
     <col min="6" max="6" width="10" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:8" ht="21.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:8" ht="21.75" customHeight="1">
       <c r="A1" s="43" t="s">
         <v>158</v>
       </c>
@@ -1957,7 +1960,7 @@
       <c r="G1" s="43"/>
       <c r="H1" s="43"/>
     </row>
-    <row r="2" spans="1:8" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:8" ht="18" customHeight="1">
       <c r="A2" s="1" t="s">
         <v>159</v>
       </c>
@@ -1977,7 +1980,7 @@
         <v>164</v>
       </c>
     </row>
-    <row r="3" spans="1:8" ht="38.25" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:8" ht="38.25">
       <c r="A3" s="2">
         <v>1</v>
       </c>
@@ -1997,7 +2000,7 @@
         <v>169</v>
       </c>
     </row>
-    <row r="4" spans="1:8" ht="25.5" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:8" ht="25.5">
       <c r="A4" s="4">
         <v>2</v>
       </c>
@@ -2017,7 +2020,7 @@
         <v>169</v>
       </c>
     </row>
-    <row r="5" spans="1:8" ht="38.25" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:8" ht="38.25">
       <c r="A5" s="2">
         <v>3</v>
       </c>
@@ -2037,7 +2040,7 @@
         <v>169</v>
       </c>
     </row>
-    <row r="6" spans="1:8" ht="38.25" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:8" ht="38.25">
       <c r="A6" s="2">
         <v>4</v>
       </c>
@@ -2057,124 +2060,124 @@
         <v>169</v>
       </c>
     </row>
-    <row r="7" spans="1:8" ht="25.5" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:8" ht="25.5">
       <c r="A7" s="2">
         <v>5</v>
       </c>
       <c r="B7" s="2" t="s">
-        <v>210</v>
+        <v>178</v>
       </c>
       <c r="C7" s="2" t="s">
-        <v>211</v>
+        <v>179</v>
       </c>
       <c r="D7" s="2" t="s">
         <v>172</v>
       </c>
       <c r="E7" s="2" t="s">
-        <v>225</v>
+        <v>180</v>
       </c>
       <c r="F7" s="10" t="s">
         <v>169</v>
       </c>
     </row>
-    <row r="8" spans="1:8" ht="25.5" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:8" ht="25.5">
       <c r="A8" s="2">
         <v>6</v>
       </c>
       <c r="B8" s="2" t="s">
-        <v>212</v>
+        <v>181</v>
       </c>
       <c r="C8" s="2" t="s">
         <v>171</v>
       </c>
       <c r="D8" s="2" t="s">
-        <v>226</v>
+        <v>182</v>
       </c>
       <c r="E8" s="2" t="s">
-        <v>233</v>
+        <v>183</v>
       </c>
       <c r="F8" s="10" t="s">
-        <v>218</v>
-      </c>
-    </row>
-    <row r="9" spans="1:8" x14ac:dyDescent="0.25">
+        <v>184</v>
+      </c>
+    </row>
+    <row r="9" spans="1:8">
       <c r="A9" s="2">
         <v>7</v>
       </c>
       <c r="B9" s="2" t="s">
-        <v>213</v>
+        <v>185</v>
       </c>
       <c r="C9" s="2" t="s">
-        <v>211</v>
+        <v>179</v>
       </c>
       <c r="D9" s="2" t="s">
-        <v>214</v>
+        <v>186</v>
       </c>
       <c r="E9" s="2" t="s">
-        <v>215</v>
+        <v>187</v>
       </c>
       <c r="F9" s="10" t="s">
         <v>169</v>
       </c>
     </row>
-    <row r="10" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:8">
       <c r="A10" s="2">
         <v>8</v>
       </c>
       <c r="B10" s="2" t="s">
-        <v>216</v>
+        <v>188</v>
       </c>
       <c r="C10" s="2" t="s">
-        <v>211</v>
+        <v>179</v>
       </c>
       <c r="D10" s="2" t="s">
-        <v>214</v>
+        <v>186</v>
       </c>
       <c r="E10" s="2" t="s">
-        <v>217</v>
+        <v>189</v>
       </c>
       <c r="F10" s="10" t="s">
-        <v>219</v>
-      </c>
-    </row>
-    <row r="11" spans="1:8" x14ac:dyDescent="0.25">
+        <v>190</v>
+      </c>
+    </row>
+    <row r="11" spans="1:8">
       <c r="A11" s="2">
         <v>9</v>
       </c>
       <c r="B11" s="2" t="s">
-        <v>220</v>
+        <v>191</v>
       </c>
       <c r="C11" s="2" t="s">
-        <v>211</v>
+        <v>179</v>
       </c>
       <c r="D11" s="2" t="s">
-        <v>214</v>
+        <v>186</v>
       </c>
       <c r="E11" s="2" t="s">
-        <v>221</v>
+        <v>192</v>
       </c>
       <c r="F11" s="10" t="s">
         <v>169</v>
       </c>
     </row>
-    <row r="12" spans="1:8" ht="25.5" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:8" ht="25.5">
       <c r="A12" s="2">
         <v>10</v>
       </c>
       <c r="B12" s="2" t="s">
-        <v>222</v>
+        <v>193</v>
       </c>
       <c r="C12" s="2" t="s">
-        <v>211</v>
+        <v>179</v>
       </c>
       <c r="D12" s="2" t="s">
-        <v>223</v>
+        <v>194</v>
       </c>
       <c r="E12" s="2" t="s">
-        <v>224</v>
+        <v>195</v>
       </c>
       <c r="F12" s="10" t="s">
-        <v>218</v>
+        <v>184</v>
       </c>
     </row>
   </sheetData>
@@ -2195,7 +2198,7 @@
     <tabColor rgb="FFE87722"/>
   </sheetPr>
   <dimension ref="A1:U28"/>
-  <sheetFormatPr defaultColWidth="8.7109375" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultColWidth="8.7109375" defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="4" customWidth="1"/>
     <col min="2" max="2" width="26" customWidth="1"/>
@@ -2204,9 +2207,9 @@
     <col min="8" max="8" width="12" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:21" ht="21.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:21" ht="21.75" customHeight="1">
       <c r="A1" s="43" t="s">
-        <v>178</v>
+        <v>196</v>
       </c>
       <c r="B1" s="43"/>
       <c r="C1" s="43"/>
@@ -2216,7 +2219,7 @@
       <c r="G1" s="43"/>
       <c r="H1" s="43"/>
     </row>
-    <row r="2" spans="1:21" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:21" ht="18" customHeight="1">
       <c r="A2" s="1" t="s">
         <v>159</v>
       </c>
@@ -2224,36 +2227,36 @@
         <v>116</v>
       </c>
       <c r="C2" s="1" t="s">
-        <v>179</v>
+        <v>197</v>
       </c>
       <c r="D2" s="1" t="s">
-        <v>180</v>
+        <v>198</v>
       </c>
       <c r="E2" s="1" t="s">
-        <v>181</v>
+        <v>199</v>
       </c>
       <c r="F2" s="1" t="s">
-        <v>182</v>
+        <v>200</v>
       </c>
       <c r="G2" s="1" t="s">
-        <v>183</v>
+        <v>201</v>
       </c>
       <c r="H2" s="1" t="s">
-        <v>184</v>
-      </c>
-    </row>
-    <row r="3" spans="1:21" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+        <v>202</v>
+      </c>
+    </row>
+    <row r="3" spans="1:21" ht="15.75" customHeight="1">
       <c r="A3" s="2">
         <v>1</v>
       </c>
       <c r="B3" s="2" t="s">
-        <v>185</v>
+        <v>203</v>
       </c>
       <c r="C3" s="2" t="s">
-        <v>186</v>
+        <v>204</v>
       </c>
       <c r="D3" s="2" t="s">
-        <v>187</v>
+        <v>205</v>
       </c>
       <c r="E3" s="13">
         <v>1</v>
@@ -2265,21 +2268,21 @@
         <v>0.95</v>
       </c>
       <c r="H3" s="10" t="s">
-        <v>196</v>
-      </c>
-    </row>
-    <row r="4" spans="1:21" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+        <v>206</v>
+      </c>
+    </row>
+    <row r="4" spans="1:21" ht="15.75" customHeight="1">
       <c r="A4" s="4">
         <v>2</v>
       </c>
       <c r="B4" s="4" t="s">
-        <v>189</v>
+        <v>207</v>
       </c>
       <c r="C4" s="4" t="s">
-        <v>190</v>
+        <v>208</v>
       </c>
       <c r="D4" s="4" t="s">
-        <v>187</v>
+        <v>205</v>
       </c>
       <c r="E4" s="34">
         <v>1</v>
@@ -2291,21 +2294,21 @@
         <v>1</v>
       </c>
       <c r="H4" s="11" t="s">
-        <v>188</v>
-      </c>
-    </row>
-    <row r="5" spans="1:21" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+        <v>209</v>
+      </c>
+    </row>
+    <row r="5" spans="1:21" ht="15.75" customHeight="1">
       <c r="A5" s="2">
         <v>3</v>
       </c>
       <c r="B5" s="2" t="s">
-        <v>191</v>
+        <v>210</v>
       </c>
       <c r="C5" s="2" t="s">
-        <v>190</v>
+        <v>208</v>
       </c>
       <c r="D5" s="2" t="s">
-        <v>187</v>
+        <v>205</v>
       </c>
       <c r="E5" s="13">
         <v>1</v>
@@ -2317,21 +2320,21 @@
         <v>1</v>
       </c>
       <c r="H5" s="11" t="s">
-        <v>188</v>
-      </c>
-    </row>
-    <row r="6" spans="1:21" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+        <v>209</v>
+      </c>
+    </row>
+    <row r="6" spans="1:21" ht="15.75" customHeight="1">
       <c r="A6" s="4">
         <v>4</v>
       </c>
       <c r="B6" s="4" t="s">
-        <v>192</v>
+        <v>211</v>
       </c>
       <c r="C6" s="4" t="s">
-        <v>193</v>
+        <v>212</v>
       </c>
       <c r="D6" s="4" t="s">
-        <v>187</v>
+        <v>205</v>
       </c>
       <c r="E6" s="34">
         <v>1</v>
@@ -2343,21 +2346,21 @@
         <v>1</v>
       </c>
       <c r="H6" s="11" t="s">
-        <v>188</v>
-      </c>
-    </row>
-    <row r="7" spans="1:21" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+        <v>209</v>
+      </c>
+    </row>
+    <row r="7" spans="1:21" ht="15.75" customHeight="1">
       <c r="A7" s="2">
         <v>5</v>
       </c>
       <c r="B7" s="4" t="s">
-        <v>232</v>
+        <v>213</v>
       </c>
       <c r="C7" s="2" t="s">
-        <v>190</v>
+        <v>208</v>
       </c>
       <c r="D7" s="4" t="s">
-        <v>187</v>
+        <v>205</v>
       </c>
       <c r="E7" s="34">
         <v>1</v>
@@ -2369,21 +2372,21 @@
         <v>1</v>
       </c>
       <c r="H7" s="11" t="s">
-        <v>188</v>
-      </c>
-    </row>
-    <row r="8" spans="1:21" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+        <v>209</v>
+      </c>
+    </row>
+    <row r="8" spans="1:21" ht="15.75" customHeight="1">
       <c r="A8" s="4">
         <v>6</v>
       </c>
       <c r="B8" s="2" t="s">
-        <v>194</v>
+        <v>214</v>
       </c>
       <c r="C8" s="2" t="s">
-        <v>195</v>
+        <v>215</v>
       </c>
       <c r="D8" s="2" t="s">
-        <v>187</v>
+        <v>205</v>
       </c>
       <c r="E8" s="13">
         <v>1</v>
@@ -2395,21 +2398,21 @@
         <v>0.9</v>
       </c>
       <c r="H8" s="10" t="s">
-        <v>196</v>
-      </c>
-    </row>
-    <row r="9" spans="1:21" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+        <v>206</v>
+      </c>
+    </row>
+    <row r="9" spans="1:21" ht="15.75" customHeight="1">
       <c r="A9" s="2">
         <v>7</v>
       </c>
       <c r="B9" s="4" t="s">
-        <v>197</v>
+        <v>216</v>
       </c>
       <c r="C9" s="4" t="s">
-        <v>195</v>
+        <v>215</v>
       </c>
       <c r="D9" s="4" t="s">
-        <v>187</v>
+        <v>205</v>
       </c>
       <c r="E9" s="34">
         <v>1</v>
@@ -2421,21 +2424,21 @@
         <v>0</v>
       </c>
       <c r="H9" s="10" t="s">
-        <v>196</v>
-      </c>
-    </row>
-    <row r="10" spans="1:21" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+        <v>206</v>
+      </c>
+    </row>
+    <row r="10" spans="1:21" ht="15.75" customHeight="1">
       <c r="A10" s="4">
         <v>8</v>
       </c>
       <c r="B10" s="4" t="s">
-        <v>230</v>
+        <v>217</v>
       </c>
       <c r="C10" s="4" t="s">
-        <v>195</v>
+        <v>215</v>
       </c>
       <c r="D10" s="4" t="s">
-        <v>187</v>
+        <v>205</v>
       </c>
       <c r="E10" s="34">
         <v>0</v>
@@ -2447,21 +2450,21 @@
         <v>0</v>
       </c>
       <c r="H10" s="10" t="s">
-        <v>196</v>
-      </c>
-    </row>
-    <row r="11" spans="1:21" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+        <v>206</v>
+      </c>
+    </row>
+    <row r="11" spans="1:21" ht="15.75" customHeight="1">
       <c r="A11" s="2">
         <v>9</v>
       </c>
       <c r="B11" s="4" t="s">
-        <v>228</v>
+        <v>218</v>
       </c>
       <c r="C11" s="4" t="s">
-        <v>195</v>
+        <v>215</v>
       </c>
       <c r="D11" s="4" t="s">
-        <v>187</v>
+        <v>205</v>
       </c>
       <c r="E11" s="34">
         <v>1</v>
@@ -2473,21 +2476,21 @@
         <v>0</v>
       </c>
       <c r="H11" s="10" t="s">
-        <v>196</v>
-      </c>
-    </row>
-    <row r="12" spans="1:21" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+        <v>206</v>
+      </c>
+    </row>
+    <row r="12" spans="1:21" ht="15.75" customHeight="1">
       <c r="A12" s="4">
         <v>10</v>
       </c>
       <c r="B12" s="2" t="s">
-        <v>198</v>
+        <v>219</v>
       </c>
       <c r="C12" s="2" t="s">
-        <v>190</v>
+        <v>208</v>
       </c>
       <c r="D12" s="2" t="s">
-        <v>187</v>
+        <v>205</v>
       </c>
       <c r="E12" s="13">
         <v>0.8</v>
@@ -2499,140 +2502,140 @@
         <v>0</v>
       </c>
       <c r="H12" s="10" t="s">
-        <v>196</v>
-      </c>
-    </row>
-    <row r="13" spans="1:21" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+        <v>206</v>
+      </c>
+    </row>
+    <row r="13" spans="1:21" ht="15.75" customHeight="1">
       <c r="A13" s="2">
         <v>11</v>
       </c>
       <c r="B13" s="4" t="s">
-        <v>199</v>
+        <v>220</v>
       </c>
       <c r="C13" s="4" t="s">
-        <v>200</v>
+        <v>221</v>
       </c>
       <c r="D13" s="4" t="s">
-        <v>187</v>
+        <v>205</v>
       </c>
       <c r="E13" s="34">
         <v>1</v>
       </c>
       <c r="F13" s="34" t="s">
-        <v>201</v>
+        <v>222</v>
       </c>
       <c r="G13" s="34">
         <v>0.15</v>
       </c>
       <c r="H13" s="10" t="s">
-        <v>196</v>
-      </c>
-    </row>
-    <row r="14" spans="1:21" x14ac:dyDescent="0.25">
+        <v>206</v>
+      </c>
+    </row>
+    <row r="14" spans="1:21">
       <c r="A14" s="4">
         <v>12</v>
       </c>
       <c r="B14" s="39" t="s">
-        <v>231</v>
+        <v>223</v>
       </c>
       <c r="C14" s="39" t="s">
-        <v>227</v>
+        <v>224</v>
       </c>
       <c r="D14" s="39" t="s">
-        <v>187</v>
+        <v>205</v>
       </c>
       <c r="E14" s="40">
         <v>1</v>
       </c>
       <c r="F14" s="39" t="s">
-        <v>201</v>
+        <v>222</v>
       </c>
       <c r="G14" s="42">
         <v>0.4</v>
       </c>
       <c r="H14" s="10" t="s">
-        <v>196</v>
+        <v>206</v>
       </c>
       <c r="S14" s="31"/>
       <c r="T14" s="31"/>
       <c r="U14" s="31"/>
     </row>
-    <row r="15" spans="1:21" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:21">
       <c r="A15" s="2">
         <v>13</v>
       </c>
       <c r="B15" s="41" t="s">
-        <v>229</v>
+        <v>225</v>
       </c>
       <c r="C15" s="41" t="s">
-        <v>226</v>
+        <v>182</v>
       </c>
       <c r="D15" s="41" t="s">
-        <v>187</v>
+        <v>205</v>
       </c>
       <c r="E15" s="42">
         <v>1</v>
       </c>
       <c r="F15" s="42" t="s">
-        <v>201</v>
+        <v>222</v>
       </c>
       <c r="G15" s="42">
         <v>0</v>
       </c>
       <c r="H15" s="10" t="s">
-        <v>196</v>
+        <v>206</v>
       </c>
       <c r="S15" s="31"/>
       <c r="T15" s="31"/>
       <c r="U15" s="31"/>
     </row>
-    <row r="16" spans="1:21" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:21">
       <c r="S16" s="31"/>
       <c r="T16" s="31"/>
       <c r="U16" s="31"/>
     </row>
-    <row r="17" spans="19:21" x14ac:dyDescent="0.25">
+    <row r="17" spans="19:21">
       <c r="S17" s="31"/>
       <c r="T17" s="31"/>
       <c r="U17" s="31"/>
     </row>
-    <row r="18" spans="19:21" x14ac:dyDescent="0.25">
+    <row r="18" spans="19:21">
       <c r="S18" s="31"/>
       <c r="T18" s="31"/>
       <c r="U18" s="31"/>
     </row>
-    <row r="19" spans="19:21" x14ac:dyDescent="0.25">
+    <row r="19" spans="19:21">
       <c r="S19" s="31"/>
       <c r="T19" s="31"/>
       <c r="U19" s="31"/>
     </row>
-    <row r="20" spans="19:21" x14ac:dyDescent="0.25">
+    <row r="20" spans="19:21">
       <c r="T20" s="31"/>
       <c r="U20" s="31"/>
     </row>
-    <row r="21" spans="19:21" x14ac:dyDescent="0.25">
+    <row r="21" spans="19:21">
       <c r="S21" s="31"/>
       <c r="U21" s="31"/>
     </row>
-    <row r="22" spans="19:21" x14ac:dyDescent="0.25">
+    <row r="22" spans="19:21">
       <c r="S22" s="30"/>
     </row>
-    <row r="23" spans="19:21" x14ac:dyDescent="0.25">
+    <row r="23" spans="19:21">
       <c r="S23" s="30"/>
     </row>
-    <row r="24" spans="19:21" x14ac:dyDescent="0.25">
+    <row r="24" spans="19:21">
       <c r="S24" s="30"/>
     </row>
-    <row r="25" spans="19:21" x14ac:dyDescent="0.25">
+    <row r="25" spans="19:21">
       <c r="S25" s="30"/>
     </row>
-    <row r="26" spans="19:21" x14ac:dyDescent="0.25">
+    <row r="26" spans="19:21">
       <c r="S26" s="30"/>
     </row>
-    <row r="27" spans="19:21" x14ac:dyDescent="0.25">
+    <row r="27" spans="19:21">
       <c r="S27" s="30"/>
     </row>
-    <row r="28" spans="19:21" x14ac:dyDescent="0.25">
+    <row r="28" spans="19:21">
       <c r="S28" s="30"/>
     </row>
   </sheetData>
@@ -2653,15 +2656,15 @@
     <tabColor rgb="FFE87722"/>
   </sheetPr>
   <dimension ref="A1:H6"/>
-  <sheetFormatPr defaultColWidth="8.7109375" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultColWidth="8.7109375" defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="30" customWidth="1"/>
     <col min="2" max="2" width="50" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:8" ht="21.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:8" ht="21.75" customHeight="1">
       <c r="A1" s="43" t="s">
-        <v>202</v>
+        <v>226</v>
       </c>
       <c r="B1" s="43"/>
       <c r="C1" s="43"/>
@@ -2671,7 +2674,7 @@
       <c r="G1" s="43"/>
       <c r="H1" s="43"/>
     </row>
-    <row r="2" spans="1:8" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:8" ht="18" customHeight="1">
       <c r="A2" s="1" t="s">
         <v>1</v>
       </c>
@@ -2679,36 +2682,36 @@
         <v>2</v>
       </c>
     </row>
-    <row r="3" spans="1:8" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:8" ht="15.75" customHeight="1">
       <c r="A3" s="2" t="s">
-        <v>203</v>
+        <v>227</v>
       </c>
       <c r="B3" s="3" t="s">
-        <v>204</v>
-      </c>
-    </row>
-    <row r="4" spans="1:8" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+        <v>228</v>
+      </c>
+    </row>
+    <row r="4" spans="1:8" ht="15.75" customHeight="1">
       <c r="A4" s="4" t="s">
-        <v>205</v>
+        <v>229</v>
       </c>
       <c r="B4" s="12">
         <v>46176</v>
       </c>
     </row>
-    <row r="5" spans="1:8" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:8" ht="15.75" customHeight="1">
       <c r="A5" s="2" t="s">
-        <v>206</v>
+        <v>230</v>
       </c>
       <c r="B5" s="3" t="s">
-        <v>207</v>
-      </c>
-    </row>
-    <row r="6" spans="1:8" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+        <v>231</v>
+      </c>
+    </row>
+    <row r="6" spans="1:8" ht="15.75" customHeight="1">
       <c r="A6" s="4" t="s">
-        <v>208</v>
+        <v>232</v>
       </c>
       <c r="B6" s="3" t="s">
-        <v>209</v>
+        <v>233</v>
       </c>
     </row>
   </sheetData>
@@ -2729,14 +2732,14 @@
     <tabColor rgb="FFE87722"/>
   </sheetPr>
   <dimension ref="A1:H9"/>
-  <sheetFormatPr defaultColWidth="8.7109375" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultColWidth="8.7109375" defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="32" customWidth="1"/>
     <col min="2" max="2" width="18" customWidth="1"/>
     <col min="3" max="3" width="40" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:8" ht="21.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:8" ht="21.75" customHeight="1">
       <c r="A1" s="43" t="s">
         <v>11</v>
       </c>
@@ -2748,7 +2751,7 @@
       <c r="G1" s="43"/>
       <c r="H1" s="43"/>
     </row>
-    <row r="2" spans="1:8" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:8" ht="18" customHeight="1">
       <c r="A2" s="1" t="s">
         <v>1</v>
       </c>
@@ -2759,7 +2762,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="3" spans="1:8" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:8" ht="15.75" customHeight="1">
       <c r="A3" s="2" t="s">
         <v>14</v>
       </c>
@@ -2768,7 +2771,7 @@
       </c>
       <c r="C3" s="2"/>
     </row>
-    <row r="4" spans="1:8" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:8" ht="15.75" customHeight="1">
       <c r="A4" s="4" t="s">
         <v>15</v>
       </c>
@@ -2777,7 +2780,7 @@
       </c>
       <c r="C4" s="4"/>
     </row>
-    <row r="5" spans="1:8" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:8" ht="15.75" customHeight="1">
       <c r="A5" s="2" t="s">
         <v>16</v>
       </c>
@@ -2786,7 +2789,7 @@
       </c>
       <c r="C5" s="2"/>
     </row>
-    <row r="6" spans="1:8" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:8" ht="15.75" customHeight="1">
       <c r="A6" s="4" t="s">
         <v>17</v>
       </c>
@@ -2795,7 +2798,7 @@
       </c>
       <c r="C6" s="4"/>
     </row>
-    <row r="7" spans="1:8" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:8" ht="15.75" customHeight="1">
       <c r="A7" s="2" t="s">
         <v>18</v>
       </c>
@@ -2804,7 +2807,7 @@
       </c>
       <c r="C7" s="2"/>
     </row>
-    <row r="8" spans="1:8" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:8" ht="15.75" customHeight="1">
       <c r="A8" s="4" t="s">
         <v>19</v>
       </c>
@@ -2815,7 +2818,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="9" spans="1:8" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:8" ht="15.75" customHeight="1">
       <c r="A9" s="2" t="s">
         <v>21</v>
       </c>
@@ -2845,7 +2848,7 @@
     <tabColor rgb="FFE87722"/>
   </sheetPr>
   <dimension ref="A1:H9"/>
-  <sheetFormatPr defaultColWidth="8.7109375" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultColWidth="8.7109375" defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="32" customWidth="1"/>
     <col min="2" max="2" width="22" customWidth="1"/>
@@ -2853,7 +2856,7 @@
     <col min="4" max="4" width="40" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:8" ht="21.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:8" ht="21.75" customHeight="1">
       <c r="A1" s="43" t="s">
         <v>23</v>
       </c>
@@ -2865,7 +2868,7 @@
       <c r="G1" s="43"/>
       <c r="H1" s="43"/>
     </row>
-    <row r="2" spans="1:8" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:8" ht="18" customHeight="1">
       <c r="A2" s="1" t="s">
         <v>1</v>
       </c>
@@ -2879,7 +2882,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="3" spans="1:8" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:8" ht="15.75" customHeight="1">
       <c r="A3" s="2" t="s">
         <v>26</v>
       </c>
@@ -2889,7 +2892,7 @@
       <c r="C3" s="2"/>
       <c r="D3" s="2"/>
     </row>
-    <row r="4" spans="1:8" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:8" ht="15.75" customHeight="1">
       <c r="A4" s="4" t="s">
         <v>27</v>
       </c>
@@ -2899,7 +2902,7 @@
       <c r="C4" s="4"/>
       <c r="D4" s="4"/>
     </row>
-    <row r="5" spans="1:8" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:8" ht="15.75" customHeight="1">
       <c r="A5" s="2" t="s">
         <v>28</v>
       </c>
@@ -2909,7 +2912,7 @@
       <c r="C5" s="2"/>
       <c r="D5" s="2"/>
     </row>
-    <row r="6" spans="1:8" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:8" ht="15.75" customHeight="1">
       <c r="A6" s="4" t="s">
         <v>29</v>
       </c>
@@ -2919,7 +2922,7 @@
       <c r="C6" s="4"/>
       <c r="D6" s="4"/>
     </row>
-    <row r="7" spans="1:8" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:8" ht="15.75" customHeight="1">
       <c r="A7" s="2" t="s">
         <v>30</v>
       </c>
@@ -2931,7 +2934,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="8" spans="1:8" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:8" ht="15.75" customHeight="1">
       <c r="A8" s="4" t="s">
         <v>32</v>
       </c>
@@ -2941,7 +2944,7 @@
       <c r="C8" s="4"/>
       <c r="D8" s="4"/>
     </row>
-    <row r="9" spans="1:8" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:8" ht="15.75" customHeight="1">
       <c r="A9" s="2" t="s">
         <v>33</v>
       </c>
@@ -2974,7 +2977,7 @@
     <tabColor rgb="FFE87722"/>
   </sheetPr>
   <dimension ref="A1:H10"/>
-  <sheetFormatPr defaultColWidth="8.7109375" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultColWidth="8.7109375" defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="32" customWidth="1"/>
     <col min="2" max="2" width="22" customWidth="1"/>
@@ -2982,7 +2985,7 @@
     <col min="4" max="4" width="40" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:8" ht="21.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:8" ht="21.75" customHeight="1">
       <c r="A1" s="43" t="s">
         <v>35</v>
       </c>
@@ -2994,7 +2997,7 @@
       <c r="G1" s="43"/>
       <c r="H1" s="43"/>
     </row>
-    <row r="2" spans="1:8" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:8" ht="18" customHeight="1">
       <c r="A2" s="1" t="s">
         <v>1</v>
       </c>
@@ -3008,7 +3011,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="3" spans="1:8" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:8" ht="15.75" customHeight="1">
       <c r="A3" s="2" t="s">
         <v>36</v>
       </c>
@@ -3020,7 +3023,7 @@
         <v>37</v>
       </c>
     </row>
-    <row r="4" spans="1:8" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:8" ht="15.75" customHeight="1">
       <c r="A4" s="4" t="s">
         <v>38</v>
       </c>
@@ -3032,7 +3035,7 @@
         <v>40</v>
       </c>
     </row>
-    <row r="5" spans="1:8" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:8" ht="15.75" customHeight="1">
       <c r="A5" s="4" t="s">
         <v>41</v>
       </c>
@@ -3042,19 +3045,19 @@
       <c r="C5" s="21"/>
       <c r="D5" s="4"/>
     </row>
-    <row r="6" spans="1:8" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:8" ht="15.75" customHeight="1">
       <c r="A6" s="2" t="s">
         <v>42</v>
       </c>
       <c r="B6" s="19">
-        <v>0.46589999999999998</v>
+        <v>0.47110000000000002</v>
       </c>
       <c r="C6" s="22"/>
       <c r="D6" s="2" t="s">
         <v>43</v>
       </c>
     </row>
-    <row r="7" spans="1:8" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:8" ht="15.75" customHeight="1">
       <c r="A7" s="4" t="s">
         <v>32</v>
       </c>
@@ -3066,7 +3069,7 @@
         <v>37</v>
       </c>
     </row>
-    <row r="8" spans="1:8" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:8" ht="15.75" customHeight="1">
       <c r="A8" s="2" t="s">
         <v>33</v>
       </c>
@@ -3078,7 +3081,7 @@
         <v>37</v>
       </c>
     </row>
-    <row r="9" spans="1:8" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:8" ht="15.75" customHeight="1">
       <c r="A9" s="4" t="s">
         <v>44</v>
       </c>
@@ -3091,7 +3094,7 @@
         <v>45</v>
       </c>
     </row>
-    <row r="10" spans="1:8" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:8" ht="15.75" customHeight="1">
       <c r="A10" s="2" t="s">
         <v>46</v>
       </c>
@@ -3121,7 +3124,7 @@
     <tabColor rgb="FFE87722"/>
   </sheetPr>
   <dimension ref="A1:H16"/>
-  <sheetFormatPr defaultColWidth="8.7109375" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultColWidth="8.7109375" defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="32" customWidth="1"/>
     <col min="2" max="2" width="22" customWidth="1"/>
@@ -3130,7 +3133,7 @@
     <col min="5" max="5" width="35" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:8" ht="21.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:8" ht="21.75" customHeight="1">
       <c r="A1" s="43" t="s">
         <v>49</v>
       </c>
@@ -3142,7 +3145,7 @@
       <c r="G1" s="43"/>
       <c r="H1" s="43"/>
     </row>
-    <row r="2" spans="1:8" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:8" ht="18" customHeight="1">
       <c r="A2" s="1" t="s">
         <v>1</v>
       </c>
@@ -3159,14 +3162,14 @@
         <v>13</v>
       </c>
     </row>
-    <row r="3" spans="1:8" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:8" ht="15.75" customHeight="1">
       <c r="A3" s="2" t="s">
         <v>52</v>
       </c>
       <c r="B3" s="14">
         <v>223311139</v>
       </c>
-      <c r="C3" s="13">
+      <c r="C3" s="45">
         <f>B3/Commercial_Info!$B$3</f>
         <v>0.57551971902554677</v>
       </c>
@@ -3176,14 +3179,14 @@
       <c r="E3" s="2"/>
       <c r="G3" s="24"/>
     </row>
-    <row r="4" spans="1:8" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:8" ht="15.75" customHeight="1">
       <c r="A4" s="4" t="s">
         <v>54</v>
       </c>
       <c r="B4" s="14">
         <v>204095236</v>
       </c>
-      <c r="C4" s="13">
+      <c r="C4" s="45">
         <f>B4/Commercial_Info!$B$3</f>
         <v>0.52599630006442566</v>
       </c>
@@ -3192,14 +3195,14 @@
       </c>
       <c r="E4" s="4"/>
     </row>
-    <row r="5" spans="1:8" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:8" ht="15.75" customHeight="1">
       <c r="A5" s="2" t="s">
         <v>56</v>
       </c>
       <c r="B5" s="14">
         <v>152961744</v>
       </c>
-      <c r="C5" s="13">
+      <c r="C5" s="45">
         <f>B5/Commercial_Info!$B$3</f>
         <v>0.39421454891481078</v>
       </c>
@@ -3208,27 +3211,27 @@
       </c>
       <c r="E5" s="2"/>
     </row>
-    <row r="6" spans="1:8" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:8" ht="15.75" customHeight="1">
       <c r="A6" s="4" t="s">
         <v>57</v>
       </c>
       <c r="B6" s="14">
         <v>0</v>
       </c>
-      <c r="C6" s="4"/>
+      <c r="C6" s="21"/>
       <c r="D6" s="4" t="s">
         <v>58</v>
       </c>
       <c r="E6" s="4"/>
     </row>
-    <row r="7" spans="1:8" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:8" ht="15.75" customHeight="1">
       <c r="A7" s="2" t="s">
         <v>59</v>
       </c>
       <c r="B7" s="14">
         <v>152961744</v>
       </c>
-      <c r="C7" s="13">
+      <c r="C7" s="45">
         <f>B7/Commercial_Info!$B$3</f>
         <v>0.39421454891481078</v>
       </c>
@@ -3237,15 +3240,15 @@
       </c>
       <c r="E7" s="2"/>
     </row>
-    <row r="8" spans="1:8" ht="28.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:8" ht="28.5" customHeight="1">
       <c r="A8" s="4" t="s">
         <v>60</v>
       </c>
       <c r="B8" s="26" t="str">
         <f>ROUNDUP(C4*100,0)&amp;"%"&amp;" / "&amp;ROUNDUP(Budgetary_Info!B6*100,0)&amp;"%"</f>
-        <v>53% / 47%</v>
-      </c>
-      <c r="C8" s="4"/>
+        <v>53% / 48%</v>
+      </c>
+      <c r="C8" s="21"/>
       <c r="D8" s="4" t="s">
         <v>58</v>
       </c>
@@ -3253,16 +3256,16 @@
         <v>61</v>
       </c>
     </row>
-    <row r="10" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:8">
       <c r="B10" s="37"/>
     </row>
-    <row r="14" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:8">
       <c r="E14" s="36"/>
     </row>
-    <row r="15" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:8">
       <c r="E15" s="36"/>
     </row>
-    <row r="16" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:8">
       <c r="E16" s="36"/>
     </row>
   </sheetData>
@@ -3283,7 +3286,7 @@
     <tabColor rgb="FFE87722"/>
   </sheetPr>
   <dimension ref="A1:H9"/>
-  <sheetFormatPr defaultColWidth="8.7109375" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultColWidth="8.7109375" defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="30" customWidth="1"/>
     <col min="2" max="2" width="20" customWidth="1"/>
@@ -3291,7 +3294,7 @@
     <col min="4" max="4" width="40" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:8" ht="21.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:8" ht="21.75" customHeight="1">
       <c r="A1" s="43" t="s">
         <v>62</v>
       </c>
@@ -3303,7 +3306,7 @@
       <c r="G1" s="43"/>
       <c r="H1" s="43"/>
     </row>
-    <row r="2" spans="1:8" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:8" ht="18" customHeight="1">
       <c r="A2" s="1" t="s">
         <v>1</v>
       </c>
@@ -3317,7 +3320,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="3" spans="1:8" ht="27" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:8" ht="27" customHeight="1">
       <c r="A3" s="2" t="s">
         <v>65</v>
       </c>
@@ -3329,7 +3332,7 @@
         <v>66</v>
       </c>
     </row>
-    <row r="4" spans="1:8" ht="46.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:8" ht="46.5" customHeight="1">
       <c r="A4" s="4" t="s">
         <v>67</v>
       </c>
@@ -3342,7 +3345,7 @@
         <v>68</v>
       </c>
     </row>
-    <row r="5" spans="1:8" ht="27" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:8" ht="27" customHeight="1">
       <c r="A5" s="2" t="s">
         <v>69</v>
       </c>
@@ -3357,7 +3360,7 @@
         <v>70</v>
       </c>
     </row>
-    <row r="6" spans="1:8" ht="27" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:8" ht="27" customHeight="1">
       <c r="A6" s="4" t="s">
         <v>71</v>
       </c>
@@ -3371,7 +3374,7 @@
         <v>72</v>
       </c>
     </row>
-    <row r="9" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:8">
       <c r="B9" s="37"/>
     </row>
   </sheetData>
@@ -3392,7 +3395,7 @@
     <tabColor rgb="FFE87722"/>
   </sheetPr>
   <dimension ref="A1:H21"/>
-  <sheetFormatPr defaultColWidth="8.7109375" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultColWidth="8.7109375" defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="28" customWidth="1"/>
     <col min="2" max="2" width="16" customWidth="1"/>
@@ -3400,7 +3403,7 @@
     <col min="4" max="4" width="10" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:8" ht="21.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:8" ht="21.75" customHeight="1">
       <c r="A1" s="43" t="s">
         <v>73</v>
       </c>
@@ -3412,7 +3415,7 @@
       <c r="G1" s="43"/>
       <c r="H1" s="43"/>
     </row>
-    <row r="2" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:8" ht="15" customHeight="1">
       <c r="A2" s="44" t="s">
         <v>74</v>
       </c>
@@ -3420,7 +3423,7 @@
       <c r="C2" s="44"/>
       <c r="D2" s="44"/>
     </row>
-    <row r="3" spans="1:8" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:8" ht="18" customHeight="1">
       <c r="A3" s="1" t="s">
         <v>1</v>
       </c>
@@ -3432,7 +3435,7 @@
       </c>
       <c r="D3" s="1"/>
     </row>
-    <row r="4" spans="1:8" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:8" ht="15.75" customHeight="1">
       <c r="A4" s="4" t="s">
         <v>75</v>
       </c>
@@ -3445,7 +3448,7 @@
       </c>
       <c r="D4" s="4"/>
     </row>
-    <row r="5" spans="1:8" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:8" ht="15.75" customHeight="1">
       <c r="A5" s="2" t="s">
         <v>77</v>
       </c>
@@ -3457,7 +3460,7 @@
       </c>
       <c r="D5" s="2"/>
     </row>
-    <row r="6" spans="1:8" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:8" ht="15.75" customHeight="1">
       <c r="A6" s="4" t="s">
         <v>79</v>
       </c>
@@ -3469,7 +3472,7 @@
       </c>
       <c r="D6" s="4"/>
     </row>
-    <row r="7" spans="1:8" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:8" ht="15.75" customHeight="1">
       <c r="A7" s="2" t="s">
         <v>81</v>
       </c>
@@ -3482,8 +3485,8 @@
       </c>
       <c r="D7" s="2"/>
     </row>
-    <row r="8" spans="1:8" ht="6" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="9" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:8" ht="6" customHeight="1"/>
+    <row r="9" spans="1:8" ht="15" customHeight="1">
       <c r="A9" s="44" t="s">
         <v>83</v>
       </c>
@@ -3491,7 +3494,7 @@
       <c r="C9" s="44"/>
       <c r="D9" s="44"/>
     </row>
-    <row r="10" spans="1:8" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:8" ht="18" customHeight="1">
       <c r="A10" s="1" t="s">
         <v>84</v>
       </c>
@@ -3503,7 +3506,7 @@
       </c>
       <c r="D10" s="1"/>
     </row>
-    <row r="11" spans="1:8" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:8" ht="15.75" customHeight="1">
       <c r="A11" s="2" t="s">
         <v>86</v>
       </c>
@@ -3515,7 +3518,7 @@
       </c>
       <c r="D11" s="2"/>
     </row>
-    <row r="12" spans="1:8" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:8" ht="15.75" customHeight="1">
       <c r="A12" s="4" t="s">
         <v>88</v>
       </c>
@@ -3527,8 +3530,8 @@
       </c>
       <c r="D12" s="4"/>
     </row>
-    <row r="13" spans="1:8" ht="6" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="14" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:8" ht="6" customHeight="1"/>
+    <row r="14" spans="1:8" ht="15" customHeight="1">
       <c r="A14" s="44" t="s">
         <v>89</v>
       </c>
@@ -3536,7 +3539,7 @@
       <c r="C14" s="44"/>
       <c r="D14" s="44"/>
     </row>
-    <row r="15" spans="1:8" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:8" ht="18" customHeight="1">
       <c r="A15" s="1" t="s">
         <v>90</v>
       </c>
@@ -3548,7 +3551,7 @@
       </c>
       <c r="D15" s="1"/>
     </row>
-    <row r="16" spans="1:8" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:8" ht="15.75" customHeight="1">
       <c r="A16" s="4" t="s">
         <v>92</v>
       </c>
@@ -3561,7 +3564,7 @@
       </c>
       <c r="D16" s="4"/>
     </row>
-    <row r="17" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:4" ht="15.75" customHeight="1">
       <c r="A17" s="2" t="s">
         <v>94</v>
       </c>
@@ -3574,7 +3577,7 @@
       </c>
       <c r="D17" s="2"/>
     </row>
-    <row r="18" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:4" ht="15.75" customHeight="1">
       <c r="A18" s="4" t="s">
         <v>96</v>
       </c>
@@ -3587,7 +3590,7 @@
       </c>
       <c r="D18" s="4"/>
     </row>
-    <row r="19" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:4" ht="15.75" customHeight="1">
       <c r="A19" s="2" t="s">
         <v>98</v>
       </c>
@@ -3600,7 +3603,7 @@
       </c>
       <c r="D19" s="2"/>
     </row>
-    <row r="20" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:4" ht="15.75" customHeight="1">
       <c r="A20" s="4" t="s">
         <v>100</v>
       </c>
@@ -3613,7 +3616,7 @@
       </c>
       <c r="D20" s="4"/>
     </row>
-    <row r="21" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:4" ht="15.75" customHeight="1">
       <c r="A21" s="2" t="s">
         <v>102</v>
       </c>
@@ -3647,7 +3650,7 @@
     <tabColor rgb="FFE87722"/>
   </sheetPr>
   <dimension ref="A1:H8"/>
-  <sheetFormatPr defaultColWidth="8.7109375" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultColWidth="8.7109375" defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="28" customWidth="1"/>
     <col min="2" max="4" width="10" customWidth="1"/>
@@ -3655,7 +3658,7 @@
     <col min="6" max="6" width="35" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:8" ht="21.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:8" ht="21.75" customHeight="1">
       <c r="A1" s="43" t="s">
         <v>104</v>
       </c>
@@ -3667,7 +3670,7 @@
       <c r="G1" s="43"/>
       <c r="H1" s="43"/>
     </row>
-    <row r="2" spans="1:8" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:8" ht="18" customHeight="1">
       <c r="A2" s="1" t="s">
         <v>105</v>
       </c>
@@ -3687,7 +3690,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="3" spans="1:8" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:8" ht="15.75" customHeight="1">
       <c r="A3" s="2" t="s">
         <v>110</v>
       </c>
@@ -3708,7 +3711,7 @@
         <v>112</v>
       </c>
     </row>
-    <row r="4" spans="1:8" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:8" ht="15.75" customHeight="1">
       <c r="A4" s="4" t="s">
         <v>113</v>
       </c>
@@ -3729,7 +3732,7 @@
         <v>115</v>
       </c>
     </row>
-    <row r="5" spans="1:8" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:8" ht="15.75" customHeight="1">
       <c r="A5" s="2" t="s">
         <v>116</v>
       </c>
@@ -3750,7 +3753,7 @@
         <v>118</v>
       </c>
     </row>
-    <row r="6" spans="1:8" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:8" ht="15.75" customHeight="1">
       <c r="A6" s="4" t="s">
         <v>119</v>
       </c>
@@ -3771,7 +3774,7 @@
         <v>112</v>
       </c>
     </row>
-    <row r="7" spans="1:8" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:8" ht="15.75" customHeight="1">
       <c r="A7" s="2" t="s">
         <v>120</v>
       </c>
@@ -3792,7 +3795,7 @@
         <v>118</v>
       </c>
     </row>
-    <row r="8" spans="1:8" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:8" ht="15.75" customHeight="1">
       <c r="A8" s="4" t="s">
         <v>121</v>
       </c>
@@ -3831,7 +3834,7 @@
     <tabColor rgb="FFE87722"/>
   </sheetPr>
   <dimension ref="A1:H8"/>
-  <sheetFormatPr defaultColWidth="8.7109375" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultColWidth="8.7109375" defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="18" customWidth="1"/>
     <col min="2" max="4" width="10" customWidth="1"/>
@@ -3839,7 +3842,7 @@
     <col min="6" max="6" width="40" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:8" ht="21.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:8" ht="21.75" customHeight="1">
       <c r="A1" s="43" t="s">
         <v>123</v>
       </c>
@@ -3851,7 +3854,7 @@
       <c r="G1" s="43"/>
       <c r="H1" s="43"/>
     </row>
-    <row r="2" spans="1:8" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:8" ht="18" customHeight="1">
       <c r="A2" s="1" t="s">
         <v>124</v>
       </c>
@@ -3871,7 +3874,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="3" spans="1:8" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:8" ht="15.75" customHeight="1">
       <c r="A3" s="2" t="s">
         <v>125</v>
       </c>
@@ -3890,7 +3893,7 @@
       </c>
       <c r="F3" s="2"/>
     </row>
-    <row r="4" spans="1:8" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:8" ht="15.75" customHeight="1">
       <c r="A4" s="4" t="s">
         <v>126</v>
       </c>
@@ -3909,7 +3912,7 @@
       </c>
       <c r="F4" s="4"/>
     </row>
-    <row r="5" spans="1:8" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:8" ht="15.75" customHeight="1">
       <c r="A5" s="2" t="s">
         <v>127</v>
       </c>
@@ -3930,7 +3933,7 @@
         <v>128</v>
       </c>
     </row>
-    <row r="6" spans="1:8" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:8" ht="15.75" customHeight="1">
       <c r="A6" s="4" t="s">
         <v>129</v>
       </c>
@@ -3949,7 +3952,7 @@
       </c>
       <c r="F6" s="4"/>
     </row>
-    <row r="7" spans="1:8" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:8" ht="15.75" customHeight="1">
       <c r="A7" s="2" t="s">
         <v>130</v>
       </c>
@@ -3970,7 +3973,7 @@
         <v>131</v>
       </c>
     </row>
-    <row r="8" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:8" ht="15" customHeight="1">
       <c r="A8" s="7" t="s">
         <v>132</v>
       </c>
